--- a/gstdatabase/GSTR-1-2024-2025.xlsx
+++ b/gstdatabase/GSTR-1-2024-2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F12E8A3-21F0-484A-A158-C20ED2658E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838375B1-97AD-4471-88CE-5AA9187FD333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,10 +183,10 @@
     <t>FINANCIAL YEAR 2024-2025</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -1257,14 +1257,14 @@
       </c>
       <c r="E10" s="3">
         <f>F10-D10</f>
-        <v>43268</v>
+        <v>43279</v>
       </c>
       <c r="F10" s="5">
-        <v>72937</v>
+        <v>72948</v>
       </c>
       <c r="G10" s="4">
         <f>F10/C10</f>
-        <v>1.0003703195720752</v>
+        <v>1.0005211905088465</v>
       </c>
       <c r="H10" s="5">
         <v>74548</v>
@@ -1274,14 +1274,14 @@
       </c>
       <c r="J10" s="3">
         <f>K10-I10</f>
-        <v>41326</v>
+        <v>41338</v>
       </c>
       <c r="K10" s="5">
-        <v>73997</v>
+        <v>74009</v>
       </c>
       <c r="L10" s="4">
         <f>K10/H10</f>
-        <v>0.99260878896818161</v>
+        <v>0.9927697590813972</v>
       </c>
       <c r="M10" s="5">
         <v>129395</v>
@@ -1291,14 +1291,14 @@
       </c>
       <c r="O10" s="3">
         <f>P10-N10</f>
-        <v>81190</v>
+        <v>81216</v>
       </c>
       <c r="P10" s="5">
-        <v>129280</v>
+        <v>129306</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/M10</f>
-        <v>0.99911124850264699</v>
+        <v>0.9993121836237876</v>
       </c>
       <c r="R10" s="5">
         <v>72583</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="T10" s="3">
         <f>U10-S10</f>
-        <v>42516</v>
+        <v>42532</v>
       </c>
       <c r="U10" s="5">
-        <v>72852</v>
+        <v>72868</v>
       </c>
       <c r="V10" s="4">
         <f>U10/R10</f>
-        <v>1.0037061019798024</v>
+        <v>1.0039265392722814</v>
       </c>
       <c r="W10" s="5">
         <v>74384</v>
@@ -1325,14 +1325,14 @@
       </c>
       <c r="Y10" s="3">
         <f>Z10-X10</f>
-        <v>15583</v>
+        <v>15608</v>
       </c>
       <c r="Z10" s="5">
-        <v>73540</v>
+        <v>73565</v>
       </c>
       <c r="AA10" s="4">
         <f>Z10/W10</f>
-        <v>0.98865347386534741</v>
+        <v>0.98898956764895674</v>
       </c>
       <c r="AB10" s="5">
         <v>130621</v>
@@ -1342,14 +1342,14 @@
       </c>
       <c r="AD10" s="3">
         <f>AE10-AC10</f>
-        <v>83744</v>
+        <v>83798</v>
       </c>
       <c r="AE10" s="5">
-        <v>130165</v>
+        <v>130219</v>
       </c>
       <c r="AF10" s="4">
         <f>AE10/AB10</f>
-        <v>0.99650898400716581</v>
+        <v>0.99692239379579084</v>
       </c>
       <c r="AG10" s="5">
         <v>72721</v>
@@ -1359,14 +1359,14 @@
       </c>
       <c r="AI10" s="3">
         <f>AJ10-AH10</f>
-        <v>41879</v>
+        <v>41911</v>
       </c>
       <c r="AJ10" s="5">
-        <v>72559</v>
+        <v>72591</v>
       </c>
       <c r="AK10" s="4">
         <f>AJ10/AG10</f>
-        <v>0.99777230786155302</v>
+        <v>0.99821234581482654</v>
       </c>
       <c r="AL10" s="5">
         <v>74187</v>
@@ -1376,14 +1376,14 @@
       </c>
       <c r="AN10" s="3">
         <f>AO10-AM10</f>
-        <v>41467</v>
+        <v>41503</v>
       </c>
       <c r="AO10" s="5">
-        <v>73656</v>
+        <v>73692</v>
       </c>
       <c r="AP10" s="4">
         <f>AO10/AL10</f>
-        <v>0.99284241174329735</v>
+        <v>0.99332767196409077</v>
       </c>
       <c r="AQ10" s="5">
         <v>132270</v>
@@ -1393,14 +1393,14 @@
       </c>
       <c r="AS10" s="3">
         <f>AT10-AR10</f>
-        <v>79273</v>
+        <v>79342</v>
       </c>
       <c r="AT10" s="5">
-        <v>132211</v>
+        <v>132280</v>
       </c>
       <c r="AU10" s="4">
         <f>AT10/AQ10</f>
-        <v>0.99955394269297648</v>
+        <v>1.0000756029333939</v>
       </c>
       <c r="AV10" s="5">
         <v>73561</v>
@@ -1410,14 +1410,14 @@
       </c>
       <c r="AX10" s="3">
         <f>AY10-AW10</f>
-        <v>41151</v>
+        <v>41192</v>
       </c>
       <c r="AY10" s="5">
-        <v>73398</v>
+        <v>73439</v>
       </c>
       <c r="AZ10" s="4">
         <f>AY10/AV10</f>
-        <v>0.99778415192833159</v>
+        <v>0.99834151248623593</v>
       </c>
       <c r="BA10" s="5">
         <v>75582</v>
@@ -1427,14 +1427,14 @@
       </c>
       <c r="BC10" s="3">
         <f>BD10-BB10</f>
-        <v>41373</v>
+        <v>41427</v>
       </c>
       <c r="BD10" s="5">
-        <v>74345</v>
+        <v>74399</v>
       </c>
       <c r="BE10" s="4">
         <f>BD10/BA10</f>
-        <v>0.98363366939218333</v>
+        <v>0.98434812521499826</v>
       </c>
       <c r="BF10" s="5">
         <v>134150</v>
@@ -1444,14 +1444,14 @@
       </c>
       <c r="BH10" s="3">
         <f>BI10-BG10</f>
-        <v>88087</v>
+        <v>88230</v>
       </c>
       <c r="BI10" s="5">
-        <v>133651</v>
+        <v>133794</v>
       </c>
       <c r="BJ10" s="4">
         <f>BI10/BF10</f>
-        <v>0.99628028326500184</v>
+        <v>0.99734625419306744</v>
       </c>
       <c r="BL10" s="9"/>
     </row>
@@ -1470,14 +1470,14 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>14868</v>
+        <v>14889</v>
       </c>
       <c r="F11" s="5">
-        <v>46140</v>
+        <v>46161</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99138394104123251</v>
+        <v>0.99183515609892348</v>
       </c>
       <c r="H11" s="5">
         <v>47616</v>
@@ -1487,14 +1487,14 @@
       </c>
       <c r="J11" s="3">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>15016</v>
+        <v>15036</v>
       </c>
       <c r="K11" s="5">
-        <v>46950</v>
+        <v>46970</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.98601310483870963</v>
+        <v>0.98643313172043012</v>
       </c>
       <c r="M11" s="5">
         <v>108402</v>
@@ -1504,14 +1504,14 @@
       </c>
       <c r="O11" s="3">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>45204</v>
+        <v>45244</v>
       </c>
       <c r="P11" s="5">
-        <v>108039</v>
+        <v>108079</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.99665135329606469</v>
+        <v>0.99702035017804103</v>
       </c>
       <c r="R11" s="5">
         <v>46539</v>
@@ -1521,14 +1521,14 @@
       </c>
       <c r="T11" s="3">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>15158</v>
+        <v>15177</v>
       </c>
       <c r="U11" s="5">
-        <v>46213</v>
+        <v>46232</v>
       </c>
       <c r="V11" s="4">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99299512237048493</v>
+        <v>0.99340338210962853</v>
       </c>
       <c r="W11" s="5">
         <v>48300</v>
@@ -1538,14 +1538,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8188</v>
+        <v>8211</v>
       </c>
       <c r="Z11" s="5">
-        <v>46893</v>
+        <v>46916</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.97086956521739132</v>
+        <v>0.97134575569358184</v>
       </c>
       <c r="AB11" s="5">
         <v>109219</v>
@@ -1555,14 +1555,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>47637</v>
+        <v>47695</v>
       </c>
       <c r="AE11" s="5">
-        <v>108565</v>
+        <v>108623</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.99401203087374912</v>
+        <v>0.99454307400726982</v>
       </c>
       <c r="AG11" s="5">
         <v>46763</v>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>15527</v>
+        <v>15552</v>
       </c>
       <c r="AJ11" s="5">
-        <v>46389</v>
+        <v>46414</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99200222398049742</v>
+        <v>0.99253683467698817</v>
       </c>
       <c r="AL11" s="5">
         <v>48206</v>
@@ -1589,14 +1589,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>14772</v>
+        <v>14800</v>
       </c>
       <c r="AO11" s="5">
-        <v>47116</v>
+        <v>47144</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.97738870679998335</v>
+        <v>0.9779695473592499</v>
       </c>
       <c r="AQ11" s="5">
         <v>110196</v>
@@ -1606,14 +1606,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>40317</v>
+        <v>40385</v>
       </c>
       <c r="AT11" s="5">
-        <v>109853</v>
+        <v>109921</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.99688736433264369</v>
+        <v>0.99750444662238191</v>
       </c>
       <c r="AV11" s="5">
         <v>47206</v>
@@ -1623,14 +1623,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>14155</v>
+        <v>14187</v>
       </c>
       <c r="AY11" s="5">
-        <v>46767</v>
+        <v>46799</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.99070033470321572</v>
+        <v>0.99137821463373299</v>
       </c>
       <c r="BA11" s="5">
         <v>48813</v>
@@ -1640,14 +1640,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>13865</v>
+        <v>13906</v>
       </c>
       <c r="BD11" s="5">
-        <v>47429</v>
+        <v>47470</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.97164689734292098</v>
+        <v>0.97248683752279108</v>
       </c>
       <c r="BF11" s="5">
         <v>111276</v>
@@ -1657,14 +1657,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>48055</v>
+        <v>48177</v>
       </c>
       <c r="BI11" s="5">
-        <v>110743</v>
+        <v>110865</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.99521010819943201</v>
+        <v>0.996306481181926</v>
       </c>
       <c r="BL11" s="9"/>
     </row>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>38004</v>
+        <v>38026</v>
       </c>
       <c r="F12" s="5">
-        <v>175248</v>
+        <v>175270</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>0.98959292115353126</v>
+        <v>0.98971715106922431</v>
       </c>
       <c r="H12" s="5">
         <v>181172</v>
@@ -1700,14 +1700,14 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="2"/>
-        <v>37777</v>
+        <v>37803</v>
       </c>
       <c r="K12" s="5">
-        <v>177919</v>
+        <v>177945</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="3"/>
-        <v>0.98204468681694745</v>
+        <v>0.98218819685161063</v>
       </c>
       <c r="M12" s="5">
         <v>363483</v>
@@ -1717,14 +1717,14 @@
       </c>
       <c r="O12" s="3">
         <f t="shared" si="4"/>
-        <v>99660</v>
+        <v>99724</v>
       </c>
       <c r="P12" s="5">
-        <v>360982</v>
+        <v>361046</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="5"/>
-        <v>0.99311934808505486</v>
+        <v>0.99329542234437374</v>
       </c>
       <c r="R12" s="5">
         <v>177513</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="T12" s="3">
         <f t="shared" si="6"/>
-        <v>39972</v>
+        <v>40007</v>
       </c>
       <c r="U12" s="5">
-        <v>176782</v>
+        <v>176817</v>
       </c>
       <c r="V12" s="4">
         <f t="shared" si="7"/>
-        <v>0.99588199174144987</v>
+        <v>0.99607916039952005</v>
       </c>
       <c r="W12" s="5">
         <v>182324</v>
@@ -1751,14 +1751,14 @@
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="8"/>
-        <v>28554</v>
+        <v>28591</v>
       </c>
       <c r="Z12" s="5">
-        <v>178626</v>
+        <v>178663</v>
       </c>
       <c r="AA12" s="4">
         <f t="shared" si="9"/>
-        <v>0.9797174261205327</v>
+        <v>0.97992036155415629</v>
       </c>
       <c r="AB12" s="5">
         <v>365690</v>
@@ -1768,14 +1768,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="10"/>
-        <v>109152</v>
+        <v>109249</v>
       </c>
       <c r="AE12" s="5">
-        <v>363084</v>
+        <v>363181</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="11"/>
-        <v>0.99287374552216356</v>
+        <v>0.99313899751155355</v>
       </c>
       <c r="AG12" s="5">
         <v>180670</v>
@@ -1785,14 +1785,14 @@
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="12"/>
-        <v>39815</v>
+        <v>39865</v>
       </c>
       <c r="AJ12" s="5">
-        <v>176976</v>
+        <v>177026</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="13"/>
-        <v>0.97955388276969058</v>
+        <v>0.97983063043117291</v>
       </c>
       <c r="AL12" s="5">
         <v>181581</v>
@@ -1802,14 +1802,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="14"/>
-        <v>37217</v>
+        <v>37285</v>
       </c>
       <c r="AO12" s="5">
-        <v>178233</v>
+        <v>178301</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="15"/>
-        <v>0.98156194756059278</v>
+        <v>0.98193643608086745</v>
       </c>
       <c r="AQ12" s="5">
         <v>363376</v>
@@ -1819,14 +1819,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="16"/>
-        <v>94652</v>
+        <v>94807</v>
       </c>
       <c r="AT12" s="5">
-        <v>362625</v>
+        <v>362780</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="17"/>
-        <v>0.9979332702214786</v>
+        <v>0.9983598256351548</v>
       </c>
       <c r="AV12" s="5">
         <v>179534</v>
@@ -1836,14 +1836,14 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="18"/>
-        <v>36336</v>
+        <v>36429</v>
       </c>
       <c r="AY12" s="5">
-        <v>178074</v>
+        <v>178167</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="19"/>
-        <v>0.99186783561888003</v>
+        <v>0.99238584335000612</v>
       </c>
       <c r="BA12" s="5">
         <v>184469</v>
@@ -1853,14 +1853,14 @@
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="20"/>
-        <v>37066</v>
+        <v>37169</v>
       </c>
       <c r="BD12" s="5">
-        <v>181499</v>
+        <v>181602</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="21"/>
-        <v>0.98389973383061657</v>
+        <v>0.98445809322975675</v>
       </c>
       <c r="BF12" s="5">
         <v>368393</v>
@@ -1870,14 +1870,14 @@
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="22"/>
-        <v>110692</v>
+        <v>110945</v>
       </c>
       <c r="BI12" s="5">
-        <v>367526</v>
+        <v>367779</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="23"/>
-        <v>0.99764653508617152</v>
+        <v>0.99833330166425527</v>
       </c>
       <c r="BL12" s="9"/>
     </row>
@@ -1930,14 +1930,14 @@
       </c>
       <c r="O13" s="3">
         <f t="shared" si="4"/>
-        <v>6814</v>
+        <v>6816</v>
       </c>
       <c r="P13" s="5">
-        <v>28678</v>
+        <v>28680</v>
       </c>
       <c r="Q13" s="4">
         <f t="shared" si="5"/>
-        <v>1.0000348711510967</v>
+        <v>1.00010461345329</v>
       </c>
       <c r="R13" s="5">
         <v>17606</v>
@@ -1947,14 +1947,14 @@
       </c>
       <c r="T13" s="3">
         <f t="shared" si="6"/>
-        <v>3642</v>
+        <v>3643</v>
       </c>
       <c r="U13" s="5">
-        <v>17594</v>
+        <v>17595</v>
       </c>
       <c r="V13" s="4">
         <f t="shared" si="7"/>
-        <v>0.99931841417698508</v>
+        <v>0.99937521299556964</v>
       </c>
       <c r="W13" s="5">
         <v>17849</v>
@@ -1964,14 +1964,14 @@
       </c>
       <c r="Y13" s="3">
         <f t="shared" si="8"/>
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="Z13" s="5">
-        <v>17730</v>
+        <v>17731</v>
       </c>
       <c r="AA13" s="4">
         <f t="shared" si="9"/>
-        <v>0.99333295982968228</v>
+        <v>0.99338898537733211</v>
       </c>
       <c r="AB13" s="5">
         <v>28890</v>
@@ -1981,14 +1981,14 @@
       </c>
       <c r="AD13" s="3">
         <f t="shared" si="10"/>
-        <v>7335</v>
+        <v>7338</v>
       </c>
       <c r="AE13" s="5">
-        <v>28862</v>
+        <v>28865</v>
       </c>
       <c r="AF13" s="4">
         <f t="shared" si="11"/>
-        <v>0.99903080650744203</v>
+        <v>0.9991346486673589</v>
       </c>
       <c r="AG13" s="5">
         <v>17747</v>
@@ -1998,14 +1998,14 @@
       </c>
       <c r="AI13" s="3">
         <f t="shared" si="12"/>
-        <v>3747</v>
+        <v>3748</v>
       </c>
       <c r="AJ13" s="5">
-        <v>17796</v>
+        <v>17797</v>
       </c>
       <c r="AK13" s="4">
         <f t="shared" si="13"/>
-        <v>1.002761030033245</v>
+        <v>1.0028173775849438</v>
       </c>
       <c r="AL13" s="5">
         <v>17937</v>
@@ -2015,14 +2015,14 @@
       </c>
       <c r="AN13" s="3">
         <f t="shared" si="14"/>
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="AO13" s="5">
-        <v>17838</v>
+        <v>17839</v>
       </c>
       <c r="AP13" s="4">
         <f t="shared" si="15"/>
-        <v>0.99448068238835929</v>
+        <v>0.99453643307130513</v>
       </c>
       <c r="AQ13" s="5">
         <v>28933</v>
@@ -2032,14 +2032,14 @@
       </c>
       <c r="AS13" s="3">
         <f t="shared" si="16"/>
-        <v>6289</v>
+        <v>6295</v>
       </c>
       <c r="AT13" s="5">
-        <v>29014</v>
+        <v>29020</v>
       </c>
       <c r="AU13" s="4">
         <f t="shared" si="17"/>
-        <v>1.002799571423634</v>
+        <v>1.0030069470846439</v>
       </c>
       <c r="AV13" s="5">
         <v>17858</v>
@@ -2049,14 +2049,14 @@
       </c>
       <c r="AX13" s="3">
         <f t="shared" si="18"/>
-        <v>3283</v>
+        <v>3284</v>
       </c>
       <c r="AY13" s="5">
-        <v>17833</v>
+        <v>17834</v>
       </c>
       <c r="AZ13" s="4">
         <f t="shared" si="19"/>
-        <v>0.99860006719677452</v>
+        <v>0.99865606450890354</v>
       </c>
       <c r="BA13" s="5">
         <v>18026</v>
@@ -2066,14 +2066,14 @@
       </c>
       <c r="BC13" s="3">
         <f t="shared" si="20"/>
-        <v>3274</v>
+        <v>3282</v>
       </c>
       <c r="BD13" s="5">
-        <v>17912</v>
+        <v>17920</v>
       </c>
       <c r="BE13" s="4">
         <f t="shared" si="21"/>
-        <v>0.99367580161988234</v>
+        <v>0.99411960501497831</v>
       </c>
       <c r="BF13" s="5">
         <v>29023</v>
@@ -2083,14 +2083,14 @@
       </c>
       <c r="BH13" s="3">
         <f t="shared" si="22"/>
-        <v>7401</v>
+        <v>7420</v>
       </c>
       <c r="BI13" s="5">
-        <v>29112</v>
+        <v>29131</v>
       </c>
       <c r="BJ13" s="4">
         <f t="shared" si="23"/>
-        <v>1.0030665334389968</v>
+        <v>1.0037211866450746</v>
       </c>
       <c r="BL13" s="9"/>
     </row>
@@ -2109,14 +2109,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>38173</v>
+        <v>38200</v>
       </c>
       <c r="F14" s="5">
-        <v>89580</v>
+        <v>89607</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>0.9901843745854888</v>
+        <v>0.99048282265552456</v>
       </c>
       <c r="H14" s="5">
         <v>94129</v>
@@ -2126,14 +2126,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>38608</v>
+        <v>38639</v>
       </c>
       <c r="K14" s="5">
-        <v>91118</v>
+        <v>91149</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.9680119835544837</v>
+        <v>0.96834131882841634</v>
       </c>
       <c r="M14" s="5">
         <v>164995</v>
@@ -2143,14 +2143,14 @@
       </c>
       <c r="O14" s="3">
         <f t="shared" si="4"/>
-        <v>80876</v>
+        <v>80929</v>
       </c>
       <c r="P14" s="5">
-        <v>164045</v>
+        <v>164098</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="5"/>
-        <v>0.99424224976514441</v>
+        <v>0.99456347162035208</v>
       </c>
       <c r="R14" s="5">
         <v>91074</v>
@@ -2160,14 +2160,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="6"/>
-        <v>39471</v>
+        <v>39504</v>
       </c>
       <c r="U14" s="5">
-        <v>90493</v>
+        <v>90526</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="7"/>
-        <v>0.99362057228188072</v>
+        <v>0.99398291499220415</v>
       </c>
       <c r="W14" s="5">
         <v>93800</v>
@@ -2177,14 +2177,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="8"/>
-        <v>18286</v>
+        <v>18327</v>
       </c>
       <c r="Z14" s="5">
-        <v>91069</v>
+        <v>91110</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="9"/>
-        <v>0.9708848614072495</v>
+        <v>0.97132196162046913</v>
       </c>
       <c r="AB14" s="5">
         <v>166352</v>
@@ -2194,14 +2194,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="10"/>
-        <v>85234</v>
+        <v>85322</v>
       </c>
       <c r="AE14" s="5">
-        <v>164717</v>
+        <v>164805</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="11"/>
-        <v>0.99017144368567855</v>
+        <v>0.99070044243531785</v>
       </c>
       <c r="AG14" s="5">
         <v>92175</v>
@@ -2211,14 +2211,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="12"/>
-        <v>39702</v>
+        <v>39754</v>
       </c>
       <c r="AJ14" s="5">
-        <v>91208</v>
+        <v>91260</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="13"/>
-        <v>0.98950908597775966</v>
+        <v>0.99007323026851102</v>
       </c>
       <c r="AL14" s="5">
         <v>94655</v>
@@ -2228,14 +2228,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="14"/>
-        <v>38474</v>
+        <v>38527</v>
       </c>
       <c r="AO14" s="5">
-        <v>92715</v>
+        <v>92768</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="15"/>
-        <v>0.97950451640166925</v>
+        <v>0.98006444456182984</v>
       </c>
       <c r="AQ14" s="5">
         <v>168400</v>
@@ -2245,14 +2245,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="16"/>
-        <v>78262</v>
+        <v>78377</v>
       </c>
       <c r="AT14" s="5">
-        <v>167674</v>
+        <v>167789</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="17"/>
-        <v>0.99568883610451309</v>
+        <v>0.99637173396674583</v>
       </c>
       <c r="AV14" s="5">
         <v>94024</v>
@@ -2262,14 +2262,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="18"/>
-        <v>38101</v>
+        <v>38163</v>
       </c>
       <c r="AY14" s="5">
-        <v>93188</v>
+        <v>93250</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="19"/>
-        <v>0.99110865310984431</v>
+        <v>0.99176805921892286</v>
       </c>
       <c r="BA14" s="5">
         <v>96514</v>
@@ -2279,14 +2279,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="20"/>
-        <v>38183</v>
+        <v>38264</v>
       </c>
       <c r="BD14" s="5">
-        <v>94648</v>
+        <v>94729</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="21"/>
-        <v>0.9806660173653563</v>
+        <v>0.98150527384628139</v>
       </c>
       <c r="BF14" s="5">
         <v>171502</v>
@@ -2296,14 +2296,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="22"/>
-        <v>86144</v>
+        <v>86335</v>
       </c>
       <c r="BI14" s="5">
-        <v>170852</v>
+        <v>171043</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="23"/>
-        <v>0.99620995673519841</v>
+        <v>0.99732364637147086</v>
       </c>
       <c r="BL14" s="9"/>
     </row>
@@ -2322,14 +2322,14 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>75134</v>
+        <v>75143</v>
       </c>
       <c r="F15" s="5">
-        <v>301278</v>
+        <v>301287</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="1"/>
-        <v>0.98925303151196353</v>
+        <v>0.98928258321266394</v>
       </c>
       <c r="H15" s="5">
         <v>309950</v>
@@ -2339,14 +2339,14 @@
       </c>
       <c r="J15" s="3">
         <f t="shared" si="2"/>
-        <v>73603</v>
+        <v>73613</v>
       </c>
       <c r="K15" s="5">
-        <v>306232</v>
+        <v>306242</v>
       </c>
       <c r="L15" s="4">
         <f t="shared" si="3"/>
-        <v>0.98800451685755764</v>
+        <v>0.98803678012582674</v>
       </c>
       <c r="M15" s="5">
         <v>517862</v>
@@ -2356,14 +2356,14 @@
       </c>
       <c r="O15" s="3">
         <f t="shared" si="4"/>
-        <v>147203</v>
+        <v>147232</v>
       </c>
       <c r="P15" s="5">
-        <v>514044</v>
+        <v>514073</v>
       </c>
       <c r="Q15" s="4">
         <f t="shared" si="5"/>
-        <v>0.99262737949492341</v>
+        <v>0.99268337896968695</v>
       </c>
       <c r="R15" s="5">
         <v>307768</v>
@@ -2373,14 +2373,14 @@
       </c>
       <c r="T15" s="3">
         <f t="shared" si="6"/>
-        <v>77294</v>
+        <v>77309</v>
       </c>
       <c r="U15" s="5">
-        <v>305812</v>
+        <v>305827</v>
       </c>
       <c r="V15" s="4">
         <f t="shared" si="7"/>
-        <v>0.99364456343739438</v>
+        <v>0.99369330144784385</v>
       </c>
       <c r="W15" s="5">
         <v>314114</v>
@@ -2390,14 +2390,14 @@
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="8"/>
-        <v>50806</v>
+        <v>50824</v>
       </c>
       <c r="Z15" s="5">
-        <v>308367</v>
+        <v>308385</v>
       </c>
       <c r="AA15" s="4">
         <f t="shared" si="9"/>
-        <v>0.98170409469173614</v>
+        <v>0.9817613987278504</v>
       </c>
       <c r="AB15" s="5">
         <v>523203</v>
@@ -2407,14 +2407,14 @@
       </c>
       <c r="AD15" s="3">
         <f t="shared" si="10"/>
-        <v>165213</v>
+        <v>165263</v>
       </c>
       <c r="AE15" s="5">
-        <v>520303</v>
+        <v>520353</v>
       </c>
       <c r="AF15" s="4">
         <f t="shared" si="11"/>
-        <v>0.99445721832634748</v>
+        <v>0.99455278352761733</v>
       </c>
       <c r="AG15" s="5">
         <v>312916</v>
@@ -2424,14 +2424,14 @@
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="12"/>
-        <v>79964</v>
+        <v>79995</v>
       </c>
       <c r="AJ15" s="5">
-        <v>310157</v>
+        <v>310188</v>
       </c>
       <c r="AK15" s="4">
         <f t="shared" si="13"/>
-        <v>0.99118293727390094</v>
+        <v>0.99128200539441891</v>
       </c>
       <c r="AL15" s="5">
         <v>318942</v>
@@ -2441,14 +2441,14 @@
       </c>
       <c r="AN15" s="3">
         <f t="shared" si="14"/>
-        <v>75071</v>
+        <v>75109</v>
       </c>
       <c r="AO15" s="5">
-        <v>313588</v>
+        <v>313626</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="15"/>
-        <v>0.98321324880385774</v>
+        <v>0.98333239272344186</v>
       </c>
       <c r="AQ15" s="5">
         <v>530087</v>
@@ -2458,14 +2458,14 @@
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="16"/>
-        <v>137351</v>
+        <v>137435</v>
       </c>
       <c r="AT15" s="5">
-        <v>527508</v>
+        <v>527592</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="17"/>
-        <v>0.99513476089773945</v>
+        <v>0.99529322545167109</v>
       </c>
       <c r="AV15" s="5">
         <v>317508</v>
@@ -2475,14 +2475,14 @@
       </c>
       <c r="AX15" s="3">
         <f t="shared" si="18"/>
-        <v>73182</v>
+        <v>73241</v>
       </c>
       <c r="AY15" s="5">
-        <v>315779</v>
+        <v>315838</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="19"/>
-        <v>0.99455446791891855</v>
+        <v>0.99474029000844078</v>
       </c>
       <c r="BA15" s="5">
         <v>324414</v>
@@ -2492,14 +2492,14 @@
       </c>
       <c r="BC15" s="3">
         <f t="shared" si="20"/>
-        <v>73855</v>
+        <v>73937</v>
       </c>
       <c r="BD15" s="5">
-        <v>320375</v>
+        <v>320457</v>
       </c>
       <c r="BE15" s="4">
         <f t="shared" si="21"/>
-        <v>0.9875498591306171</v>
+        <v>0.98780262257485807</v>
       </c>
       <c r="BF15" s="5">
         <v>538701</v>
@@ -2509,14 +2509,14 @@
       </c>
       <c r="BH15" s="3">
         <f t="shared" si="22"/>
-        <v>165384</v>
+        <v>165606</v>
       </c>
       <c r="BI15" s="5">
-        <v>537059</v>
+        <v>537281</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="23"/>
-        <v>0.99695192695020063</v>
+        <v>0.99736402939664115</v>
       </c>
       <c r="BL15" s="9"/>
     </row>
@@ -2535,14 +2535,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>111514</v>
+        <v>111611</v>
       </c>
       <c r="F16" s="5">
-        <v>439276</v>
+        <v>439373</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.98563536903324822</v>
+        <v>0.98585301495698685</v>
       </c>
       <c r="H16" s="5">
         <v>453561</v>
@@ -2552,14 +2552,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>109979</v>
+        <v>110092</v>
       </c>
       <c r="K16" s="5">
-        <v>444208</v>
+        <v>444321</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.97937873847178214</v>
+        <v>0.97962787805829865</v>
       </c>
       <c r="M16" s="5">
         <v>776551</v>
@@ -2569,14 +2569,14 @@
       </c>
       <c r="O16" s="3">
         <f t="shared" si="4"/>
-        <v>203667</v>
+        <v>203900</v>
       </c>
       <c r="P16" s="5">
-        <v>770267</v>
+        <v>770500</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="5"/>
-        <v>0.99190780772930565</v>
+        <v>0.99220785241407194</v>
       </c>
       <c r="R16" s="5">
         <v>446959</v>
@@ -2586,14 +2586,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="6"/>
-        <v>113970</v>
+        <v>114111</v>
       </c>
       <c r="U16" s="5">
-        <v>442766</v>
+        <v>442907</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="7"/>
-        <v>0.99061882633530141</v>
+        <v>0.99093429151219692</v>
       </c>
       <c r="W16" s="5">
         <v>453618</v>
@@ -2603,14 +2603,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="8"/>
-        <v>73419</v>
+        <v>73575</v>
       </c>
       <c r="Z16" s="5">
-        <v>442766</v>
+        <v>442922</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="9"/>
-        <v>0.97607678707635059</v>
+        <v>0.97642068877337318</v>
       </c>
       <c r="AB16" s="5">
         <v>775718</v>
@@ -2620,14 +2620,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="10"/>
-        <v>220487</v>
+        <v>220817</v>
       </c>
       <c r="AE16" s="5">
-        <v>768950</v>
+        <v>769280</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="11"/>
-        <v>0.99127517989784952</v>
+        <v>0.9917005922255252</v>
       </c>
       <c r="AG16" s="5">
         <v>444751</v>
@@ -2637,14 +2637,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="12"/>
-        <v>115134</v>
+        <v>115326</v>
       </c>
       <c r="AJ16" s="5">
-        <v>438511</v>
+        <v>438703</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="13"/>
-        <v>0.98596967741500297</v>
+        <v>0.98640137964838748</v>
       </c>
       <c r="AL16" s="5">
         <v>448369</v>
@@ -2654,14 +2654,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="14"/>
-        <v>107433</v>
+        <v>107655</v>
       </c>
       <c r="AO16" s="5">
-        <v>439698</v>
+        <v>439920</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="15"/>
-        <v>0.98066101804540462</v>
+        <v>0.98115614594229306</v>
       </c>
       <c r="AQ16" s="5">
         <v>770483</v>
@@ -2671,14 +2671,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="16"/>
-        <v>182385</v>
+        <v>182838</v>
       </c>
       <c r="AT16" s="5">
-        <v>768213</v>
+        <v>768666</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="17"/>
-        <v>0.99705379612528766</v>
+        <v>0.99764173901306064</v>
       </c>
       <c r="AV16" s="5">
         <v>444563</v>
@@ -2688,14 +2688,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="18"/>
-        <v>108258</v>
+        <v>108537</v>
       </c>
       <c r="AY16" s="5">
-        <v>442955</v>
+        <v>443234</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="19"/>
-        <v>0.99638296484412781</v>
+        <v>0.99701054743647133</v>
       </c>
       <c r="BA16" s="5">
         <v>453397</v>
@@ -2705,14 +2705,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="20"/>
-        <v>105647</v>
+        <v>105959</v>
       </c>
       <c r="BD16" s="5">
-        <v>447534</v>
+        <v>447846</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="21"/>
-        <v>0.98706872784778021</v>
+        <v>0.98775686649889616</v>
       </c>
       <c r="BF16" s="5">
         <v>780218</v>
@@ -2722,14 +2722,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="22"/>
-        <v>216267</v>
+        <v>216944</v>
       </c>
       <c r="BI16" s="5">
-        <v>778085</v>
+        <v>778762</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="23"/>
-        <v>0.99726614869177588</v>
+        <v>0.99813385489696471</v>
       </c>
       <c r="BL16" s="9"/>
     </row>
@@ -2748,14 +2748,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>91865</v>
+        <v>91921</v>
       </c>
       <c r="F17" s="5">
-        <v>320811</v>
+        <v>320867</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.99026438041146425</v>
+        <v>0.99043723859058852</v>
       </c>
       <c r="H17" s="5">
         <v>333085</v>
@@ -2765,14 +2765,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>90127</v>
+        <v>90195</v>
       </c>
       <c r="K17" s="5">
-        <v>328177</v>
+        <v>328245</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.9852650224417191</v>
+        <v>0.98546917453502858</v>
       </c>
       <c r="M17" s="5">
         <v>731481</v>
@@ -2782,14 +2782,14 @@
       </c>
       <c r="O17" s="3">
         <f t="shared" si="4"/>
-        <v>270178</v>
+        <v>270371</v>
       </c>
       <c r="P17" s="5">
-        <v>728461</v>
+        <v>728654</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="5"/>
-        <v>0.995871389687497</v>
+        <v>0.99613523796243508</v>
       </c>
       <c r="R17" s="5">
         <v>324758</v>
@@ -2799,14 +2799,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="6"/>
-        <v>95119</v>
+        <v>95196</v>
       </c>
       <c r="U17" s="5">
-        <v>323065</v>
+        <v>323142</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="7"/>
-        <v>0.99478688746697541</v>
+        <v>0.99502398709192696</v>
       </c>
       <c r="W17" s="5">
         <v>336053</v>
@@ -2816,14 +2816,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="8"/>
-        <v>55863</v>
+        <v>55955</v>
       </c>
       <c r="Z17" s="5">
-        <v>326749</v>
+        <v>326841</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="9"/>
-        <v>0.97231389096362775</v>
+        <v>0.97258765730405616</v>
       </c>
       <c r="AB17" s="5">
         <v>736224</v>
@@ -2833,14 +2833,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="10"/>
-        <v>293765</v>
+        <v>294059</v>
       </c>
       <c r="AE17" s="5">
-        <v>730211</v>
+        <v>730505</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="11"/>
-        <v>0.99183264875907329</v>
+        <v>0.99223198374407784</v>
       </c>
       <c r="AG17" s="5">
         <v>328692</v>
@@ -2850,14 +2850,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="12"/>
-        <v>97187</v>
+        <v>97300</v>
       </c>
       <c r="AJ17" s="5">
-        <v>325638</v>
+        <v>325751</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="13"/>
-        <v>0.9907086269212515</v>
+        <v>0.99105241380988884</v>
       </c>
       <c r="AL17" s="5">
         <v>339621</v>
@@ -2867,14 +2867,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="14"/>
-        <v>93018</v>
+        <v>93148</v>
       </c>
       <c r="AO17" s="5">
-        <v>332151</v>
+        <v>332281</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="15"/>
-        <v>0.97800489369031951</v>
+        <v>0.97838767331819887</v>
       </c>
       <c r="AQ17" s="5">
         <v>745574</v>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="16"/>
-        <v>255499</v>
+        <v>255894</v>
       </c>
       <c r="AT17" s="5">
-        <v>741365</v>
+        <v>741760</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="17"/>
-        <v>0.99435468511509251</v>
+        <v>0.99488447826775073</v>
       </c>
       <c r="AV17" s="5">
         <v>334329</v>
@@ -2901,14 +2901,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="18"/>
-        <v>91016</v>
+        <v>91175</v>
       </c>
       <c r="AY17" s="5">
-        <v>331950</v>
+        <v>332109</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="19"/>
-        <v>0.99288425473111819</v>
+        <v>0.99335983417531837</v>
       </c>
       <c r="BA17" s="5">
         <v>348862</v>
@@ -2918,14 +2918,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="20"/>
-        <v>92645</v>
+        <v>92856</v>
       </c>
       <c r="BD17" s="5">
-        <v>339306</v>
+        <v>339517</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="21"/>
-        <v>0.97260807998578236</v>
+        <v>0.97321290366964586</v>
       </c>
       <c r="BF17" s="5">
         <v>757181</v>
@@ -2935,14 +2935,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="22"/>
-        <v>299260</v>
+        <v>299971</v>
       </c>
       <c r="BI17" s="5">
-        <v>754737</v>
+        <v>755448</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="23"/>
-        <v>0.99677223807781756</v>
+        <v>0.99771124737678307</v>
       </c>
       <c r="BL17" s="9"/>
     </row>
@@ -2961,14 +2961,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>482214</v>
+        <v>482364</v>
       </c>
       <c r="F18" s="5">
-        <v>988228</v>
+        <v>988378</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.98976014871020335</v>
+        <v>0.98991038127020625</v>
       </c>
       <c r="H18" s="5">
         <v>1018686</v>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>481708</v>
+        <v>481876</v>
       </c>
       <c r="K18" s="5">
-        <v>1001767</v>
+        <v>1001935</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.9833913492479528</v>
+        <v>0.98355626758392678</v>
       </c>
       <c r="M18" s="5">
         <v>1536859</v>
@@ -2995,14 +2995,14 @@
       </c>
       <c r="O18" s="3">
         <f t="shared" si="4"/>
-        <v>795885</v>
+        <v>796176</v>
       </c>
       <c r="P18" s="5">
-        <v>1524480</v>
+        <v>1524771</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="5"/>
-        <v>0.99194525977984971</v>
+        <v>0.99213460701339551</v>
       </c>
       <c r="R18" s="5">
         <v>1011292</v>
@@ -3012,14 +3012,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="6"/>
-        <v>494838</v>
+        <v>495037</v>
       </c>
       <c r="U18" s="5">
-        <v>1002422</v>
+        <v>1002621</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="7"/>
-        <v>0.99122904166155767</v>
+        <v>0.99142581964457344</v>
       </c>
       <c r="W18" s="5">
         <v>1030498</v>
@@ -3029,14 +3029,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="8"/>
-        <v>182044</v>
+        <v>182283</v>
       </c>
       <c r="Z18" s="5">
-        <v>1008362</v>
+        <v>1008601</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="9"/>
-        <v>0.97851912376346195</v>
+        <v>0.97875105046298005</v>
       </c>
       <c r="AB18" s="5">
         <v>1557879</v>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="10"/>
-        <v>827397</v>
+        <v>827825</v>
       </c>
       <c r="AE18" s="5">
-        <v>1540883</v>
+        <v>1541311</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="11"/>
-        <v>0.98909029520264413</v>
+        <v>0.98936502770754342</v>
       </c>
       <c r="AG18" s="5">
         <v>1025067</v>
@@ -3063,14 +3063,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="12"/>
-        <v>506896</v>
+        <v>507198</v>
       </c>
       <c r="AJ18" s="5">
-        <v>1017420</v>
+        <v>1017722</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="13"/>
-        <v>0.99253999982440178</v>
+        <v>0.9928346147129895</v>
       </c>
       <c r="AL18" s="5">
         <v>1045736</v>
@@ -3080,14 +3080,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="14"/>
-        <v>495620</v>
+        <v>495984</v>
       </c>
       <c r="AO18" s="5">
-        <v>1031409</v>
+        <v>1031773</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="15"/>
-        <v>0.98629960142904138</v>
+        <v>0.98664768163284045</v>
       </c>
       <c r="AQ18" s="5">
         <v>1584961</v>
@@ -3097,14 +3097,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="16"/>
-        <v>770478</v>
+        <v>771143</v>
       </c>
       <c r="AT18" s="5">
-        <v>1573940</v>
+        <v>1574605</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="17"/>
-        <v>0.99304651660198584</v>
+        <v>0.99346608528537927</v>
       </c>
       <c r="AV18" s="5">
         <v>1051416</v>
@@ -3114,14 +3114,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="18"/>
-        <v>500597</v>
+        <v>501088</v>
       </c>
       <c r="AY18" s="5">
-        <v>1044125</v>
+        <v>1044616</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="19"/>
-        <v>0.99306554208800324</v>
+        <v>0.99353253136722286</v>
       </c>
       <c r="BA18" s="5">
         <v>1075670</v>
@@ -3131,14 +3131,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="20"/>
-        <v>499837</v>
+        <v>500441</v>
       </c>
       <c r="BD18" s="5">
-        <v>1059825</v>
+        <v>1060429</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="21"/>
-        <v>0.98526964589511656</v>
+        <v>0.98583115639554886</v>
       </c>
       <c r="BF18" s="5">
         <v>1620029</v>
@@ -3148,14 +3148,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="22"/>
-        <v>861920</v>
+        <v>863230</v>
       </c>
       <c r="BI18" s="5">
-        <v>1607702</v>
+        <v>1609012</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="23"/>
-        <v>0.99239087695343731</v>
+        <v>0.9931995044533154</v>
       </c>
       <c r="BL18" s="9"/>
     </row>
@@ -3174,14 +3174,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>171910</v>
+        <v>171995</v>
       </c>
       <c r="F19" s="5">
-        <v>284688</v>
+        <v>284773</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.97708372659722342</v>
+        <v>0.9773754569011377</v>
       </c>
       <c r="H19" s="5">
         <v>301141</v>
@@ -3191,14 +3191,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>156293</v>
+        <v>156388</v>
       </c>
       <c r="K19" s="5">
-        <v>288882</v>
+        <v>288977</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.95929149468189323</v>
+        <v>0.95960696152300751</v>
       </c>
       <c r="M19" s="5">
         <v>505864</v>
@@ -3208,14 +3208,14 @@
       </c>
       <c r="O19" s="3">
         <f t="shared" si="4"/>
-        <v>245040</v>
+        <v>245227</v>
       </c>
       <c r="P19" s="5">
-        <v>497751</v>
+        <v>497938</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="5"/>
-        <v>0.98396209257824241</v>
+        <v>0.98433175715211996</v>
       </c>
       <c r="R19" s="5">
         <v>293000</v>
@@ -3225,14 +3225,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="6"/>
-        <v>124280</v>
+        <v>124399</v>
       </c>
       <c r="U19" s="5">
-        <v>286290</v>
+        <v>286409</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="7"/>
-        <v>0.97709897610921503</v>
+        <v>0.97750511945392493</v>
       </c>
       <c r="W19" s="5">
         <v>302979</v>
@@ -3242,14 +3242,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="8"/>
-        <v>59307</v>
+        <v>59446</v>
       </c>
       <c r="Z19" s="5">
-        <v>287367</v>
+        <v>287506</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="9"/>
-        <v>0.9484716762547899</v>
+        <v>0.94893045392584963</v>
       </c>
       <c r="AB19" s="5">
         <v>514622</v>
@@ -3259,14 +3259,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="10"/>
-        <v>298353</v>
+        <v>298644</v>
       </c>
       <c r="AE19" s="5">
-        <v>498438</v>
+        <v>498729</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="11"/>
-        <v>0.96855167482151949</v>
+        <v>0.96911713840449887</v>
       </c>
       <c r="AG19" s="5">
         <v>295766</v>
@@ -3276,14 +3276,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="12"/>
-        <v>161488</v>
+        <v>161676</v>
       </c>
       <c r="AJ19" s="5">
-        <v>286993</v>
+        <v>287181</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="13"/>
-        <v>0.97033803750262027</v>
+        <v>0.97097367513507304</v>
       </c>
       <c r="AL19" s="5">
         <v>302797</v>
@@ -3293,14 +3293,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="14"/>
-        <v>149527</v>
+        <v>149744</v>
       </c>
       <c r="AO19" s="5">
-        <v>290996</v>
+        <v>291213</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="15"/>
-        <v>0.96102669445205868</v>
+        <v>0.96174334620224111</v>
       </c>
       <c r="AQ19" s="5">
         <v>519490</v>
@@ -3310,14 +3310,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="16"/>
-        <v>278496</v>
+        <v>278960</v>
       </c>
       <c r="AT19" s="5">
-        <v>507286</v>
+        <v>507750</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="17"/>
-        <v>0.97650772873395064</v>
+        <v>0.97740091243334815</v>
       </c>
       <c r="AV19" s="5">
         <v>299668</v>
@@ -3327,14 +3327,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="18"/>
-        <v>152870</v>
+        <v>153187</v>
       </c>
       <c r="AY19" s="5">
-        <v>294158</v>
+        <v>294475</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="19"/>
-        <v>0.98161298503677408</v>
+        <v>0.98267082237676362</v>
       </c>
       <c r="BA19" s="5">
         <v>313772</v>
@@ -3344,14 +3344,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="20"/>
-        <v>154550</v>
+        <v>154916</v>
       </c>
       <c r="BD19" s="5">
-        <v>299123</v>
+        <v>299489</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="21"/>
-        <v>0.95331323381308719</v>
+        <v>0.95447968588656729</v>
       </c>
       <c r="BF19" s="5">
         <v>528004</v>
@@ -3361,14 +3361,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="22"/>
-        <v>332445</v>
+        <v>333321</v>
       </c>
       <c r="BI19" s="5">
-        <v>517200</v>
+        <v>518076</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="23"/>
-        <v>0.97953803380277427</v>
+        <v>0.9811971121430898</v>
       </c>
       <c r="BL19" s="9"/>
     </row>
@@ -3387,14 +3387,14 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>3796</v>
+        <v>3805</v>
       </c>
       <c r="F20" s="5">
-        <v>6394</v>
+        <v>6403</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>0.98947694212318171</v>
+        <v>0.99086969978334882</v>
       </c>
       <c r="H20" s="5">
         <v>6957</v>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="2"/>
-        <v>3732</v>
+        <v>3743</v>
       </c>
       <c r="K20" s="5">
-        <v>6428</v>
+        <v>6439</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="3"/>
-        <v>0.92396147764841163</v>
+        <v>0.92554261894494749</v>
       </c>
       <c r="M20" s="5">
         <v>9947</v>
@@ -3421,14 +3421,14 @@
       </c>
       <c r="O20" s="3">
         <f t="shared" si="4"/>
-        <v>5524</v>
+        <v>5538</v>
       </c>
       <c r="P20" s="5">
-        <v>9832</v>
+        <v>9846</v>
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="5"/>
-        <v>0.98843872524379206</v>
+        <v>0.98984618477933051</v>
       </c>
       <c r="R20" s="5">
         <v>6587</v>
@@ -3438,14 +3438,14 @@
       </c>
       <c r="T20" s="3">
         <f t="shared" si="6"/>
-        <v>3667</v>
+        <v>3680</v>
       </c>
       <c r="U20" s="5">
-        <v>6478</v>
+        <v>6491</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" si="7"/>
-        <v>0.98345225444056472</v>
+        <v>0.98542583877334144</v>
       </c>
       <c r="W20" s="5">
         <v>6643</v>
@@ -3455,14 +3455,14 @@
       </c>
       <c r="Y20" s="3">
         <f t="shared" si="8"/>
-        <v>1705</v>
+        <v>1719</v>
       </c>
       <c r="Z20" s="5">
-        <v>6498</v>
+        <v>6512</v>
       </c>
       <c r="AA20" s="4">
         <f t="shared" si="9"/>
-        <v>0.97817251241908776</v>
+        <v>0.98027999397862409</v>
       </c>
       <c r="AB20" s="5">
         <v>9927</v>
@@ -3472,14 +3472,14 @@
       </c>
       <c r="AD20" s="3">
         <f t="shared" si="10"/>
-        <v>5967</v>
+        <v>5991</v>
       </c>
       <c r="AE20" s="5">
-        <v>9867</v>
+        <v>9891</v>
       </c>
       <c r="AF20" s="4">
         <f t="shared" si="11"/>
-        <v>0.99395587790873374</v>
+        <v>0.99637352674524027</v>
       </c>
       <c r="AG20" s="5">
         <v>6546</v>
@@ -3489,14 +3489,14 @@
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="12"/>
-        <v>3864</v>
+        <v>3883</v>
       </c>
       <c r="AJ20" s="5">
-        <v>6471</v>
+        <v>6490</v>
       </c>
       <c r="AK20" s="4">
         <f t="shared" si="13"/>
-        <v>0.9885426214482127</v>
+        <v>0.99144515734799876</v>
       </c>
       <c r="AL20" s="5">
         <v>6627</v>
@@ -3506,14 +3506,14 @@
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="14"/>
-        <v>3733</v>
+        <v>3752</v>
       </c>
       <c r="AO20" s="5">
-        <v>6527</v>
+        <v>6546</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" si="15"/>
-        <v>0.98491021578391424</v>
+        <v>0.98777727478497057</v>
       </c>
       <c r="AQ20" s="5">
         <v>9949</v>
@@ -3523,14 +3523,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="16"/>
-        <v>5444</v>
+        <v>5471</v>
       </c>
       <c r="AT20" s="5">
-        <v>9955</v>
+        <v>9982</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="17"/>
-        <v>1.0006030756859985</v>
+        <v>1.0033169162729922</v>
       </c>
       <c r="AV20" s="5">
         <v>6437</v>
@@ -3540,14 +3540,14 @@
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="18"/>
-        <v>3601</v>
+        <v>3624</v>
       </c>
       <c r="AY20" s="5">
-        <v>6402</v>
+        <v>6425</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" si="19"/>
-        <v>0.99456268448034801</v>
+        <v>0.99813577753611926</v>
       </c>
       <c r="BA20" s="5">
         <v>6564</v>
@@ -3557,14 +3557,14 @@
       </c>
       <c r="BC20" s="3">
         <f t="shared" si="20"/>
-        <v>3465</v>
+        <v>3492</v>
       </c>
       <c r="BD20" s="5">
-        <v>6474</v>
+        <v>6501</v>
       </c>
       <c r="BE20" s="4">
         <f t="shared" si="21"/>
-        <v>0.98628884826325414</v>
+        <v>0.99040219378427785</v>
       </c>
       <c r="BF20" s="5">
         <v>10109</v>
@@ -3574,14 +3574,14 @@
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="22"/>
-        <v>5972</v>
+        <v>6023</v>
       </c>
       <c r="BI20" s="5">
-        <v>10028</v>
+        <v>10079</v>
       </c>
       <c r="BJ20" s="4">
         <f t="shared" si="23"/>
-        <v>0.99198733801562966</v>
+        <v>0.99703234741319613</v>
       </c>
       <c r="BL20" s="9"/>
     </row>
@@ -3600,14 +3600,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>8211</v>
+        <v>8233</v>
       </c>
       <c r="F21" s="5">
-        <v>10870</v>
+        <v>10892</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>0.98935105124237732</v>
+        <v>0.99135341767543461</v>
       </c>
       <c r="H21" s="5">
         <v>10970</v>
@@ -3617,14 +3617,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>7930</v>
+        <v>7951</v>
       </c>
       <c r="K21" s="5">
-        <v>10930</v>
+        <v>10951</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>0.99635369188696443</v>
+        <v>0.99826800364630808</v>
       </c>
       <c r="M21" s="5">
         <v>14288</v>
@@ -3634,14 +3634,14 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="4"/>
-        <v>10692</v>
+        <v>10722</v>
       </c>
       <c r="P21" s="5">
-        <v>14521</v>
+        <v>14551</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="5"/>
-        <v>1.0163073908174691</v>
+        <v>1.0184070548712205</v>
       </c>
       <c r="R21" s="5">
         <v>10910</v>
@@ -3651,14 +3651,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="6"/>
-        <v>8251</v>
+        <v>8276</v>
       </c>
       <c r="U21" s="5">
-        <v>11154</v>
+        <v>11179</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="7"/>
-        <v>1.022364802933089</v>
+        <v>1.0246562786434463</v>
       </c>
       <c r="W21" s="5">
         <v>11256</v>
@@ -3668,14 +3668,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="8"/>
-        <v>3646</v>
+        <v>3674</v>
       </c>
       <c r="Z21" s="5">
-        <v>11285</v>
+        <v>11313</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="9"/>
-        <v>1.0025764036958067</v>
+        <v>1.0050639658848615</v>
       </c>
       <c r="AB21" s="5">
         <v>14831</v>
@@ -3685,14 +3685,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="10"/>
-        <v>11254</v>
+        <v>11295</v>
       </c>
       <c r="AE21" s="5">
-        <v>14957</v>
+        <v>14998</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="11"/>
-        <v>1.0084957184276178</v>
+        <v>1.0112601982334299</v>
       </c>
       <c r="AG21" s="5">
         <v>11222</v>
@@ -3702,14 +3702,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="12"/>
-        <v>8156</v>
+        <v>8189</v>
       </c>
       <c r="AJ21" s="5">
-        <v>11316</v>
+        <v>11349</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="13"/>
-        <v>1.0083764034931384</v>
+        <v>1.0113170557832829</v>
       </c>
       <c r="AL21" s="5">
         <v>11337</v>
@@ -3719,14 +3719,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="14"/>
-        <v>8286</v>
+        <v>8325</v>
       </c>
       <c r="AO21" s="5">
-        <v>11488</v>
+        <v>11527</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="15"/>
-        <v>1.0133192202522714</v>
+        <v>1.0167592837611361</v>
       </c>
       <c r="AQ21" s="5">
         <v>15149</v>
@@ -3736,14 +3736,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="16"/>
-        <v>10923</v>
+        <v>10982</v>
       </c>
       <c r="AT21" s="5">
-        <v>15339</v>
+        <v>15398</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="17"/>
-        <v>1.0125420819856097</v>
+        <v>1.0164367284969305</v>
       </c>
       <c r="AV21" s="5">
         <v>11422</v>
@@ -3753,14 +3753,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="18"/>
-        <v>8350</v>
+        <v>8410</v>
       </c>
       <c r="AY21" s="5">
-        <v>11632</v>
+        <v>11692</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="19"/>
-        <v>1.0183855717037296</v>
+        <v>1.0236385921905096</v>
       </c>
       <c r="BA21" s="5">
         <v>11689</v>
@@ -3770,14 +3770,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="20"/>
-        <v>8301</v>
+        <v>8370</v>
       </c>
       <c r="BD21" s="5">
-        <v>11778</v>
+        <v>11847</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="21"/>
-        <v>1.0076139960646762</v>
+        <v>1.0135169817777399</v>
       </c>
       <c r="BF21" s="5">
         <v>15725</v>
@@ -3787,14 +3787,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="22"/>
-        <v>11745</v>
+        <v>11877</v>
       </c>
       <c r="BI21" s="5">
-        <v>15683</v>
+        <v>15815</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="23"/>
-        <v>0.99732909379968204</v>
+        <v>1.0057233704292527</v>
       </c>
       <c r="BL21" s="9"/>
     </row>
@@ -3813,14 +3813,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>4603</v>
+        <v>4618</v>
       </c>
       <c r="F22" s="5">
-        <v>6675</v>
+        <v>6690</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>0.9880106571936057</v>
+        <v>0.99023090586145646</v>
       </c>
       <c r="H22" s="5">
         <v>6770</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>4618</v>
+        <v>4634</v>
       </c>
       <c r="K22" s="5">
-        <v>6755</v>
+        <v>6771</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>0.99778434268833083</v>
+        <v>1.0001477104874446</v>
       </c>
       <c r="M22" s="5">
         <v>8074</v>
@@ -3847,14 +3847,14 @@
       </c>
       <c r="O22" s="3">
         <f t="shared" si="4"/>
-        <v>5504</v>
+        <v>5524</v>
       </c>
       <c r="P22" s="5">
-        <v>8071</v>
+        <v>8091</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="5"/>
-        <v>0.99962843695813719</v>
+        <v>1.002105523903889</v>
       </c>
       <c r="R22" s="5">
         <v>6748</v>
@@ -3864,14 +3864,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="6"/>
-        <v>4603</v>
+        <v>4623</v>
       </c>
       <c r="U22" s="5">
-        <v>6770</v>
+        <v>6790</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="7"/>
-        <v>1.0032602252519265</v>
+        <v>1.0062240663900415</v>
       </c>
       <c r="W22" s="5">
         <v>6876</v>
@@ -3881,14 +3881,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="8"/>
-        <v>1662</v>
+        <v>1681</v>
       </c>
       <c r="Z22" s="5">
-        <v>6828</v>
+        <v>6847</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="9"/>
-        <v>0.99301919720767884</v>
+        <v>0.99578243164630598</v>
       </c>
       <c r="AB22" s="5">
         <v>8219</v>
@@ -3898,14 +3898,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="10"/>
-        <v>5716</v>
+        <v>5738</v>
       </c>
       <c r="AE22" s="5">
-        <v>8220</v>
+        <v>8242</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="11"/>
-        <v>1.000121669302835</v>
+        <v>1.0027983939652025</v>
       </c>
       <c r="AG22" s="5">
         <v>6901</v>
@@ -3915,14 +3915,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="12"/>
-        <v>4652</v>
+        <v>4675</v>
       </c>
       <c r="AJ22" s="5">
-        <v>6888</v>
+        <v>6911</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="13"/>
-        <v>0.99811621504129833</v>
+        <v>1.0014490653528474</v>
       </c>
       <c r="AL22" s="5">
         <v>6948</v>
@@ -3932,14 +3932,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="14"/>
-        <v>4619</v>
+        <v>4645</v>
       </c>
       <c r="AO22" s="5">
-        <v>6925</v>
+        <v>6951</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="15"/>
-        <v>0.99668969487622339</v>
+        <v>1.0004317789291883</v>
       </c>
       <c r="AQ22" s="5">
         <v>8297</v>
@@ -3949,14 +3949,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="16"/>
-        <v>5544</v>
+        <v>5574</v>
       </c>
       <c r="AT22" s="5">
-        <v>8282</v>
+        <v>8312</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="17"/>
-        <v>0.99819211763287941</v>
+        <v>1.0018078823671206</v>
       </c>
       <c r="AV22" s="5">
         <v>6958</v>
@@ -3966,14 +3966,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="18"/>
-        <v>4638</v>
+        <v>4668</v>
       </c>
       <c r="AY22" s="5">
-        <v>6956</v>
+        <v>6986</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="19"/>
-        <v>0.99971256108077033</v>
+        <v>1.0040241448692153</v>
       </c>
       <c r="BA22" s="5">
         <v>7049</v>
@@ -3983,14 +3983,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="20"/>
-        <v>4615</v>
+        <v>4649</v>
       </c>
       <c r="BD22" s="5">
-        <v>7010</v>
+        <v>7044</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="21"/>
-        <v>0.99446730032628738</v>
+        <v>0.99929067952901118</v>
       </c>
       <c r="BF22" s="5">
         <v>8436</v>
@@ -4000,14 +4000,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="22"/>
-        <v>5722</v>
+        <v>5763</v>
       </c>
       <c r="BI22" s="5">
-        <v>8378</v>
+        <v>8419</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="23"/>
-        <v>0.99312470365101946</v>
+        <v>0.99798482693219537</v>
       </c>
       <c r="BL22" s="9"/>
     </row>
@@ -4026,14 +4026,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>6222</v>
+        <v>6240</v>
       </c>
       <c r="F23" s="5">
-        <v>8668</v>
+        <v>8686</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.98410535876475935</v>
+        <v>0.98614895549500459</v>
       </c>
       <c r="H23" s="5">
         <v>8878</v>
@@ -4043,14 +4043,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>6307</v>
+        <v>6326</v>
       </c>
       <c r="K23" s="5">
-        <v>8783</v>
+        <v>8802</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.98929939175489978</v>
+        <v>0.99143951340391978</v>
       </c>
       <c r="M23" s="5">
         <v>11255</v>
@@ -4060,14 +4060,14 @@
       </c>
       <c r="O23" s="3">
         <f t="shared" si="4"/>
-        <v>7967</v>
+        <v>7991</v>
       </c>
       <c r="P23" s="5">
-        <v>11206</v>
+        <v>11230</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="5"/>
-        <v>0.99564637938693912</v>
+        <v>0.99777876499333629</v>
       </c>
       <c r="R23" s="5">
         <v>8944</v>
@@ -4077,14 +4077,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="6"/>
-        <v>6210</v>
+        <v>6233</v>
       </c>
       <c r="U23" s="5">
-        <v>8902</v>
+        <v>8925</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="7"/>
-        <v>0.99530411449016098</v>
+        <v>0.9978756708407871</v>
       </c>
       <c r="W23" s="5">
         <v>10422</v>
@@ -4094,14 +4094,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="8"/>
-        <v>2928</v>
+        <v>2959</v>
       </c>
       <c r="Z23" s="5">
-        <v>9005</v>
+        <v>9036</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="9"/>
-        <v>0.86403761274227597</v>
+        <v>0.86701208981001732</v>
       </c>
       <c r="AB23" s="5">
         <v>11673</v>
@@ -4111,14 +4111,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="10"/>
-        <v>8230</v>
+        <v>8266</v>
       </c>
       <c r="AE23" s="5">
-        <v>11396</v>
+        <v>11432</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="11"/>
-        <v>0.97627002484365633</v>
+        <v>0.97935406493617749</v>
       </c>
       <c r="AG23" s="5">
         <v>9370</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="12"/>
-        <v>6351</v>
+        <v>6379</v>
       </c>
       <c r="AJ23" s="5">
-        <v>8981</v>
+        <v>9009</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="13"/>
-        <v>0.95848452508004267</v>
+        <v>0.96147278548559234</v>
       </c>
       <c r="AL23" s="5">
         <v>9238</v>
@@ -4145,14 +4145,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="14"/>
-        <v>6400</v>
+        <v>6430</v>
       </c>
       <c r="AO23" s="5">
-        <v>9019</v>
+        <v>9049</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="15"/>
-        <v>0.9762935700368045</v>
+        <v>0.97954102619614636</v>
       </c>
       <c r="AQ23" s="5">
         <v>11727</v>
@@ -4162,14 +4162,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="16"/>
-        <v>8028</v>
+        <v>8068</v>
       </c>
       <c r="AT23" s="5">
-        <v>11508</v>
+        <v>11548</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="17"/>
-        <v>0.98132514709644414</v>
+        <v>0.98473607913362327</v>
       </c>
       <c r="AV23" s="5">
         <v>9359</v>
@@ -4179,14 +4179,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="18"/>
-        <v>6448</v>
+        <v>6483</v>
       </c>
       <c r="AY23" s="5">
-        <v>9130</v>
+        <v>9165</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="19"/>
-        <v>0.9755315738860989</v>
+        <v>0.9792712896676995</v>
       </c>
       <c r="BA23" s="5">
         <v>9570</v>
@@ -4196,14 +4196,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="20"/>
-        <v>6383</v>
+        <v>6421</v>
       </c>
       <c r="BD23" s="5">
-        <v>9180</v>
+        <v>9218</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="21"/>
-        <v>0.95924764890282133</v>
+        <v>0.9632183908045977</v>
       </c>
       <c r="BF23" s="5">
         <v>11968</v>
@@ -4213,14 +4213,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="22"/>
-        <v>8535</v>
+        <v>8591</v>
       </c>
       <c r="BI23" s="5">
-        <v>11685</v>
+        <v>11741</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="23"/>
-        <v>0.97635360962566842</v>
+        <v>0.98103275401069523</v>
       </c>
       <c r="BL23" s="9"/>
     </row>
@@ -4239,14 +4239,14 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="0"/>
-        <v>4829</v>
+        <v>4837</v>
       </c>
       <c r="F24" s="5">
-        <v>6182</v>
+        <v>6190</v>
       </c>
       <c r="G24" s="4">
         <f t="shared" si="1"/>
-        <v>0.98912</v>
+        <v>0.99039999999999995</v>
       </c>
       <c r="H24" s="5">
         <v>6322</v>
@@ -4256,14 +4256,14 @@
       </c>
       <c r="J24" s="3">
         <f t="shared" si="2"/>
-        <v>4867</v>
+        <v>4875</v>
       </c>
       <c r="K24" s="5">
-        <v>6231</v>
+        <v>6239</v>
       </c>
       <c r="L24" s="4">
         <f t="shared" si="3"/>
-        <v>0.98560582094273963</v>
+        <v>0.9868712432774438</v>
       </c>
       <c r="M24" s="5">
         <v>7266</v>
@@ -4273,14 +4273,14 @@
       </c>
       <c r="O24" s="3">
         <f t="shared" si="4"/>
-        <v>5665</v>
+        <v>5674</v>
       </c>
       <c r="P24" s="5">
-        <v>7159</v>
+        <v>7168</v>
       </c>
       <c r="Q24" s="4">
         <f t="shared" si="5"/>
-        <v>0.98527387833746216</v>
+        <v>0.98651252408477841</v>
       </c>
       <c r="R24" s="5">
         <v>6403</v>
@@ -4290,14 +4290,14 @@
       </c>
       <c r="T24" s="3">
         <f t="shared" si="6"/>
-        <v>4991</v>
+        <v>4999</v>
       </c>
       <c r="U24" s="5">
-        <v>6301</v>
+        <v>6309</v>
       </c>
       <c r="V24" s="4">
         <f t="shared" si="7"/>
-        <v>0.98406996720287365</v>
+        <v>0.98531938153990317</v>
       </c>
       <c r="W24" s="5">
         <v>6540</v>
@@ -4307,14 +4307,14 @@
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="8"/>
-        <v>1288</v>
+        <v>1298</v>
       </c>
       <c r="Z24" s="5">
-        <v>6395</v>
+        <v>6405</v>
       </c>
       <c r="AA24" s="4">
         <f t="shared" si="9"/>
-        <v>0.97782874617737003</v>
+        <v>0.97935779816513757</v>
       </c>
       <c r="AB24" s="5">
         <v>7473</v>
@@ -4324,14 +4324,14 @@
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="10"/>
-        <v>5835</v>
+        <v>5849</v>
       </c>
       <c r="AE24" s="5">
-        <v>7369</v>
+        <v>7383</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="11"/>
-        <v>0.9860832329720326</v>
+        <v>0.98795664391810523</v>
       </c>
       <c r="AG24" s="5">
         <v>6660</v>
@@ -4341,14 +4341,14 @@
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="12"/>
-        <v>5208</v>
+        <v>5218</v>
       </c>
       <c r="AJ24" s="5">
-        <v>6582</v>
+        <v>6592</v>
       </c>
       <c r="AK24" s="4">
         <f t="shared" si="13"/>
-        <v>0.9882882882882883</v>
+        <v>0.98978978978978982</v>
       </c>
       <c r="AL24" s="5">
         <v>6723</v>
@@ -4358,14 +4358,14 @@
       </c>
       <c r="AN24" s="3">
         <f t="shared" si="14"/>
-        <v>4993</v>
+        <v>5003</v>
       </c>
       <c r="AO24" s="5">
-        <v>6629</v>
+        <v>6639</v>
       </c>
       <c r="AP24" s="4">
         <f t="shared" si="15"/>
-        <v>0.98601814666071697</v>
+        <v>0.98750557786702364</v>
       </c>
       <c r="AQ24" s="5">
         <v>7657</v>
@@ -4375,14 +4375,14 @@
       </c>
       <c r="AS24" s="3">
         <f t="shared" si="16"/>
-        <v>5924</v>
+        <v>5939</v>
       </c>
       <c r="AT24" s="5">
-        <v>7554</v>
+        <v>7569</v>
       </c>
       <c r="AU24" s="4">
         <f t="shared" si="17"/>
-        <v>0.9865482564973227</v>
+        <v>0.98850724826955727</v>
       </c>
       <c r="AV24" s="5">
         <v>6786</v>
@@ -4392,14 +4392,14 @@
       </c>
       <c r="AX24" s="3">
         <f t="shared" si="18"/>
-        <v>5243</v>
+        <v>5256</v>
       </c>
       <c r="AY24" s="5">
-        <v>6731</v>
+        <v>6744</v>
       </c>
       <c r="AZ24" s="4">
         <f t="shared" si="19"/>
-        <v>0.99189507810197464</v>
+        <v>0.99381078691423519</v>
       </c>
       <c r="BA24" s="5">
         <v>7025</v>
@@ -4409,14 +4409,14 @@
       </c>
       <c r="BC24" s="3">
         <f t="shared" si="20"/>
-        <v>5287</v>
+        <v>5299</v>
       </c>
       <c r="BD24" s="5">
-        <v>6791</v>
+        <v>6803</v>
       </c>
       <c r="BE24" s="4">
         <f t="shared" si="21"/>
-        <v>0.96669039145907476</v>
+        <v>0.96839857651245553</v>
       </c>
       <c r="BF24" s="5">
         <v>7878</v>
@@ -4426,14 +4426,14 @@
       </c>
       <c r="BH24" s="3">
         <f t="shared" si="22"/>
-        <v>6221</v>
+        <v>6236</v>
       </c>
       <c r="BI24" s="5">
-        <v>7737</v>
+        <v>7752</v>
       </c>
       <c r="BJ24" s="4">
         <f t="shared" si="23"/>
-        <v>0.98210205635948211</v>
+        <v>0.98400609291698404</v>
       </c>
       <c r="BL24" s="9"/>
     </row>
@@ -4452,14 +4452,14 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>11725</v>
+        <v>11739</v>
       </c>
       <c r="F25" s="5">
-        <v>20202</v>
+        <v>20216</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>0.96530963302752293</v>
+        <v>0.96597859327217128</v>
       </c>
       <c r="H25" s="5">
         <v>20519</v>
@@ -4469,14 +4469,14 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>11452</v>
+        <v>11470</v>
       </c>
       <c r="K25" s="5">
-        <v>20329</v>
+        <v>20347</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="3"/>
-        <v>0.9907402894877918</v>
+        <v>0.99161752522052726</v>
       </c>
       <c r="M25" s="5">
         <v>27924</v>
@@ -4486,14 +4486,14 @@
       </c>
       <c r="O25" s="3">
         <f t="shared" si="4"/>
-        <v>16446</v>
+        <v>16475</v>
       </c>
       <c r="P25" s="5">
-        <v>27893</v>
+        <v>27922</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="5"/>
-        <v>0.99888984386191093</v>
+        <v>0.99992837702334914</v>
       </c>
       <c r="R25" s="5">
         <v>20481</v>
@@ -4503,14 +4503,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="6"/>
-        <v>11633</v>
+        <v>11657</v>
       </c>
       <c r="U25" s="5">
-        <v>20468</v>
+        <v>20492</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="7"/>
-        <v>0.99936526536790193</v>
+        <v>1.0005370831502367</v>
       </c>
       <c r="W25" s="5">
         <v>20934</v>
@@ -4520,14 +4520,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="8"/>
-        <v>4192</v>
+        <v>4216</v>
       </c>
       <c r="Z25" s="5">
-        <v>20591</v>
+        <v>20615</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="9"/>
-        <v>0.9836151714913538</v>
+        <v>0.98476163179516574</v>
       </c>
       <c r="AB25" s="5">
         <v>28211</v>
@@ -4537,14 +4537,14 @@
       </c>
       <c r="AD25" s="3">
         <f t="shared" si="10"/>
-        <v>18072</v>
+        <v>18108</v>
       </c>
       <c r="AE25" s="5">
-        <v>28203</v>
+        <v>28239</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="11"/>
-        <v>0.99971642267200733</v>
+        <v>1.0009925206479742</v>
       </c>
       <c r="AG25" s="5">
         <v>20778</v>
@@ -4554,14 +4554,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="12"/>
-        <v>11751</v>
+        <v>11778</v>
       </c>
       <c r="AJ25" s="5">
-        <v>20699</v>
+        <v>20726</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="13"/>
-        <v>0.99619790162672062</v>
+        <v>0.99749735296948694</v>
       </c>
       <c r="AL25" s="5">
         <v>21081</v>
@@ -4571,14 +4571,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="14"/>
-        <v>11821</v>
+        <v>11848</v>
       </c>
       <c r="AO25" s="5">
-        <v>20880</v>
+        <v>20907</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="15"/>
-        <v>0.99046534794364594</v>
+        <v>0.99174612210046964</v>
       </c>
       <c r="AQ25" s="5">
         <v>28478</v>
@@ -4588,14 +4588,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="16"/>
-        <v>16432</v>
+        <v>16482</v>
       </c>
       <c r="AT25" s="5">
-        <v>28447</v>
+        <v>28497</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="17"/>
-        <v>0.99891144041014113</v>
+        <v>1.0006671816841071</v>
       </c>
       <c r="AV25" s="5">
         <v>21086</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="18"/>
-        <v>12049</v>
+        <v>12085</v>
       </c>
       <c r="AY25" s="5">
-        <v>21015</v>
+        <v>21051</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="19"/>
-        <v>0.99663283695342886</v>
+        <v>0.99834013089253537</v>
       </c>
       <c r="BA25" s="5">
         <v>21405</v>
@@ -4622,14 +4622,14 @@
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="20"/>
-        <v>11987</v>
+        <v>12028</v>
       </c>
       <c r="BD25" s="5">
-        <v>21197</v>
+        <v>21238</v>
       </c>
       <c r="BE25" s="4">
         <f t="shared" si="21"/>
-        <v>0.99028264424199952</v>
+        <v>0.99219808455968228</v>
       </c>
       <c r="BF25" s="5">
         <v>28924</v>
@@ -4639,14 +4639,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="22"/>
-        <v>17812</v>
+        <v>17885</v>
       </c>
       <c r="BI25" s="5">
-        <v>28782</v>
+        <v>28855</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="23"/>
-        <v>0.99509058221546121</v>
+        <v>0.99761443783709025</v>
       </c>
       <c r="BL25" s="9"/>
     </row>
@@ -4665,14 +4665,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>9653</v>
+        <v>9660</v>
       </c>
       <c r="F26" s="5">
-        <v>14024</v>
+        <v>14031</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.99588126686550205</v>
+        <v>0.99637835534725183</v>
       </c>
       <c r="H26" s="5">
         <v>14494</v>
@@ -4682,14 +4682,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>9741</v>
+        <v>9750</v>
       </c>
       <c r="K26" s="5">
-        <v>14307</v>
+        <v>14316</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>0.9870981095625776</v>
+        <v>0.98771905616117017</v>
       </c>
       <c r="M26" s="5">
         <v>27473</v>
@@ -4699,14 +4699,14 @@
       </c>
       <c r="O26" s="3">
         <f t="shared" si="4"/>
-        <v>18996</v>
+        <v>19023</v>
       </c>
       <c r="P26" s="5">
-        <v>27405</v>
+        <v>27432</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="5"/>
-        <v>0.99752484257270779</v>
+        <v>0.99850762566883855</v>
       </c>
       <c r="R26" s="5">
         <v>14274</v>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="6"/>
-        <v>9995</v>
+        <v>10003</v>
       </c>
       <c r="U26" s="5">
-        <v>14201</v>
+        <v>14209</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="7"/>
-        <v>0.99488580636121615</v>
+        <v>0.99544626593806917</v>
       </c>
       <c r="W26" s="5">
         <v>14651</v>
@@ -4733,14 +4733,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="8"/>
-        <v>3110</v>
+        <v>3119</v>
       </c>
       <c r="Z26" s="5">
-        <v>14423</v>
+        <v>14432</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="9"/>
-        <v>0.98443792232612104</v>
+        <v>0.98505221486587946</v>
       </c>
       <c r="AB26" s="5">
         <v>28023</v>
@@ -4750,14 +4750,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="10"/>
-        <v>20251</v>
+        <v>20290</v>
       </c>
       <c r="AE26" s="5">
-        <v>27672</v>
+        <v>27711</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="11"/>
-        <v>0.98747457445669629</v>
+        <v>0.98886628840595225</v>
       </c>
       <c r="AG26" s="5">
         <v>14346</v>
@@ -4767,14 +4767,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="12"/>
-        <v>9747</v>
+        <v>9761</v>
       </c>
       <c r="AJ26" s="5">
-        <v>14229</v>
+        <v>14243</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="13"/>
-        <v>0.99184441656210787</v>
+        <v>0.99282029834100094</v>
       </c>
       <c r="AL26" s="5">
         <v>14687</v>
@@ -4784,14 +4784,14 @@
       </c>
       <c r="AN26" s="3">
         <f t="shared" si="14"/>
-        <v>9428</v>
+        <v>9446</v>
       </c>
       <c r="AO26" s="5">
-        <v>14401</v>
+        <v>14419</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="15"/>
-        <v>0.98052699666371623</v>
+        <v>0.98175257030026553</v>
       </c>
       <c r="AQ26" s="5">
         <v>27948</v>
@@ -4801,14 +4801,14 @@
       </c>
       <c r="AS26" s="3">
         <f t="shared" si="16"/>
-        <v>18741</v>
+        <v>18790</v>
       </c>
       <c r="AT26" s="5">
-        <v>27780</v>
+        <v>27829</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="17"/>
-        <v>0.99398883641047664</v>
+        <v>0.99574209245742096</v>
       </c>
       <c r="AV26" s="5">
         <v>14478</v>
@@ -4818,14 +4818,14 @@
       </c>
       <c r="AX26" s="3">
         <f t="shared" si="18"/>
-        <v>9466</v>
+        <v>9487</v>
       </c>
       <c r="AY26" s="5">
-        <v>14362</v>
+        <v>14383</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="19"/>
-        <v>0.99198784362481007</v>
+        <v>0.9934383202099738</v>
       </c>
       <c r="BA26" s="5">
         <v>14902</v>
@@ -4835,14 +4835,14 @@
       </c>
       <c r="BC26" s="3">
         <f t="shared" si="20"/>
-        <v>9549</v>
+        <v>9574</v>
       </c>
       <c r="BD26" s="5">
-        <v>14496</v>
+        <v>14521</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="21"/>
-        <v>0.97275533485438193</v>
+        <v>0.97443296201852103</v>
       </c>
       <c r="BF26" s="5">
         <v>28105</v>
@@ -4852,14 +4852,14 @@
       </c>
       <c r="BH26" s="3">
         <f t="shared" si="22"/>
-        <v>20098</v>
+        <v>20171</v>
       </c>
       <c r="BI26" s="5">
-        <v>27861</v>
+        <v>27934</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="23"/>
-        <v>0.99131827077032553</v>
+        <v>0.99391567336772813</v>
       </c>
       <c r="BL26" s="9"/>
     </row>
@@ -4878,14 +4878,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>76198</v>
+        <v>76297</v>
       </c>
       <c r="F27" s="5">
-        <v>124985</v>
+        <v>125084</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>0.96784809930538884</v>
+        <v>0.96861472699536155</v>
       </c>
       <c r="H27" s="5">
         <v>129298</v>
@@ -4895,14 +4895,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>74488</v>
+        <v>74596</v>
       </c>
       <c r="K27" s="5">
-        <v>125884</v>
+        <v>125992</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.97359587928660918</v>
+        <v>0.97443115902798183</v>
       </c>
       <c r="M27" s="5">
         <v>186733</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="O27" s="3">
         <f t="shared" si="4"/>
-        <v>116467</v>
+        <v>116655</v>
       </c>
       <c r="P27" s="5">
-        <v>185561</v>
+        <v>185749</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="5"/>
-        <v>0.99372365891406444</v>
+        <v>0.99473044400293464</v>
       </c>
       <c r="R27" s="5">
         <v>126872</v>
@@ -4929,14 +4929,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="6"/>
-        <v>74990</v>
+        <v>75127</v>
       </c>
       <c r="U27" s="5">
-        <v>125517</v>
+        <v>125654</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="7"/>
-        <v>0.98931994451100325</v>
+        <v>0.99039977299955861</v>
       </c>
       <c r="W27" s="5">
         <v>129739</v>
@@ -4946,14 +4946,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="8"/>
-        <v>33603</v>
+        <v>33754</v>
       </c>
       <c r="Z27" s="5">
-        <v>126464</v>
+        <v>126615</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="9"/>
-        <v>0.97475701215517307</v>
+        <v>0.97592088731992688</v>
       </c>
       <c r="AB27" s="5">
         <v>188270</v>
@@ -4963,14 +4963,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="10"/>
-        <v>125415</v>
+        <v>125659</v>
       </c>
       <c r="AE27" s="5">
-        <v>186903</v>
+        <v>187147</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="11"/>
-        <v>0.99273915121899403</v>
+        <v>0.99403516226695698</v>
       </c>
       <c r="AG27" s="5">
         <v>127800</v>
@@ -4980,14 +4980,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="12"/>
-        <v>76235</v>
+        <v>76414</v>
       </c>
       <c r="AJ27" s="5">
-        <v>126580</v>
+        <v>126759</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="13"/>
-        <v>0.9904538341158059</v>
+        <v>0.99185446009389666</v>
       </c>
       <c r="AL27" s="5">
         <v>130262</v>
@@ -4997,14 +4997,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" si="14"/>
-        <v>74382</v>
+        <v>74587</v>
       </c>
       <c r="AO27" s="5">
-        <v>127623</v>
+        <v>127828</v>
       </c>
       <c r="AP27" s="4">
         <f t="shared" si="15"/>
-        <v>0.97974083001949919</v>
+        <v>0.98131458138213756</v>
       </c>
       <c r="AQ27" s="5">
         <v>189830</v>
@@ -5014,14 +5014,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" si="16"/>
-        <v>115588</v>
+        <v>115915</v>
       </c>
       <c r="AT27" s="5">
-        <v>188841</v>
+        <v>189168</v>
       </c>
       <c r="AU27" s="4">
         <f t="shared" si="17"/>
-        <v>0.99479007533055896</v>
+        <v>0.99651266923036397</v>
       </c>
       <c r="AV27" s="5">
         <v>128733</v>
@@ -5031,14 +5031,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" si="18"/>
-        <v>73560</v>
+        <v>73802</v>
       </c>
       <c r="AY27" s="5">
-        <v>128221</v>
+        <v>128463</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" si="19"/>
-        <v>0.99602277582282706</v>
+        <v>0.99790263568781901</v>
       </c>
       <c r="BA27" s="5">
         <v>132099</v>
@@ -5048,14 +5048,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" si="20"/>
-        <v>74119</v>
+        <v>74400</v>
       </c>
       <c r="BD27" s="5">
-        <v>129687</v>
+        <v>129968</v>
       </c>
       <c r="BE27" s="4">
         <f t="shared" si="21"/>
-        <v>0.98174096700202118</v>
+        <v>0.98386815948644579</v>
       </c>
       <c r="BF27" s="5">
         <v>192460</v>
@@ -5065,14 +5065,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="22"/>
-        <v>122791</v>
+        <v>123337</v>
       </c>
       <c r="BI27" s="5">
-        <v>191169</v>
+        <v>191715</v>
       </c>
       <c r="BJ27" s="4">
         <f t="shared" si="23"/>
-        <v>0.99329211264678374</v>
+        <v>0.99612906577990235</v>
       </c>
       <c r="BL27" s="9"/>
     </row>
@@ -5091,14 +5091,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>175594</v>
+        <v>175668</v>
       </c>
       <c r="F28" s="5">
-        <v>409319</v>
+        <v>409393</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.99026713955997692</v>
+        <v>0.99044616806421804</v>
       </c>
       <c r="H28" s="5">
         <v>423216</v>
@@ -5108,14 +5108,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>174167</v>
+        <v>174251</v>
       </c>
       <c r="K28" s="5">
-        <v>413736</v>
+        <v>413820</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.97760009073380971</v>
+        <v>0.97779857094249745</v>
       </c>
       <c r="M28" s="5">
         <v>688530</v>
@@ -5125,14 +5125,14 @@
       </c>
       <c r="O28" s="3">
         <f t="shared" si="4"/>
-        <v>299136</v>
+        <v>299306</v>
       </c>
       <c r="P28" s="5">
-        <v>681820</v>
+        <v>681990</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="5"/>
-        <v>0.99025460038052082</v>
+        <v>0.99050150320247488</v>
       </c>
       <c r="R28" s="5">
         <v>417505</v>
@@ -5142,14 +5142,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="6"/>
-        <v>173179</v>
+        <v>173288</v>
       </c>
       <c r="U28" s="5">
-        <v>413980</v>
+        <v>414089</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="7"/>
-        <v>0.99155698734146891</v>
+        <v>0.99181806205913703</v>
       </c>
       <c r="W28" s="5">
         <v>426115</v>
@@ -5159,14 +5159,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="8"/>
-        <v>67444</v>
+        <v>67572</v>
       </c>
       <c r="Z28" s="5">
-        <v>416109</v>
+        <v>416237</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="9"/>
-        <v>0.97651807610621544</v>
+        <v>0.97681846449902021</v>
       </c>
       <c r="AB28" s="5">
         <v>693825</v>
@@ -5176,14 +5176,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="10"/>
-        <v>331801</v>
+        <v>332041</v>
       </c>
       <c r="AE28" s="5">
-        <v>686975</v>
+        <v>687215</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="11"/>
-        <v>0.9901271934565633</v>
+        <v>0.99047310200699024</v>
       </c>
       <c r="AG28" s="5">
         <v>421441</v>
@@ -5193,14 +5193,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="12"/>
-        <v>172748</v>
+        <v>172904</v>
       </c>
       <c r="AJ28" s="5">
-        <v>416626</v>
+        <v>416782</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="13"/>
-        <v>0.98857491321442381</v>
+        <v>0.98894507178940827</v>
       </c>
       <c r="AL28" s="5">
         <v>428935</v>
@@ -5210,14 +5210,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="14"/>
-        <v>166644</v>
+        <v>166813</v>
       </c>
       <c r="AO28" s="5">
-        <v>421145</v>
+        <v>421314</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" si="15"/>
-        <v>0.9818387401354518</v>
+        <v>0.98223273922622312</v>
       </c>
       <c r="AQ28" s="5">
         <v>700018</v>
@@ -5227,14 +5227,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="16"/>
-        <v>291924</v>
+        <v>292253</v>
       </c>
       <c r="AT28" s="5">
-        <v>695910</v>
+        <v>696239</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" si="17"/>
-        <v>0.9941315794736707</v>
+        <v>0.9946015673882671</v>
       </c>
       <c r="AV28" s="5">
         <v>428584</v>
@@ -5244,14 +5244,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="18"/>
-        <v>169339</v>
+        <v>169558</v>
       </c>
       <c r="AY28" s="5">
-        <v>426063</v>
+        <v>426282</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" si="19"/>
-        <v>0.99411783921004981</v>
+        <v>0.99462882422115617</v>
       </c>
       <c r="BA28" s="5">
         <v>438333</v>
@@ -5261,14 +5261,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="20"/>
-        <v>169957</v>
+        <v>170208</v>
       </c>
       <c r="BD28" s="5">
-        <v>431297</v>
+        <v>431548</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" si="21"/>
-        <v>0.98394827676675034</v>
+        <v>0.98452090077635035</v>
       </c>
       <c r="BF28" s="5">
         <v>711748</v>
@@ -5278,14 +5278,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="22"/>
-        <v>331290</v>
+        <v>331863</v>
       </c>
       <c r="BI28" s="5">
-        <v>706608</v>
+        <v>707181</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="23"/>
-        <v>0.99277834289664324</v>
+        <v>0.99358340311458548</v>
       </c>
       <c r="BL28" s="9"/>
     </row>
@@ -5304,14 +5304,14 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>70885</v>
+        <v>70910</v>
       </c>
       <c r="F29" s="5">
-        <v>135461</v>
+        <v>135486</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>0.99025542055938121</v>
+        <v>0.99043817711303128</v>
       </c>
       <c r="H29" s="5">
         <v>138439</v>
@@ -5321,14 +5321,14 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>70875</v>
+        <v>70904</v>
       </c>
       <c r="K29" s="5">
-        <v>136659</v>
+        <v>136688</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="3"/>
-        <v>0.98714235150499496</v>
+        <v>0.98735183004789118</v>
       </c>
       <c r="M29" s="5">
         <v>184711</v>
@@ -5338,14 +5338,14 @@
       </c>
       <c r="O29" s="3">
         <f t="shared" si="4"/>
-        <v>98935</v>
+        <v>98982</v>
       </c>
       <c r="P29" s="5">
-        <v>183070</v>
+        <v>183117</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="5"/>
-        <v>0.99111585124870749</v>
+        <v>0.99137030279734284</v>
       </c>
       <c r="R29" s="5">
         <v>138323</v>
@@ -5355,14 +5355,14 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="6"/>
-        <v>72653</v>
+        <v>72690</v>
       </c>
       <c r="U29" s="5">
-        <v>136808</v>
+        <v>136845</v>
       </c>
       <c r="V29" s="4">
         <f t="shared" si="7"/>
-        <v>0.98904737462316461</v>
+        <v>0.98931486448385297</v>
       </c>
       <c r="W29" s="5">
         <v>139858</v>
@@ -5372,14 +5372,14 @@
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="8"/>
-        <v>25737</v>
+        <v>25773</v>
       </c>
       <c r="Z29" s="5">
-        <v>137289</v>
+        <v>137325</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" si="9"/>
-        <v>0.98163136895994507</v>
+        <v>0.98188877289822529</v>
       </c>
       <c r="AB29" s="5">
         <v>187429</v>
@@ -5389,14 +5389,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="10"/>
-        <v>107088</v>
+        <v>107153</v>
       </c>
       <c r="AE29" s="5">
-        <v>184428</v>
+        <v>184493</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="11"/>
-        <v>0.98398860368459529</v>
+        <v>0.98433540167209987</v>
       </c>
       <c r="AG29" s="5">
         <v>139419</v>
@@ -5406,14 +5406,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="12"/>
-        <v>74722</v>
+        <v>74771</v>
       </c>
       <c r="AJ29" s="5">
-        <v>137967</v>
+        <v>138016</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="13"/>
-        <v>0.98958535063370134</v>
+        <v>0.98993680918669624</v>
       </c>
       <c r="AL29" s="5">
         <v>141276</v>
@@ -5423,14 +5423,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="14"/>
-        <v>71058</v>
+        <v>71109</v>
       </c>
       <c r="AO29" s="5">
-        <v>139172</v>
+        <v>139223</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="15"/>
-        <v>0.98510716611455595</v>
+        <v>0.98546816161272965</v>
       </c>
       <c r="AQ29" s="5">
         <v>188424</v>
@@ -5440,14 +5440,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="16"/>
-        <v>96987</v>
+        <v>97077</v>
       </c>
       <c r="AT29" s="5">
-        <v>187094</v>
+        <v>187184</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="17"/>
-        <v>0.99294145119517685</v>
+        <v>0.99341909735490175</v>
       </c>
       <c r="AV29" s="5">
         <v>141887</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="AX29" s="3">
         <f t="shared" si="18"/>
-        <v>71600</v>
+        <v>71677</v>
       </c>
       <c r="AY29" s="5">
-        <v>140391</v>
+        <v>140468</v>
       </c>
       <c r="AZ29" s="4">
         <f t="shared" si="19"/>
-        <v>0.98945639840154487</v>
+        <v>0.989999083777936</v>
       </c>
       <c r="BA29" s="5">
         <v>143795</v>
@@ -5474,14 +5474,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="20"/>
-        <v>71360</v>
+        <v>71449</v>
       </c>
       <c r="BD29" s="5">
-        <v>141597</v>
+        <v>141686</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="21"/>
-        <v>0.98471435029034393</v>
+        <v>0.98533328697103517</v>
       </c>
       <c r="BF29" s="5">
         <v>191754</v>
@@ -5491,14 +5491,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="22"/>
-        <v>105185</v>
+        <v>105360</v>
       </c>
       <c r="BI29" s="5">
-        <v>189391</v>
+        <v>189566</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="23"/>
-        <v>0.98767691938629698</v>
+        <v>0.98858954702379087</v>
       </c>
       <c r="BL29" s="9"/>
     </row>
@@ -5517,14 +5517,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>100911</v>
+        <v>100966</v>
       </c>
       <c r="F30" s="5">
-        <v>175947</v>
+        <v>176002</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.98710209485766864</v>
+        <v>0.98741065718164789</v>
       </c>
       <c r="H30" s="5">
         <v>181910</v>
@@ -5534,14 +5534,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>100012</v>
+        <v>100069</v>
       </c>
       <c r="K30" s="5">
-        <v>178195</v>
+        <v>178252</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.97957781320433179</v>
+        <v>0.97989115496674184</v>
       </c>
       <c r="M30" s="5">
         <v>304709</v>
@@ -5551,14 +5551,14 @@
       </c>
       <c r="O30" s="3">
         <f t="shared" si="4"/>
-        <v>184930</v>
+        <v>185045</v>
       </c>
       <c r="P30" s="5">
-        <v>301397</v>
+        <v>301512</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="5"/>
-        <v>0.98913061314237516</v>
+        <v>0.98950802240826496</v>
       </c>
       <c r="R30" s="5">
         <v>179361</v>
@@ -5568,14 +5568,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="6"/>
-        <v>100430</v>
+        <v>100504</v>
       </c>
       <c r="U30" s="5">
-        <v>177736</v>
+        <v>177810</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="7"/>
-        <v>0.99094005943321006</v>
+        <v>0.99135263518825167</v>
       </c>
       <c r="W30" s="5">
         <v>184404</v>
@@ -5585,14 +5585,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="8"/>
-        <v>38428</v>
+        <v>38516</v>
       </c>
       <c r="Z30" s="5">
-        <v>178961</v>
+        <v>179049</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="9"/>
-        <v>0.97048328669660089</v>
+        <v>0.97096049977223919</v>
       </c>
       <c r="AB30" s="5">
         <v>307610</v>
@@ -5602,14 +5602,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="10"/>
-        <v>193225</v>
+        <v>193396</v>
       </c>
       <c r="AE30" s="5">
-        <v>304350</v>
+        <v>304521</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="11"/>
-        <v>0.98940216507915868</v>
+        <v>0.98995806378206175</v>
       </c>
       <c r="AG30" s="5">
         <v>180656</v>
@@ -5619,14 +5619,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="12"/>
-        <v>99449</v>
+        <v>99560</v>
       </c>
       <c r="AJ30" s="5">
-        <v>178660</v>
+        <v>178771</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="13"/>
-        <v>0.98895137720308213</v>
+        <v>0.98956580462315114</v>
       </c>
       <c r="AL30" s="5">
         <v>185185</v>
@@ -5636,14 +5636,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="14"/>
-        <v>98694</v>
+        <v>98815</v>
       </c>
       <c r="AO30" s="5">
-        <v>181538</v>
+        <v>181659</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="15"/>
-        <v>0.98030618030618033</v>
+        <v>0.98095958095958091</v>
       </c>
       <c r="AQ30" s="5">
         <v>311830</v>
@@ -5653,14 +5653,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="16"/>
-        <v>178009</v>
+        <v>178244</v>
       </c>
       <c r="AT30" s="5">
-        <v>309247</v>
+        <v>309482</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="17"/>
-        <v>0.99171664047718311</v>
+        <v>0.9924702562293557</v>
       </c>
       <c r="AV30" s="5">
         <v>184055</v>
@@ -5670,14 +5670,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="18"/>
-        <v>99988</v>
+        <v>100134</v>
       </c>
       <c r="AY30" s="5">
-        <v>182332</v>
+        <v>182478</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="19"/>
-        <v>0.99063866778951948</v>
+        <v>0.99143190894026245</v>
       </c>
       <c r="BA30" s="5">
         <v>188792</v>
@@ -5687,14 +5687,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="20"/>
-        <v>100135</v>
+        <v>100305</v>
       </c>
       <c r="BD30" s="5">
-        <v>184682</v>
+        <v>184852</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="21"/>
-        <v>0.97823000974617569</v>
+        <v>0.97913047163015376</v>
       </c>
       <c r="BF30" s="5">
         <v>315967</v>
@@ -5704,14 +5704,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="22"/>
-        <v>193128</v>
+        <v>193487</v>
       </c>
       <c r="BI30" s="5">
-        <v>313529</v>
+        <v>313888</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="23"/>
-        <v>0.99228400434222563</v>
+        <v>0.99342019894482647</v>
       </c>
       <c r="BL30" s="9"/>
     </row>
@@ -5730,14 +5730,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>35376</v>
+        <v>35395</v>
       </c>
       <c r="F31" s="5">
-        <v>78718</v>
+        <v>78737</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>1.0006737430877772</v>
+        <v>1.0009152736286786</v>
       </c>
       <c r="H31" s="5">
         <v>80911</v>
@@ -5747,14 +5747,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>33704</v>
+        <v>33725</v>
       </c>
       <c r="K31" s="5">
-        <v>80362</v>
+        <v>80383</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.99321476684258014</v>
+        <v>0.99347431128029562</v>
       </c>
       <c r="M31" s="5">
         <v>142260</v>
@@ -5764,14 +5764,14 @@
       </c>
       <c r="O31" s="3">
         <f t="shared" si="4"/>
-        <v>72118</v>
+        <v>72167</v>
       </c>
       <c r="P31" s="5">
-        <v>142708</v>
+        <v>142757</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="5"/>
-        <v>1.0031491635034444</v>
+        <v>1.0034936032616337</v>
       </c>
       <c r="R31" s="5">
         <v>79665</v>
@@ -5781,14 +5781,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="6"/>
-        <v>33816</v>
+        <v>33839</v>
       </c>
       <c r="U31" s="5">
-        <v>79752</v>
+        <v>79775</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="7"/>
-        <v>1.0010920730559216</v>
+        <v>1.0013807820247285</v>
       </c>
       <c r="W31" s="5">
         <v>81657</v>
@@ -5798,14 +5798,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="8"/>
-        <v>20645</v>
+        <v>20670</v>
       </c>
       <c r="Z31" s="5">
-        <v>80662</v>
+        <v>80687</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="9"/>
-        <v>0.98781488421078412</v>
+        <v>0.98812104289895542</v>
       </c>
       <c r="AB31" s="5">
         <v>144167</v>
@@ -5815,14 +5815,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="10"/>
-        <v>77193</v>
+        <v>77258</v>
       </c>
       <c r="AE31" s="5">
-        <v>144542</v>
+        <v>144607</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="11"/>
-        <v>1.0026011500551444</v>
+        <v>1.0030520160647027</v>
       </c>
       <c r="AG31" s="5">
         <v>80917</v>
@@ -5832,14 +5832,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="12"/>
-        <v>35613</v>
+        <v>35643</v>
       </c>
       <c r="AJ31" s="5">
-        <v>81437</v>
+        <v>81467</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="13"/>
-        <v>1.0064263380995342</v>
+        <v>1.0067970883745072</v>
       </c>
       <c r="AL31" s="5">
         <v>83546</v>
@@ -5849,14 +5849,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="14"/>
-        <v>33625</v>
+        <v>33658</v>
       </c>
       <c r="AO31" s="5">
-        <v>82683</v>
+        <v>82716</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="15"/>
-        <v>0.98967036123812036</v>
+        <v>0.99006535321858613</v>
       </c>
       <c r="AQ31" s="5">
         <v>147023</v>
@@ -5866,14 +5866,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="16"/>
-        <v>69412</v>
+        <v>69501</v>
       </c>
       <c r="AT31" s="5">
-        <v>147225</v>
+        <v>147314</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="17"/>
-        <v>1.0013739346904906</v>
+        <v>1.0019792821531326</v>
       </c>
       <c r="AV31" s="5">
         <v>81694</v>
@@ -5883,14 +5883,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="18"/>
-        <v>33762</v>
+        <v>33810</v>
       </c>
       <c r="AY31" s="5">
-        <v>82267</v>
+        <v>82315</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="19"/>
-        <v>1.0070139789947854</v>
+        <v>1.0076015374446103</v>
       </c>
       <c r="BA31" s="5">
         <v>83957</v>
@@ -5900,14 +5900,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="20"/>
-        <v>32752</v>
+        <v>32810</v>
       </c>
       <c r="BD31" s="5">
-        <v>83309</v>
+        <v>83367</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="21"/>
-        <v>0.99228176328358564</v>
+        <v>0.99297259311314123</v>
       </c>
       <c r="BF31" s="5">
         <v>148810</v>
@@ -5917,14 +5917,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="22"/>
-        <v>78600</v>
+        <v>78752</v>
       </c>
       <c r="BI31" s="5">
-        <v>149188</v>
+        <v>149340</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="23"/>
-        <v>1.002540151871514</v>
+        <v>1.0035615886029166</v>
       </c>
       <c r="BL31" s="9"/>
     </row>
@@ -5943,14 +5943,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>97833</v>
+        <v>97859</v>
       </c>
       <c r="F32" s="5">
-        <v>217231</v>
+        <v>217257</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.98924373727759995</v>
+        <v>0.98936213813737228</v>
       </c>
       <c r="H32" s="5">
         <v>225984</v>
@@ -5960,14 +5960,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>97737</v>
+        <v>97763</v>
       </c>
       <c r="K32" s="5">
-        <v>222055</v>
+        <v>222081</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.98261381336731801</v>
+        <v>0.98272886576040785</v>
       </c>
       <c r="M32" s="5">
         <v>469379</v>
@@ -5977,14 +5977,14 @@
       </c>
       <c r="O32" s="3">
         <f t="shared" si="4"/>
-        <v>251890</v>
+        <v>251962</v>
       </c>
       <c r="P32" s="5">
-        <v>466808</v>
+        <v>466880</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="5"/>
-        <v>0.99452255000756318</v>
+        <v>0.99467594417304561</v>
       </c>
       <c r="R32" s="5">
         <v>220673</v>
@@ -5994,14 +5994,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="6"/>
-        <v>98781</v>
+        <v>98811</v>
       </c>
       <c r="U32" s="5">
-        <v>219184</v>
+        <v>219214</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="7"/>
-        <v>0.9932524595215545</v>
+        <v>0.99338840728136202</v>
       </c>
       <c r="W32" s="5">
         <v>228851</v>
@@ -6011,14 +6011,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="8"/>
-        <v>47458</v>
+        <v>47495</v>
       </c>
       <c r="Z32" s="5">
-        <v>222408</v>
+        <v>222445</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="9"/>
-        <v>0.97184631048149228</v>
+        <v>0.97200798773000774</v>
       </c>
       <c r="AB32" s="5">
         <v>476427</v>
@@ -6028,14 +6028,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="10"/>
-        <v>269871</v>
+        <v>269975</v>
       </c>
       <c r="AE32" s="5">
-        <v>472573</v>
+        <v>472677</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="11"/>
-        <v>0.99191061799604141</v>
+        <v>0.99212890957061628</v>
       </c>
       <c r="AG32" s="5">
         <v>224544</v>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="12"/>
-        <v>99774</v>
+        <v>99817</v>
       </c>
       <c r="AJ32" s="5">
-        <v>222908</v>
+        <v>222951</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="13"/>
-        <v>0.99271412284452043</v>
+        <v>0.99290562206070976</v>
       </c>
       <c r="AL32" s="5">
         <v>231787</v>
@@ -6062,14 +6062,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="14"/>
-        <v>96296</v>
+        <v>96349</v>
       </c>
       <c r="AO32" s="5">
-        <v>226941</v>
+        <v>226994</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="15"/>
-        <v>0.97909287406109924</v>
+        <v>0.97932153226885033</v>
       </c>
       <c r="AQ32" s="5">
         <v>484390</v>
@@ -6079,14 +6079,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="16"/>
-        <v>236069</v>
+        <v>236237</v>
       </c>
       <c r="AT32" s="5">
-        <v>481236</v>
+        <v>481404</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="17"/>
-        <v>0.99348871776874004</v>
+        <v>0.99383554573793842</v>
       </c>
       <c r="AV32" s="5">
         <v>227629</v>
@@ -6096,14 +6096,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="18"/>
-        <v>93983</v>
+        <v>94058</v>
       </c>
       <c r="AY32" s="5">
-        <v>226610</v>
+        <v>226685</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="19"/>
-        <v>0.99552341749074147</v>
+        <v>0.99585290099240431</v>
       </c>
       <c r="BA32" s="5">
         <v>234918</v>
@@ -6113,14 +6113,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="20"/>
-        <v>94874</v>
+        <v>94969</v>
       </c>
       <c r="BD32" s="5">
-        <v>231339</v>
+        <v>231434</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="21"/>
-        <v>0.98476489668735478</v>
+        <v>0.98516929311504442</v>
       </c>
       <c r="BF32" s="5">
         <v>492680</v>
@@ -6130,14 +6130,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="22"/>
-        <v>269956</v>
+        <v>270284</v>
       </c>
       <c r="BI32" s="5">
-        <v>490308</v>
+        <v>490636</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="23"/>
-        <v>0.99518551595356008</v>
+        <v>0.99585126248274747</v>
       </c>
       <c r="BL32" s="9"/>
     </row>
@@ -6156,14 +6156,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>93931</v>
+        <v>93948</v>
       </c>
       <c r="F33" s="5">
-        <v>662141</v>
+        <v>662158</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>0.99808414680470059</v>
+        <v>0.99810977190644723</v>
       </c>
       <c r="H33" s="5">
         <v>674602</v>
@@ -6173,14 +6173,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>92418</v>
+        <v>92438</v>
       </c>
       <c r="K33" s="5">
-        <v>670076</v>
+        <v>670096</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>0.99329085890643665</v>
+        <v>0.99332050601688104</v>
       </c>
       <c r="M33" s="5">
         <v>1077651</v>
@@ -6190,14 +6190,14 @@
       </c>
       <c r="O33" s="3">
         <f t="shared" si="4"/>
-        <v>180217</v>
+        <v>180250</v>
       </c>
       <c r="P33" s="5">
-        <v>1078188</v>
+        <v>1078221</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="5"/>
-        <v>1.0004983060378545</v>
+        <v>1.0005289281966054</v>
       </c>
       <c r="R33" s="5">
         <v>670885</v>
@@ -6207,14 +6207,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="6"/>
-        <v>98721</v>
+        <v>98743</v>
       </c>
       <c r="U33" s="5">
-        <v>670976</v>
+        <v>670998</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="7"/>
-        <v>1.0001356417269727</v>
+        <v>1.0001684342323944</v>
       </c>
       <c r="W33" s="5">
         <v>679851</v>
@@ -6224,14 +6224,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="8"/>
-        <v>75073</v>
+        <v>75094</v>
       </c>
       <c r="Z33" s="5">
-        <v>677858</v>
+        <v>677879</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="9"/>
-        <v>0.99706847529826392</v>
+        <v>0.9970993644195566</v>
       </c>
       <c r="AB33" s="5">
         <v>1091619</v>
@@ -6241,14 +6241,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="10"/>
-        <v>205375</v>
+        <v>205430</v>
       </c>
       <c r="AE33" s="5">
-        <v>1092017</v>
+        <v>1092072</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="11"/>
-        <v>1.0003645960724392</v>
+        <v>1.0004149799517963</v>
       </c>
       <c r="AG33" s="5">
         <v>681949</v>
@@ -6258,14 +6258,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="12"/>
-        <v>121239</v>
+        <v>121272</v>
       </c>
       <c r="AJ33" s="5">
-        <v>682528</v>
+        <v>682561</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="13"/>
-        <v>1.000849037098082</v>
+        <v>1.0008974278135168</v>
       </c>
       <c r="AL33" s="5">
         <v>691548</v>
@@ -6275,14 +6275,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="14"/>
-        <v>90769</v>
+        <v>90808</v>
       </c>
       <c r="AO33" s="5">
-        <v>688959</v>
+        <v>688998</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="15"/>
-        <v>0.9962562251644137</v>
+        <v>0.99631262038209933</v>
       </c>
       <c r="AQ33" s="5">
         <v>1107071</v>
@@ -6292,14 +6292,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="16"/>
-        <v>167805</v>
+        <v>167879</v>
       </c>
       <c r="AT33" s="5">
-        <v>1110168</v>
+        <v>1110242</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="17"/>
-        <v>1.0027974718875303</v>
+        <v>1.0028643149355372</v>
       </c>
       <c r="AV33" s="5">
         <v>697202</v>
@@ -6309,14 +6309,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="18"/>
-        <v>89849</v>
+        <v>89906</v>
       </c>
       <c r="AY33" s="5">
-        <v>698834</v>
+        <v>698891</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="19"/>
-        <v>1.0023407850235657</v>
+        <v>1.0024225403828446</v>
       </c>
       <c r="BA33" s="5">
         <v>707985</v>
@@ -6326,14 +6326,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="20"/>
-        <v>90062</v>
+        <v>90142</v>
       </c>
       <c r="BD33" s="5">
-        <v>709159</v>
+        <v>709239</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="21"/>
-        <v>1.0016582272223282</v>
+        <v>1.0017712239666094</v>
       </c>
       <c r="BF33" s="5">
         <v>1132408</v>
@@ -6343,14 +6343,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="22"/>
-        <v>207519</v>
+        <v>207689</v>
       </c>
       <c r="BI33" s="5">
-        <v>1134749</v>
+        <v>1134919</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="23"/>
-        <v>1.0020672761054319</v>
+        <v>1.0022173986760956</v>
       </c>
       <c r="BL33" s="9"/>
     </row>
@@ -6575,14 +6575,14 @@
       </c>
       <c r="J35" s="3">
         <f t="shared" ref="J35:J47" si="26">K35-I35</f>
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="K35" s="5">
-        <v>11942</v>
+        <v>11943</v>
       </c>
       <c r="L35" s="4">
         <f t="shared" ref="L35:L48" si="27">K35/H35</f>
-        <v>0.99400699184285002</v>
+        <v>0.99409022806725489</v>
       </c>
       <c r="M35" s="5">
         <v>14733</v>
@@ -6592,14 +6592,14 @@
       </c>
       <c r="O35" s="3">
         <f t="shared" ref="O35:O47" si="28">P35-N35</f>
-        <v>2858</v>
+        <v>2862</v>
       </c>
       <c r="P35" s="5">
-        <v>14681</v>
+        <v>14685</v>
       </c>
       <c r="Q35" s="4">
         <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
-        <v>0.99647050838254259</v>
+        <v>0.99674200773773158</v>
       </c>
       <c r="R35" s="5">
         <v>12053</v>
@@ -6609,14 +6609,14 @@
       </c>
       <c r="T35" s="3">
         <f t="shared" ref="T35:T47" si="30">U35-S35</f>
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="U35" s="5">
-        <v>11970</v>
+        <v>11971</v>
       </c>
       <c r="V35" s="4">
         <f t="shared" ref="V35:V48" si="31">U35/R35</f>
-        <v>0.99311374761470173</v>
+        <v>0.99319671451091018</v>
       </c>
       <c r="W35" s="5">
         <v>12107</v>
@@ -6626,14 +6626,14 @@
       </c>
       <c r="Y35" s="3">
         <f t="shared" ref="Y35:Y47" si="32">Z35-X35</f>
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="Z35" s="5">
-        <v>11983</v>
+        <v>11984</v>
       </c>
       <c r="AA35" s="4">
         <f t="shared" ref="AA35:AA48" si="33">Z35/W35</f>
-        <v>0.9897579912447344</v>
+        <v>0.98984058808953501</v>
       </c>
       <c r="AB35" s="5">
         <v>14785</v>
@@ -6643,14 +6643,14 @@
       </c>
       <c r="AD35" s="3">
         <f t="shared" ref="AD35:AD47" si="34">AE35-AC35</f>
-        <v>3063</v>
+        <v>3066</v>
       </c>
       <c r="AE35" s="5">
-        <v>14710</v>
+        <v>14713</v>
       </c>
       <c r="AF35" s="4">
         <f t="shared" ref="AF35:AF48" si="35">AE35/AB35</f>
-        <v>0.99492729117348666</v>
+        <v>0.99513019952654713</v>
       </c>
       <c r="AG35" s="5">
         <v>12076</v>
@@ -6660,14 +6660,14 @@
       </c>
       <c r="AI35" s="3">
         <f t="shared" ref="AI35:AI47" si="36">AJ35-AH35</f>
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="AJ35" s="5">
-        <v>12031</v>
+        <v>12033</v>
       </c>
       <c r="AK35" s="4">
         <f t="shared" ref="AK35:AK48" si="37">AJ35/AG35</f>
-        <v>0.99627360052997682</v>
+        <v>0.99643921828420001</v>
       </c>
       <c r="AL35" s="5">
         <v>12179</v>
@@ -6677,14 +6677,14 @@
       </c>
       <c r="AN35" s="3">
         <f t="shared" ref="AN35:AN47" si="38">AO35-AM35</f>
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="AO35" s="5">
-        <v>12094</v>
+        <v>12096</v>
       </c>
       <c r="AP35" s="4">
         <f t="shared" ref="AP35:AP48" si="39">AO35/AL35</f>
-        <v>0.99302077346251749</v>
+        <v>0.99318499055751708</v>
       </c>
       <c r="AQ35" s="5">
         <v>14849</v>
@@ -6694,14 +6694,14 @@
       </c>
       <c r="AS35" s="3">
         <f t="shared" ref="AS35:AS47" si="40">AT35-AR35</f>
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="AT35" s="5">
-        <v>14856</v>
+        <v>14858</v>
       </c>
       <c r="AU35" s="4">
         <f t="shared" ref="AU35:AU48" si="41">AT35/AQ35</f>
-        <v>1.000471412216311</v>
+        <v>1.0006061014209711</v>
       </c>
       <c r="AV35" s="5">
         <v>12178</v>
@@ -6711,14 +6711,14 @@
       </c>
       <c r="AX35" s="3">
         <f t="shared" ref="AX35:AX47" si="42">AY35-AW35</f>
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="AY35" s="5">
-        <v>12190</v>
+        <v>12191</v>
       </c>
       <c r="AZ35" s="4">
         <f t="shared" ref="AZ35:AZ48" si="43">AY35/AV35</f>
-        <v>1.0009853834784037</v>
+        <v>1.0010674987682706</v>
       </c>
       <c r="BA35" s="5">
         <v>12308</v>
@@ -6728,14 +6728,14 @@
       </c>
       <c r="BC35" s="3">
         <f t="shared" ref="BC35:BC47" si="44">BD35-BB35</f>
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="BD35" s="5">
-        <v>12247</v>
+        <v>12248</v>
       </c>
       <c r="BE35" s="4">
         <f t="shared" ref="BE35:BE48" si="45">BD35/BA35</f>
-        <v>0.99504387390315241</v>
+        <v>0.99512512187195323</v>
       </c>
       <c r="BF35" s="5">
         <v>15013</v>
@@ -6745,14 +6745,14 @@
       </c>
       <c r="BH35" s="3">
         <f t="shared" ref="BH35:BH47" si="46">BI35-BG35</f>
-        <v>2888</v>
+        <v>2896</v>
       </c>
       <c r="BI35" s="5">
-        <v>14984</v>
+        <v>14992</v>
       </c>
       <c r="BJ35" s="4">
         <f t="shared" ref="BJ35:BJ48" si="47">BI35/BF35</f>
-        <v>0.99806834077133155</v>
+        <v>0.99860121228268839</v>
       </c>
       <c r="BL35" s="9"/>
     </row>
@@ -6771,14 +6771,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="24"/>
-        <v>250062</v>
+        <v>250151</v>
       </c>
       <c r="F36" s="5">
-        <v>887155</v>
+        <v>887244</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="25"/>
-        <v>0.99137863600299481</v>
+        <v>0.9914780917898689</v>
       </c>
       <c r="H36" s="5">
         <v>910737</v>
@@ -6788,14 +6788,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="26"/>
-        <v>242574</v>
+        <v>242670</v>
       </c>
       <c r="K36" s="5">
-        <v>898274</v>
+        <v>898370</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="27"/>
-        <v>0.98631547856296609</v>
+        <v>0.98642088769864411</v>
       </c>
       <c r="M36" s="5">
         <v>1579599</v>
@@ -6805,14 +6805,14 @@
       </c>
       <c r="O36" s="3">
         <f t="shared" si="28"/>
-        <v>489817</v>
+        <v>490029</v>
       </c>
       <c r="P36" s="5">
-        <v>1571006</v>
+        <v>1571218</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="29"/>
-        <v>0.99456001174981756</v>
+        <v>0.99469422302748989</v>
       </c>
       <c r="R36" s="5">
         <v>901122</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="30"/>
-        <v>252131</v>
+        <v>252256</v>
       </c>
       <c r="U36" s="5">
-        <v>897575</v>
+        <v>897700</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="31"/>
-        <v>0.99606379602317996</v>
+        <v>0.99620251197951004</v>
       </c>
       <c r="W36" s="5">
         <v>923866</v>
@@ -6839,14 +6839,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="32"/>
-        <v>177713</v>
+        <v>177862</v>
       </c>
       <c r="Z36" s="5">
-        <v>906942</v>
+        <v>907091</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="33"/>
-        <v>0.98168132607975611</v>
+        <v>0.98184260487992847</v>
       </c>
       <c r="AB36" s="5">
         <v>1592928</v>
@@ -6856,14 +6856,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="34"/>
-        <v>534249</v>
+        <v>534576</v>
       </c>
       <c r="AE36" s="5">
-        <v>1587875</v>
+        <v>1588202</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="35"/>
-        <v>0.99682785411518915</v>
+        <v>0.99703313646316716</v>
       </c>
       <c r="AG36" s="5">
         <v>914936</v>
@@ -6873,14 +6873,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="36"/>
-        <v>259485</v>
+        <v>259679</v>
       </c>
       <c r="AJ36" s="5">
-        <v>911831</v>
+        <v>912025</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="37"/>
-        <v>0.99660632000489646</v>
+        <v>0.99681835669380159</v>
       </c>
       <c r="AL36" s="5">
         <v>934551</v>
@@ -6890,14 +6890,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="38"/>
-        <v>238208</v>
+        <v>238432</v>
       </c>
       <c r="AO36" s="5">
-        <v>922472</v>
+        <v>922696</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="39"/>
-        <v>0.98707507669458383</v>
+        <v>0.98731476398826812</v>
       </c>
       <c r="AQ36" s="5">
         <v>1610673</v>
@@ -6907,14 +6907,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="40"/>
-        <v>454532</v>
+        <v>455052</v>
       </c>
       <c r="AT36" s="5">
-        <v>1612205</v>
+        <v>1612725</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="41"/>
-        <v>1.0009511552003416</v>
+        <v>1.0012740016129904</v>
       </c>
       <c r="AV36" s="5">
         <v>933166</v>
@@ -6924,14 +6924,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="42"/>
-        <v>233637</v>
+        <v>233944</v>
       </c>
       <c r="AY36" s="5">
-        <v>932831</v>
+        <v>933138</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="43"/>
-        <v>0.99964100706626691</v>
+        <v>0.9999699946204641</v>
       </c>
       <c r="BA36" s="5">
         <v>952259</v>
@@ -6941,14 +6941,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="44"/>
-        <v>233824</v>
+        <v>234208</v>
       </c>
       <c r="BD36" s="5">
-        <v>944822</v>
+        <v>945206</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="45"/>
-        <v>0.99219014994870092</v>
+        <v>0.99259340158507292</v>
       </c>
       <c r="BF36" s="5">
         <v>1640364</v>
@@ -6958,14 +6958,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="46"/>
-        <v>521614</v>
+        <v>522693</v>
       </c>
       <c r="BI36" s="5">
-        <v>1640650</v>
+        <v>1641729</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="47"/>
-        <v>1.0001743515463641</v>
+        <v>1.0008321323803742</v>
       </c>
       <c r="BL36" s="9"/>
     </row>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="24"/>
-        <v>284457</v>
+        <v>284536</v>
       </c>
       <c r="F37" s="5">
-        <v>700874</v>
+        <v>700953</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="25"/>
-        <v>0.9874329735106242</v>
+        <v>0.9875442734089046</v>
       </c>
       <c r="H37" s="5">
         <v>717455</v>
@@ -7001,14 +7001,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="26"/>
-        <v>273273</v>
+        <v>273365</v>
       </c>
       <c r="K37" s="5">
-        <v>706454</v>
+        <v>706546</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="27"/>
-        <v>0.98466663414430178</v>
+        <v>0.98479486518318227</v>
       </c>
       <c r="M37" s="5">
         <v>885615</v>
@@ -7018,14 +7018,14 @@
       </c>
       <c r="O37" s="3">
         <f t="shared" si="28"/>
-        <v>352144</v>
+        <v>352300</v>
       </c>
       <c r="P37" s="5">
-        <v>879158</v>
+        <v>879314</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="29"/>
-        <v>0.99270902141449724</v>
+        <v>0.99288517019246514</v>
       </c>
       <c r="R37" s="5">
         <v>713906</v>
@@ -7035,14 +7035,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="30"/>
-        <v>285366</v>
+        <v>285481</v>
       </c>
       <c r="U37" s="5">
-        <v>707604</v>
+        <v>707719</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="31"/>
-        <v>0.99117250730488327</v>
+        <v>0.99133359293800583</v>
       </c>
       <c r="W37" s="5">
         <v>721933</v>
@@ -7052,14 +7052,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="32"/>
-        <v>128888</v>
+        <v>129031</v>
       </c>
       <c r="Z37" s="5">
-        <v>709511</v>
+        <v>709654</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="33"/>
-        <v>0.982793417117655</v>
+        <v>0.98299149644080541</v>
       </c>
       <c r="AB37" s="5">
         <v>896229</v>
@@ -7069,14 +7069,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="34"/>
-        <v>387680</v>
+        <v>387906</v>
       </c>
       <c r="AE37" s="5">
-        <v>884495</v>
+        <v>884721</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="35"/>
-        <v>0.98690736407770785</v>
+        <v>0.98715953177145577</v>
       </c>
       <c r="AG37" s="5">
         <v>721282</v>
@@ -7086,14 +7086,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="36"/>
-        <v>282964</v>
+        <v>283152</v>
       </c>
       <c r="AJ37" s="5">
-        <v>711929</v>
+        <v>712117</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="37"/>
-        <v>0.98703281102259588</v>
+        <v>0.98729345803721702</v>
       </c>
       <c r="AL37" s="5">
         <v>727480</v>
@@ -7103,14 +7103,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="38"/>
-        <v>265373</v>
+        <v>265597</v>
       </c>
       <c r="AO37" s="5">
-        <v>717841</v>
+        <v>718065</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="39"/>
-        <v>0.98675015120690601</v>
+        <v>0.98705806345191616</v>
       </c>
       <c r="AQ37" s="5">
         <v>903787</v>
@@ -7120,14 +7120,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="40"/>
-        <v>338531</v>
+        <v>338885</v>
       </c>
       <c r="AT37" s="5">
-        <v>896905</v>
+        <v>897259</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="41"/>
-        <v>0.99238537398745497</v>
+        <v>0.99277705919646997</v>
       </c>
       <c r="AV37" s="5">
         <v>732294</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="42"/>
-        <v>269505</v>
+        <v>269856</v>
       </c>
       <c r="AY37" s="5">
-        <v>725877</v>
+        <v>726228</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="43"/>
-        <v>0.99123712607231518</v>
+        <v>0.99171644175699925</v>
       </c>
       <c r="BA37" s="5">
         <v>740889</v>
@@ -7154,14 +7154,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="44"/>
-        <v>266766</v>
+        <v>267212</v>
       </c>
       <c r="BD37" s="5">
-        <v>730966</v>
+        <v>731412</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="45"/>
-        <v>0.9866066306828688</v>
+        <v>0.98720861019666917</v>
       </c>
       <c r="BF37" s="5">
         <v>918028</v>
@@ -7171,14 +7171,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="46"/>
-        <v>376942</v>
+        <v>377703</v>
       </c>
       <c r="BI37" s="5">
-        <v>909317</v>
+        <v>910078</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="47"/>
-        <v>0.99051118266545246</v>
+        <v>0.99134013341640992</v>
       </c>
       <c r="BL37" s="9"/>
     </row>
@@ -7197,14 +7197,14 @@
       </c>
       <c r="E38" s="3">
         <f t="shared" si="24"/>
-        <v>9266</v>
+        <v>9274</v>
       </c>
       <c r="F38" s="5">
-        <v>24439</v>
+        <v>24447</v>
       </c>
       <c r="G38" s="4">
         <f t="shared" si="25"/>
-        <v>1.0034489837815643</v>
+        <v>1.0037774584274277</v>
       </c>
       <c r="H38" s="5">
         <v>24747</v>
@@ -7214,14 +7214,14 @@
       </c>
       <c r="J38" s="3">
         <f t="shared" si="26"/>
-        <v>8844</v>
+        <v>8853</v>
       </c>
       <c r="K38" s="5">
-        <v>24686</v>
+        <v>24695</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="27"/>
-        <v>0.99753505475411164</v>
+        <v>0.99789873520022632</v>
       </c>
       <c r="M38" s="5">
         <v>37604</v>
@@ -7231,14 +7231,14 @@
       </c>
       <c r="O38" s="3">
         <f t="shared" si="28"/>
-        <v>13777</v>
+        <v>13788</v>
       </c>
       <c r="P38" s="5">
-        <v>37819</v>
+        <v>37830</v>
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="29"/>
-        <v>1.0057174768641635</v>
+        <v>1.0060099989362834</v>
       </c>
       <c r="R38" s="5">
         <v>24596</v>
@@ -7248,14 +7248,14 @@
       </c>
       <c r="T38" s="3">
         <f t="shared" si="30"/>
-        <v>9369</v>
+        <v>9379</v>
       </c>
       <c r="U38" s="5">
-        <v>24770</v>
+        <v>24780</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" si="31"/>
-        <v>1.0070743210278095</v>
+        <v>1.0074808912018214</v>
       </c>
       <c r="W38" s="5">
         <v>25148</v>
@@ -7265,14 +7265,14 @@
       </c>
       <c r="Y38" s="3">
         <f t="shared" si="32"/>
-        <v>6007</v>
+        <v>6019</v>
       </c>
       <c r="Z38" s="5">
-        <v>24959</v>
+        <v>24971</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" si="33"/>
-        <v>0.99248449180849374</v>
+        <v>0.99296166693176391</v>
       </c>
       <c r="AB38" s="5">
         <v>38035</v>
@@ -7282,14 +7282,14 @@
       </c>
       <c r="AD38" s="3">
         <f t="shared" si="34"/>
-        <v>14746</v>
+        <v>14766</v>
       </c>
       <c r="AE38" s="5">
-        <v>38214</v>
+        <v>38234</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" si="35"/>
-        <v>1.0047061916655713</v>
+        <v>1.0052320231365848</v>
       </c>
       <c r="AG38" s="5">
         <v>24962</v>
@@ -7299,14 +7299,14 @@
       </c>
       <c r="AI38" s="3">
         <f t="shared" si="36"/>
-        <v>9200</v>
+        <v>9211</v>
       </c>
       <c r="AJ38" s="5">
-        <v>25171</v>
+        <v>25182</v>
       </c>
       <c r="AK38" s="4">
         <f t="shared" si="37"/>
-        <v>1.0083727265443474</v>
+        <v>1.008813396362471</v>
       </c>
       <c r="AL38" s="5">
         <v>25436</v>
@@ -7316,14 +7316,14 @@
       </c>
       <c r="AN38" s="3">
         <f t="shared" si="38"/>
-        <v>8593</v>
+        <v>8604</v>
       </c>
       <c r="AO38" s="5">
-        <v>25453</v>
+        <v>25464</v>
       </c>
       <c r="AP38" s="4">
         <f t="shared" si="39"/>
-        <v>1.0006683440792576</v>
+        <v>1.0011008020128951</v>
       </c>
       <c r="AQ38" s="5">
         <v>38569</v>
@@ -7333,14 +7333,14 @@
       </c>
       <c r="AS38" s="3">
         <f t="shared" si="40"/>
-        <v>13179</v>
+        <v>13202</v>
       </c>
       <c r="AT38" s="5">
-        <v>38934</v>
+        <v>38957</v>
       </c>
       <c r="AU38" s="4">
         <f t="shared" si="41"/>
-        <v>1.0094635588166663</v>
+        <v>1.0100598926599083</v>
       </c>
       <c r="AV38" s="5">
         <v>25488</v>
@@ -7350,14 +7350,14 @@
       </c>
       <c r="AX38" s="3">
         <f t="shared" si="42"/>
-        <v>8609</v>
+        <v>8632</v>
       </c>
       <c r="AY38" s="5">
-        <v>25637</v>
+        <v>25660</v>
       </c>
       <c r="AZ38" s="4">
         <f t="shared" si="43"/>
-        <v>1.0058458882611425</v>
+        <v>1.0067482736974263</v>
       </c>
       <c r="BA38" s="5">
         <v>25933</v>
@@ -7367,14 +7367,14 @@
       </c>
       <c r="BC38" s="3">
         <f t="shared" si="44"/>
-        <v>8579</v>
+        <v>8606</v>
       </c>
       <c r="BD38" s="5">
-        <v>25911</v>
+        <v>25938</v>
       </c>
       <c r="BE38" s="4">
         <f t="shared" si="45"/>
-        <v>0.99915166004704425</v>
+        <v>1.0001928045347626</v>
       </c>
       <c r="BF38" s="5">
         <v>39379</v>
@@ -7384,14 +7384,14 @@
       </c>
       <c r="BH38" s="3">
         <f t="shared" si="46"/>
-        <v>15191</v>
+        <v>15246</v>
       </c>
       <c r="BI38" s="5">
-        <v>39530</v>
+        <v>39585</v>
       </c>
       <c r="BJ38" s="4">
         <f t="shared" si="47"/>
-        <v>1.0038345310952539</v>
+        <v>1.0052312146067701</v>
       </c>
       <c r="BL38" s="9"/>
     </row>
@@ -7623,14 +7623,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="24"/>
-        <v>112532</v>
+        <v>112582</v>
       </c>
       <c r="F40" s="5">
-        <v>289262</v>
+        <v>289312</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="25"/>
-        <v>0.990799731459027</v>
+        <v>0.99097099483469664</v>
       </c>
       <c r="H40" s="5">
         <v>293812</v>
@@ -7640,14 +7640,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="26"/>
-        <v>110729</v>
+        <v>110794</v>
       </c>
       <c r="K40" s="5">
-        <v>290843</v>
+        <v>290908</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="27"/>
-        <v>0.98989489877881098</v>
+        <v>0.99011612868092524</v>
       </c>
       <c r="M40" s="5">
         <v>351809</v>
@@ -7657,14 +7657,14 @@
       </c>
       <c r="O40" s="3">
         <f t="shared" si="28"/>
-        <v>137959</v>
+        <v>138036</v>
       </c>
       <c r="P40" s="5">
-        <v>349695</v>
+        <v>349772</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="29"/>
-        <v>0.99399105764775775</v>
+        <v>0.99420992640893213</v>
       </c>
       <c r="R40" s="5">
         <v>293831</v>
@@ -7674,14 +7674,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="30"/>
-        <v>115418</v>
+        <v>115491</v>
       </c>
       <c r="U40" s="5">
-        <v>292822</v>
+        <v>292895</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="31"/>
-        <v>0.99656605327552228</v>
+        <v>0.99681449540722389</v>
       </c>
       <c r="W40" s="5">
         <v>297227</v>
@@ -7691,14 +7691,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="32"/>
-        <v>66716</v>
+        <v>66796</v>
       </c>
       <c r="Z40" s="5">
-        <v>294261</v>
+        <v>294341</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="33"/>
-        <v>0.99002109498800583</v>
+        <v>0.99029024953991396</v>
       </c>
       <c r="AB40" s="5">
         <v>355500</v>
@@ -7708,14 +7708,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="34"/>
-        <v>142852</v>
+        <v>142952</v>
       </c>
       <c r="AE40" s="5">
-        <v>353322</v>
+        <v>353422</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="35"/>
-        <v>0.99387341772151894</v>
+        <v>0.99415471167369907</v>
       </c>
       <c r="AG40" s="5">
         <v>298328</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="36"/>
-        <v>116362</v>
+        <v>116466</v>
       </c>
       <c r="AJ40" s="5">
-        <v>296003</v>
+        <v>296107</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="37"/>
-        <v>0.99220656458662948</v>
+        <v>0.99255517417071149</v>
       </c>
       <c r="AL40" s="5">
         <v>299711</v>
@@ -7742,14 +7742,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="38"/>
-        <v>111146</v>
+        <v>111262</v>
       </c>
       <c r="AO40" s="5">
-        <v>297301</v>
+        <v>297417</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="39"/>
-        <v>0.99195892042667766</v>
+        <v>0.99234595994141017</v>
       </c>
       <c r="AQ40" s="5">
         <v>357015</v>
@@ -7759,14 +7759,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="40"/>
-        <v>136451</v>
+        <v>136631</v>
       </c>
       <c r="AT40" s="5">
-        <v>355708</v>
+        <v>355888</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="41"/>
-        <v>0.99633908939400306</v>
+        <v>0.99684326989062089</v>
       </c>
       <c r="AV40" s="5">
         <v>300800</v>
@@ -7776,14 +7776,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="42"/>
-        <v>112606</v>
+        <v>112779</v>
       </c>
       <c r="AY40" s="5">
-        <v>299233</v>
+        <v>299406</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="43"/>
-        <v>0.99479055851063825</v>
+        <v>0.99536569148936171</v>
       </c>
       <c r="BA40" s="5">
         <v>303731</v>
@@ -7793,14 +7793,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="44"/>
-        <v>110609</v>
+        <v>110814</v>
       </c>
       <c r="BD40" s="5">
-        <v>300653</v>
+        <v>300858</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="45"/>
-        <v>0.98986603277242036</v>
+        <v>0.99054097211018965</v>
       </c>
       <c r="BF40" s="5">
         <v>361393</v>
@@ -7810,14 +7810,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="46"/>
-        <v>148958</v>
+        <v>149263</v>
       </c>
       <c r="BI40" s="5">
-        <v>358943</v>
+        <v>359248</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="47"/>
-        <v>0.99322067665948155</v>
+        <v>0.99406463323860728</v>
       </c>
       <c r="BL40" s="9"/>
     </row>
@@ -7836,14 +7836,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="24"/>
-        <v>362590</v>
+        <v>362749</v>
       </c>
       <c r="F41" s="5">
-        <v>944904</v>
+        <v>945063</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="25"/>
-        <v>0.9921210237629251</v>
+        <v>0.99228796902167982</v>
       </c>
       <c r="H41" s="5">
         <v>959446</v>
@@ -7853,14 +7853,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="26"/>
-        <v>364135</v>
+        <v>364300</v>
       </c>
       <c r="K41" s="5">
-        <v>948667</v>
+        <v>948832</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="27"/>
-        <v>0.9887653916947905</v>
+        <v>0.9889373659382602</v>
       </c>
       <c r="M41" s="5">
         <v>1062442</v>
@@ -7870,14 +7870,14 @@
       </c>
       <c r="O41" s="3">
         <f t="shared" si="28"/>
-        <v>401709</v>
+        <v>401898</v>
       </c>
       <c r="P41" s="5">
-        <v>1053280</v>
+        <v>1053469</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="29"/>
-        <v>0.99137647043320953</v>
+        <v>0.99155436249696449</v>
       </c>
       <c r="R41" s="5">
         <v>959218</v>
@@ -7887,14 +7887,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="30"/>
-        <v>375205</v>
+        <v>375387</v>
       </c>
       <c r="U41" s="5">
-        <v>951976</v>
+        <v>952158</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="31"/>
-        <v>0.99245009997727318</v>
+        <v>0.99263983786792986</v>
       </c>
       <c r="W41" s="5">
         <v>961845</v>
@@ -7904,14 +7904,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="32"/>
-        <v>151569</v>
+        <v>151794</v>
       </c>
       <c r="Z41" s="5">
-        <v>951176</v>
+        <v>951401</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="33"/>
-        <v>0.98890777620094716</v>
+        <v>0.98914170162552173</v>
       </c>
       <c r="AB41" s="5">
         <v>1065577</v>
@@ -7921,14 +7921,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="34"/>
-        <v>434163</v>
+        <v>434436</v>
       </c>
       <c r="AE41" s="5">
-        <v>1056553</v>
+        <v>1056826</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="35"/>
-        <v>0.99153134874345072</v>
+        <v>0.99178754796697</v>
       </c>
       <c r="AG41" s="5">
         <v>963364</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="36"/>
-        <v>374142</v>
+        <v>374407</v>
       </c>
       <c r="AJ41" s="5">
-        <v>957035</v>
+        <v>957300</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="37"/>
-        <v>0.99343031294505502</v>
+        <v>0.9937053906934451</v>
       </c>
       <c r="AL41" s="5">
         <v>968650</v>
@@ -7955,14 +7955,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="38"/>
-        <v>342036</v>
+        <v>342325</v>
       </c>
       <c r="AO41" s="5">
-        <v>959555</v>
+        <v>959844</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="39"/>
-        <v>0.99061064367934759</v>
+        <v>0.99090899705776081</v>
       </c>
       <c r="AQ41" s="5">
         <v>1071657</v>
@@ -7972,14 +7972,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="40"/>
-        <v>363388</v>
+        <v>363739</v>
       </c>
       <c r="AT41" s="5">
-        <v>1064619</v>
+        <v>1064970</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="41"/>
-        <v>0.99343260016964385</v>
+        <v>0.99376013034021149</v>
       </c>
       <c r="AV41" s="5">
         <v>970535</v>
@@ -7989,14 +7989,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="42"/>
-        <v>340295</v>
+        <v>340642</v>
       </c>
       <c r="AY41" s="5">
-        <v>964713</v>
+        <v>965060</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="43"/>
-        <v>0.99400124673504819</v>
+        <v>0.99435878149680335</v>
       </c>
       <c r="BA41" s="5">
         <v>973311</v>
@@ -8006,14 +8006,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="44"/>
-        <v>336065</v>
+        <v>336460</v>
       </c>
       <c r="BD41" s="5">
-        <v>969570</v>
+        <v>969965</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="45"/>
-        <v>0.99615641865755133</v>
+        <v>0.99656224988724051</v>
       </c>
       <c r="BF41" s="5">
         <v>1078355</v>
@@ -8023,14 +8023,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="46"/>
-        <v>403634</v>
+        <v>404242</v>
       </c>
       <c r="BI41" s="5">
-        <v>1075220</v>
+        <v>1075828</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="47"/>
-        <v>0.99709279411696516</v>
+        <v>0.99765661586397802</v>
       </c>
       <c r="BL41" s="9"/>
     </row>
@@ -8049,14 +8049,14 @@
       </c>
       <c r="E42" s="3">
         <f t="shared" si="24"/>
-        <v>8504</v>
+        <v>8507</v>
       </c>
       <c r="F42" s="5">
-        <v>18782</v>
+        <v>18785</v>
       </c>
       <c r="G42" s="4">
         <f t="shared" si="25"/>
-        <v>0.98779846428947093</v>
+        <v>0.98795624276848637</v>
       </c>
       <c r="H42" s="5">
         <v>19101</v>
@@ -8066,14 +8066,14 @@
       </c>
       <c r="J42" s="3">
         <f t="shared" si="26"/>
-        <v>8452</v>
+        <v>8456</v>
       </c>
       <c r="K42" s="5">
-        <v>18924</v>
+        <v>18928</v>
       </c>
       <c r="L42" s="4">
         <f t="shared" si="27"/>
-        <v>0.99073346945186114</v>
+        <v>0.99094288257159313</v>
       </c>
       <c r="M42" s="5">
         <v>21195</v>
@@ -8083,14 +8083,14 @@
       </c>
       <c r="O42" s="3">
         <f t="shared" si="28"/>
-        <v>9345</v>
+        <v>9350</v>
       </c>
       <c r="P42" s="5">
-        <v>21016</v>
+        <v>21021</v>
       </c>
       <c r="Q42" s="4">
         <f t="shared" si="29"/>
-        <v>0.99155461193677752</v>
+        <v>0.99179051663128093</v>
       </c>
       <c r="R42" s="5">
         <v>19210</v>
@@ -8100,14 +8100,14 @@
       </c>
       <c r="T42" s="3">
         <f t="shared" si="30"/>
-        <v>8831</v>
+        <v>8834</v>
       </c>
       <c r="U42" s="5">
-        <v>19077</v>
+        <v>19080</v>
       </c>
       <c r="V42" s="4">
         <f t="shared" si="31"/>
-        <v>0.99307652264445601</v>
+        <v>0.99323269130661118</v>
       </c>
       <c r="W42" s="5">
         <v>19384</v>
@@ -8117,14 +8117,14 @@
       </c>
       <c r="Y42" s="3">
         <f t="shared" si="32"/>
-        <v>4070</v>
+        <v>4075</v>
       </c>
       <c r="Z42" s="5">
-        <v>19095</v>
+        <v>19100</v>
       </c>
       <c r="AA42" s="4">
         <f t="shared" si="33"/>
-        <v>0.98509079653322329</v>
+        <v>0.98534874122988036</v>
       </c>
       <c r="AB42" s="5">
         <v>21463</v>
@@ -8134,14 +8134,14 @@
       </c>
       <c r="AD42" s="3">
         <f t="shared" si="34"/>
-        <v>10259</v>
+        <v>10264</v>
       </c>
       <c r="AE42" s="5">
-        <v>21184</v>
+        <v>21189</v>
       </c>
       <c r="AF42" s="4">
         <f t="shared" si="35"/>
-        <v>0.98700088524437402</v>
+        <v>0.9872338442901738</v>
       </c>
       <c r="AG42" s="5">
         <v>19423</v>
@@ -8151,14 +8151,14 @@
       </c>
       <c r="AI42" s="3">
         <f t="shared" si="36"/>
-        <v>8869</v>
+        <v>8873</v>
       </c>
       <c r="AJ42" s="5">
-        <v>19189</v>
+        <v>19193</v>
       </c>
       <c r="AK42" s="4">
         <f t="shared" si="37"/>
-        <v>0.98795242753436652</v>
+        <v>0.98815836894403541</v>
       </c>
       <c r="AL42" s="5">
         <v>19535</v>
@@ -8168,14 +8168,14 @@
       </c>
       <c r="AN42" s="3">
         <f t="shared" si="38"/>
-        <v>8598</v>
+        <v>8601</v>
       </c>
       <c r="AO42" s="5">
-        <v>19241</v>
+        <v>19244</v>
       </c>
       <c r="AP42" s="4">
         <f t="shared" si="39"/>
-        <v>0.98495008958280006</v>
+        <v>0.98510366009726136</v>
       </c>
       <c r="AQ42" s="5">
         <v>21570</v>
@@ -8185,14 +8185,14 @@
       </c>
       <c r="AS42" s="3">
         <f t="shared" si="40"/>
-        <v>9120</v>
+        <v>9123</v>
       </c>
       <c r="AT42" s="5">
-        <v>21314</v>
+        <v>21317</v>
       </c>
       <c r="AU42" s="4">
         <f t="shared" si="41"/>
-        <v>0.98813166434863231</v>
+        <v>0.98827074640704682</v>
       </c>
       <c r="AV42" s="5">
         <v>19570</v>
@@ -8202,14 +8202,14 @@
       </c>
       <c r="AX42" s="3">
         <f t="shared" si="42"/>
-        <v>8388</v>
+        <v>8393</v>
       </c>
       <c r="AY42" s="5">
-        <v>19326</v>
+        <v>19331</v>
       </c>
       <c r="AZ42" s="4">
         <f t="shared" si="43"/>
-        <v>0.98753193663771077</v>
+        <v>0.98778742973939704</v>
       </c>
       <c r="BA42" s="5">
         <v>19671</v>
@@ -8219,14 +8219,14 @@
       </c>
       <c r="BC42" s="3">
         <f t="shared" si="44"/>
-        <v>8217</v>
+        <v>8225</v>
       </c>
       <c r="BD42" s="5">
-        <v>19425</v>
+        <v>19433</v>
       </c>
       <c r="BE42" s="4">
         <f t="shared" si="45"/>
-        <v>0.98749428092115299</v>
+        <v>0.98790097097249763</v>
       </c>
       <c r="BF42" s="5">
         <v>21792</v>
@@ -8236,14 +8236,14 @@
       </c>
       <c r="BH42" s="3">
         <f t="shared" si="46"/>
-        <v>9792</v>
+        <v>9807</v>
       </c>
       <c r="BI42" s="5">
-        <v>21610</v>
+        <v>21625</v>
       </c>
       <c r="BJ42" s="4">
         <f t="shared" si="47"/>
-        <v>0.99164831130690156</v>
+        <v>0.99233663729809107</v>
       </c>
       <c r="BL42" s="9"/>
     </row>
@@ -8279,14 +8279,14 @@
       </c>
       <c r="J43" s="3">
         <f t="shared" si="26"/>
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="K43" s="5">
-        <v>3707</v>
+        <v>3709</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" si="27"/>
-        <v>0.99356740820155454</v>
+        <v>0.9941034575180917</v>
       </c>
       <c r="M43" s="5">
         <v>4602</v>
@@ -8296,14 +8296,14 @@
       </c>
       <c r="O43" s="3">
         <f t="shared" si="28"/>
-        <v>2678</v>
+        <v>2681</v>
       </c>
       <c r="P43" s="5">
-        <v>4596</v>
+        <v>4599</v>
       </c>
       <c r="Q43" s="4">
         <f t="shared" si="29"/>
-        <v>0.99869621903520212</v>
+        <v>0.999348109517601</v>
       </c>
       <c r="R43" s="5">
         <v>3744</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="T43" s="3">
         <f t="shared" si="30"/>
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="U43" s="5">
-        <v>3738</v>
+        <v>3740</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" si="31"/>
-        <v>0.9983974358974359</v>
+        <v>0.99893162393162394</v>
       </c>
       <c r="W43" s="5">
         <v>3795</v>
@@ -8330,14 +8330,14 @@
       </c>
       <c r="Y43" s="3">
         <f t="shared" si="32"/>
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="Z43" s="5">
-        <v>3763</v>
+        <v>3765</v>
       </c>
       <c r="AA43" s="4">
         <f t="shared" si="33"/>
-        <v>0.99156785243741763</v>
+        <v>0.9920948616600791</v>
       </c>
       <c r="AB43" s="5">
         <v>4656</v>
@@ -8347,14 +8347,14 @@
       </c>
       <c r="AD43" s="3">
         <f t="shared" si="34"/>
-        <v>2784</v>
+        <v>2788</v>
       </c>
       <c r="AE43" s="5">
-        <v>4637</v>
+        <v>4641</v>
       </c>
       <c r="AF43" s="4">
         <f t="shared" si="35"/>
-        <v>0.99591924398625431</v>
+        <v>0.99677835051546393</v>
       </c>
       <c r="AG43" s="5">
         <v>3765</v>
@@ -8364,14 +8364,14 @@
       </c>
       <c r="AI43" s="3">
         <f t="shared" si="36"/>
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="AJ43" s="5">
-        <v>3769</v>
+        <v>3773</v>
       </c>
       <c r="AK43" s="4">
         <f t="shared" si="37"/>
-        <v>1.0010624169986719</v>
+        <v>1.0021248339973439</v>
       </c>
       <c r="AL43" s="5">
         <v>3815</v>
@@ -8381,14 +8381,14 @@
       </c>
       <c r="AN43" s="3">
         <f t="shared" si="38"/>
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="AO43" s="5">
-        <v>3812</v>
+        <v>3817</v>
       </c>
       <c r="AP43" s="4">
         <f t="shared" si="39"/>
-        <v>0.99921363040629096</v>
+        <v>1.0005242463958059</v>
       </c>
       <c r="AQ43" s="5">
         <v>4752</v>
@@ -8398,14 +8398,14 @@
       </c>
       <c r="AS43" s="3">
         <f t="shared" si="40"/>
-        <v>2520</v>
+        <v>2527</v>
       </c>
       <c r="AT43" s="5">
-        <v>4764</v>
+        <v>4771</v>
       </c>
       <c r="AU43" s="4">
         <f t="shared" si="41"/>
-        <v>1.0025252525252526</v>
+        <v>1.0039983164983164</v>
       </c>
       <c r="AV43" s="5">
         <v>3858</v>
@@ -8415,14 +8415,14 @@
       </c>
       <c r="AX43" s="3">
         <f t="shared" si="42"/>
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="AY43" s="5">
-        <v>3831</v>
+        <v>3836</v>
       </c>
       <c r="AZ43" s="4">
         <f t="shared" si="43"/>
-        <v>0.99300155520995337</v>
+        <v>0.99429756350440646</v>
       </c>
       <c r="BA43" s="5">
         <v>3902</v>
@@ -8432,14 +8432,14 @@
       </c>
       <c r="BC43" s="3">
         <f t="shared" si="44"/>
-        <v>1988</v>
+        <v>1995</v>
       </c>
       <c r="BD43" s="5">
-        <v>3860</v>
+        <v>3867</v>
       </c>
       <c r="BE43" s="4">
         <f t="shared" si="45"/>
-        <v>0.98923628908252181</v>
+        <v>0.99103024090210146</v>
       </c>
       <c r="BF43" s="5">
         <v>4852</v>
@@ -8449,14 +8449,14 @@
       </c>
       <c r="BH43" s="3">
         <f t="shared" si="46"/>
-        <v>2824</v>
+        <v>2838</v>
       </c>
       <c r="BI43" s="5">
-        <v>4806</v>
+        <v>4820</v>
       </c>
       <c r="BJ43" s="4">
         <f t="shared" si="47"/>
-        <v>0.99051937345424568</v>
+        <v>0.99340478153338829</v>
       </c>
       <c r="BL43" s="9"/>
     </row>
@@ -8475,14 +8475,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="24"/>
-        <v>174627</v>
+        <v>174683</v>
       </c>
       <c r="F44" s="5">
-        <v>359837</v>
+        <v>359893</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="25"/>
-        <v>0.98932420543275046</v>
+        <v>0.98947817002089522</v>
       </c>
       <c r="H44" s="5">
         <v>368428</v>
@@ -8492,14 +8492,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="26"/>
-        <v>171042</v>
+        <v>171105</v>
       </c>
       <c r="K44" s="5">
-        <v>362549</v>
+        <v>362612</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="27"/>
-        <v>0.9840430151888564</v>
+        <v>0.98421401196434577</v>
       </c>
       <c r="M44" s="5">
         <v>437654</v>
@@ -8509,14 +8509,14 @@
       </c>
       <c r="O44" s="3">
         <f t="shared" si="28"/>
-        <v>205819</v>
+        <v>205907</v>
       </c>
       <c r="P44" s="5">
-        <v>431360</v>
+        <v>431448</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="29"/>
-        <v>0.98561877647639462</v>
+        <v>0.98581984855616533</v>
       </c>
       <c r="R44" s="5">
         <v>368991</v>
@@ -8526,14 +8526,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="30"/>
-        <v>177451</v>
+        <v>177536</v>
       </c>
       <c r="U44" s="5">
-        <v>364888</v>
+        <v>364973</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="31"/>
-        <v>0.98888048759996861</v>
+        <v>0.98911084552197748</v>
       </c>
       <c r="W44" s="5">
         <v>375659</v>
@@ -8543,14 +8543,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="32"/>
-        <v>79516</v>
+        <v>79615</v>
       </c>
       <c r="Z44" s="5">
-        <v>365015</v>
+        <v>365114</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="33"/>
-        <v>0.97166579264705488</v>
+        <v>0.97192932952491484</v>
       </c>
       <c r="AB44" s="5">
         <v>443838</v>
@@ -8560,14 +8560,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="34"/>
-        <v>217252</v>
+        <v>217390</v>
       </c>
       <c r="AE44" s="5">
-        <v>434414</v>
+        <v>434552</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="35"/>
-        <v>0.97876702760917267</v>
+        <v>0.97907795186532021</v>
       </c>
       <c r="AG44" s="5">
         <v>373881</v>
@@ -8577,14 +8577,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="36"/>
-        <v>173892</v>
+        <v>174016</v>
       </c>
       <c r="AJ44" s="5">
-        <v>367013</v>
+        <v>367137</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="37"/>
-        <v>0.98163051880143681</v>
+        <v>0.9819621751305897</v>
       </c>
       <c r="AL44" s="5">
         <v>377474</v>
@@ -8594,14 +8594,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="38"/>
-        <v>166782</v>
+        <v>166922</v>
       </c>
       <c r="AO44" s="5">
-        <v>370278</v>
+        <v>370418</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="39"/>
-        <v>0.98093643535713715</v>
+        <v>0.98130732182878821</v>
       </c>
       <c r="AQ44" s="5">
         <v>447335</v>
@@ -8611,14 +8611,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="40"/>
-        <v>201447</v>
+        <v>201655</v>
       </c>
       <c r="AT44" s="5">
-        <v>441084</v>
+        <v>441292</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="41"/>
-        <v>0.98602613254048976</v>
+        <v>0.98649110845339627</v>
       </c>
       <c r="AV44" s="5">
         <v>379419</v>
@@ -8628,14 +8628,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="42"/>
-        <v>166833</v>
+        <v>167029</v>
       </c>
       <c r="AY44" s="5">
-        <v>374325</v>
+        <v>374521</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="43"/>
-        <v>0.98657420951507435</v>
+        <v>0.98709078881131418</v>
       </c>
       <c r="BA44" s="5">
         <v>384239</v>
@@ -8645,14 +8645,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="44"/>
-        <v>165547</v>
+        <v>165794</v>
       </c>
       <c r="BD44" s="5">
-        <v>377207</v>
+        <v>377454</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="45"/>
-        <v>0.98169889053427684</v>
+        <v>0.98234171960680727</v>
       </c>
       <c r="BF44" s="5">
         <v>454173</v>
@@ -8662,14 +8662,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="46"/>
-        <v>218602</v>
+        <v>219017</v>
       </c>
       <c r="BI44" s="5">
-        <v>448484</v>
+        <v>448899</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="47"/>
-        <v>0.98747393614327583</v>
+        <v>0.98838768486898165</v>
       </c>
       <c r="BL44" s="9"/>
     </row>
@@ -8688,14 +8688,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="24"/>
-        <v>126068</v>
+        <v>126107</v>
       </c>
       <c r="F45" s="5">
-        <v>262577</v>
+        <v>262616</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="25"/>
-        <v>0.98482870880872542</v>
+        <v>0.98497498330970434</v>
       </c>
       <c r="H45" s="5">
         <v>269495</v>
@@ -8705,14 +8705,14 @@
       </c>
       <c r="J45" s="3">
         <f t="shared" si="26"/>
-        <v>123563</v>
+        <v>123605</v>
       </c>
       <c r="K45" s="5">
-        <v>263915</v>
+        <v>263957</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="27"/>
-        <v>0.97929460657897183</v>
+        <v>0.97945045362622685</v>
       </c>
       <c r="M45" s="5">
         <v>320759</v>
@@ -8722,14 +8722,14 @@
       </c>
       <c r="O45" s="3">
         <f t="shared" si="28"/>
-        <v>151972</v>
+        <v>152023</v>
       </c>
       <c r="P45" s="5">
-        <v>315179</v>
+        <v>315230</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="29"/>
-        <v>0.98260376170271135</v>
+        <v>0.98276275957962211</v>
       </c>
       <c r="R45" s="5">
         <v>267358</v>
@@ -8739,14 +8739,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="30"/>
-        <v>127864</v>
+        <v>127911</v>
       </c>
       <c r="U45" s="5">
-        <v>264014</v>
+        <v>264061</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="31"/>
-        <v>0.98749242588589081</v>
+        <v>0.9876682201392889</v>
       </c>
       <c r="W45" s="5">
         <v>269851</v>
@@ -8756,14 +8756,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="32"/>
-        <v>56978</v>
+        <v>57028</v>
       </c>
       <c r="Z45" s="5">
-        <v>263982</v>
+        <v>264032</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="33"/>
-        <v>0.97825096071535778</v>
+        <v>0.97843624815175778</v>
       </c>
       <c r="AB45" s="5">
         <v>321990</v>
@@ -8773,14 +8773,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="34"/>
-        <v>161695</v>
+        <v>161775</v>
       </c>
       <c r="AE45" s="5">
-        <v>316818</v>
+        <v>316898</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="35"/>
-        <v>0.98393738935991804</v>
+        <v>0.9841858442808783</v>
       </c>
       <c r="AG45" s="5">
         <v>270238</v>
@@ -8790,14 +8790,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="36"/>
-        <v>128082</v>
+        <v>128148</v>
       </c>
       <c r="AJ45" s="5">
-        <v>266673</v>
+        <v>266739</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="37"/>
-        <v>0.98680792486622904</v>
+        <v>0.98705215402719082</v>
       </c>
       <c r="AL45" s="5">
         <v>273027</v>
@@ -8807,14 +8807,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="38"/>
-        <v>124347</v>
+        <v>124420</v>
       </c>
       <c r="AO45" s="5">
-        <v>269482</v>
+        <v>269555</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="39"/>
-        <v>0.98701593615283467</v>
+        <v>0.98728330897676786</v>
       </c>
       <c r="AQ45" s="5">
         <v>326184</v>
@@ -8824,14 +8824,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="40"/>
-        <v>153472</v>
+        <v>153578</v>
       </c>
       <c r="AT45" s="5">
-        <v>323322</v>
+        <v>323428</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="41"/>
-        <v>0.99122581119858733</v>
+        <v>0.99155078115419515</v>
       </c>
       <c r="AV45" s="5">
         <v>274208</v>
@@ -8841,14 +8841,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="42"/>
-        <v>124862</v>
+        <v>124957</v>
       </c>
       <c r="AY45" s="5">
-        <v>272351</v>
+        <v>272446</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="43"/>
-        <v>0.99322776870113194</v>
+        <v>0.9935742210292916</v>
       </c>
       <c r="BA45" s="5">
         <v>277741</v>
@@ -8858,14 +8858,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="44"/>
-        <v>123775</v>
+        <v>123896</v>
       </c>
       <c r="BD45" s="5">
-        <v>274745</v>
+        <v>274866</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="45"/>
-        <v>0.98921297179746603</v>
+        <v>0.98964862947854293</v>
       </c>
       <c r="BF45" s="5">
         <v>331328</v>
@@ -8875,14 +8875,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="46"/>
-        <v>167442</v>
+        <v>167638</v>
       </c>
       <c r="BI45" s="5">
-        <v>329414</v>
+        <v>329610</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="47"/>
-        <v>0.99422324705427856</v>
+        <v>0.99481480587212667</v>
       </c>
       <c r="BL45" s="9"/>
     </row>
@@ -8935,14 +8935,14 @@
       </c>
       <c r="O46" s="3">
         <f t="shared" si="28"/>
-        <v>4819</v>
+        <v>4821</v>
       </c>
       <c r="P46" s="5">
-        <v>7685</v>
+        <v>7687</v>
       </c>
       <c r="Q46" s="4">
         <f t="shared" si="29"/>
-        <v>1.0163999470969449</v>
+        <v>1.0166644623727019</v>
       </c>
       <c r="R46" s="5">
         <v>2328</v>
@@ -8969,14 +8969,14 @@
       </c>
       <c r="Y46" s="3">
         <f t="shared" si="32"/>
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="Z46" s="5">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="AA46" s="4">
         <f t="shared" si="33"/>
-        <v>0.98091451292246523</v>
+        <v>0.98131212723658057</v>
       </c>
       <c r="AB46" s="5">
         <v>7764</v>
@@ -8986,14 +8986,14 @@
       </c>
       <c r="AD46" s="3">
         <f t="shared" si="34"/>
-        <v>5340</v>
+        <v>5345</v>
       </c>
       <c r="AE46" s="5">
-        <v>7906</v>
+        <v>7911</v>
       </c>
       <c r="AF46" s="4">
         <f t="shared" si="35"/>
-        <v>1.0182895414734672</v>
+        <v>1.0189335394126739</v>
       </c>
       <c r="AG46" s="5">
         <v>2401</v>
@@ -9003,14 +9003,14 @@
       </c>
       <c r="AI46" s="3">
         <f t="shared" si="36"/>
-        <v>1553</v>
+        <v>1556</v>
       </c>
       <c r="AJ46" s="5">
-        <v>2462</v>
+        <v>2465</v>
       </c>
       <c r="AK46" s="4">
         <f t="shared" si="37"/>
-        <v>1.0254060807996668</v>
+        <v>1.026655560183257</v>
       </c>
       <c r="AL46" s="5">
         <v>2561</v>
@@ -9020,14 +9020,14 @@
       </c>
       <c r="AN46" s="3">
         <f t="shared" si="38"/>
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="AO46" s="5">
-        <v>2559</v>
+        <v>2562</v>
       </c>
       <c r="AP46" s="4">
         <f t="shared" si="39"/>
-        <v>0.99921905505661845</v>
+        <v>1.0003904724716908</v>
       </c>
       <c r="AQ46" s="5">
         <v>7981</v>
@@ -9037,14 +9037,14 @@
       </c>
       <c r="AS46" s="3">
         <f t="shared" si="40"/>
-        <v>5053</v>
+        <v>5061</v>
       </c>
       <c r="AT46" s="5">
-        <v>8147</v>
+        <v>8155</v>
       </c>
       <c r="AU46" s="4">
         <f t="shared" si="41"/>
-        <v>1.0207993985716075</v>
+        <v>1.0218017792256608</v>
       </c>
       <c r="AV46" s="5">
         <v>2437</v>
@@ -9054,14 +9054,14 @@
       </c>
       <c r="AX46" s="3">
         <f t="shared" si="42"/>
-        <v>1506</v>
+        <v>1511</v>
       </c>
       <c r="AY46" s="5">
-        <v>2488</v>
+        <v>2493</v>
       </c>
       <c r="AZ46" s="4">
         <f t="shared" si="43"/>
-        <v>1.020927369716865</v>
+        <v>1.0229790726302832</v>
       </c>
       <c r="BA46" s="5">
         <v>2592</v>
@@ -9071,14 +9071,14 @@
       </c>
       <c r="BC46" s="3">
         <f t="shared" si="44"/>
-        <v>1541</v>
+        <v>1547</v>
       </c>
       <c r="BD46" s="5">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="BE46" s="4">
         <f t="shared" si="45"/>
-        <v>0.99112654320987659</v>
+        <v>0.99344135802469136</v>
       </c>
       <c r="BF46" s="5">
         <v>8179</v>
@@ -9088,14 +9088,14 @@
       </c>
       <c r="BH46" s="3">
         <f t="shared" si="46"/>
-        <v>5443</v>
+        <v>5462</v>
       </c>
       <c r="BI46" s="5">
-        <v>8326</v>
+        <v>8345</v>
       </c>
       <c r="BJ46" s="4">
         <f t="shared" si="47"/>
-        <v>1.0179728573175204</v>
+        <v>1.0202958796918939</v>
       </c>
       <c r="BL46" s="9"/>
     </row>
@@ -9327,15 +9327,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>3104426</v>
+        <v>3105795</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>8118697</v>
+        <v>8120066</v>
       </c>
       <c r="G48" s="6">
         <f t="shared" si="25"/>
-        <v>0.98970698021194836</v>
+        <v>0.98987386768858532</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9347,15 +9347,15 @@
       </c>
       <c r="J48" s="8">
         <f>K48-I48</f>
-        <v>3048422</v>
+        <v>3049951</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>8210408</v>
+        <v>8211937</v>
       </c>
       <c r="L48" s="6">
         <f t="shared" si="27"/>
-        <v>0.98413629550430282</v>
+        <v>0.98431956829608447</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9367,15 +9367,15 @@
       </c>
       <c r="O48" s="8">
         <f>P48-N48</f>
-        <v>5023226</v>
+        <v>5025969</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>12657461</v>
+        <v>12660204</v>
       </c>
       <c r="Q48" s="6">
         <f t="shared" si="29"/>
-        <v>0.99292286799211593</v>
+        <v>0.9931380444344452</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9387,15 +9387,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>3105779</v>
+        <v>3107630</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>8203613</v>
+        <v>8205464</v>
       </c>
       <c r="V48" s="6">
         <f t="shared" si="31"/>
-        <v>0.99277072945346267</v>
+        <v>0.99299473058811127</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9407,15 +9407,15 @@
       </c>
       <c r="Y48" s="8">
         <f>Z48-X48</f>
-        <v>1497064</v>
+        <v>1499223</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>8249691</v>
+        <v>8251850</v>
       </c>
       <c r="AA48" s="6">
         <f t="shared" si="33"/>
-        <v>0.98031734239204249</v>
+        <v>0.98057389807906459</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9427,15 +9427,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>5437855</v>
+        <v>5441885</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>12754156</v>
+        <v>12758186</v>
       </c>
       <c r="AF48" s="6">
         <f t="shared" si="35"/>
-        <v>0.99105759020075623</v>
+        <v>0.99137074005469472</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9447,15 +9447,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>3190036</v>
+        <v>3192742</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8278968</v>
+        <v>8281674</v>
       </c>
       <c r="AK48" s="6">
         <f t="shared" si="37"/>
-        <v>0.99092579446427143</v>
+        <v>0.99124968087134779</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9467,15 +9467,15 @@
       </c>
       <c r="AN48" s="8">
         <f>AO48-AM48</f>
-        <v>3007629</v>
+        <v>3010716</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>8361789</v>
+        <v>8364876</v>
       </c>
       <c r="AP48" s="6">
         <f t="shared" si="39"/>
-        <v>0.98536863874993375</v>
+        <v>0.98573241652378341</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9487,15 +9487,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>4830289</v>
+        <v>4836107</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>12930582</v>
+        <v>12936400</v>
       </c>
       <c r="AU48" s="6">
         <f t="shared" si="41"/>
-        <v>0.99494088024220984</v>
+        <v>0.99538854501408547</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9507,15 +9507,15 @@
       </c>
       <c r="AX48" s="8">
         <f>AY48-AW48</f>
-        <v>3011408</v>
+        <v>3015532</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>8432376</v>
+        <v>8436500</v>
       </c>
       <c r="AZ48" s="6">
         <f t="shared" si="43"/>
-        <v>0.99434726053153932</v>
+        <v>0.99483356333663631</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9527,15 +9527,15 @@
       </c>
       <c r="BC48" s="8">
         <f>BD48-BB48</f>
-        <v>3002190</v>
+        <v>3007169</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>8532358</v>
+        <v>8537337</v>
       </c>
       <c r="BE48" s="6">
         <f t="shared" si="45"/>
-        <v>0.98701708236018137</v>
+        <v>0.98759304952577276</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9547,15 +9547,15 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5473731</v>
+        <v>5484474</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>13143459</v>
+        <v>13154202</v>
       </c>
       <c r="BJ48" s="6">
         <f t="shared" si="47"/>
-        <v>0.99506150874916433</v>
+        <v>0.9958748369444661</v>
       </c>
       <c r="BL48" s="9"/>
     </row>

--- a/gstdatabase/GSTR-1-2024-2025.xlsx
+++ b/gstdatabase/GSTR-1-2024-2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838375B1-97AD-4471-88CE-5AA9187FD333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3880E656-6457-44DC-8F6D-F1004F1CB3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,10 +183,10 @@
     <t>FINANCIAL YEAR 2024-2025</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -359,6 +359,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -381,9 +384,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -703,13 +703,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -776,10 +776,10 @@
       <c r="BJ2" s="1"/>
     </row>
     <row r="3" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -906,11 +906,11 @@
       <c r="BJ4" s="1"/>
     </row>
     <row r="5" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -967,100 +967,100 @@
       <c r="BG6" s="1"/>
     </row>
     <row r="8" spans="1:64" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="14">
         <v>45383</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="13">
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="14">
         <v>45413</v>
       </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="13">
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="14">
         <v>45444</v>
       </c>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="13">
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="14">
         <v>45474</v>
       </c>
-      <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="13">
+      <c r="S8" s="15"/>
+      <c r="T8" s="15"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="14">
         <v>45505</v>
       </c>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="15"/>
-      <c r="AB8" s="13">
+      <c r="X8" s="15"/>
+      <c r="Y8" s="15"/>
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="14">
         <v>45536</v>
       </c>
-      <c r="AC8" s="14"/>
-      <c r="AD8" s="14"/>
-      <c r="AE8" s="14"/>
-      <c r="AF8" s="15"/>
-      <c r="AG8" s="13">
+      <c r="AC8" s="15"/>
+      <c r="AD8" s="15"/>
+      <c r="AE8" s="15"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="14">
         <v>45566</v>
       </c>
-      <c r="AH8" s="14"/>
-      <c r="AI8" s="14"/>
-      <c r="AJ8" s="14"/>
-      <c r="AK8" s="15"/>
-      <c r="AL8" s="13">
+      <c r="AH8" s="15"/>
+      <c r="AI8" s="15"/>
+      <c r="AJ8" s="15"/>
+      <c r="AK8" s="16"/>
+      <c r="AL8" s="14">
         <v>45597</v>
       </c>
-      <c r="AM8" s="14"/>
-      <c r="AN8" s="14"/>
-      <c r="AO8" s="14"/>
-      <c r="AP8" s="15"/>
-      <c r="AQ8" s="13">
+      <c r="AM8" s="15"/>
+      <c r="AN8" s="15"/>
+      <c r="AO8" s="15"/>
+      <c r="AP8" s="16"/>
+      <c r="AQ8" s="14">
         <v>45627</v>
       </c>
-      <c r="AR8" s="14"/>
-      <c r="AS8" s="14"/>
-      <c r="AT8" s="14"/>
-      <c r="AU8" s="15"/>
-      <c r="AV8" s="13">
+      <c r="AR8" s="15"/>
+      <c r="AS8" s="15"/>
+      <c r="AT8" s="15"/>
+      <c r="AU8" s="16"/>
+      <c r="AV8" s="14">
         <v>45658</v>
       </c>
-      <c r="AW8" s="14"/>
-      <c r="AX8" s="14"/>
-      <c r="AY8" s="14"/>
-      <c r="AZ8" s="15"/>
-      <c r="BA8" s="13">
+      <c r="AW8" s="15"/>
+      <c r="AX8" s="15"/>
+      <c r="AY8" s="15"/>
+      <c r="AZ8" s="16"/>
+      <c r="BA8" s="14">
         <v>45689</v>
       </c>
-      <c r="BB8" s="14"/>
-      <c r="BC8" s="14"/>
-      <c r="BD8" s="14"/>
-      <c r="BE8" s="15"/>
-      <c r="BF8" s="13">
+      <c r="BB8" s="15"/>
+      <c r="BC8" s="15"/>
+      <c r="BD8" s="15"/>
+      <c r="BE8" s="16"/>
+      <c r="BF8" s="14">
         <v>45717</v>
       </c>
-      <c r="BG8" s="14"/>
-      <c r="BH8" s="14"/>
-      <c r="BI8" s="14"/>
-      <c r="BJ8" s="15"/>
+      <c r="BG8" s="15"/>
+      <c r="BH8" s="15"/>
+      <c r="BI8" s="15"/>
+      <c r="BJ8" s="16"/>
     </row>
     <row r="9" spans="1:64" s="9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
       <c r="C9" s="12" t="s">
         <v>2</v>
       </c>
@@ -1257,14 +1257,14 @@
       </c>
       <c r="E10" s="3">
         <f>F10-D10</f>
-        <v>43279</v>
+        <v>43281</v>
       </c>
       <c r="F10" s="5">
-        <v>72948</v>
+        <v>72950</v>
       </c>
       <c r="G10" s="4">
         <f>F10/C10</f>
-        <v>1.0005211905088465</v>
+        <v>1.0005486215882595</v>
       </c>
       <c r="H10" s="5">
         <v>74548</v>
@@ -1274,14 +1274,14 @@
       </c>
       <c r="J10" s="3">
         <f>K10-I10</f>
-        <v>41338</v>
+        <v>41341</v>
       </c>
       <c r="K10" s="5">
-        <v>74009</v>
+        <v>74012</v>
       </c>
       <c r="L10" s="4">
         <f>K10/H10</f>
-        <v>0.9927697590813972</v>
+        <v>0.99281000160970112</v>
       </c>
       <c r="M10" s="5">
         <v>129395</v>
@@ -1291,14 +1291,14 @@
       </c>
       <c r="O10" s="3">
         <f>P10-N10</f>
-        <v>81216</v>
+        <v>81220</v>
       </c>
       <c r="P10" s="5">
-        <v>129306</v>
+        <v>129310</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/M10</f>
-        <v>0.9993121836237876</v>
+        <v>0.99934309671934773</v>
       </c>
       <c r="R10" s="5">
         <v>72583</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="T10" s="3">
         <f>U10-S10</f>
-        <v>42532</v>
+        <v>42535</v>
       </c>
       <c r="U10" s="5">
-        <v>72868</v>
+        <v>72871</v>
       </c>
       <c r="V10" s="4">
         <f>U10/R10</f>
-        <v>1.0039265392722814</v>
+        <v>1.0039678712646212</v>
       </c>
       <c r="W10" s="5">
         <v>74384</v>
@@ -1325,14 +1325,14 @@
       </c>
       <c r="Y10" s="3">
         <f>Z10-X10</f>
-        <v>15608</v>
+        <v>15615</v>
       </c>
       <c r="Z10" s="5">
-        <v>73565</v>
+        <v>73572</v>
       </c>
       <c r="AA10" s="4">
         <f>Z10/W10</f>
-        <v>0.98898956764895674</v>
+        <v>0.98908367390836738</v>
       </c>
       <c r="AB10" s="5">
         <v>130621</v>
@@ -1342,14 +1342,14 @@
       </c>
       <c r="AD10" s="3">
         <f>AE10-AC10</f>
-        <v>83798</v>
+        <v>83811</v>
       </c>
       <c r="AE10" s="5">
-        <v>130219</v>
+        <v>130232</v>
       </c>
       <c r="AF10" s="4">
         <f>AE10/AB10</f>
-        <v>0.99692239379579084</v>
+        <v>0.99702191837453391</v>
       </c>
       <c r="AG10" s="5">
         <v>72721</v>
@@ -1359,14 +1359,14 @@
       </c>
       <c r="AI10" s="3">
         <f>AJ10-AH10</f>
-        <v>41911</v>
+        <v>41920</v>
       </c>
       <c r="AJ10" s="5">
-        <v>72591</v>
+        <v>72600</v>
       </c>
       <c r="AK10" s="4">
         <f>AJ10/AG10</f>
-        <v>0.99821234581482654</v>
+        <v>0.99833610648918469</v>
       </c>
       <c r="AL10" s="5">
         <v>74187</v>
@@ -1376,14 +1376,14 @@
       </c>
       <c r="AN10" s="3">
         <f>AO10-AM10</f>
-        <v>41503</v>
+        <v>41513</v>
       </c>
       <c r="AO10" s="5">
-        <v>73692</v>
+        <v>73702</v>
       </c>
       <c r="AP10" s="4">
         <f>AO10/AL10</f>
-        <v>0.99332767196409077</v>
+        <v>0.99346246646986669</v>
       </c>
       <c r="AQ10" s="5">
         <v>132270</v>
@@ -1393,14 +1393,14 @@
       </c>
       <c r="AS10" s="3">
         <f>AT10-AR10</f>
-        <v>79342</v>
+        <v>79357</v>
       </c>
       <c r="AT10" s="5">
-        <v>132280</v>
+        <v>132295</v>
       </c>
       <c r="AU10" s="4">
         <f>AT10/AQ10</f>
-        <v>1.0000756029333939</v>
+        <v>1.0001890073334845</v>
       </c>
       <c r="AV10" s="5">
         <v>73561</v>
@@ -1410,14 +1410,14 @@
       </c>
       <c r="AX10" s="3">
         <f>AY10-AW10</f>
-        <v>41192</v>
+        <v>41204</v>
       </c>
       <c r="AY10" s="5">
-        <v>73439</v>
+        <v>73451</v>
       </c>
       <c r="AZ10" s="4">
         <f>AY10/AV10</f>
-        <v>0.99834151248623593</v>
+        <v>0.99850464240562253</v>
       </c>
       <c r="BA10" s="5">
         <v>75582</v>
@@ -1427,14 +1427,14 @@
       </c>
       <c r="BC10" s="3">
         <f>BD10-BB10</f>
-        <v>41427</v>
+        <v>41440</v>
       </c>
       <c r="BD10" s="5">
-        <v>74399</v>
+        <v>74412</v>
       </c>
       <c r="BE10" s="4">
         <f>BD10/BA10</f>
-        <v>0.98434812521499826</v>
+        <v>0.98452012383900933</v>
       </c>
       <c r="BF10" s="5">
         <v>134150</v>
@@ -1444,14 +1444,14 @@
       </c>
       <c r="BH10" s="3">
         <f>BI10-BG10</f>
-        <v>88230</v>
+        <v>88250</v>
       </c>
       <c r="BI10" s="5">
-        <v>133794</v>
+        <v>133814</v>
       </c>
       <c r="BJ10" s="4">
         <f>BI10/BF10</f>
-        <v>0.99734625419306744</v>
+        <v>0.99749534103615356</v>
       </c>
       <c r="BL10" s="9"/>
     </row>
@@ -1470,14 +1470,14 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>14889</v>
+        <v>14892</v>
       </c>
       <c r="F11" s="5">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99183515609892348</v>
+        <v>0.99189961539287941</v>
       </c>
       <c r="H11" s="5">
         <v>47616</v>
@@ -1487,14 +1487,14 @@
       </c>
       <c r="J11" s="3">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>15036</v>
+        <v>15039</v>
       </c>
       <c r="K11" s="5">
-        <v>46970</v>
+        <v>46973</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.98643313172043012</v>
+        <v>0.98649613575268813</v>
       </c>
       <c r="M11" s="5">
         <v>108402</v>
@@ -1504,14 +1504,14 @@
       </c>
       <c r="O11" s="3">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>45244</v>
+        <v>45252</v>
       </c>
       <c r="P11" s="5">
-        <v>108079</v>
+        <v>108087</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.99702035017804103</v>
+        <v>0.99709414955443632</v>
       </c>
       <c r="R11" s="5">
         <v>46539</v>
@@ -1521,14 +1521,14 @@
       </c>
       <c r="T11" s="3">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>15177</v>
+        <v>15179</v>
       </c>
       <c r="U11" s="5">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="V11" s="4">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99340338210962853</v>
+        <v>0.99344635681901206</v>
       </c>
       <c r="W11" s="5">
         <v>48300</v>
@@ -1538,14 +1538,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8211</v>
+        <v>8214</v>
       </c>
       <c r="Z11" s="5">
-        <v>46916</v>
+        <v>46919</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.97134575569358184</v>
+        <v>0.971407867494824</v>
       </c>
       <c r="AB11" s="5">
         <v>109219</v>
@@ -1555,14 +1555,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>47695</v>
+        <v>47707</v>
       </c>
       <c r="AE11" s="5">
-        <v>108623</v>
+        <v>108635</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.99454307400726982</v>
+        <v>0.99465294500041201</v>
       </c>
       <c r="AG11" s="5">
         <v>46763</v>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>15552</v>
+        <v>15559</v>
       </c>
       <c r="AJ11" s="5">
-        <v>46414</v>
+        <v>46421</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99253683467698817</v>
+        <v>0.99268652567200566</v>
       </c>
       <c r="AL11" s="5">
         <v>48206</v>
@@ -1589,14 +1589,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>14800</v>
+        <v>14804</v>
       </c>
       <c r="AO11" s="5">
-        <v>47144</v>
+        <v>47148</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.9779695473592499</v>
+        <v>0.9780525245820022</v>
       </c>
       <c r="AQ11" s="5">
         <v>110196</v>
@@ -1606,14 +1606,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>40385</v>
+        <v>40402</v>
       </c>
       <c r="AT11" s="5">
-        <v>109921</v>
+        <v>109938</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.99750444662238191</v>
+        <v>0.99765871719481647</v>
       </c>
       <c r="AV11" s="5">
         <v>47206</v>
@@ -1623,14 +1623,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>14187</v>
+        <v>14192</v>
       </c>
       <c r="AY11" s="5">
-        <v>46799</v>
+        <v>46804</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.99137821463373299</v>
+        <v>0.99148413337287633</v>
       </c>
       <c r="BA11" s="5">
         <v>48813</v>
@@ -1640,14 +1640,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>13906</v>
+        <v>13913</v>
       </c>
       <c r="BD11" s="5">
-        <v>47470</v>
+        <v>47477</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.97248683752279108</v>
+        <v>0.97263024194374448</v>
       </c>
       <c r="BF11" s="5">
         <v>111276</v>
@@ -1657,14 +1657,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>48177</v>
+        <v>48198</v>
       </c>
       <c r="BI11" s="5">
-        <v>110865</v>
+        <v>110886</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.996306481181926</v>
+        <v>0.99649520112153567</v>
       </c>
       <c r="BL11" s="9"/>
     </row>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>38026</v>
+        <v>38036</v>
       </c>
       <c r="F12" s="5">
-        <v>175270</v>
+        <v>175280</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>0.98971715106922431</v>
+        <v>0.98977361921272111</v>
       </c>
       <c r="H12" s="5">
         <v>181172</v>
@@ -1700,14 +1700,14 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="2"/>
-        <v>37803</v>
+        <v>37812</v>
       </c>
       <c r="K12" s="5">
-        <v>177945</v>
+        <v>177954</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="3"/>
-        <v>0.98218819685161063</v>
+        <v>0.98223787340207092</v>
       </c>
       <c r="M12" s="5">
         <v>363483</v>
@@ -1717,14 +1717,14 @@
       </c>
       <c r="O12" s="3">
         <f t="shared" si="4"/>
-        <v>99724</v>
+        <v>99737</v>
       </c>
       <c r="P12" s="5">
-        <v>361046</v>
+        <v>361059</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="5"/>
-        <v>0.99329542234437374</v>
+        <v>0.99333118742829785</v>
       </c>
       <c r="R12" s="5">
         <v>177513</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="T12" s="3">
         <f t="shared" si="6"/>
-        <v>40007</v>
+        <v>40016</v>
       </c>
       <c r="U12" s="5">
-        <v>176817</v>
+        <v>176826</v>
       </c>
       <c r="V12" s="4">
         <f t="shared" si="7"/>
-        <v>0.99607916039952005</v>
+        <v>0.99612986091159517</v>
       </c>
       <c r="W12" s="5">
         <v>182324</v>
@@ -1751,14 +1751,14 @@
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="8"/>
-        <v>28591</v>
+        <v>28599</v>
       </c>
       <c r="Z12" s="5">
-        <v>178663</v>
+        <v>178671</v>
       </c>
       <c r="AA12" s="4">
         <f t="shared" si="9"/>
-        <v>0.97992036155415629</v>
+        <v>0.97996423948575062</v>
       </c>
       <c r="AB12" s="5">
         <v>365690</v>
@@ -1768,14 +1768,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="10"/>
-        <v>109249</v>
+        <v>109271</v>
       </c>
       <c r="AE12" s="5">
-        <v>363181</v>
+        <v>363203</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="11"/>
-        <v>0.99313899751155355</v>
+        <v>0.99319915775656975</v>
       </c>
       <c r="AG12" s="5">
         <v>180670</v>
@@ -1785,14 +1785,14 @@
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="12"/>
-        <v>39865</v>
+        <v>39872</v>
       </c>
       <c r="AJ12" s="5">
-        <v>177026</v>
+        <v>177033</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="13"/>
-        <v>0.97983063043117291</v>
+        <v>0.97986937510378036</v>
       </c>
       <c r="AL12" s="5">
         <v>181581</v>
@@ -1802,14 +1802,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="14"/>
-        <v>37285</v>
+        <v>37295</v>
       </c>
       <c r="AO12" s="5">
-        <v>178301</v>
+        <v>178311</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="15"/>
-        <v>0.98193643608086745</v>
+        <v>0.98199150792208434</v>
       </c>
       <c r="AQ12" s="5">
         <v>363376</v>
@@ -1819,14 +1819,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="16"/>
-        <v>94807</v>
+        <v>94839</v>
       </c>
       <c r="AT12" s="5">
-        <v>362780</v>
+        <v>362812</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="17"/>
-        <v>0.9983598256351548</v>
+        <v>0.99844788868830081</v>
       </c>
       <c r="AV12" s="5">
         <v>179534</v>
@@ -1836,14 +1836,14 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="18"/>
-        <v>36429</v>
+        <v>36442</v>
       </c>
       <c r="AY12" s="5">
-        <v>178167</v>
+        <v>178180</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="19"/>
-        <v>0.99238584335000612</v>
+        <v>0.99245825303285173</v>
       </c>
       <c r="BA12" s="5">
         <v>184469</v>
@@ -1853,14 +1853,14 @@
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="20"/>
-        <v>37169</v>
+        <v>37185</v>
       </c>
       <c r="BD12" s="5">
-        <v>181602</v>
+        <v>181618</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="21"/>
-        <v>0.98445809322975675</v>
+        <v>0.98454482867039994</v>
       </c>
       <c r="BF12" s="5">
         <v>368393</v>
@@ -1870,14 +1870,14 @@
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="22"/>
-        <v>110945</v>
+        <v>111004</v>
       </c>
       <c r="BI12" s="5">
-        <v>367779</v>
+        <v>367838</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="23"/>
-        <v>0.99833330166425527</v>
+        <v>0.99849345671606138</v>
       </c>
       <c r="BL12" s="9"/>
     </row>
@@ -2066,14 +2066,14 @@
       </c>
       <c r="BC13" s="3">
         <f t="shared" si="20"/>
-        <v>3282</v>
+        <v>3283</v>
       </c>
       <c r="BD13" s="5">
-        <v>17920</v>
+        <v>17921</v>
       </c>
       <c r="BE13" s="4">
         <f t="shared" si="21"/>
-        <v>0.99411960501497831</v>
+        <v>0.99417508043936531</v>
       </c>
       <c r="BF13" s="5">
         <v>29023</v>
@@ -2083,14 +2083,14 @@
       </c>
       <c r="BH13" s="3">
         <f t="shared" si="22"/>
-        <v>7420</v>
+        <v>7423</v>
       </c>
       <c r="BI13" s="5">
-        <v>29131</v>
+        <v>29134</v>
       </c>
       <c r="BJ13" s="4">
         <f t="shared" si="23"/>
-        <v>1.0037211866450746</v>
+        <v>1.0038245529407712</v>
       </c>
       <c r="BL13" s="9"/>
     </row>
@@ -2109,14 +2109,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>38200</v>
+        <v>38208</v>
       </c>
       <c r="F14" s="5">
-        <v>89607</v>
+        <v>89615</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>0.99048282265552456</v>
+        <v>0.99057125171331295</v>
       </c>
       <c r="H14" s="5">
         <v>94129</v>
@@ -2126,14 +2126,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>38639</v>
+        <v>38644</v>
       </c>
       <c r="K14" s="5">
-        <v>91149</v>
+        <v>91154</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.96834131882841634</v>
+        <v>0.96839443742098608</v>
       </c>
       <c r="M14" s="5">
         <v>164995</v>
@@ -2143,14 +2143,14 @@
       </c>
       <c r="O14" s="3">
         <f t="shared" si="4"/>
-        <v>80929</v>
+        <v>80936</v>
       </c>
       <c r="P14" s="5">
-        <v>164098</v>
+        <v>164105</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="5"/>
-        <v>0.99456347162035208</v>
+        <v>0.99460589714839842</v>
       </c>
       <c r="R14" s="5">
         <v>91074</v>
@@ -2160,14 +2160,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="6"/>
-        <v>39504</v>
+        <v>39508</v>
       </c>
       <c r="U14" s="5">
-        <v>90526</v>
+        <v>90530</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="7"/>
-        <v>0.99398291499220415</v>
+        <v>0.99402683532072822</v>
       </c>
       <c r="W14" s="5">
         <v>93800</v>
@@ -2177,14 +2177,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="8"/>
-        <v>18327</v>
+        <v>18331</v>
       </c>
       <c r="Z14" s="5">
-        <v>91110</v>
+        <v>91114</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="9"/>
-        <v>0.97132196162046913</v>
+        <v>0.97136460554371007</v>
       </c>
       <c r="AB14" s="5">
         <v>166352</v>
@@ -2194,14 +2194,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="10"/>
-        <v>85322</v>
+        <v>85334</v>
       </c>
       <c r="AE14" s="5">
-        <v>164805</v>
+        <v>164817</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="11"/>
-        <v>0.99070044243531785</v>
+        <v>0.99077257862845047</v>
       </c>
       <c r="AG14" s="5">
         <v>92175</v>
@@ -2211,14 +2211,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="12"/>
-        <v>39754</v>
+        <v>39764</v>
       </c>
       <c r="AJ14" s="5">
-        <v>91260</v>
+        <v>91270</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="13"/>
-        <v>0.99007323026851102</v>
+        <v>0.99018171955519396</v>
       </c>
       <c r="AL14" s="5">
         <v>94655</v>
@@ -2228,14 +2228,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="14"/>
-        <v>38527</v>
+        <v>38537</v>
       </c>
       <c r="AO14" s="5">
-        <v>92768</v>
+        <v>92778</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="15"/>
-        <v>0.98006444456182984</v>
+        <v>0.98017009138450162</v>
       </c>
       <c r="AQ14" s="5">
         <v>168400</v>
@@ -2245,14 +2245,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="16"/>
-        <v>78377</v>
+        <v>78398</v>
       </c>
       <c r="AT14" s="5">
-        <v>167789</v>
+        <v>167810</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="17"/>
-        <v>0.99637173396674583</v>
+        <v>0.99649643705463187</v>
       </c>
       <c r="AV14" s="5">
         <v>94024</v>
@@ -2262,14 +2262,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="18"/>
-        <v>38163</v>
+        <v>38176</v>
       </c>
       <c r="AY14" s="5">
-        <v>93250</v>
+        <v>93263</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="19"/>
-        <v>0.99176805921892286</v>
+        <v>0.99190632179018123</v>
       </c>
       <c r="BA14" s="5">
         <v>96514</v>
@@ -2279,14 +2279,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="20"/>
-        <v>38264</v>
+        <v>38280</v>
       </c>
       <c r="BD14" s="5">
-        <v>94729</v>
+        <v>94745</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="21"/>
-        <v>0.98150527384628139</v>
+        <v>0.98167105290424184</v>
       </c>
       <c r="BF14" s="5">
         <v>171502</v>
@@ -2296,14 +2296,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="22"/>
-        <v>86335</v>
+        <v>86369</v>
       </c>
       <c r="BI14" s="5">
-        <v>171043</v>
+        <v>171077</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="23"/>
-        <v>0.99732364637147086</v>
+        <v>0.99752189478839892</v>
       </c>
       <c r="BL14" s="9"/>
     </row>
@@ -2322,14 +2322,14 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>75143</v>
+        <v>75145</v>
       </c>
       <c r="F15" s="5">
-        <v>301287</v>
+        <v>301289</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="1"/>
-        <v>0.98928258321266394</v>
+        <v>0.98928915025726394</v>
       </c>
       <c r="H15" s="5">
         <v>309950</v>
@@ -2339,14 +2339,14 @@
       </c>
       <c r="J15" s="3">
         <f t="shared" si="2"/>
-        <v>73613</v>
+        <v>73616</v>
       </c>
       <c r="K15" s="5">
-        <v>306242</v>
+        <v>306245</v>
       </c>
       <c r="L15" s="4">
         <f t="shared" si="3"/>
-        <v>0.98803678012582674</v>
+        <v>0.98804645910630751</v>
       </c>
       <c r="M15" s="5">
         <v>517862</v>
@@ -2356,14 +2356,14 @@
       </c>
       <c r="O15" s="3">
         <f t="shared" si="4"/>
-        <v>147232</v>
+        <v>147239</v>
       </c>
       <c r="P15" s="5">
-        <v>514073</v>
+        <v>514080</v>
       </c>
       <c r="Q15" s="4">
         <f t="shared" si="5"/>
-        <v>0.99268337896968695</v>
+        <v>0.99269689608428502</v>
       </c>
       <c r="R15" s="5">
         <v>307768</v>
@@ -2373,14 +2373,14 @@
       </c>
       <c r="T15" s="3">
         <f t="shared" si="6"/>
-        <v>77309</v>
+        <v>77313</v>
       </c>
       <c r="U15" s="5">
-        <v>305827</v>
+        <v>305831</v>
       </c>
       <c r="V15" s="4">
         <f t="shared" si="7"/>
-        <v>0.99369330144784385</v>
+        <v>0.99370629825063039</v>
       </c>
       <c r="W15" s="5">
         <v>314114</v>
@@ -2390,14 +2390,14 @@
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="8"/>
-        <v>50824</v>
+        <v>50829</v>
       </c>
       <c r="Z15" s="5">
-        <v>308385</v>
+        <v>308390</v>
       </c>
       <c r="AA15" s="4">
         <f t="shared" si="9"/>
-        <v>0.9817613987278504</v>
+        <v>0.98177731651565991</v>
       </c>
       <c r="AB15" s="5">
         <v>523203</v>
@@ -2407,14 +2407,14 @@
       </c>
       <c r="AD15" s="3">
         <f t="shared" si="10"/>
-        <v>165263</v>
+        <v>165271</v>
       </c>
       <c r="AE15" s="5">
-        <v>520353</v>
+        <v>520361</v>
       </c>
       <c r="AF15" s="4">
         <f t="shared" si="11"/>
-        <v>0.99455278352761733</v>
+        <v>0.99456807395982061</v>
       </c>
       <c r="AG15" s="5">
         <v>312916</v>
@@ -2424,14 +2424,14 @@
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="12"/>
-        <v>79995</v>
+        <v>80000</v>
       </c>
       <c r="AJ15" s="5">
-        <v>310188</v>
+        <v>310193</v>
       </c>
       <c r="AK15" s="4">
         <f t="shared" si="13"/>
-        <v>0.99128200539441891</v>
+        <v>0.99129798412353476</v>
       </c>
       <c r="AL15" s="5">
         <v>318942</v>
@@ -2441,14 +2441,14 @@
       </c>
       <c r="AN15" s="3">
         <f t="shared" si="14"/>
-        <v>75109</v>
+        <v>75116</v>
       </c>
       <c r="AO15" s="5">
-        <v>313626</v>
+        <v>313633</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="15"/>
-        <v>0.98333239272344186</v>
+        <v>0.98335434028757585</v>
       </c>
       <c r="AQ15" s="5">
         <v>530087</v>
@@ -2458,14 +2458,14 @@
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="16"/>
-        <v>137435</v>
+        <v>137448</v>
       </c>
       <c r="AT15" s="5">
-        <v>527592</v>
+        <v>527605</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="17"/>
-        <v>0.99529322545167109</v>
+        <v>0.9953177497278749</v>
       </c>
       <c r="AV15" s="5">
         <v>317508</v>
@@ -2475,14 +2475,14 @@
       </c>
       <c r="AX15" s="3">
         <f t="shared" si="18"/>
-        <v>73241</v>
+        <v>73251</v>
       </c>
       <c r="AY15" s="5">
-        <v>315838</v>
+        <v>315848</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="19"/>
-        <v>0.99474029000844078</v>
+        <v>0.99477178527785126</v>
       </c>
       <c r="BA15" s="5">
         <v>324414</v>
@@ -2492,14 +2492,14 @@
       </c>
       <c r="BC15" s="3">
         <f t="shared" si="20"/>
-        <v>73937</v>
+        <v>73952</v>
       </c>
       <c r="BD15" s="5">
-        <v>320457</v>
+        <v>320472</v>
       </c>
       <c r="BE15" s="4">
         <f t="shared" si="21"/>
-        <v>0.98780262257485807</v>
+        <v>0.98784885979026804</v>
       </c>
       <c r="BF15" s="5">
         <v>538701</v>
@@ -2509,14 +2509,14 @@
       </c>
       <c r="BH15" s="3">
         <f t="shared" si="22"/>
-        <v>165606</v>
+        <v>165642</v>
       </c>
       <c r="BI15" s="5">
-        <v>537281</v>
+        <v>537317</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="23"/>
-        <v>0.99736402939664115</v>
+        <v>0.99743085682038835</v>
       </c>
       <c r="BL15" s="9"/>
     </row>
@@ -2535,14 +2535,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>111611</v>
+        <v>111639</v>
       </c>
       <c r="F16" s="5">
-        <v>439373</v>
+        <v>439401</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.98585301495698685</v>
+        <v>0.9859158405844578</v>
       </c>
       <c r="H16" s="5">
         <v>453561</v>
@@ -2552,14 +2552,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>110092</v>
+        <v>110124</v>
       </c>
       <c r="K16" s="5">
-        <v>444321</v>
+        <v>444353</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.97962787805829865</v>
+        <v>0.97969843086155994</v>
       </c>
       <c r="M16" s="5">
         <v>776551</v>
@@ -2569,14 +2569,14 @@
       </c>
       <c r="O16" s="3">
         <f t="shared" si="4"/>
-        <v>203900</v>
+        <v>203963</v>
       </c>
       <c r="P16" s="5">
-        <v>770500</v>
+        <v>770563</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="5"/>
-        <v>0.99220785241407194</v>
+        <v>0.9922889803760474</v>
       </c>
       <c r="R16" s="5">
         <v>446959</v>
@@ -2586,14 +2586,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="6"/>
-        <v>114111</v>
+        <v>114153</v>
       </c>
       <c r="U16" s="5">
-        <v>442907</v>
+        <v>442949</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="7"/>
-        <v>0.99093429151219692</v>
+        <v>0.99102825986276144</v>
       </c>
       <c r="W16" s="5">
         <v>453618</v>
@@ -2603,14 +2603,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="8"/>
-        <v>73575</v>
+        <v>73622</v>
       </c>
       <c r="Z16" s="5">
-        <v>442922</v>
+        <v>442969</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="9"/>
-        <v>0.97642068877337318</v>
+        <v>0.97652430018209158</v>
       </c>
       <c r="AB16" s="5">
         <v>775718</v>
@@ -2620,14 +2620,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="10"/>
-        <v>220817</v>
+        <v>220911</v>
       </c>
       <c r="AE16" s="5">
-        <v>769280</v>
+        <v>769374</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="11"/>
-        <v>0.9917005922255252</v>
+        <v>0.99182177028249952</v>
       </c>
       <c r="AG16" s="5">
         <v>444751</v>
@@ -2637,14 +2637,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="12"/>
-        <v>115326</v>
+        <v>115381</v>
       </c>
       <c r="AJ16" s="5">
-        <v>438703</v>
+        <v>438758</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="13"/>
-        <v>0.98640137964838748</v>
+        <v>0.98652504435065913</v>
       </c>
       <c r="AL16" s="5">
         <v>448369</v>
@@ -2654,14 +2654,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="14"/>
-        <v>107655</v>
+        <v>107711</v>
       </c>
       <c r="AO16" s="5">
-        <v>439920</v>
+        <v>439976</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="15"/>
-        <v>0.98115614594229306</v>
+        <v>0.98128104306943609</v>
       </c>
       <c r="AQ16" s="5">
         <v>770483</v>
@@ -2671,14 +2671,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="16"/>
-        <v>182838</v>
+        <v>182956</v>
       </c>
       <c r="AT16" s="5">
-        <v>768666</v>
+        <v>768784</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="17"/>
-        <v>0.99764173901306064</v>
+        <v>0.99779488969905894</v>
       </c>
       <c r="AV16" s="5">
         <v>444563</v>
@@ -2688,14 +2688,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="18"/>
-        <v>108537</v>
+        <v>108604</v>
       </c>
       <c r="AY16" s="5">
-        <v>443234</v>
+        <v>443301</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="19"/>
-        <v>0.99701054743647133</v>
+        <v>0.99716125723463267</v>
       </c>
       <c r="BA16" s="5">
         <v>453397</v>
@@ -2705,14 +2705,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="20"/>
-        <v>105959</v>
+        <v>106035</v>
       </c>
       <c r="BD16" s="5">
-        <v>447846</v>
+        <v>447922</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="21"/>
-        <v>0.98775686649889616</v>
+        <v>0.98792449001647564</v>
       </c>
       <c r="BF16" s="5">
         <v>780218</v>
@@ -2722,14 +2722,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="22"/>
-        <v>216944</v>
+        <v>217107</v>
       </c>
       <c r="BI16" s="5">
-        <v>778762</v>
+        <v>778925</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="23"/>
-        <v>0.99813385489696471</v>
+        <v>0.99834277086660395</v>
       </c>
       <c r="BL16" s="9"/>
     </row>
@@ -2748,14 +2748,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>91921</v>
+        <v>91932</v>
       </c>
       <c r="F17" s="5">
-        <v>320867</v>
+        <v>320878</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.99043723859058852</v>
+        <v>0.99047119287577357</v>
       </c>
       <c r="H17" s="5">
         <v>333085</v>
@@ -2765,14 +2765,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>90195</v>
+        <v>90208</v>
       </c>
       <c r="K17" s="5">
-        <v>328245</v>
+        <v>328258</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.98546917453502858</v>
+        <v>0.98550820361169067</v>
       </c>
       <c r="M17" s="5">
         <v>731481</v>
@@ -2782,14 +2782,14 @@
       </c>
       <c r="O17" s="3">
         <f t="shared" si="4"/>
-        <v>270371</v>
+        <v>270422</v>
       </c>
       <c r="P17" s="5">
-        <v>728654</v>
+        <v>728705</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="5"/>
-        <v>0.99613523796243508</v>
+        <v>0.99620495952731514</v>
       </c>
       <c r="R17" s="5">
         <v>324758</v>
@@ -2799,14 +2799,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="6"/>
-        <v>95196</v>
+        <v>95215</v>
       </c>
       <c r="U17" s="5">
-        <v>323142</v>
+        <v>323161</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="7"/>
-        <v>0.99502398709192696</v>
+        <v>0.99508249219418765</v>
       </c>
       <c r="W17" s="5">
         <v>336053</v>
@@ -2816,14 +2816,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="8"/>
-        <v>55955</v>
+        <v>55978</v>
       </c>
       <c r="Z17" s="5">
-        <v>326841</v>
+        <v>326864</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="9"/>
-        <v>0.97258765730405616</v>
+        <v>0.97265609888916327</v>
       </c>
       <c r="AB17" s="5">
         <v>736224</v>
@@ -2833,14 +2833,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="10"/>
-        <v>294059</v>
+        <v>294134</v>
       </c>
       <c r="AE17" s="5">
-        <v>730505</v>
+        <v>730580</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="11"/>
-        <v>0.99223198374407784</v>
+        <v>0.99233385491372195</v>
       </c>
       <c r="AG17" s="5">
         <v>328692</v>
@@ -2850,14 +2850,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="12"/>
-        <v>97300</v>
+        <v>97327</v>
       </c>
       <c r="AJ17" s="5">
-        <v>325751</v>
+        <v>325778</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="13"/>
-        <v>0.99105241380988884</v>
+        <v>0.99113455757974034</v>
       </c>
       <c r="AL17" s="5">
         <v>339621</v>
@@ -2867,14 +2867,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="14"/>
-        <v>93148</v>
+        <v>93175</v>
       </c>
       <c r="AO17" s="5">
-        <v>332281</v>
+        <v>332308</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="15"/>
-        <v>0.97838767331819887</v>
+        <v>0.97846717370245062</v>
       </c>
       <c r="AQ17" s="5">
         <v>745574</v>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="16"/>
-        <v>255894</v>
+        <v>255988</v>
       </c>
       <c r="AT17" s="5">
-        <v>741760</v>
+        <v>741854</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="17"/>
-        <v>0.99488447826775073</v>
+        <v>0.99501055562559848</v>
       </c>
       <c r="AV17" s="5">
         <v>334329</v>
@@ -2901,14 +2901,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="18"/>
-        <v>91175</v>
+        <v>91219</v>
       </c>
       <c r="AY17" s="5">
-        <v>332109</v>
+        <v>332153</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="19"/>
-        <v>0.99335983417531837</v>
+        <v>0.99349144106553722</v>
       </c>
       <c r="BA17" s="5">
         <v>348862</v>
@@ -2918,14 +2918,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="20"/>
-        <v>92856</v>
+        <v>92899</v>
       </c>
       <c r="BD17" s="5">
-        <v>339517</v>
+        <v>339560</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="21"/>
-        <v>0.97321290366964586</v>
+        <v>0.97333616157678393</v>
       </c>
       <c r="BF17" s="5">
         <v>757181</v>
@@ -2935,14 +2935,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="22"/>
-        <v>299971</v>
+        <v>300113</v>
       </c>
       <c r="BI17" s="5">
-        <v>755448</v>
+        <v>755590</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="23"/>
-        <v>0.99771124737678307</v>
+        <v>0.99789878509893937</v>
       </c>
       <c r="BL17" s="9"/>
     </row>
@@ -2961,14 +2961,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>482364</v>
+        <v>482406</v>
       </c>
       <c r="F18" s="5">
-        <v>988378</v>
+        <v>988420</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.98991038127020625</v>
+        <v>0.98995244638700708</v>
       </c>
       <c r="H18" s="5">
         <v>1018686</v>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>481876</v>
+        <v>481918</v>
       </c>
       <c r="K18" s="5">
-        <v>1001935</v>
+        <v>1001977</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.98355626758392678</v>
+        <v>0.98359749716792022</v>
       </c>
       <c r="M18" s="5">
         <v>1536859</v>
@@ -2995,14 +2995,14 @@
       </c>
       <c r="O18" s="3">
         <f t="shared" si="4"/>
-        <v>796176</v>
+        <v>796247</v>
       </c>
       <c r="P18" s="5">
-        <v>1524771</v>
+        <v>1524842</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="5"/>
-        <v>0.99213460701339551</v>
+        <v>0.99218080513566953</v>
       </c>
       <c r="R18" s="5">
         <v>1011292</v>
@@ -3012,14 +3012,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="6"/>
-        <v>495037</v>
+        <v>495081</v>
       </c>
       <c r="U18" s="5">
-        <v>1002621</v>
+        <v>1002665</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="7"/>
-        <v>0.99142581964457344</v>
+        <v>0.99146932834433577</v>
       </c>
       <c r="W18" s="5">
         <v>1030498</v>
@@ -3029,14 +3029,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="8"/>
-        <v>182283</v>
+        <v>182339</v>
       </c>
       <c r="Z18" s="5">
-        <v>1008601</v>
+        <v>1008657</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="9"/>
-        <v>0.97875105046298005</v>
+        <v>0.97880539312060766</v>
       </c>
       <c r="AB18" s="5">
         <v>1557879</v>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="10"/>
-        <v>827825</v>
+        <v>827930</v>
       </c>
       <c r="AE18" s="5">
-        <v>1541311</v>
+        <v>1541416</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="11"/>
-        <v>0.98936502770754342</v>
+        <v>0.98943242703701639</v>
       </c>
       <c r="AG18" s="5">
         <v>1025067</v>
@@ -3063,14 +3063,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="12"/>
-        <v>507198</v>
+        <v>507267</v>
       </c>
       <c r="AJ18" s="5">
-        <v>1017722</v>
+        <v>1017791</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="13"/>
-        <v>0.9928346147129895</v>
+        <v>0.99290192738620986</v>
       </c>
       <c r="AL18" s="5">
         <v>1045736</v>
@@ -3080,14 +3080,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="14"/>
-        <v>495984</v>
+        <v>496061</v>
       </c>
       <c r="AO18" s="5">
-        <v>1031773</v>
+        <v>1031850</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="15"/>
-        <v>0.98664768163284045</v>
+        <v>0.98672131398364404</v>
       </c>
       <c r="AQ18" s="5">
         <v>1584961</v>
@@ -3097,14 +3097,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="16"/>
-        <v>771143</v>
+        <v>771281</v>
       </c>
       <c r="AT18" s="5">
-        <v>1574605</v>
+        <v>1574743</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="17"/>
-        <v>0.99346608528537927</v>
+        <v>0.99355315367381281</v>
       </c>
       <c r="AV18" s="5">
         <v>1051416</v>
@@ -3114,14 +3114,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="18"/>
-        <v>501088</v>
+        <v>501198</v>
       </c>
       <c r="AY18" s="5">
-        <v>1044616</v>
+        <v>1044726</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="19"/>
-        <v>0.99353253136722286</v>
+        <v>0.99363715218334137</v>
       </c>
       <c r="BA18" s="5">
         <v>1075670</v>
@@ -3131,14 +3131,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="20"/>
-        <v>500441</v>
+        <v>500568</v>
       </c>
       <c r="BD18" s="5">
-        <v>1060429</v>
+        <v>1060556</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="21"/>
-        <v>0.98583115639554886</v>
+        <v>0.98594922234514304</v>
       </c>
       <c r="BF18" s="5">
         <v>1620029</v>
@@ -3148,14 +3148,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="22"/>
-        <v>863230</v>
+        <v>863508</v>
       </c>
       <c r="BI18" s="5">
-        <v>1609012</v>
+        <v>1609290</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="23"/>
-        <v>0.9931995044533154</v>
+        <v>0.99337110631970171</v>
       </c>
       <c r="BL18" s="9"/>
     </row>
@@ -3174,14 +3174,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>171995</v>
+        <v>172023</v>
       </c>
       <c r="F19" s="5">
-        <v>284773</v>
+        <v>284801</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.9773754569011377</v>
+        <v>0.9774715562953683</v>
       </c>
       <c r="H19" s="5">
         <v>301141</v>
@@ -3191,14 +3191,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>156388</v>
+        <v>156417</v>
       </c>
       <c r="K19" s="5">
-        <v>288977</v>
+        <v>289006</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.95960696152300751</v>
+        <v>0.95970326192713717</v>
       </c>
       <c r="M19" s="5">
         <v>505864</v>
@@ -3208,14 +3208,14 @@
       </c>
       <c r="O19" s="3">
         <f t="shared" si="4"/>
-        <v>245227</v>
+        <v>245275</v>
       </c>
       <c r="P19" s="5">
-        <v>497938</v>
+        <v>497986</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="5"/>
-        <v>0.98433175715211996</v>
+        <v>0.98442664431546822</v>
       </c>
       <c r="R19" s="5">
         <v>293000</v>
@@ -3225,14 +3225,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="6"/>
-        <v>124399</v>
+        <v>124427</v>
       </c>
       <c r="U19" s="5">
-        <v>286409</v>
+        <v>286437</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="7"/>
-        <v>0.97750511945392493</v>
+        <v>0.97760068259385668</v>
       </c>
       <c r="W19" s="5">
         <v>302979</v>
@@ -3242,14 +3242,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="8"/>
-        <v>59446</v>
+        <v>59481</v>
       </c>
       <c r="Z19" s="5">
-        <v>287506</v>
+        <v>287541</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="9"/>
-        <v>0.94893045392584963</v>
+        <v>0.94904597348331077</v>
       </c>
       <c r="AB19" s="5">
         <v>514622</v>
@@ -3259,14 +3259,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="10"/>
-        <v>298644</v>
+        <v>298724</v>
       </c>
       <c r="AE19" s="5">
-        <v>498729</v>
+        <v>498809</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="11"/>
-        <v>0.96911713840449887</v>
+        <v>0.96927259231047258</v>
       </c>
       <c r="AG19" s="5">
         <v>295766</v>
@@ -3276,14 +3276,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="12"/>
-        <v>161676</v>
+        <v>161720</v>
       </c>
       <c r="AJ19" s="5">
-        <v>287181</v>
+        <v>287225</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="13"/>
-        <v>0.97097367513507304</v>
+        <v>0.97112244138947679</v>
       </c>
       <c r="AL19" s="5">
         <v>302797</v>
@@ -3293,14 +3293,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="14"/>
-        <v>149744</v>
+        <v>149798</v>
       </c>
       <c r="AO19" s="5">
-        <v>291213</v>
+        <v>291267</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="15"/>
-        <v>0.96174334620224111</v>
+        <v>0.96192168350412988</v>
       </c>
       <c r="AQ19" s="5">
         <v>519490</v>
@@ -3310,14 +3310,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="16"/>
-        <v>278960</v>
+        <v>279089</v>
       </c>
       <c r="AT19" s="5">
-        <v>507750</v>
+        <v>507879</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="17"/>
-        <v>0.97740091243334815</v>
+        <v>0.97764923290149952</v>
       </c>
       <c r="AV19" s="5">
         <v>299668</v>
@@ -3327,14 +3327,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="18"/>
-        <v>153187</v>
+        <v>153264</v>
       </c>
       <c r="AY19" s="5">
-        <v>294475</v>
+        <v>294552</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="19"/>
-        <v>0.98267082237676362</v>
+        <v>0.98292777340256554</v>
       </c>
       <c r="BA19" s="5">
         <v>313772</v>
@@ -3344,14 +3344,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="20"/>
-        <v>154916</v>
+        <v>155010</v>
       </c>
       <c r="BD19" s="5">
-        <v>299489</v>
+        <v>299583</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="21"/>
-        <v>0.95447968588656729</v>
+        <v>0.95477926647374523</v>
       </c>
       <c r="BF19" s="5">
         <v>528004</v>
@@ -3361,14 +3361,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="22"/>
-        <v>333321</v>
+        <v>333517</v>
       </c>
       <c r="BI19" s="5">
-        <v>518076</v>
+        <v>518272</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="23"/>
-        <v>0.9811971121430898</v>
+        <v>0.98156832145211026</v>
       </c>
       <c r="BL19" s="9"/>
     </row>
@@ -3387,14 +3387,14 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>3805</v>
+        <v>3807</v>
       </c>
       <c r="F20" s="5">
-        <v>6403</v>
+        <v>6405</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>0.99086969978334882</v>
+        <v>0.99117920148560812</v>
       </c>
       <c r="H20" s="5">
         <v>6957</v>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="2"/>
-        <v>3743</v>
+        <v>3745</v>
       </c>
       <c r="K20" s="5">
-        <v>6439</v>
+        <v>6441</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="3"/>
-        <v>0.92554261894494749</v>
+        <v>0.92583009918068138</v>
       </c>
       <c r="M20" s="5">
         <v>9947</v>
@@ -3421,14 +3421,14 @@
       </c>
       <c r="O20" s="3">
         <f t="shared" si="4"/>
-        <v>5538</v>
+        <v>5541</v>
       </c>
       <c r="P20" s="5">
-        <v>9846</v>
+        <v>9849</v>
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="5"/>
-        <v>0.98984618477933051</v>
+        <v>0.99014778325123154</v>
       </c>
       <c r="R20" s="5">
         <v>6587</v>
@@ -3438,14 +3438,14 @@
       </c>
       <c r="T20" s="3">
         <f t="shared" si="6"/>
-        <v>3680</v>
+        <v>3684</v>
       </c>
       <c r="U20" s="5">
-        <v>6491</v>
+        <v>6495</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" si="7"/>
-        <v>0.98542583877334144</v>
+        <v>0.98603309549111884</v>
       </c>
       <c r="W20" s="5">
         <v>6643</v>
@@ -3455,14 +3455,14 @@
       </c>
       <c r="Y20" s="3">
         <f t="shared" si="8"/>
-        <v>1719</v>
+        <v>1724</v>
       </c>
       <c r="Z20" s="5">
-        <v>6512</v>
+        <v>6517</v>
       </c>
       <c r="AA20" s="4">
         <f t="shared" si="9"/>
-        <v>0.98027999397862409</v>
+        <v>0.98103266596417282</v>
       </c>
       <c r="AB20" s="5">
         <v>9927</v>
@@ -3472,14 +3472,14 @@
       </c>
       <c r="AD20" s="3">
         <f t="shared" si="10"/>
-        <v>5991</v>
+        <v>5995</v>
       </c>
       <c r="AE20" s="5">
-        <v>9891</v>
+        <v>9895</v>
       </c>
       <c r="AF20" s="4">
         <f t="shared" si="11"/>
-        <v>0.99637352674524027</v>
+        <v>0.99677646821799137</v>
       </c>
       <c r="AG20" s="5">
         <v>6546</v>
@@ -3489,14 +3489,14 @@
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="12"/>
-        <v>3883</v>
+        <v>3886</v>
       </c>
       <c r="AJ20" s="5">
-        <v>6490</v>
+        <v>6493</v>
       </c>
       <c r="AK20" s="4">
         <f t="shared" si="13"/>
-        <v>0.99144515734799876</v>
+        <v>0.99190345249007028</v>
       </c>
       <c r="AL20" s="5">
         <v>6627</v>
@@ -3506,14 +3506,14 @@
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="14"/>
-        <v>3752</v>
+        <v>3758</v>
       </c>
       <c r="AO20" s="5">
-        <v>6546</v>
+        <v>6552</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" si="15"/>
-        <v>0.98777727478497057</v>
+        <v>0.98868266183793574</v>
       </c>
       <c r="AQ20" s="5">
         <v>9949</v>
@@ -3523,14 +3523,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="16"/>
-        <v>5471</v>
+        <v>5477</v>
       </c>
       <c r="AT20" s="5">
-        <v>9982</v>
+        <v>9988</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="17"/>
-        <v>1.0033169162729922</v>
+        <v>1.003919991958991</v>
       </c>
       <c r="AV20" s="5">
         <v>6437</v>
@@ -3540,14 +3540,14 @@
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="18"/>
-        <v>3624</v>
+        <v>3628</v>
       </c>
       <c r="AY20" s="5">
-        <v>6425</v>
+        <v>6429</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" si="19"/>
-        <v>0.99813577753611926</v>
+        <v>0.99875718502407951</v>
       </c>
       <c r="BA20" s="5">
         <v>6564</v>
@@ -3557,14 +3557,14 @@
       </c>
       <c r="BC20" s="3">
         <f t="shared" si="20"/>
-        <v>3492</v>
+        <v>3496</v>
       </c>
       <c r="BD20" s="5">
-        <v>6501</v>
+        <v>6505</v>
       </c>
       <c r="BE20" s="4">
         <f t="shared" si="21"/>
-        <v>0.99040219378427785</v>
+        <v>0.99101157830591102</v>
       </c>
       <c r="BF20" s="5">
         <v>10109</v>
@@ -3574,14 +3574,14 @@
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="22"/>
-        <v>6023</v>
+        <v>6030</v>
       </c>
       <c r="BI20" s="5">
-        <v>10079</v>
+        <v>10086</v>
       </c>
       <c r="BJ20" s="4">
         <f t="shared" si="23"/>
-        <v>0.99703234741319613</v>
+        <v>0.9977247996834504</v>
       </c>
       <c r="BL20" s="9"/>
     </row>
@@ -3600,14 +3600,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>8233</v>
+        <v>8239</v>
       </c>
       <c r="F21" s="5">
-        <v>10892</v>
+        <v>10898</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>0.99135341767543461</v>
+        <v>0.9918995176117229</v>
       </c>
       <c r="H21" s="5">
         <v>10970</v>
@@ -3617,14 +3617,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>7951</v>
+        <v>7957</v>
       </c>
       <c r="K21" s="5">
-        <v>10951</v>
+        <v>10957</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>0.99826800364630808</v>
+        <v>0.99881494986326347</v>
       </c>
       <c r="M21" s="5">
         <v>14288</v>
@@ -3634,14 +3634,14 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="4"/>
-        <v>10722</v>
+        <v>10734</v>
       </c>
       <c r="P21" s="5">
-        <v>14551</v>
+        <v>14563</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="5"/>
-        <v>1.0184070548712205</v>
+        <v>1.0192469204927213</v>
       </c>
       <c r="R21" s="5">
         <v>10910</v>
@@ -3651,14 +3651,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="6"/>
-        <v>8276</v>
+        <v>8286</v>
       </c>
       <c r="U21" s="5">
-        <v>11179</v>
+        <v>11189</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="7"/>
-        <v>1.0246562786434463</v>
+        <v>1.0255728689275894</v>
       </c>
       <c r="W21" s="5">
         <v>11256</v>
@@ -3668,14 +3668,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="8"/>
-        <v>3674</v>
+        <v>3686</v>
       </c>
       <c r="Z21" s="5">
-        <v>11313</v>
+        <v>11325</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="9"/>
-        <v>1.0050639658848615</v>
+        <v>1.0061300639658848</v>
       </c>
       <c r="AB21" s="5">
         <v>14831</v>
@@ -3685,14 +3685,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="10"/>
-        <v>11295</v>
+        <v>11310</v>
       </c>
       <c r="AE21" s="5">
-        <v>14998</v>
+        <v>15013</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="11"/>
-        <v>1.0112601982334299</v>
+        <v>1.0122715932843369</v>
       </c>
       <c r="AG21" s="5">
         <v>11222</v>
@@ -3702,14 +3702,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="12"/>
-        <v>8189</v>
+        <v>8200</v>
       </c>
       <c r="AJ21" s="5">
-        <v>11349</v>
+        <v>11360</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="13"/>
-        <v>1.0113170557832829</v>
+        <v>1.0122972732133309</v>
       </c>
       <c r="AL21" s="5">
         <v>11337</v>
@@ -3719,14 +3719,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="14"/>
-        <v>8325</v>
+        <v>8336</v>
       </c>
       <c r="AO21" s="5">
-        <v>11527</v>
+        <v>11538</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="15"/>
-        <v>1.0167592837611361</v>
+        <v>1.0177295580841492</v>
       </c>
       <c r="AQ21" s="5">
         <v>15149</v>
@@ -3736,14 +3736,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="16"/>
-        <v>10982</v>
+        <v>10995</v>
       </c>
       <c r="AT21" s="5">
-        <v>15398</v>
+        <v>15411</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="17"/>
-        <v>1.0164367284969305</v>
+        <v>1.0172948709485774</v>
       </c>
       <c r="AV21" s="5">
         <v>11422</v>
@@ -3753,14 +3753,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="18"/>
-        <v>8410</v>
+        <v>8422</v>
       </c>
       <c r="AY21" s="5">
-        <v>11692</v>
+        <v>11704</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="19"/>
-        <v>1.0236385921905096</v>
+        <v>1.0246891962878655</v>
       </c>
       <c r="BA21" s="5">
         <v>11689</v>
@@ -3770,14 +3770,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="20"/>
-        <v>8370</v>
+        <v>8383</v>
       </c>
       <c r="BD21" s="5">
-        <v>11847</v>
+        <v>11860</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="21"/>
-        <v>1.0135169817777399</v>
+        <v>1.014629138506288</v>
       </c>
       <c r="BF21" s="5">
         <v>15725</v>
@@ -3787,14 +3787,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="22"/>
-        <v>11877</v>
+        <v>11899</v>
       </c>
       <c r="BI21" s="5">
-        <v>15815</v>
+        <v>15837</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="23"/>
-        <v>1.0057233704292527</v>
+        <v>1.0071224165341812</v>
       </c>
       <c r="BL21" s="9"/>
     </row>
@@ -3813,14 +3813,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>4618</v>
+        <v>4620</v>
       </c>
       <c r="F22" s="5">
-        <v>6690</v>
+        <v>6692</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>0.99023090586145646</v>
+        <v>0.99052693901716993</v>
       </c>
       <c r="H22" s="5">
         <v>6770</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>4634</v>
+        <v>4636</v>
       </c>
       <c r="K22" s="5">
-        <v>6771</v>
+        <v>6773</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>1.0001477104874446</v>
+        <v>1.0004431314623339</v>
       </c>
       <c r="M22" s="5">
         <v>8074</v>
@@ -3847,14 +3847,14 @@
       </c>
       <c r="O22" s="3">
         <f t="shared" si="4"/>
-        <v>5524</v>
+        <v>5526</v>
       </c>
       <c r="P22" s="5">
-        <v>8091</v>
+        <v>8093</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="5"/>
-        <v>1.002105523903889</v>
+        <v>1.0023532325984643</v>
       </c>
       <c r="R22" s="5">
         <v>6748</v>
@@ -3864,14 +3864,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="6"/>
-        <v>4623</v>
+        <v>4626</v>
       </c>
       <c r="U22" s="5">
-        <v>6790</v>
+        <v>6793</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="7"/>
-        <v>1.0062240663900415</v>
+        <v>1.0066686425607587</v>
       </c>
       <c r="W22" s="5">
         <v>6876</v>
@@ -3881,14 +3881,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="8"/>
-        <v>1681</v>
+        <v>1684</v>
       </c>
       <c r="Z22" s="5">
-        <v>6847</v>
+        <v>6850</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="9"/>
-        <v>0.99578243164630598</v>
+        <v>0.9962187318208261</v>
       </c>
       <c r="AB22" s="5">
         <v>8219</v>
@@ -3898,14 +3898,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="10"/>
-        <v>5738</v>
+        <v>5742</v>
       </c>
       <c r="AE22" s="5">
-        <v>8242</v>
+        <v>8246</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="11"/>
-        <v>1.0027983939652025</v>
+        <v>1.0032850711765422</v>
       </c>
       <c r="AG22" s="5">
         <v>6901</v>
@@ -3915,14 +3915,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="12"/>
-        <v>4675</v>
+        <v>4679</v>
       </c>
       <c r="AJ22" s="5">
-        <v>6911</v>
+        <v>6915</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="13"/>
-        <v>1.0014490653528474</v>
+        <v>1.0020286914939864</v>
       </c>
       <c r="AL22" s="5">
         <v>6948</v>
@@ -3932,14 +3932,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="14"/>
-        <v>4645</v>
+        <v>4651</v>
       </c>
       <c r="AO22" s="5">
-        <v>6951</v>
+        <v>6957</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="15"/>
-        <v>1.0004317789291883</v>
+        <v>1.0012953367875648</v>
       </c>
       <c r="AQ22" s="5">
         <v>8297</v>
@@ -3949,14 +3949,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="16"/>
-        <v>5574</v>
+        <v>5579</v>
       </c>
       <c r="AT22" s="5">
-        <v>8312</v>
+        <v>8317</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="17"/>
-        <v>1.0018078823671206</v>
+        <v>1.0024105098228275</v>
       </c>
       <c r="AV22" s="5">
         <v>6958</v>
@@ -3966,14 +3966,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="18"/>
-        <v>4668</v>
+        <v>4675</v>
       </c>
       <c r="AY22" s="5">
-        <v>6986</v>
+        <v>6993</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="19"/>
-        <v>1.0040241448692153</v>
+        <v>1.0050301810865192</v>
       </c>
       <c r="BA22" s="5">
         <v>7049</v>
@@ -3983,14 +3983,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="20"/>
-        <v>4649</v>
+        <v>4656</v>
       </c>
       <c r="BD22" s="5">
-        <v>7044</v>
+        <v>7051</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="21"/>
-        <v>0.99929067952901118</v>
+        <v>1.0002837281883956</v>
       </c>
       <c r="BF22" s="5">
         <v>8436</v>
@@ -4000,14 +4000,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="22"/>
-        <v>5763</v>
+        <v>5770</v>
       </c>
       <c r="BI22" s="5">
-        <v>8419</v>
+        <v>8426</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="23"/>
-        <v>0.99798482693219537</v>
+        <v>0.99881460407776201</v>
       </c>
       <c r="BL22" s="9"/>
     </row>
@@ -4026,14 +4026,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>6240</v>
+        <v>6241</v>
       </c>
       <c r="F23" s="5">
-        <v>8686</v>
+        <v>8687</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.98614895549500459</v>
+        <v>0.98626248864668487</v>
       </c>
       <c r="H23" s="5">
         <v>8878</v>
@@ -4043,14 +4043,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>6326</v>
+        <v>6327</v>
       </c>
       <c r="K23" s="5">
-        <v>8802</v>
+        <v>8803</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.99143951340391978</v>
+        <v>0.99155215138544717</v>
       </c>
       <c r="M23" s="5">
         <v>11255</v>
@@ -4060,14 +4060,14 @@
       </c>
       <c r="O23" s="3">
         <f t="shared" si="4"/>
-        <v>7991</v>
+        <v>7994</v>
       </c>
       <c r="P23" s="5">
-        <v>11230</v>
+        <v>11233</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="5"/>
-        <v>0.99777876499333629</v>
+        <v>0.99804531319413592</v>
       </c>
       <c r="R23" s="5">
         <v>8944</v>
@@ -4077,14 +4077,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="6"/>
-        <v>6233</v>
+        <v>6236</v>
       </c>
       <c r="U23" s="5">
-        <v>8925</v>
+        <v>8928</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="7"/>
-        <v>0.9978756708407871</v>
+        <v>0.99821109123434704</v>
       </c>
       <c r="W23" s="5">
         <v>10422</v>
@@ -4094,14 +4094,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="8"/>
-        <v>2959</v>
+        <v>2962</v>
       </c>
       <c r="Z23" s="5">
-        <v>9036</v>
+        <v>9039</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="9"/>
-        <v>0.86701208981001732</v>
+        <v>0.86729994242947606</v>
       </c>
       <c r="AB23" s="5">
         <v>11673</v>
@@ -4111,14 +4111,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="10"/>
-        <v>8266</v>
+        <v>8270</v>
       </c>
       <c r="AE23" s="5">
-        <v>11432</v>
+        <v>11436</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="11"/>
-        <v>0.97935406493617749</v>
+        <v>0.9796967360575688</v>
       </c>
       <c r="AG23" s="5">
         <v>9370</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="12"/>
-        <v>6379</v>
+        <v>6384</v>
       </c>
       <c r="AJ23" s="5">
-        <v>9009</v>
+        <v>9014</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="13"/>
-        <v>0.96147278548559234</v>
+        <v>0.96200640341515475</v>
       </c>
       <c r="AL23" s="5">
         <v>9238</v>
@@ -4145,14 +4145,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="14"/>
-        <v>6430</v>
+        <v>6436</v>
       </c>
       <c r="AO23" s="5">
-        <v>9049</v>
+        <v>9055</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="15"/>
-        <v>0.97954102619614636</v>
+        <v>0.98019051742801477</v>
       </c>
       <c r="AQ23" s="5">
         <v>11727</v>
@@ -4162,14 +4162,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="16"/>
-        <v>8068</v>
+        <v>8074</v>
       </c>
       <c r="AT23" s="5">
-        <v>11548</v>
+        <v>11554</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="17"/>
-        <v>0.98473607913362327</v>
+        <v>0.98524771893920016</v>
       </c>
       <c r="AV23" s="5">
         <v>9359</v>
@@ -4179,14 +4179,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="18"/>
-        <v>6483</v>
+        <v>6490</v>
       </c>
       <c r="AY23" s="5">
-        <v>9165</v>
+        <v>9172</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="19"/>
-        <v>0.9792712896676995</v>
+        <v>0.9800192328240197</v>
       </c>
       <c r="BA23" s="5">
         <v>9570</v>
@@ -4196,14 +4196,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="20"/>
-        <v>6421</v>
+        <v>6427</v>
       </c>
       <c r="BD23" s="5">
-        <v>9218</v>
+        <v>9224</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="21"/>
-        <v>0.9632183908045977</v>
+        <v>0.96384535005224659</v>
       </c>
       <c r="BF23" s="5">
         <v>11968</v>
@@ -4213,14 +4213,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="22"/>
-        <v>8591</v>
+        <v>8597</v>
       </c>
       <c r="BI23" s="5">
-        <v>11741</v>
+        <v>11747</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="23"/>
-        <v>0.98103275401069523</v>
+        <v>0.98153409090909094</v>
       </c>
       <c r="BL23" s="9"/>
     </row>
@@ -4307,14 +4307,14 @@
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="8"/>
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="Z24" s="5">
-        <v>6405</v>
+        <v>6407</v>
       </c>
       <c r="AA24" s="4">
         <f t="shared" si="9"/>
-        <v>0.97935779816513757</v>
+        <v>0.97966360856269108</v>
       </c>
       <c r="AB24" s="5">
         <v>7473</v>
@@ -4324,14 +4324,14 @@
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="10"/>
-        <v>5849</v>
+        <v>5851</v>
       </c>
       <c r="AE24" s="5">
-        <v>7383</v>
+        <v>7385</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="11"/>
-        <v>0.98795664391810523</v>
+        <v>0.98822427405325841</v>
       </c>
       <c r="AG24" s="5">
         <v>6660</v>
@@ -4341,14 +4341,14 @@
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="12"/>
-        <v>5218</v>
+        <v>5220</v>
       </c>
       <c r="AJ24" s="5">
-        <v>6592</v>
+        <v>6594</v>
       </c>
       <c r="AK24" s="4">
         <f t="shared" si="13"/>
-        <v>0.98978978978978982</v>
+        <v>0.99009009009009008</v>
       </c>
       <c r="AL24" s="5">
         <v>6723</v>
@@ -4358,14 +4358,14 @@
       </c>
       <c r="AN24" s="3">
         <f t="shared" si="14"/>
-        <v>5003</v>
+        <v>5005</v>
       </c>
       <c r="AO24" s="5">
-        <v>6639</v>
+        <v>6641</v>
       </c>
       <c r="AP24" s="4">
         <f t="shared" si="15"/>
-        <v>0.98750557786702364</v>
+        <v>0.987803064108285</v>
       </c>
       <c r="AQ24" s="5">
         <v>7657</v>
@@ -4375,14 +4375,14 @@
       </c>
       <c r="AS24" s="3">
         <f t="shared" si="16"/>
-        <v>5939</v>
+        <v>5941</v>
       </c>
       <c r="AT24" s="5">
-        <v>7569</v>
+        <v>7571</v>
       </c>
       <c r="AU24" s="4">
         <f t="shared" si="17"/>
-        <v>0.98850724826955727</v>
+        <v>0.98876844717252188</v>
       </c>
       <c r="AV24" s="5">
         <v>6786</v>
@@ -4392,14 +4392,14 @@
       </c>
       <c r="AX24" s="3">
         <f t="shared" si="18"/>
-        <v>5256</v>
+        <v>5259</v>
       </c>
       <c r="AY24" s="5">
-        <v>6744</v>
+        <v>6747</v>
       </c>
       <c r="AZ24" s="4">
         <f t="shared" si="19"/>
-        <v>0.99381078691423519</v>
+        <v>0.99425287356321834</v>
       </c>
       <c r="BA24" s="5">
         <v>7025</v>
@@ -4409,14 +4409,14 @@
       </c>
       <c r="BC24" s="3">
         <f t="shared" si="20"/>
-        <v>5299</v>
+        <v>5302</v>
       </c>
       <c r="BD24" s="5">
-        <v>6803</v>
+        <v>6806</v>
       </c>
       <c r="BE24" s="4">
         <f t="shared" si="21"/>
-        <v>0.96839857651245553</v>
+        <v>0.96882562277580075</v>
       </c>
       <c r="BF24" s="5">
         <v>7878</v>
@@ -4426,14 +4426,14 @@
       </c>
       <c r="BH24" s="3">
         <f t="shared" si="22"/>
-        <v>6236</v>
+        <v>6239</v>
       </c>
       <c r="BI24" s="5">
-        <v>7752</v>
+        <v>7755</v>
       </c>
       <c r="BJ24" s="4">
         <f t="shared" si="23"/>
-        <v>0.98400609291698404</v>
+        <v>0.98438690022848441</v>
       </c>
       <c r="BL24" s="9"/>
     </row>
@@ -4452,14 +4452,14 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>11739</v>
+        <v>11740</v>
       </c>
       <c r="F25" s="5">
-        <v>20216</v>
+        <v>20217</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>0.96597859327217128</v>
+        <v>0.96602637614678899</v>
       </c>
       <c r="H25" s="5">
         <v>20519</v>
@@ -4469,14 +4469,14 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>11470</v>
+        <v>11471</v>
       </c>
       <c r="K25" s="5">
-        <v>20347</v>
+        <v>20348</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="3"/>
-        <v>0.99161752522052726</v>
+        <v>0.99166626053901263</v>
       </c>
       <c r="M25" s="5">
         <v>27924</v>
@@ -4486,14 +4486,14 @@
       </c>
       <c r="O25" s="3">
         <f t="shared" si="4"/>
-        <v>16475</v>
+        <v>16477</v>
       </c>
       <c r="P25" s="5">
-        <v>27922</v>
+        <v>27924</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="5"/>
-        <v>0.99992837702334914</v>
+        <v>1</v>
       </c>
       <c r="R25" s="5">
         <v>20481</v>
@@ -4503,14 +4503,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="6"/>
-        <v>11657</v>
+        <v>11658</v>
       </c>
       <c r="U25" s="5">
-        <v>20492</v>
+        <v>20493</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="7"/>
-        <v>1.0005370831502367</v>
+        <v>1.0005859088911675</v>
       </c>
       <c r="W25" s="5">
         <v>20934</v>
@@ -4520,14 +4520,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="8"/>
-        <v>4216</v>
+        <v>4217</v>
       </c>
       <c r="Z25" s="5">
-        <v>20615</v>
+        <v>20616</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="9"/>
-        <v>0.98476163179516574</v>
+        <v>0.98480940097449121</v>
       </c>
       <c r="AB25" s="5">
         <v>28211</v>
@@ -4554,14 +4554,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="12"/>
-        <v>11778</v>
+        <v>11781</v>
       </c>
       <c r="AJ25" s="5">
-        <v>20726</v>
+        <v>20729</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="13"/>
-        <v>0.99749735296948694</v>
+        <v>0.99764173645201659</v>
       </c>
       <c r="AL25" s="5">
         <v>21081</v>
@@ -4571,14 +4571,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="14"/>
-        <v>11848</v>
+        <v>11852</v>
       </c>
       <c r="AO25" s="5">
-        <v>20907</v>
+        <v>20911</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="15"/>
-        <v>0.99174612210046964</v>
+        <v>0.99193586641999909</v>
       </c>
       <c r="AQ25" s="5">
         <v>28478</v>
@@ -4588,14 +4588,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="16"/>
-        <v>16482</v>
+        <v>16488</v>
       </c>
       <c r="AT25" s="5">
-        <v>28497</v>
+        <v>28503</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="17"/>
-        <v>1.0006671816841071</v>
+        <v>1.000877870636983</v>
       </c>
       <c r="AV25" s="5">
         <v>21086</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="18"/>
-        <v>12085</v>
+        <v>12092</v>
       </c>
       <c r="AY25" s="5">
-        <v>21051</v>
+        <v>21058</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="19"/>
-        <v>0.99834013089253537</v>
+        <v>0.99867210471402823</v>
       </c>
       <c r="BA25" s="5">
         <v>21405</v>
@@ -4622,14 +4622,14 @@
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="20"/>
-        <v>12028</v>
+        <v>12034</v>
       </c>
       <c r="BD25" s="5">
-        <v>21238</v>
+        <v>21244</v>
       </c>
       <c r="BE25" s="4">
         <f t="shared" si="21"/>
-        <v>0.99219808455968228</v>
+        <v>0.99247839289885542</v>
       </c>
       <c r="BF25" s="5">
         <v>28924</v>
@@ -4639,14 +4639,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="22"/>
-        <v>17885</v>
+        <v>17892</v>
       </c>
       <c r="BI25" s="5">
-        <v>28855</v>
+        <v>28862</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="23"/>
-        <v>0.99761443783709025</v>
+        <v>0.99785645138984924</v>
       </c>
       <c r="BL25" s="9"/>
     </row>
@@ -4665,14 +4665,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>9660</v>
+        <v>9666</v>
       </c>
       <c r="F26" s="5">
-        <v>14031</v>
+        <v>14037</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.99637835534725183</v>
+        <v>0.99680443118875162</v>
       </c>
       <c r="H26" s="5">
         <v>14494</v>
@@ -4682,14 +4682,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>9750</v>
+        <v>9755</v>
       </c>
       <c r="K26" s="5">
-        <v>14316</v>
+        <v>14321</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>0.98771905616117017</v>
+        <v>0.98806402649372149</v>
       </c>
       <c r="M26" s="5">
         <v>27473</v>
@@ -4699,14 +4699,14 @@
       </c>
       <c r="O26" s="3">
         <f t="shared" si="4"/>
-        <v>19023</v>
+        <v>19030</v>
       </c>
       <c r="P26" s="5">
-        <v>27432</v>
+        <v>27439</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="5"/>
-        <v>0.99850762566883855</v>
+        <v>0.99876242128635384</v>
       </c>
       <c r="R26" s="5">
         <v>14274</v>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="6"/>
-        <v>10003</v>
+        <v>10011</v>
       </c>
       <c r="U26" s="5">
-        <v>14209</v>
+        <v>14217</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="7"/>
-        <v>0.99544626593806917</v>
+        <v>0.9960067255149222</v>
       </c>
       <c r="W26" s="5">
         <v>14651</v>
@@ -4733,14 +4733,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="8"/>
-        <v>3119</v>
+        <v>3129</v>
       </c>
       <c r="Z26" s="5">
-        <v>14432</v>
+        <v>14442</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="9"/>
-        <v>0.98505221486587946</v>
+        <v>0.98573476213227762</v>
       </c>
       <c r="AB26" s="5">
         <v>28023</v>
@@ -4750,14 +4750,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="10"/>
-        <v>20290</v>
+        <v>20303</v>
       </c>
       <c r="AE26" s="5">
-        <v>27711</v>
+        <v>27724</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="11"/>
-        <v>0.98886628840595225</v>
+        <v>0.98933019305570424</v>
       </c>
       <c r="AG26" s="5">
         <v>14346</v>
@@ -4767,14 +4767,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="12"/>
-        <v>9761</v>
+        <v>9770</v>
       </c>
       <c r="AJ26" s="5">
-        <v>14243</v>
+        <v>14252</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="13"/>
-        <v>0.99282029834100094</v>
+        <v>0.99344765091314657</v>
       </c>
       <c r="AL26" s="5">
         <v>14687</v>
@@ -4784,14 +4784,14 @@
       </c>
       <c r="AN26" s="3">
         <f t="shared" si="14"/>
-        <v>9446</v>
+        <v>9454</v>
       </c>
       <c r="AO26" s="5">
-        <v>14419</v>
+        <v>14427</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="15"/>
-        <v>0.98175257030026553</v>
+        <v>0.98229726969428743</v>
       </c>
       <c r="AQ26" s="5">
         <v>27948</v>
@@ -4801,14 +4801,14 @@
       </c>
       <c r="AS26" s="3">
         <f t="shared" si="16"/>
-        <v>18790</v>
+        <v>18806</v>
       </c>
       <c r="AT26" s="5">
-        <v>27829</v>
+        <v>27845</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="17"/>
-        <v>0.99574209245742096</v>
+        <v>0.99631458422785169</v>
       </c>
       <c r="AV26" s="5">
         <v>14478</v>
@@ -4818,14 +4818,14 @@
       </c>
       <c r="AX26" s="3">
         <f t="shared" si="18"/>
-        <v>9487</v>
+        <v>9495</v>
       </c>
       <c r="AY26" s="5">
-        <v>14383</v>
+        <v>14391</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="19"/>
-        <v>0.9934383202099738</v>
+        <v>0.99399088271860758</v>
       </c>
       <c r="BA26" s="5">
         <v>14902</v>
@@ -4835,14 +4835,14 @@
       </c>
       <c r="BC26" s="3">
         <f t="shared" si="20"/>
-        <v>9574</v>
+        <v>9584</v>
       </c>
       <c r="BD26" s="5">
-        <v>14521</v>
+        <v>14531</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="21"/>
-        <v>0.97443296201852103</v>
+        <v>0.97510401288417659</v>
       </c>
       <c r="BF26" s="5">
         <v>28105</v>
@@ -4852,14 +4852,14 @@
       </c>
       <c r="BH26" s="3">
         <f t="shared" si="22"/>
-        <v>20171</v>
+        <v>20188</v>
       </c>
       <c r="BI26" s="5">
-        <v>27934</v>
+        <v>27951</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="23"/>
-        <v>0.99391567336772813</v>
+        <v>0.9945205479452055</v>
       </c>
       <c r="BL26" s="9"/>
     </row>
@@ -4878,14 +4878,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>76297</v>
+        <v>76327</v>
       </c>
       <c r="F27" s="5">
-        <v>125084</v>
+        <v>125114</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>0.96861472699536155</v>
+        <v>0.96884703841656539</v>
       </c>
       <c r="H27" s="5">
         <v>129298</v>
@@ -4895,14 +4895,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>74596</v>
+        <v>74630</v>
       </c>
       <c r="K27" s="5">
-        <v>125992</v>
+        <v>126026</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.97443115902798183</v>
+        <v>0.97469411746508061</v>
       </c>
       <c r="M27" s="5">
         <v>186733</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="O27" s="3">
         <f t="shared" si="4"/>
-        <v>116655</v>
+        <v>116719</v>
       </c>
       <c r="P27" s="5">
-        <v>185749</v>
+        <v>185813</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="5"/>
-        <v>0.99473044400293464</v>
+        <v>0.9950731793523373</v>
       </c>
       <c r="R27" s="5">
         <v>126872</v>
@@ -4929,14 +4929,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="6"/>
-        <v>75127</v>
+        <v>75167</v>
       </c>
       <c r="U27" s="5">
-        <v>125654</v>
+        <v>125694</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="7"/>
-        <v>0.99039977299955861</v>
+        <v>0.99071505139037774</v>
       </c>
       <c r="W27" s="5">
         <v>129739</v>
@@ -4946,14 +4946,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="8"/>
-        <v>33754</v>
+        <v>33801</v>
       </c>
       <c r="Z27" s="5">
-        <v>126615</v>
+        <v>126662</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="9"/>
-        <v>0.97592088731992688</v>
+        <v>0.97628315309968472</v>
       </c>
       <c r="AB27" s="5">
         <v>188270</v>
@@ -4963,14 +4963,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="10"/>
-        <v>125659</v>
+        <v>125744</v>
       </c>
       <c r="AE27" s="5">
-        <v>187147</v>
+        <v>187232</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="11"/>
-        <v>0.99403516226695698</v>
+        <v>0.99448664152546873</v>
       </c>
       <c r="AG27" s="5">
         <v>127800</v>
@@ -4980,14 +4980,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="12"/>
-        <v>76414</v>
+        <v>76472</v>
       </c>
       <c r="AJ27" s="5">
-        <v>126759</v>
+        <v>126817</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="13"/>
-        <v>0.99185446009389666</v>
+        <v>0.99230829420970268</v>
       </c>
       <c r="AL27" s="5">
         <v>130262</v>
@@ -4997,14 +4997,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" si="14"/>
-        <v>74587</v>
+        <v>74651</v>
       </c>
       <c r="AO27" s="5">
-        <v>127828</v>
+        <v>127892</v>
       </c>
       <c r="AP27" s="4">
         <f t="shared" si="15"/>
-        <v>0.98131458138213756</v>
+        <v>0.98180589888071734</v>
       </c>
       <c r="AQ27" s="5">
         <v>189830</v>
@@ -5014,14 +5014,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" si="16"/>
-        <v>115915</v>
+        <v>116035</v>
       </c>
       <c r="AT27" s="5">
-        <v>189168</v>
+        <v>189288</v>
       </c>
       <c r="AU27" s="4">
         <f t="shared" si="17"/>
-        <v>0.99651266923036397</v>
+        <v>0.99714481378075115</v>
       </c>
       <c r="AV27" s="5">
         <v>128733</v>
@@ -5031,14 +5031,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" si="18"/>
-        <v>73802</v>
+        <v>73883</v>
       </c>
       <c r="AY27" s="5">
-        <v>128463</v>
+        <v>128544</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" si="19"/>
-        <v>0.99790263568781901</v>
+        <v>0.99853184498147329</v>
       </c>
       <c r="BA27" s="5">
         <v>132099</v>
@@ -5048,14 +5048,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" si="20"/>
-        <v>74400</v>
+        <v>74487</v>
       </c>
       <c r="BD27" s="5">
-        <v>129968</v>
+        <v>130055</v>
       </c>
       <c r="BE27" s="4">
         <f t="shared" si="21"/>
-        <v>0.98386815948644579</v>
+        <v>0.98452675644781562</v>
       </c>
       <c r="BF27" s="5">
         <v>192460</v>
@@ -5065,14 +5065,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="22"/>
-        <v>123337</v>
+        <v>123513</v>
       </c>
       <c r="BI27" s="5">
-        <v>191715</v>
+        <v>191891</v>
       </c>
       <c r="BJ27" s="4">
         <f t="shared" si="23"/>
-        <v>0.99612906577990235</v>
+        <v>0.99704354151511998</v>
       </c>
       <c r="BL27" s="9"/>
     </row>
@@ -5091,14 +5091,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>175668</v>
+        <v>175691</v>
       </c>
       <c r="F28" s="5">
-        <v>409393</v>
+        <v>409416</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.99044616806421804</v>
+        <v>0.99050181205877941</v>
       </c>
       <c r="H28" s="5">
         <v>423216</v>
@@ -5108,14 +5108,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>174251</v>
+        <v>174269</v>
       </c>
       <c r="K28" s="5">
-        <v>413820</v>
+        <v>413838</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.97779857094249745</v>
+        <v>0.9778411024157877</v>
       </c>
       <c r="M28" s="5">
         <v>688530</v>
@@ -5125,14 +5125,14 @@
       </c>
       <c r="O28" s="3">
         <f t="shared" si="4"/>
-        <v>299306</v>
+        <v>299350</v>
       </c>
       <c r="P28" s="5">
-        <v>681990</v>
+        <v>682034</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="5"/>
-        <v>0.99050150320247488</v>
+        <v>0.99056540746227473</v>
       </c>
       <c r="R28" s="5">
         <v>417505</v>
@@ -5142,14 +5142,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="6"/>
-        <v>173288</v>
+        <v>173312</v>
       </c>
       <c r="U28" s="5">
-        <v>414089</v>
+        <v>414113</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="7"/>
-        <v>0.99181806205913703</v>
+        <v>0.99187554640064191</v>
       </c>
       <c r="W28" s="5">
         <v>426115</v>
@@ -5159,14 +5159,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="8"/>
-        <v>67572</v>
+        <v>67605</v>
       </c>
       <c r="Z28" s="5">
-        <v>416237</v>
+        <v>416270</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="9"/>
-        <v>0.97681846449902021</v>
+        <v>0.97689590838154017</v>
       </c>
       <c r="AB28" s="5">
         <v>693825</v>
@@ -5176,14 +5176,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="10"/>
-        <v>332041</v>
+        <v>332110</v>
       </c>
       <c r="AE28" s="5">
-        <v>687215</v>
+        <v>687284</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="11"/>
-        <v>0.99047310200699024</v>
+        <v>0.99057255071523798</v>
       </c>
       <c r="AG28" s="5">
         <v>421441</v>
@@ -5193,14 +5193,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="12"/>
-        <v>172904</v>
+        <v>172946</v>
       </c>
       <c r="AJ28" s="5">
-        <v>416782</v>
+        <v>416824</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="13"/>
-        <v>0.98894507178940827</v>
+        <v>0.98904472986728864</v>
       </c>
       <c r="AL28" s="5">
         <v>428935</v>
@@ -5210,14 +5210,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="14"/>
-        <v>166813</v>
+        <v>166861</v>
       </c>
       <c r="AO28" s="5">
-        <v>421314</v>
+        <v>421362</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" si="15"/>
-        <v>0.98223273922622312</v>
+        <v>0.98234464429342438</v>
       </c>
       <c r="AQ28" s="5">
         <v>700018</v>
@@ -5227,14 +5227,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="16"/>
-        <v>292253</v>
+        <v>292355</v>
       </c>
       <c r="AT28" s="5">
-        <v>696239</v>
+        <v>696341</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" si="17"/>
-        <v>0.9946015673882671</v>
+        <v>0.99474727792713902</v>
       </c>
       <c r="AV28" s="5">
         <v>428584</v>
@@ -5244,14 +5244,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="18"/>
-        <v>169558</v>
+        <v>169625</v>
       </c>
       <c r="AY28" s="5">
-        <v>426282</v>
+        <v>426349</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" si="19"/>
-        <v>0.99462882422115617</v>
+        <v>0.99478515296884629</v>
       </c>
       <c r="BA28" s="5">
         <v>438333</v>
@@ -5261,14 +5261,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="20"/>
-        <v>170208</v>
+        <v>170287</v>
       </c>
       <c r="BD28" s="5">
-        <v>431548</v>
+        <v>431627</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" si="21"/>
-        <v>0.98452090077635035</v>
+        <v>0.98470112905028828</v>
       </c>
       <c r="BF28" s="5">
         <v>711748</v>
@@ -5278,14 +5278,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="22"/>
-        <v>331863</v>
+        <v>332031</v>
       </c>
       <c r="BI28" s="5">
-        <v>707181</v>
+        <v>707349</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="23"/>
-        <v>0.99358340311458548</v>
+        <v>0.99381944171251624</v>
       </c>
       <c r="BL28" s="9"/>
     </row>
@@ -5304,14 +5304,14 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>70910</v>
+        <v>70913</v>
       </c>
       <c r="F29" s="5">
-        <v>135486</v>
+        <v>135489</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>0.99043817711303128</v>
+        <v>0.99046010789946926</v>
       </c>
       <c r="H29" s="5">
         <v>138439</v>
@@ -5321,14 +5321,14 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>70904</v>
+        <v>70909</v>
       </c>
       <c r="K29" s="5">
-        <v>136688</v>
+        <v>136693</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="3"/>
-        <v>0.98735183004789118</v>
+        <v>0.98738794703804567</v>
       </c>
       <c r="M29" s="5">
         <v>184711</v>
@@ -5338,14 +5338,14 @@
       </c>
       <c r="O29" s="3">
         <f t="shared" si="4"/>
-        <v>98982</v>
+        <v>98993</v>
       </c>
       <c r="P29" s="5">
-        <v>183117</v>
+        <v>183128</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="5"/>
-        <v>0.99137030279734284</v>
+        <v>0.99142985528744909</v>
       </c>
       <c r="R29" s="5">
         <v>138323</v>
@@ -5355,14 +5355,14 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="6"/>
-        <v>72690</v>
+        <v>72698</v>
       </c>
       <c r="U29" s="5">
-        <v>136845</v>
+        <v>136853</v>
       </c>
       <c r="V29" s="4">
         <f t="shared" si="7"/>
-        <v>0.98931486448385297</v>
+        <v>0.98937270012940726</v>
       </c>
       <c r="W29" s="5">
         <v>139858</v>
@@ -5372,14 +5372,14 @@
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="8"/>
-        <v>25773</v>
+        <v>25782</v>
       </c>
       <c r="Z29" s="5">
-        <v>137325</v>
+        <v>137334</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" si="9"/>
-        <v>0.98188877289822529</v>
+        <v>0.98195312388279543</v>
       </c>
       <c r="AB29" s="5">
         <v>187429</v>
@@ -5389,14 +5389,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="10"/>
-        <v>107153</v>
+        <v>107167</v>
       </c>
       <c r="AE29" s="5">
-        <v>184493</v>
+        <v>184507</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="11"/>
-        <v>0.98433540167209987</v>
+        <v>0.98441009662325463</v>
       </c>
       <c r="AG29" s="5">
         <v>139419</v>
@@ -5406,14 +5406,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="12"/>
-        <v>74771</v>
+        <v>74786</v>
       </c>
       <c r="AJ29" s="5">
-        <v>138016</v>
+        <v>138031</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="13"/>
-        <v>0.98993680918669624</v>
+        <v>0.99004439853965387</v>
       </c>
       <c r="AL29" s="5">
         <v>141276</v>
@@ -5423,14 +5423,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="14"/>
-        <v>71109</v>
+        <v>71126</v>
       </c>
       <c r="AO29" s="5">
-        <v>139223</v>
+        <v>139240</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="15"/>
-        <v>0.98546816161272965</v>
+        <v>0.98558849344545429</v>
       </c>
       <c r="AQ29" s="5">
         <v>188424</v>
@@ -5440,14 +5440,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="16"/>
-        <v>97077</v>
+        <v>97100</v>
       </c>
       <c r="AT29" s="5">
-        <v>187184</v>
+        <v>187207</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="17"/>
-        <v>0.99341909735490175</v>
+        <v>0.99354116248460922</v>
       </c>
       <c r="AV29" s="5">
         <v>141887</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="AX29" s="3">
         <f t="shared" si="18"/>
-        <v>71677</v>
+        <v>71694</v>
       </c>
       <c r="AY29" s="5">
-        <v>140468</v>
+        <v>140485</v>
       </c>
       <c r="AZ29" s="4">
         <f t="shared" si="19"/>
-        <v>0.989999083777936</v>
+        <v>0.99011889743246384</v>
       </c>
       <c r="BA29" s="5">
         <v>143795</v>
@@ -5474,14 +5474,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="20"/>
-        <v>71449</v>
+        <v>71467</v>
       </c>
       <c r="BD29" s="5">
-        <v>141686</v>
+        <v>141704</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="21"/>
-        <v>0.98533328697103517</v>
+        <v>0.98545846517611879</v>
       </c>
       <c r="BF29" s="5">
         <v>191754</v>
@@ -5491,14 +5491,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="22"/>
-        <v>105360</v>
+        <v>105398</v>
       </c>
       <c r="BI29" s="5">
-        <v>189566</v>
+        <v>189604</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="23"/>
-        <v>0.98858954702379087</v>
+        <v>0.98878771759650386</v>
       </c>
       <c r="BL29" s="9"/>
     </row>
@@ -5517,14 +5517,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>100966</v>
+        <v>100980</v>
       </c>
       <c r="F30" s="5">
-        <v>176002</v>
+        <v>176016</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.98741065718164789</v>
+        <v>0.98748920031866072</v>
       </c>
       <c r="H30" s="5">
         <v>181910</v>
@@ -5534,14 +5534,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>100069</v>
+        <v>100082</v>
       </c>
       <c r="K30" s="5">
-        <v>178252</v>
+        <v>178265</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.97989115496674184</v>
+        <v>0.97996261887746683</v>
       </c>
       <c r="M30" s="5">
         <v>304709</v>
@@ -5551,14 +5551,14 @@
       </c>
       <c r="O30" s="3">
         <f t="shared" si="4"/>
-        <v>185045</v>
+        <v>185069</v>
       </c>
       <c r="P30" s="5">
-        <v>301512</v>
+        <v>301536</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="5"/>
-        <v>0.98950802240826496</v>
+        <v>0.98958678608114625</v>
       </c>
       <c r="R30" s="5">
         <v>179361</v>
@@ -5568,14 +5568,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="6"/>
-        <v>100504</v>
+        <v>100518</v>
       </c>
       <c r="U30" s="5">
-        <v>177810</v>
+        <v>177824</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="7"/>
-        <v>0.99135263518825167</v>
+        <v>0.99143069006082707</v>
       </c>
       <c r="W30" s="5">
         <v>184404</v>
@@ -5585,14 +5585,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="8"/>
-        <v>38516</v>
+        <v>38537</v>
       </c>
       <c r="Z30" s="5">
-        <v>179049</v>
+        <v>179070</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="9"/>
-        <v>0.97096049977223919</v>
+        <v>0.97107438016528924</v>
       </c>
       <c r="AB30" s="5">
         <v>307610</v>
@@ -5602,14 +5602,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="10"/>
-        <v>193396</v>
+        <v>193434</v>
       </c>
       <c r="AE30" s="5">
-        <v>304521</v>
+        <v>304559</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="11"/>
-        <v>0.98995806378206175</v>
+        <v>0.99008159682715124</v>
       </c>
       <c r="AG30" s="5">
         <v>180656</v>
@@ -5619,14 +5619,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="12"/>
-        <v>99560</v>
+        <v>99584</v>
       </c>
       <c r="AJ30" s="5">
-        <v>178771</v>
+        <v>178795</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="13"/>
-        <v>0.98956580462315114</v>
+        <v>0.98969865379505806</v>
       </c>
       <c r="AL30" s="5">
         <v>185185</v>
@@ -5636,14 +5636,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="14"/>
-        <v>98815</v>
+        <v>98842</v>
       </c>
       <c r="AO30" s="5">
-        <v>181659</v>
+        <v>181686</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="15"/>
-        <v>0.98095958095958091</v>
+        <v>0.98110538110538115</v>
       </c>
       <c r="AQ30" s="5">
         <v>311830</v>
@@ -5653,14 +5653,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="16"/>
-        <v>178244</v>
+        <v>178305</v>
       </c>
       <c r="AT30" s="5">
-        <v>309482</v>
+        <v>309543</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="17"/>
-        <v>0.9924702562293557</v>
+        <v>0.99266587563736652</v>
       </c>
       <c r="AV30" s="5">
         <v>184055</v>
@@ -5670,14 +5670,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="18"/>
-        <v>100134</v>
+        <v>100169</v>
       </c>
       <c r="AY30" s="5">
-        <v>182478</v>
+        <v>182513</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="19"/>
-        <v>0.99143190894026245</v>
+        <v>0.99162206949009812</v>
       </c>
       <c r="BA30" s="5">
         <v>188792</v>
@@ -5687,14 +5687,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="20"/>
-        <v>100305</v>
+        <v>100342</v>
       </c>
       <c r="BD30" s="5">
-        <v>184852</v>
+        <v>184889</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="21"/>
-        <v>0.97913047163015376</v>
+        <v>0.97932645451078437</v>
       </c>
       <c r="BF30" s="5">
         <v>315967</v>
@@ -5704,14 +5704,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="22"/>
-        <v>193487</v>
+        <v>193571</v>
       </c>
       <c r="BI30" s="5">
-        <v>313888</v>
+        <v>313972</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="23"/>
-        <v>0.99342019894482647</v>
+        <v>0.99368604949251027</v>
       </c>
       <c r="BL30" s="9"/>
     </row>
@@ -5730,14 +5730,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>35395</v>
+        <v>35399</v>
       </c>
       <c r="F31" s="5">
-        <v>78737</v>
+        <v>78741</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>1.0009152736286786</v>
+        <v>1.0009661221636053</v>
       </c>
       <c r="H31" s="5">
         <v>80911</v>
@@ -5747,14 +5747,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>33725</v>
+        <v>33729</v>
       </c>
       <c r="K31" s="5">
-        <v>80383</v>
+        <v>80387</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.99347431128029562</v>
+        <v>0.99352374831605095</v>
       </c>
       <c r="M31" s="5">
         <v>142260</v>
@@ -5764,14 +5764,14 @@
       </c>
       <c r="O31" s="3">
         <f t="shared" si="4"/>
-        <v>72167</v>
+        <v>72175</v>
       </c>
       <c r="P31" s="5">
-        <v>142757</v>
+        <v>142765</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="5"/>
-        <v>1.0034936032616337</v>
+        <v>1.0035498383241952</v>
       </c>
       <c r="R31" s="5">
         <v>79665</v>
@@ -5781,14 +5781,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="6"/>
-        <v>33839</v>
+        <v>33844</v>
       </c>
       <c r="U31" s="5">
-        <v>79775</v>
+        <v>79780</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="7"/>
-        <v>1.0013807820247285</v>
+        <v>1.0014435448440344</v>
       </c>
       <c r="W31" s="5">
         <v>81657</v>
@@ -5798,14 +5798,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="8"/>
-        <v>20670</v>
+        <v>20676</v>
       </c>
       <c r="Z31" s="5">
-        <v>80687</v>
+        <v>80693</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="9"/>
-        <v>0.98812104289895542</v>
+        <v>0.98819452098411653</v>
       </c>
       <c r="AB31" s="5">
         <v>144167</v>
@@ -5815,14 +5815,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="10"/>
-        <v>77258</v>
+        <v>77268</v>
       </c>
       <c r="AE31" s="5">
-        <v>144607</v>
+        <v>144617</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="11"/>
-        <v>1.0030520160647027</v>
+        <v>1.0031213800661734</v>
       </c>
       <c r="AG31" s="5">
         <v>80917</v>
@@ -5832,14 +5832,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="12"/>
-        <v>35643</v>
+        <v>35652</v>
       </c>
       <c r="AJ31" s="5">
-        <v>81467</v>
+        <v>81476</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="13"/>
-        <v>1.0067970883745072</v>
+        <v>1.0069083134569992</v>
       </c>
       <c r="AL31" s="5">
         <v>83546</v>
@@ -5849,14 +5849,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="14"/>
-        <v>33658</v>
+        <v>33670</v>
       </c>
       <c r="AO31" s="5">
-        <v>82716</v>
+        <v>82728</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="15"/>
-        <v>0.99006535321858613</v>
+        <v>0.9902089866660283</v>
       </c>
       <c r="AQ31" s="5">
         <v>147023</v>
@@ -5866,14 +5866,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="16"/>
-        <v>69501</v>
+        <v>69522</v>
       </c>
       <c r="AT31" s="5">
-        <v>147314</v>
+        <v>147335</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="17"/>
-        <v>1.0019792821531326</v>
+        <v>1.0021221169476884</v>
       </c>
       <c r="AV31" s="5">
         <v>81694</v>
@@ -5883,14 +5883,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="18"/>
-        <v>33810</v>
+        <v>33822</v>
       </c>
       <c r="AY31" s="5">
-        <v>82315</v>
+        <v>82327</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="19"/>
-        <v>1.0076015374446103</v>
+        <v>1.0077484270570667</v>
       </c>
       <c r="BA31" s="5">
         <v>83957</v>
@@ -5900,14 +5900,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="20"/>
-        <v>32810</v>
+        <v>32825</v>
       </c>
       <c r="BD31" s="5">
-        <v>83367</v>
+        <v>83382</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="21"/>
-        <v>0.99297259311314123</v>
+        <v>0.99315125600009524</v>
       </c>
       <c r="BF31" s="5">
         <v>148810</v>
@@ -5917,14 +5917,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="22"/>
-        <v>78752</v>
+        <v>78787</v>
       </c>
       <c r="BI31" s="5">
-        <v>149340</v>
+        <v>149375</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="23"/>
-        <v>1.0035615886029166</v>
+        <v>1.0037967878502789</v>
       </c>
       <c r="BL31" s="9"/>
     </row>
@@ -5943,14 +5943,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>97859</v>
+        <v>97867</v>
       </c>
       <c r="F32" s="5">
-        <v>217257</v>
+        <v>217265</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.98936213813737228</v>
+        <v>0.98939856917114843</v>
       </c>
       <c r="H32" s="5">
         <v>225984</v>
@@ -5960,14 +5960,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>97763</v>
+        <v>97769</v>
       </c>
       <c r="K32" s="5">
-        <v>222081</v>
+        <v>222087</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.98272886576040785</v>
+        <v>0.98275541631265928</v>
       </c>
       <c r="M32" s="5">
         <v>469379</v>
@@ -5977,14 +5977,14 @@
       </c>
       <c r="O32" s="3">
         <f t="shared" si="4"/>
-        <v>251962</v>
+        <v>251976</v>
       </c>
       <c r="P32" s="5">
-        <v>466880</v>
+        <v>466894</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="5"/>
-        <v>0.99467594417304561</v>
+        <v>0.99470577081633393</v>
       </c>
       <c r="R32" s="5">
         <v>220673</v>
@@ -5994,14 +5994,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="6"/>
-        <v>98811</v>
+        <v>98816</v>
       </c>
       <c r="U32" s="5">
-        <v>219214</v>
+        <v>219219</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="7"/>
-        <v>0.99338840728136202</v>
+        <v>0.99341106524132994</v>
       </c>
       <c r="W32" s="5">
         <v>228851</v>
@@ -6011,14 +6011,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="8"/>
-        <v>47495</v>
+        <v>47502</v>
       </c>
       <c r="Z32" s="5">
-        <v>222445</v>
+        <v>222452</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="9"/>
-        <v>0.97200798773000774</v>
+        <v>0.97203857531756466</v>
       </c>
       <c r="AB32" s="5">
         <v>476427</v>
@@ -6028,14 +6028,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="10"/>
-        <v>269975</v>
+        <v>269992</v>
       </c>
       <c r="AE32" s="5">
-        <v>472677</v>
+        <v>472694</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="11"/>
-        <v>0.99212890957061628</v>
+        <v>0.99216459184722949</v>
       </c>
       <c r="AG32" s="5">
         <v>224544</v>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="12"/>
-        <v>99817</v>
+        <v>99826</v>
       </c>
       <c r="AJ32" s="5">
-        <v>222951</v>
+        <v>222960</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="13"/>
-        <v>0.99290562206070976</v>
+        <v>0.99294570329200516</v>
       </c>
       <c r="AL32" s="5">
         <v>231787</v>
@@ -6062,14 +6062,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="14"/>
-        <v>96349</v>
+        <v>96357</v>
       </c>
       <c r="AO32" s="5">
-        <v>226994</v>
+        <v>227002</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="15"/>
-        <v>0.97932153226885033</v>
+        <v>0.9793560467153033</v>
       </c>
       <c r="AQ32" s="5">
         <v>484390</v>
@@ -6079,14 +6079,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="16"/>
-        <v>236237</v>
+        <v>236264</v>
       </c>
       <c r="AT32" s="5">
-        <v>481404</v>
+        <v>481431</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="17"/>
-        <v>0.99383554573793842</v>
+        <v>0.99389128594727394</v>
       </c>
       <c r="AV32" s="5">
         <v>227629</v>
@@ -6096,14 +6096,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="18"/>
-        <v>94058</v>
+        <v>94073</v>
       </c>
       <c r="AY32" s="5">
-        <v>226685</v>
+        <v>226700</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="19"/>
-        <v>0.99585290099240431</v>
+        <v>0.99591879769273683</v>
       </c>
       <c r="BA32" s="5">
         <v>234918</v>
@@ -6113,14 +6113,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="20"/>
-        <v>94969</v>
+        <v>94987</v>
       </c>
       <c r="BD32" s="5">
-        <v>231434</v>
+        <v>231452</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="21"/>
-        <v>0.98516929311504442</v>
+        <v>0.98524591559608032</v>
       </c>
       <c r="BF32" s="5">
         <v>492680</v>
@@ -6130,14 +6130,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="22"/>
-        <v>270284</v>
+        <v>270346</v>
       </c>
       <c r="BI32" s="5">
-        <v>490636</v>
+        <v>490698</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="23"/>
-        <v>0.99585126248274747</v>
+        <v>0.99597710481448409</v>
       </c>
       <c r="BL32" s="9"/>
     </row>
@@ -6156,14 +6156,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>93948</v>
+        <v>93954</v>
       </c>
       <c r="F33" s="5">
-        <v>662158</v>
+        <v>662164</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>0.99810977190644723</v>
+        <v>0.99811881606000497</v>
       </c>
       <c r="H33" s="5">
         <v>674602</v>
@@ -6173,14 +6173,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>92438</v>
+        <v>92447</v>
       </c>
       <c r="K33" s="5">
-        <v>670096</v>
+        <v>670105</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>0.99332050601688104</v>
+        <v>0.99333384721658102</v>
       </c>
       <c r="M33" s="5">
         <v>1077651</v>
@@ -6190,14 +6190,14 @@
       </c>
       <c r="O33" s="3">
         <f t="shared" si="4"/>
-        <v>180250</v>
+        <v>180261</v>
       </c>
       <c r="P33" s="5">
-        <v>1078221</v>
+        <v>1078232</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="5"/>
-        <v>1.0005289281966054</v>
+        <v>1.0005391355828557</v>
       </c>
       <c r="R33" s="5">
         <v>670885</v>
@@ -6207,14 +6207,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="6"/>
-        <v>98743</v>
+        <v>98750</v>
       </c>
       <c r="U33" s="5">
-        <v>670998</v>
+        <v>671005</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="7"/>
-        <v>1.0001684342323944</v>
+        <v>1.0001788682113923</v>
       </c>
       <c r="W33" s="5">
         <v>679851</v>
@@ -6224,14 +6224,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="8"/>
-        <v>75094</v>
+        <v>75102</v>
       </c>
       <c r="Z33" s="5">
-        <v>677879</v>
+        <v>677887</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="9"/>
-        <v>0.9970993644195566</v>
+        <v>0.99711113170385868</v>
       </c>
       <c r="AB33" s="5">
         <v>1091619</v>
@@ -6241,14 +6241,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="10"/>
-        <v>205430</v>
+        <v>205440</v>
       </c>
       <c r="AE33" s="5">
-        <v>1092072</v>
+        <v>1092082</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="11"/>
-        <v>1.0004149799517963</v>
+        <v>1.0004241406571341</v>
       </c>
       <c r="AG33" s="5">
         <v>681949</v>
@@ -6258,14 +6258,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="12"/>
-        <v>121272</v>
+        <v>121276</v>
       </c>
       <c r="AJ33" s="5">
-        <v>682561</v>
+        <v>682565</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="13"/>
-        <v>1.0008974278135168</v>
+        <v>1.0009032933547817</v>
       </c>
       <c r="AL33" s="5">
         <v>691548</v>
@@ -6275,14 +6275,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="14"/>
-        <v>90808</v>
+        <v>90815</v>
       </c>
       <c r="AO33" s="5">
-        <v>688998</v>
+        <v>689005</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="15"/>
-        <v>0.99631262038209933</v>
+        <v>0.99632274260065823</v>
       </c>
       <c r="AQ33" s="5">
         <v>1107071</v>
@@ -6292,14 +6292,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="16"/>
-        <v>167879</v>
+        <v>167894</v>
       </c>
       <c r="AT33" s="5">
-        <v>1110242</v>
+        <v>1110257</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="17"/>
-        <v>1.0028643149355372</v>
+        <v>1.0028778642020251</v>
       </c>
       <c r="AV33" s="5">
         <v>697202</v>
@@ -6309,14 +6309,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="18"/>
-        <v>89906</v>
+        <v>89916</v>
       </c>
       <c r="AY33" s="5">
-        <v>698891</v>
+        <v>698901</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="19"/>
-        <v>1.0024225403828446</v>
+        <v>1.0024368834283321</v>
       </c>
       <c r="BA33" s="5">
         <v>707985</v>
@@ -6326,14 +6326,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="20"/>
-        <v>90142</v>
+        <v>90157</v>
       </c>
       <c r="BD33" s="5">
-        <v>709239</v>
+        <v>709254</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="21"/>
-        <v>1.0017712239666094</v>
+        <v>1.0017924108561622</v>
       </c>
       <c r="BF33" s="5">
         <v>1132408</v>
@@ -6343,14 +6343,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="22"/>
-        <v>207689</v>
+        <v>207722</v>
       </c>
       <c r="BI33" s="5">
-        <v>1134919</v>
+        <v>1134952</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="23"/>
-        <v>1.0022173986760956</v>
+        <v>1.0022465401162832</v>
       </c>
       <c r="BL33" s="9"/>
     </row>
@@ -6592,14 +6592,14 @@
       </c>
       <c r="O35" s="3">
         <f t="shared" ref="O35:O47" si="28">P35-N35</f>
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="P35" s="5">
-        <v>14685</v>
+        <v>14686</v>
       </c>
       <c r="Q35" s="4">
         <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
-        <v>0.99674200773773158</v>
+        <v>0.99680988257652892</v>
       </c>
       <c r="R35" s="5">
         <v>12053</v>
@@ -6609,14 +6609,14 @@
       </c>
       <c r="T35" s="3">
         <f t="shared" ref="T35:T47" si="30">U35-S35</f>
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="U35" s="5">
-        <v>11971</v>
+        <v>11972</v>
       </c>
       <c r="V35" s="4">
         <f t="shared" ref="V35:V48" si="31">U35/R35</f>
-        <v>0.99319671451091018</v>
+        <v>0.99327968140711853</v>
       </c>
       <c r="W35" s="5">
         <v>12107</v>
@@ -6626,14 +6626,14 @@
       </c>
       <c r="Y35" s="3">
         <f t="shared" ref="Y35:Y47" si="32">Z35-X35</f>
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="Z35" s="5">
-        <v>11984</v>
+        <v>11985</v>
       </c>
       <c r="AA35" s="4">
         <f t="shared" ref="AA35:AA48" si="33">Z35/W35</f>
-        <v>0.98984058808953501</v>
+        <v>0.98992318493433551</v>
       </c>
       <c r="AB35" s="5">
         <v>14785</v>
@@ -6643,14 +6643,14 @@
       </c>
       <c r="AD35" s="3">
         <f t="shared" ref="AD35:AD47" si="34">AE35-AC35</f>
-        <v>3066</v>
+        <v>3068</v>
       </c>
       <c r="AE35" s="5">
-        <v>14713</v>
+        <v>14715</v>
       </c>
       <c r="AF35" s="4">
         <f t="shared" ref="AF35:AF48" si="35">AE35/AB35</f>
-        <v>0.99513019952654713</v>
+        <v>0.99526547176192082</v>
       </c>
       <c r="AG35" s="5">
         <v>12076</v>
@@ -6660,14 +6660,14 @@
       </c>
       <c r="AI35" s="3">
         <f t="shared" ref="AI35:AI47" si="36">AJ35-AH35</f>
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="AJ35" s="5">
-        <v>12033</v>
+        <v>12034</v>
       </c>
       <c r="AK35" s="4">
         <f t="shared" ref="AK35:AK48" si="37">AJ35/AG35</f>
-        <v>0.99643921828420001</v>
+        <v>0.99652202716131166</v>
       </c>
       <c r="AL35" s="5">
         <v>12179</v>
@@ -6677,14 +6677,14 @@
       </c>
       <c r="AN35" s="3">
         <f t="shared" ref="AN35:AN47" si="38">AO35-AM35</f>
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="AO35" s="5">
-        <v>12096</v>
+        <v>12098</v>
       </c>
       <c r="AP35" s="4">
         <f t="shared" ref="AP35:AP48" si="39">AO35/AL35</f>
-        <v>0.99318499055751708</v>
+        <v>0.99334920765251666</v>
       </c>
       <c r="AQ35" s="5">
         <v>14849</v>
@@ -6694,14 +6694,14 @@
       </c>
       <c r="AS35" s="3">
         <f t="shared" ref="AS35:AS47" si="40">AT35-AR35</f>
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="AT35" s="5">
-        <v>14858</v>
+        <v>14860</v>
       </c>
       <c r="AU35" s="4">
         <f t="shared" ref="AU35:AU48" si="41">AT35/AQ35</f>
-        <v>1.0006061014209711</v>
+        <v>1.0007407906256314</v>
       </c>
       <c r="AV35" s="5">
         <v>12178</v>
@@ -6711,14 +6711,14 @@
       </c>
       <c r="AX35" s="3">
         <f t="shared" ref="AX35:AX47" si="42">AY35-AW35</f>
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="AY35" s="5">
-        <v>12191</v>
+        <v>12193</v>
       </c>
       <c r="AZ35" s="4">
         <f t="shared" ref="AZ35:AZ48" si="43">AY35/AV35</f>
-        <v>1.0010674987682706</v>
+        <v>1.0012317293480046</v>
       </c>
       <c r="BA35" s="5">
         <v>12308</v>
@@ -6728,14 +6728,14 @@
       </c>
       <c r="BC35" s="3">
         <f t="shared" ref="BC35:BC47" si="44">BD35-BB35</f>
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="BD35" s="5">
-        <v>12248</v>
+        <v>12250</v>
       </c>
       <c r="BE35" s="4">
         <f t="shared" ref="BE35:BE48" si="45">BD35/BA35</f>
-        <v>0.99512512187195323</v>
+        <v>0.99528761780955477</v>
       </c>
       <c r="BF35" s="5">
         <v>15013</v>
@@ -6745,14 +6745,14 @@
       </c>
       <c r="BH35" s="3">
         <f t="shared" ref="BH35:BH47" si="46">BI35-BG35</f>
-        <v>2896</v>
+        <v>2898</v>
       </c>
       <c r="BI35" s="5">
-        <v>14992</v>
+        <v>14994</v>
       </c>
       <c r="BJ35" s="4">
         <f t="shared" ref="BJ35:BJ48" si="47">BI35/BF35</f>
-        <v>0.99860121228268839</v>
+        <v>0.99873443016052754</v>
       </c>
       <c r="BL35" s="9"/>
     </row>
@@ -6771,14 +6771,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="24"/>
-        <v>250151</v>
+        <v>250187</v>
       </c>
       <c r="F36" s="5">
-        <v>887244</v>
+        <v>887280</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="25"/>
-        <v>0.9914780917898689</v>
+        <v>0.99151832109691906</v>
       </c>
       <c r="H36" s="5">
         <v>910737</v>
@@ -6788,14 +6788,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="26"/>
-        <v>242670</v>
+        <v>242700</v>
       </c>
       <c r="K36" s="5">
-        <v>898370</v>
+        <v>898400</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="27"/>
-        <v>0.98642088769864411</v>
+        <v>0.98645382805354342</v>
       </c>
       <c r="M36" s="5">
         <v>1579599</v>
@@ -6805,14 +6805,14 @@
       </c>
       <c r="O36" s="3">
         <f t="shared" si="28"/>
-        <v>490029</v>
+        <v>490090</v>
       </c>
       <c r="P36" s="5">
-        <v>1571218</v>
+        <v>1571279</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="29"/>
-        <v>0.99469422302748989</v>
+        <v>0.99473284042342391</v>
       </c>
       <c r="R36" s="5">
         <v>901122</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="30"/>
-        <v>252256</v>
+        <v>252290</v>
       </c>
       <c r="U36" s="5">
-        <v>897700</v>
+        <v>897734</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="31"/>
-        <v>0.99620251197951004</v>
+        <v>0.99624024271963174</v>
       </c>
       <c r="W36" s="5">
         <v>923866</v>
@@ -6839,14 +6839,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="32"/>
-        <v>177862</v>
+        <v>177904</v>
       </c>
       <c r="Z36" s="5">
-        <v>907091</v>
+        <v>907133</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="33"/>
-        <v>0.98184260487992847</v>
+        <v>0.98188806601823209</v>
       </c>
       <c r="AB36" s="5">
         <v>1592928</v>
@@ -6856,14 +6856,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="34"/>
-        <v>534576</v>
+        <v>534658</v>
       </c>
       <c r="AE36" s="5">
-        <v>1588202</v>
+        <v>1588284</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="35"/>
-        <v>0.99703313646316716</v>
+        <v>0.99708461399385284</v>
       </c>
       <c r="AG36" s="5">
         <v>914936</v>
@@ -6873,14 +6873,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="36"/>
-        <v>259679</v>
+        <v>259730</v>
       </c>
       <c r="AJ36" s="5">
-        <v>912025</v>
+        <v>912076</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="37"/>
-        <v>0.99681835669380159</v>
+        <v>0.99687409829758589</v>
       </c>
       <c r="AL36" s="5">
         <v>934551</v>
@@ -6890,14 +6890,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="38"/>
-        <v>238432</v>
+        <v>238486</v>
       </c>
       <c r="AO36" s="5">
-        <v>922696</v>
+        <v>922750</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="39"/>
-        <v>0.98731476398826812</v>
+        <v>0.98737254574656708</v>
       </c>
       <c r="AQ36" s="5">
         <v>1610673</v>
@@ -6907,14 +6907,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="40"/>
-        <v>455052</v>
+        <v>455168</v>
       </c>
       <c r="AT36" s="5">
-        <v>1612725</v>
+        <v>1612841</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="41"/>
-        <v>1.0012740016129904</v>
+        <v>1.0013460211973504</v>
       </c>
       <c r="AV36" s="5">
         <v>933166</v>
@@ -6924,14 +6924,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="42"/>
-        <v>233944</v>
+        <v>234010</v>
       </c>
       <c r="AY36" s="5">
-        <v>933138</v>
+        <v>933204</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="43"/>
-        <v>0.9999699946204641</v>
+        <v>1.000040721586513</v>
       </c>
       <c r="BA36" s="5">
         <v>952259</v>
@@ -6941,14 +6941,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="44"/>
-        <v>234208</v>
+        <v>234281</v>
       </c>
       <c r="BD36" s="5">
-        <v>945206</v>
+        <v>945279</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="45"/>
-        <v>0.99259340158507292</v>
+        <v>0.99267006140136249</v>
       </c>
       <c r="BF36" s="5">
         <v>1640364</v>
@@ -6958,14 +6958,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="46"/>
-        <v>522693</v>
+        <v>522889</v>
       </c>
       <c r="BI36" s="5">
-        <v>1641729</v>
+        <v>1641925</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="47"/>
-        <v>1.0008321323803742</v>
+        <v>1.0009516180555047</v>
       </c>
       <c r="BL36" s="9"/>
     </row>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="24"/>
-        <v>284536</v>
+        <v>284565</v>
       </c>
       <c r="F37" s="5">
-        <v>700953</v>
+        <v>700982</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="25"/>
-        <v>0.9875442734089046</v>
+        <v>0.98758513033358974</v>
       </c>
       <c r="H37" s="5">
         <v>717455</v>
@@ -7001,14 +7001,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="26"/>
-        <v>273365</v>
+        <v>273398</v>
       </c>
       <c r="K37" s="5">
-        <v>706546</v>
+        <v>706579</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="27"/>
-        <v>0.98479486518318227</v>
+        <v>0.98484086109930236</v>
       </c>
       <c r="M37" s="5">
         <v>885615</v>
@@ -7018,14 +7018,14 @@
       </c>
       <c r="O37" s="3">
         <f t="shared" si="28"/>
-        <v>352300</v>
+        <v>352344</v>
       </c>
       <c r="P37" s="5">
-        <v>879314</v>
+        <v>879358</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="29"/>
-        <v>0.99288517019246514</v>
+        <v>0.99293485318112273</v>
       </c>
       <c r="R37" s="5">
         <v>713906</v>
@@ -7035,14 +7035,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="30"/>
-        <v>285481</v>
+        <v>285514</v>
       </c>
       <c r="U37" s="5">
-        <v>707719</v>
+        <v>707752</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="31"/>
-        <v>0.99133359293800583</v>
+        <v>0.9913798175109888</v>
       </c>
       <c r="W37" s="5">
         <v>721933</v>
@@ -7052,14 +7052,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="32"/>
-        <v>129031</v>
+        <v>129067</v>
       </c>
       <c r="Z37" s="5">
-        <v>709654</v>
+        <v>709690</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="33"/>
-        <v>0.98299149644080541</v>
+        <v>0.98304136256411601</v>
       </c>
       <c r="AB37" s="5">
         <v>896229</v>
@@ -7069,14 +7069,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="34"/>
-        <v>387906</v>
+        <v>387963</v>
       </c>
       <c r="AE37" s="5">
-        <v>884721</v>
+        <v>884778</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="35"/>
-        <v>0.98715953177145577</v>
+        <v>0.98722313158802044</v>
       </c>
       <c r="AG37" s="5">
         <v>721282</v>
@@ -7086,14 +7086,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="36"/>
-        <v>283152</v>
+        <v>283198</v>
       </c>
       <c r="AJ37" s="5">
-        <v>712117</v>
+        <v>712163</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="37"/>
-        <v>0.98729345803721702</v>
+        <v>0.98735723337058179</v>
       </c>
       <c r="AL37" s="5">
         <v>727480</v>
@@ -7103,14 +7103,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="38"/>
-        <v>265597</v>
+        <v>265643</v>
       </c>
       <c r="AO37" s="5">
-        <v>718065</v>
+        <v>718111</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="39"/>
-        <v>0.98705806345191616</v>
+        <v>0.98712129543080218</v>
       </c>
       <c r="AQ37" s="5">
         <v>903787</v>
@@ -7120,14 +7120,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="40"/>
-        <v>338885</v>
+        <v>338968</v>
       </c>
       <c r="AT37" s="5">
-        <v>897259</v>
+        <v>897342</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="41"/>
-        <v>0.99277705919646997</v>
+        <v>0.99286889499406383</v>
       </c>
       <c r="AV37" s="5">
         <v>732294</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="42"/>
-        <v>269856</v>
+        <v>269927</v>
       </c>
       <c r="AY37" s="5">
-        <v>726228</v>
+        <v>726299</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="43"/>
-        <v>0.99171644175699925</v>
+        <v>0.991813397351337</v>
       </c>
       <c r="BA37" s="5">
         <v>740889</v>
@@ -7154,14 +7154,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="44"/>
-        <v>267212</v>
+        <v>267297</v>
       </c>
       <c r="BD37" s="5">
-        <v>731412</v>
+        <v>731497</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="45"/>
-        <v>0.98720861019666917</v>
+        <v>0.98732333723405263</v>
       </c>
       <c r="BF37" s="5">
         <v>918028</v>
@@ -7171,14 +7171,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="46"/>
-        <v>377703</v>
+        <v>377856</v>
       </c>
       <c r="BI37" s="5">
-        <v>910078</v>
+        <v>910231</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="47"/>
-        <v>0.99134013341640992</v>
+        <v>0.99150679499971683</v>
       </c>
       <c r="BL37" s="9"/>
     </row>
@@ -7197,14 +7197,14 @@
       </c>
       <c r="E38" s="3">
         <f t="shared" si="24"/>
-        <v>9274</v>
+        <v>9275</v>
       </c>
       <c r="F38" s="5">
-        <v>24447</v>
+        <v>24448</v>
       </c>
       <c r="G38" s="4">
         <f t="shared" si="25"/>
-        <v>1.0037774584274277</v>
+        <v>1.0038185177581604</v>
       </c>
       <c r="H38" s="5">
         <v>24747</v>
@@ -7214,14 +7214,14 @@
       </c>
       <c r="J38" s="3">
         <f t="shared" si="26"/>
-        <v>8853</v>
+        <v>8855</v>
       </c>
       <c r="K38" s="5">
-        <v>24695</v>
+        <v>24697</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="27"/>
-        <v>0.99789873520022632</v>
+        <v>0.9979795530771407</v>
       </c>
       <c r="M38" s="5">
         <v>37604</v>
@@ -7231,14 +7231,14 @@
       </c>
       <c r="O38" s="3">
         <f t="shared" si="28"/>
-        <v>13788</v>
+        <v>13790</v>
       </c>
       <c r="P38" s="5">
-        <v>37830</v>
+        <v>37832</v>
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="29"/>
-        <v>1.0060099989362834</v>
+        <v>1.0060631847675778</v>
       </c>
       <c r="R38" s="5">
         <v>24596</v>
@@ -7248,14 +7248,14 @@
       </c>
       <c r="T38" s="3">
         <f t="shared" si="30"/>
-        <v>9379</v>
+        <v>9383</v>
       </c>
       <c r="U38" s="5">
-        <v>24780</v>
+        <v>24784</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" si="31"/>
-        <v>1.0074808912018214</v>
+        <v>1.0076435192714261</v>
       </c>
       <c r="W38" s="5">
         <v>25148</v>
@@ -7265,14 +7265,14 @@
       </c>
       <c r="Y38" s="3">
         <f t="shared" si="32"/>
-        <v>6019</v>
+        <v>6022</v>
       </c>
       <c r="Z38" s="5">
-        <v>24971</v>
+        <v>24974</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" si="33"/>
-        <v>0.99296166693176391</v>
+        <v>0.99308096071258156</v>
       </c>
       <c r="AB38" s="5">
         <v>38035</v>
@@ -7282,14 +7282,14 @@
       </c>
       <c r="AD38" s="3">
         <f t="shared" si="34"/>
-        <v>14766</v>
+        <v>14769</v>
       </c>
       <c r="AE38" s="5">
-        <v>38234</v>
+        <v>38237</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" si="35"/>
-        <v>1.0052320231365848</v>
+        <v>1.0053108978572367</v>
       </c>
       <c r="AG38" s="5">
         <v>24962</v>
@@ -7299,14 +7299,14 @@
       </c>
       <c r="AI38" s="3">
         <f t="shared" si="36"/>
-        <v>9211</v>
+        <v>9213</v>
       </c>
       <c r="AJ38" s="5">
-        <v>25182</v>
+        <v>25184</v>
       </c>
       <c r="AK38" s="4">
         <f t="shared" si="37"/>
-        <v>1.008813396362471</v>
+        <v>1.0088935181475844</v>
       </c>
       <c r="AL38" s="5">
         <v>25436</v>
@@ -7316,14 +7316,14 @@
       </c>
       <c r="AN38" s="3">
         <f t="shared" si="38"/>
-        <v>8604</v>
+        <v>8607</v>
       </c>
       <c r="AO38" s="5">
-        <v>25464</v>
+        <v>25467</v>
       </c>
       <c r="AP38" s="4">
         <f t="shared" si="39"/>
-        <v>1.0011008020128951</v>
+        <v>1.0012187450857053</v>
       </c>
       <c r="AQ38" s="5">
         <v>38569</v>
@@ -7333,14 +7333,14 @@
       </c>
       <c r="AS38" s="3">
         <f t="shared" si="40"/>
-        <v>13202</v>
+        <v>13205</v>
       </c>
       <c r="AT38" s="5">
-        <v>38957</v>
+        <v>38960</v>
       </c>
       <c r="AU38" s="4">
         <f t="shared" si="41"/>
-        <v>1.0100598926599083</v>
+        <v>1.0101376753351137</v>
       </c>
       <c r="AV38" s="5">
         <v>25488</v>
@@ -7350,14 +7350,14 @@
       </c>
       <c r="AX38" s="3">
         <f t="shared" si="42"/>
-        <v>8632</v>
+        <v>8635</v>
       </c>
       <c r="AY38" s="5">
-        <v>25660</v>
+        <v>25663</v>
       </c>
       <c r="AZ38" s="4">
         <f t="shared" si="43"/>
-        <v>1.0067482736974263</v>
+        <v>1.0068659761456371</v>
       </c>
       <c r="BA38" s="5">
         <v>25933</v>
@@ -7367,14 +7367,14 @@
       </c>
       <c r="BC38" s="3">
         <f t="shared" si="44"/>
-        <v>8606</v>
+        <v>8610</v>
       </c>
       <c r="BD38" s="5">
-        <v>25938</v>
+        <v>25942</v>
       </c>
       <c r="BE38" s="4">
         <f t="shared" si="45"/>
-        <v>1.0001928045347626</v>
+        <v>1.0003470481625727</v>
       </c>
       <c r="BF38" s="5">
         <v>39379</v>
@@ -7384,14 +7384,14 @@
       </c>
       <c r="BH38" s="3">
         <f t="shared" si="46"/>
-        <v>15246</v>
+        <v>15253</v>
       </c>
       <c r="BI38" s="5">
-        <v>39585</v>
+        <v>39592</v>
       </c>
       <c r="BJ38" s="4">
         <f t="shared" si="47"/>
-        <v>1.0052312146067701</v>
+        <v>1.0054089743264176</v>
       </c>
       <c r="BL38" s="9"/>
     </row>
@@ -7623,14 +7623,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="24"/>
-        <v>112582</v>
+        <v>112597</v>
       </c>
       <c r="F40" s="5">
-        <v>289312</v>
+        <v>289327</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="25"/>
-        <v>0.99097099483469664</v>
+        <v>0.99102237384739744</v>
       </c>
       <c r="H40" s="5">
         <v>293812</v>
@@ -7640,14 +7640,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="26"/>
-        <v>110794</v>
+        <v>110810</v>
       </c>
       <c r="K40" s="5">
-        <v>290908</v>
+        <v>290924</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="27"/>
-        <v>0.99011612868092524</v>
+        <v>0.99017058527221491</v>
       </c>
       <c r="M40" s="5">
         <v>351809</v>
@@ -7657,14 +7657,14 @@
       </c>
       <c r="O40" s="3">
         <f t="shared" si="28"/>
-        <v>138036</v>
+        <v>138060</v>
       </c>
       <c r="P40" s="5">
-        <v>349772</v>
+        <v>349796</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="29"/>
-        <v>0.99420992640893213</v>
+        <v>0.99427814524358382</v>
       </c>
       <c r="R40" s="5">
         <v>293831</v>
@@ -7674,14 +7674,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="30"/>
-        <v>115491</v>
+        <v>115511</v>
       </c>
       <c r="U40" s="5">
-        <v>292895</v>
+        <v>292915</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="31"/>
-        <v>0.99681449540722389</v>
+        <v>0.99688256174467638</v>
       </c>
       <c r="W40" s="5">
         <v>297227</v>
@@ -7691,14 +7691,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="32"/>
-        <v>66796</v>
+        <v>66821</v>
       </c>
       <c r="Z40" s="5">
-        <v>294341</v>
+        <v>294366</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="33"/>
-        <v>0.99029024953991396</v>
+        <v>0.99037436033738524</v>
       </c>
       <c r="AB40" s="5">
         <v>355500</v>
@@ -7708,14 +7708,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="34"/>
-        <v>142952</v>
+        <v>142987</v>
       </c>
       <c r="AE40" s="5">
-        <v>353422</v>
+        <v>353457</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="35"/>
-        <v>0.99415471167369907</v>
+        <v>0.994253164556962</v>
       </c>
       <c r="AG40" s="5">
         <v>298328</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="36"/>
-        <v>116466</v>
+        <v>116496</v>
       </c>
       <c r="AJ40" s="5">
-        <v>296107</v>
+        <v>296137</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="37"/>
-        <v>0.99255517417071149</v>
+        <v>0.9926557346276581</v>
       </c>
       <c r="AL40" s="5">
         <v>299711</v>
@@ -7742,14 +7742,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="38"/>
-        <v>111262</v>
+        <v>111294</v>
       </c>
       <c r="AO40" s="5">
-        <v>297417</v>
+        <v>297449</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="39"/>
-        <v>0.99234595994141017</v>
+        <v>0.99245272946271579</v>
       </c>
       <c r="AQ40" s="5">
         <v>357015</v>
@@ -7759,14 +7759,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="40"/>
-        <v>136631</v>
+        <v>136674</v>
       </c>
       <c r="AT40" s="5">
-        <v>355888</v>
+        <v>355931</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="41"/>
-        <v>0.99684326989062089</v>
+        <v>0.99696371300925735</v>
       </c>
       <c r="AV40" s="5">
         <v>300800</v>
@@ -7776,14 +7776,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="42"/>
-        <v>112779</v>
+        <v>112824</v>
       </c>
       <c r="AY40" s="5">
-        <v>299406</v>
+        <v>299451</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="43"/>
-        <v>0.99536569148936171</v>
+        <v>0.99551529255319149</v>
       </c>
       <c r="BA40" s="5">
         <v>303731</v>
@@ -7793,14 +7793,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="44"/>
-        <v>110814</v>
+        <v>110858</v>
       </c>
       <c r="BD40" s="5">
-        <v>300858</v>
+        <v>300902</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="45"/>
-        <v>0.99054097211018965</v>
+        <v>0.990685837138784</v>
       </c>
       <c r="BF40" s="5">
         <v>361393</v>
@@ -7810,14 +7810,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="46"/>
-        <v>149263</v>
+        <v>149327</v>
       </c>
       <c r="BI40" s="5">
-        <v>359248</v>
+        <v>359312</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="47"/>
-        <v>0.99406463323860728</v>
+        <v>0.99424172576668612</v>
       </c>
       <c r="BL40" s="9"/>
     </row>
@@ -7836,14 +7836,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="24"/>
-        <v>362749</v>
+        <v>362793</v>
       </c>
       <c r="F41" s="5">
-        <v>945063</v>
+        <v>945107</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="25"/>
-        <v>0.99228796902167982</v>
+        <v>0.99233416770963701</v>
       </c>
       <c r="H41" s="5">
         <v>959446</v>
@@ -7853,14 +7853,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="26"/>
-        <v>364300</v>
+        <v>364343</v>
       </c>
       <c r="K41" s="5">
-        <v>948832</v>
+        <v>948875</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="27"/>
-        <v>0.9889373659382602</v>
+        <v>0.98898218346837652</v>
       </c>
       <c r="M41" s="5">
         <v>1062442</v>
@@ -7870,14 +7870,14 @@
       </c>
       <c r="O41" s="3">
         <f t="shared" si="28"/>
-        <v>401898</v>
+        <v>401951</v>
       </c>
       <c r="P41" s="5">
-        <v>1053469</v>
+        <v>1053522</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="29"/>
-        <v>0.99155436249696449</v>
+        <v>0.991604247573044</v>
       </c>
       <c r="R41" s="5">
         <v>959218</v>
@@ -7887,14 +7887,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="30"/>
-        <v>375387</v>
+        <v>375433</v>
       </c>
       <c r="U41" s="5">
-        <v>952158</v>
+        <v>952204</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="31"/>
-        <v>0.99263983786792986</v>
+        <v>0.99268779359853543</v>
       </c>
       <c r="W41" s="5">
         <v>961845</v>
@@ -7904,14 +7904,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="32"/>
-        <v>151794</v>
+        <v>151854</v>
       </c>
       <c r="Z41" s="5">
-        <v>951401</v>
+        <v>951461</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="33"/>
-        <v>0.98914170162552173</v>
+        <v>0.98920408173874164</v>
       </c>
       <c r="AB41" s="5">
         <v>1065577</v>
@@ -7921,14 +7921,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="34"/>
-        <v>434436</v>
+        <v>434508</v>
       </c>
       <c r="AE41" s="5">
-        <v>1056826</v>
+        <v>1056898</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="35"/>
-        <v>0.99178754796697</v>
+        <v>0.99185511699295315</v>
       </c>
       <c r="AG41" s="5">
         <v>963364</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="36"/>
-        <v>374407</v>
+        <v>374468</v>
       </c>
       <c r="AJ41" s="5">
-        <v>957300</v>
+        <v>957361</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="37"/>
-        <v>0.9937053906934451</v>
+        <v>0.99376871047703674</v>
       </c>
       <c r="AL41" s="5">
         <v>968650</v>
@@ -7955,14 +7955,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="38"/>
-        <v>342325</v>
+        <v>342401</v>
       </c>
       <c r="AO41" s="5">
-        <v>959844</v>
+        <v>959920</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="39"/>
-        <v>0.99090899705776081</v>
+        <v>0.9909874567697311</v>
       </c>
       <c r="AQ41" s="5">
         <v>1071657</v>
@@ -7972,14 +7972,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="40"/>
-        <v>363739</v>
+        <v>363839</v>
       </c>
       <c r="AT41" s="5">
-        <v>1064970</v>
+        <v>1065070</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="41"/>
-        <v>0.99376013034021149</v>
+        <v>0.99385344377911966</v>
       </c>
       <c r="AV41" s="5">
         <v>970535</v>
@@ -7989,14 +7989,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="42"/>
-        <v>340642</v>
+        <v>340736</v>
       </c>
       <c r="AY41" s="5">
-        <v>965060</v>
+        <v>965154</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="43"/>
-        <v>0.99435878149680335</v>
+        <v>0.99445563529393577</v>
       </c>
       <c r="BA41" s="5">
         <v>973311</v>
@@ -8006,14 +8006,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="44"/>
-        <v>336460</v>
+        <v>336562</v>
       </c>
       <c r="BD41" s="5">
-        <v>969965</v>
+        <v>970067</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="45"/>
-        <v>0.99656224988724051</v>
+        <v>0.9966670468123755</v>
       </c>
       <c r="BF41" s="5">
         <v>1078355</v>
@@ -8023,14 +8023,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="46"/>
-        <v>404242</v>
+        <v>404362</v>
       </c>
       <c r="BI41" s="5">
-        <v>1075828</v>
+        <v>1075948</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="47"/>
-        <v>0.99765661586397802</v>
+        <v>0.99776789647194108</v>
       </c>
       <c r="BL41" s="9"/>
     </row>
@@ -8049,14 +8049,14 @@
       </c>
       <c r="E42" s="3">
         <f t="shared" si="24"/>
-        <v>8507</v>
+        <v>8509</v>
       </c>
       <c r="F42" s="5">
-        <v>18785</v>
+        <v>18787</v>
       </c>
       <c r="G42" s="4">
         <f t="shared" si="25"/>
-        <v>0.98795624276848637</v>
+        <v>0.9880614284211634</v>
       </c>
       <c r="H42" s="5">
         <v>19101</v>
@@ -8066,14 +8066,14 @@
       </c>
       <c r="J42" s="3">
         <f t="shared" si="26"/>
-        <v>8456</v>
+        <v>8459</v>
       </c>
       <c r="K42" s="5">
-        <v>18928</v>
+        <v>18931</v>
       </c>
       <c r="L42" s="4">
         <f t="shared" si="27"/>
-        <v>0.99094288257159313</v>
+        <v>0.9910999424113921</v>
       </c>
       <c r="M42" s="5">
         <v>21195</v>
@@ -8083,14 +8083,14 @@
       </c>
       <c r="O42" s="3">
         <f t="shared" si="28"/>
-        <v>9350</v>
+        <v>9352</v>
       </c>
       <c r="P42" s="5">
-        <v>21021</v>
+        <v>21023</v>
       </c>
       <c r="Q42" s="4">
         <f t="shared" si="29"/>
-        <v>0.99179051663128093</v>
+        <v>0.99188487850908236</v>
       </c>
       <c r="R42" s="5">
         <v>19210</v>
@@ -8100,14 +8100,14 @@
       </c>
       <c r="T42" s="3">
         <f t="shared" si="30"/>
-        <v>8834</v>
+        <v>8836</v>
       </c>
       <c r="U42" s="5">
-        <v>19080</v>
+        <v>19082</v>
       </c>
       <c r="V42" s="4">
         <f t="shared" si="31"/>
-        <v>0.99323269130661118</v>
+        <v>0.99333680374804789</v>
       </c>
       <c r="W42" s="5">
         <v>19384</v>
@@ -8117,14 +8117,14 @@
       </c>
       <c r="Y42" s="3">
         <f t="shared" si="32"/>
-        <v>4075</v>
+        <v>4078</v>
       </c>
       <c r="Z42" s="5">
-        <v>19100</v>
+        <v>19103</v>
       </c>
       <c r="AA42" s="4">
         <f t="shared" si="33"/>
-        <v>0.98534874122988036</v>
+        <v>0.98550350804787457</v>
       </c>
       <c r="AB42" s="5">
         <v>21463</v>
@@ -8134,14 +8134,14 @@
       </c>
       <c r="AD42" s="3">
         <f t="shared" si="34"/>
-        <v>10264</v>
+        <v>10268</v>
       </c>
       <c r="AE42" s="5">
-        <v>21189</v>
+        <v>21193</v>
       </c>
       <c r="AF42" s="4">
         <f t="shared" si="35"/>
-        <v>0.9872338442901738</v>
+        <v>0.98742021152681358</v>
       </c>
       <c r="AG42" s="5">
         <v>19423</v>
@@ -8151,14 +8151,14 @@
       </c>
       <c r="AI42" s="3">
         <f t="shared" si="36"/>
-        <v>8873</v>
+        <v>8876</v>
       </c>
       <c r="AJ42" s="5">
-        <v>19193</v>
+        <v>19196</v>
       </c>
       <c r="AK42" s="4">
         <f t="shared" si="37"/>
-        <v>0.98815836894403541</v>
+        <v>0.98831282500128714</v>
       </c>
       <c r="AL42" s="5">
         <v>19535</v>
@@ -8168,14 +8168,14 @@
       </c>
       <c r="AN42" s="3">
         <f t="shared" si="38"/>
-        <v>8601</v>
+        <v>8604</v>
       </c>
       <c r="AO42" s="5">
-        <v>19244</v>
+        <v>19247</v>
       </c>
       <c r="AP42" s="4">
         <f t="shared" si="39"/>
-        <v>0.98510366009726136</v>
+        <v>0.98525723061172255</v>
       </c>
       <c r="AQ42" s="5">
         <v>21570</v>
@@ -8185,14 +8185,14 @@
       </c>
       <c r="AS42" s="3">
         <f t="shared" si="40"/>
-        <v>9123</v>
+        <v>9126</v>
       </c>
       <c r="AT42" s="5">
-        <v>21317</v>
+        <v>21320</v>
       </c>
       <c r="AU42" s="4">
         <f t="shared" si="41"/>
-        <v>0.98827074640704682</v>
+        <v>0.98840982846546133</v>
       </c>
       <c r="AV42" s="5">
         <v>19570</v>
@@ -8202,14 +8202,14 @@
       </c>
       <c r="AX42" s="3">
         <f t="shared" si="42"/>
-        <v>8393</v>
+        <v>8396</v>
       </c>
       <c r="AY42" s="5">
-        <v>19331</v>
+        <v>19334</v>
       </c>
       <c r="AZ42" s="4">
         <f t="shared" si="43"/>
-        <v>0.98778742973939704</v>
+        <v>0.9879407256004088</v>
       </c>
       <c r="BA42" s="5">
         <v>19671</v>
@@ -8219,14 +8219,14 @@
       </c>
       <c r="BC42" s="3">
         <f t="shared" si="44"/>
-        <v>8225</v>
+        <v>8231</v>
       </c>
       <c r="BD42" s="5">
-        <v>19433</v>
+        <v>19439</v>
       </c>
       <c r="BE42" s="4">
         <f t="shared" si="45"/>
-        <v>0.98790097097249763</v>
+        <v>0.98820598851100605</v>
       </c>
       <c r="BF42" s="5">
         <v>21792</v>
@@ -8236,14 +8236,14 @@
       </c>
       <c r="BH42" s="3">
         <f t="shared" si="46"/>
-        <v>9807</v>
+        <v>9811</v>
       </c>
       <c r="BI42" s="5">
-        <v>21625</v>
+        <v>21629</v>
       </c>
       <c r="BJ42" s="4">
         <f t="shared" si="47"/>
-        <v>0.99233663729809107</v>
+        <v>0.99252019089574151</v>
       </c>
       <c r="BL42" s="9"/>
     </row>
@@ -8262,14 +8262,14 @@
       </c>
       <c r="E43" s="3">
         <f t="shared" si="24"/>
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="F43" s="5">
-        <v>3670</v>
+        <v>3671</v>
       </c>
       <c r="G43" s="4">
         <f t="shared" si="25"/>
-        <v>1.0002725538293813</v>
+        <v>1.0005451076587626</v>
       </c>
       <c r="H43" s="5">
         <v>3731</v>
@@ -8279,14 +8279,14 @@
       </c>
       <c r="J43" s="3">
         <f t="shared" si="26"/>
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="K43" s="5">
-        <v>3709</v>
+        <v>3710</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" si="27"/>
-        <v>0.9941034575180917</v>
+        <v>0.99437148217636018</v>
       </c>
       <c r="M43" s="5">
         <v>4602</v>
@@ -8296,14 +8296,14 @@
       </c>
       <c r="O43" s="3">
         <f t="shared" si="28"/>
-        <v>2681</v>
+        <v>2682</v>
       </c>
       <c r="P43" s="5">
-        <v>4599</v>
+        <v>4600</v>
       </c>
       <c r="Q43" s="4">
         <f t="shared" si="29"/>
-        <v>0.999348109517601</v>
+        <v>0.99956540634506741</v>
       </c>
       <c r="R43" s="5">
         <v>3744</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="T43" s="3">
         <f t="shared" si="30"/>
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="U43" s="5">
-        <v>3740</v>
+        <v>3741</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" si="31"/>
-        <v>0.99893162393162394</v>
+        <v>0.99919871794871795</v>
       </c>
       <c r="W43" s="5">
         <v>3795</v>
@@ -8330,14 +8330,14 @@
       </c>
       <c r="Y43" s="3">
         <f t="shared" si="32"/>
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="Z43" s="5">
-        <v>3765</v>
+        <v>3766</v>
       </c>
       <c r="AA43" s="4">
         <f t="shared" si="33"/>
-        <v>0.9920948616600791</v>
+        <v>0.99235836627140972</v>
       </c>
       <c r="AB43" s="5">
         <v>4656</v>
@@ -8364,14 +8364,14 @@
       </c>
       <c r="AI43" s="3">
         <f t="shared" si="36"/>
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="AJ43" s="5">
-        <v>3773</v>
+        <v>3774</v>
       </c>
       <c r="AK43" s="4">
         <f t="shared" si="37"/>
-        <v>1.0021248339973439</v>
+        <v>1.0023904382470119</v>
       </c>
       <c r="AL43" s="5">
         <v>3815</v>
@@ -8449,14 +8449,14 @@
       </c>
       <c r="BH43" s="3">
         <f t="shared" si="46"/>
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="BI43" s="5">
-        <v>4820</v>
+        <v>4821</v>
       </c>
       <c r="BJ43" s="4">
         <f t="shared" si="47"/>
-        <v>0.99340478153338829</v>
+        <v>0.99361088211046988</v>
       </c>
       <c r="BL43" s="9"/>
     </row>
@@ -8475,14 +8475,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="24"/>
-        <v>174683</v>
+        <v>174693</v>
       </c>
       <c r="F44" s="5">
-        <v>359893</v>
+        <v>359903</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="25"/>
-        <v>0.98947817002089522</v>
+        <v>0.9895056636973496</v>
       </c>
       <c r="H44" s="5">
         <v>368428</v>
@@ -8492,14 +8492,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="26"/>
-        <v>171105</v>
+        <v>171118</v>
       </c>
       <c r="K44" s="5">
-        <v>362612</v>
+        <v>362625</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="27"/>
-        <v>0.98421401196434577</v>
+        <v>0.98424929701325636</v>
       </c>
       <c r="M44" s="5">
         <v>437654</v>
@@ -8509,14 +8509,14 @@
       </c>
       <c r="O44" s="3">
         <f t="shared" si="28"/>
-        <v>205907</v>
+        <v>205928</v>
       </c>
       <c r="P44" s="5">
-        <v>431448</v>
+        <v>431469</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="29"/>
-        <v>0.98581984855616533</v>
+        <v>0.98586783166611069</v>
       </c>
       <c r="R44" s="5">
         <v>368991</v>
@@ -8526,14 +8526,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="30"/>
-        <v>177536</v>
+        <v>177553</v>
       </c>
       <c r="U44" s="5">
-        <v>364973</v>
+        <v>364990</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="31"/>
-        <v>0.98911084552197748</v>
+        <v>0.98915691710637932</v>
       </c>
       <c r="W44" s="5">
         <v>375659</v>
@@ -8543,14 +8543,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="32"/>
-        <v>79615</v>
+        <v>79637</v>
       </c>
       <c r="Z44" s="5">
-        <v>365114</v>
+        <v>365136</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="33"/>
-        <v>0.97192932952491484</v>
+        <v>0.97198789327555046</v>
       </c>
       <c r="AB44" s="5">
         <v>443838</v>
@@ -8560,14 +8560,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="34"/>
-        <v>217390</v>
+        <v>217419</v>
       </c>
       <c r="AE44" s="5">
-        <v>434552</v>
+        <v>434581</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="35"/>
-        <v>0.97907795186532021</v>
+        <v>0.97914329102059761</v>
       </c>
       <c r="AG44" s="5">
         <v>373881</v>
@@ -8577,14 +8577,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="36"/>
-        <v>174016</v>
+        <v>174039</v>
       </c>
       <c r="AJ44" s="5">
-        <v>367137</v>
+        <v>367160</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="37"/>
-        <v>0.9819621751305897</v>
+        <v>0.98202369203035189</v>
       </c>
       <c r="AL44" s="5">
         <v>377474</v>
@@ -8594,14 +8594,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="38"/>
-        <v>166922</v>
+        <v>166946</v>
       </c>
       <c r="AO44" s="5">
-        <v>370418</v>
+        <v>370442</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="39"/>
-        <v>0.98130732182878821</v>
+        <v>0.98137090236678548</v>
       </c>
       <c r="AQ44" s="5">
         <v>447335</v>
@@ -8611,14 +8611,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="40"/>
-        <v>201655</v>
+        <v>201688</v>
       </c>
       <c r="AT44" s="5">
-        <v>441292</v>
+        <v>441325</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="41"/>
-        <v>0.98649110845339627</v>
+        <v>0.9865648786703477</v>
       </c>
       <c r="AV44" s="5">
         <v>379419</v>
@@ -8628,14 +8628,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="42"/>
-        <v>167029</v>
+        <v>167057</v>
       </c>
       <c r="AY44" s="5">
-        <v>374521</v>
+        <v>374549</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="43"/>
-        <v>0.98709078881131418</v>
+        <v>0.98716458585363409</v>
       </c>
       <c r="BA44" s="5">
         <v>384239</v>
@@ -8645,14 +8645,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="44"/>
-        <v>165794</v>
+        <v>165835</v>
       </c>
       <c r="BD44" s="5">
-        <v>377454</v>
+        <v>377495</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="45"/>
-        <v>0.98234171960680727</v>
+        <v>0.98244842402775356</v>
       </c>
       <c r="BF44" s="5">
         <v>454173</v>
@@ -8662,14 +8662,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="46"/>
-        <v>219017</v>
+        <v>219081</v>
       </c>
       <c r="BI44" s="5">
-        <v>448899</v>
+        <v>448963</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="47"/>
-        <v>0.98838768486898165</v>
+        <v>0.98852860033511458</v>
       </c>
       <c r="BL44" s="9"/>
     </row>
@@ -8688,14 +8688,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="24"/>
-        <v>126107</v>
+        <v>126119</v>
       </c>
       <c r="F45" s="5">
-        <v>262616</v>
+        <v>262628</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="25"/>
-        <v>0.98497498330970434</v>
+        <v>0.98501999084846714</v>
       </c>
       <c r="H45" s="5">
         <v>269495</v>
@@ -8705,14 +8705,14 @@
       </c>
       <c r="J45" s="3">
         <f t="shared" si="26"/>
-        <v>123605</v>
+        <v>123616</v>
       </c>
       <c r="K45" s="5">
-        <v>263957</v>
+        <v>263968</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="27"/>
-        <v>0.97945045362622685</v>
+        <v>0.97949127071003173</v>
       </c>
       <c r="M45" s="5">
         <v>320759</v>
@@ -8722,14 +8722,14 @@
       </c>
       <c r="O45" s="3">
         <f t="shared" si="28"/>
-        <v>152023</v>
+        <v>152040</v>
       </c>
       <c r="P45" s="5">
-        <v>315230</v>
+        <v>315247</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="29"/>
-        <v>0.98276275957962211</v>
+        <v>0.98281575887192563</v>
       </c>
       <c r="R45" s="5">
         <v>267358</v>
@@ -8739,14 +8739,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="30"/>
-        <v>127911</v>
+        <v>127923</v>
       </c>
       <c r="U45" s="5">
-        <v>264061</v>
+        <v>264073</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="31"/>
-        <v>0.9876682201392889</v>
+        <v>0.98771310377845434</v>
       </c>
       <c r="W45" s="5">
         <v>269851</v>
@@ -8756,14 +8756,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="32"/>
-        <v>57028</v>
+        <v>57040</v>
       </c>
       <c r="Z45" s="5">
-        <v>264032</v>
+        <v>264044</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="33"/>
-        <v>0.97843624815175778</v>
+        <v>0.97848071713649387</v>
       </c>
       <c r="AB45" s="5">
         <v>321990</v>
@@ -8773,14 +8773,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="34"/>
-        <v>161775</v>
+        <v>161794</v>
       </c>
       <c r="AE45" s="5">
-        <v>316898</v>
+        <v>316917</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="35"/>
-        <v>0.9841858442808783</v>
+        <v>0.98424485232460635</v>
       </c>
       <c r="AG45" s="5">
         <v>270238</v>
@@ -8790,14 +8790,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="36"/>
-        <v>128148</v>
+        <v>128166</v>
       </c>
       <c r="AJ45" s="5">
-        <v>266739</v>
+        <v>266757</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="37"/>
-        <v>0.98705215402719082</v>
+        <v>0.98711876198018045</v>
       </c>
       <c r="AL45" s="5">
         <v>273027</v>
@@ -8807,14 +8807,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="38"/>
-        <v>124420</v>
+        <v>124438</v>
       </c>
       <c r="AO45" s="5">
-        <v>269555</v>
+        <v>269573</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="39"/>
-        <v>0.98728330897676786</v>
+        <v>0.98734923652239526</v>
       </c>
       <c r="AQ45" s="5">
         <v>326184</v>
@@ -8824,14 +8824,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="40"/>
-        <v>153578</v>
+        <v>153609</v>
       </c>
       <c r="AT45" s="5">
-        <v>323428</v>
+        <v>323459</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="41"/>
-        <v>0.99155078115419515</v>
+        <v>0.99164581953743902</v>
       </c>
       <c r="AV45" s="5">
         <v>274208</v>
@@ -8841,14 +8841,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="42"/>
-        <v>124957</v>
+        <v>124982</v>
       </c>
       <c r="AY45" s="5">
-        <v>272446</v>
+        <v>272471</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="43"/>
-        <v>0.9935742210292916</v>
+        <v>0.99366539269459675</v>
       </c>
       <c r="BA45" s="5">
         <v>277741</v>
@@ -8858,14 +8858,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="44"/>
-        <v>123896</v>
+        <v>123920</v>
       </c>
       <c r="BD45" s="5">
-        <v>274866</v>
+        <v>274890</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="45"/>
-        <v>0.98964862947854293</v>
+        <v>0.98973504091941777</v>
       </c>
       <c r="BF45" s="5">
         <v>331328</v>
@@ -8875,14 +8875,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="46"/>
-        <v>167638</v>
+        <v>167683</v>
       </c>
       <c r="BI45" s="5">
-        <v>329610</v>
+        <v>329655</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="47"/>
-        <v>0.99481480587212667</v>
+        <v>0.99495062294765313</v>
       </c>
       <c r="BL45" s="9"/>
     </row>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="E46" s="3">
         <f t="shared" si="24"/>
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="F46" s="5">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="G46" s="4">
         <f t="shared" si="25"/>
-        <v>1.0202312138728324</v>
+        <v>1.0206440957886045</v>
       </c>
       <c r="H46" s="5">
         <v>2553</v>
@@ -8918,14 +8918,14 @@
       </c>
       <c r="J46" s="3">
         <f t="shared" si="26"/>
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="K46" s="5">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="L46" s="4">
         <f t="shared" si="27"/>
-        <v>0.99334116725421073</v>
+        <v>0.99373286329808064</v>
       </c>
       <c r="M46" s="5">
         <v>7561</v>
@@ -8935,14 +8935,14 @@
       </c>
       <c r="O46" s="3">
         <f t="shared" si="28"/>
-        <v>4821</v>
+        <v>4823</v>
       </c>
       <c r="P46" s="5">
-        <v>7687</v>
+        <v>7689</v>
       </c>
       <c r="Q46" s="4">
         <f t="shared" si="29"/>
-        <v>1.0166644623727019</v>
+        <v>1.0169289776484591</v>
       </c>
       <c r="R46" s="5">
         <v>2328</v>
@@ -8952,14 +8952,14 @@
       </c>
       <c r="T46" s="3">
         <f t="shared" si="30"/>
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="U46" s="5">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="V46" s="4">
         <f t="shared" si="31"/>
-        <v>1.0223367697594501</v>
+        <v>1.0227663230240549</v>
       </c>
       <c r="W46" s="5">
         <v>2515</v>
@@ -8969,14 +8969,14 @@
       </c>
       <c r="Y46" s="3">
         <f t="shared" si="32"/>
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="Z46" s="5">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="AA46" s="4">
         <f t="shared" si="33"/>
-        <v>0.98131212723658057</v>
+        <v>0.98170974155069579</v>
       </c>
       <c r="AB46" s="5">
         <v>7764</v>
@@ -8986,14 +8986,14 @@
       </c>
       <c r="AD46" s="3">
         <f t="shared" si="34"/>
-        <v>5345</v>
+        <v>5348</v>
       </c>
       <c r="AE46" s="5">
-        <v>7911</v>
+        <v>7914</v>
       </c>
       <c r="AF46" s="4">
         <f t="shared" si="35"/>
-        <v>1.0189335394126739</v>
+        <v>1.0193199381761979</v>
       </c>
       <c r="AG46" s="5">
         <v>2401</v>
@@ -9003,14 +9003,14 @@
       </c>
       <c r="AI46" s="3">
         <f t="shared" si="36"/>
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="AJ46" s="5">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="AK46" s="4">
         <f t="shared" si="37"/>
-        <v>1.026655560183257</v>
+        <v>1.0270720533111204</v>
       </c>
       <c r="AL46" s="5">
         <v>2561</v>
@@ -9020,14 +9020,14 @@
       </c>
       <c r="AN46" s="3">
         <f t="shared" si="38"/>
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="AO46" s="5">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="AP46" s="4">
         <f t="shared" si="39"/>
-        <v>1.0003904724716908</v>
+        <v>1.0007809449433815</v>
       </c>
       <c r="AQ46" s="5">
         <v>7981</v>
@@ -9037,14 +9037,14 @@
       </c>
       <c r="AS46" s="3">
         <f t="shared" si="40"/>
-        <v>5061</v>
+        <v>5064</v>
       </c>
       <c r="AT46" s="5">
-        <v>8155</v>
+        <v>8158</v>
       </c>
       <c r="AU46" s="4">
         <f t="shared" si="41"/>
-        <v>1.0218017792256608</v>
+        <v>1.022177671970931</v>
       </c>
       <c r="AV46" s="5">
         <v>2437</v>
@@ -9054,14 +9054,14 @@
       </c>
       <c r="AX46" s="3">
         <f t="shared" si="42"/>
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="AY46" s="5">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AZ46" s="4">
         <f t="shared" si="43"/>
-        <v>1.0229790726302832</v>
+        <v>1.0233894132129668</v>
       </c>
       <c r="BA46" s="5">
         <v>2592</v>
@@ -9071,14 +9071,14 @@
       </c>
       <c r="BC46" s="3">
         <f t="shared" si="44"/>
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="BD46" s="5">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="BE46" s="4">
         <f t="shared" si="45"/>
-        <v>0.99344135802469136</v>
+        <v>0.99382716049382713</v>
       </c>
       <c r="BF46" s="5">
         <v>8179</v>
@@ -9088,14 +9088,14 @@
       </c>
       <c r="BH46" s="3">
         <f t="shared" si="46"/>
-        <v>5462</v>
+        <v>5465</v>
       </c>
       <c r="BI46" s="5">
-        <v>8345</v>
+        <v>8348</v>
       </c>
       <c r="BJ46" s="4">
         <f t="shared" si="47"/>
-        <v>1.0202958796918939</v>
+        <v>1.0206626726983739</v>
       </c>
       <c r="BL46" s="9"/>
     </row>
@@ -9313,10 +9313,10 @@
       <c r="BL47" s="9"/>
     </row>
     <row r="48" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="16"/>
+      <c r="B48" s="17"/>
       <c r="C48" s="7">
         <f>SUM(C10:C47)</f>
         <v>8203132</v>
@@ -9327,15 +9327,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>3105795</v>
+        <v>3106186</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>8120066</v>
+        <v>8120457</v>
       </c>
       <c r="G48" s="6">
         <f t="shared" si="25"/>
-        <v>0.98987386768858532</v>
+        <v>0.98992153240981617</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9347,15 +9347,15 @@
       </c>
       <c r="J48" s="8">
         <f>K48-I48</f>
-        <v>3049951</v>
+        <v>3050349</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>8211937</v>
+        <v>8212335</v>
       </c>
       <c r="L48" s="6">
         <f t="shared" si="27"/>
-        <v>0.98431956829608447</v>
+        <v>0.98436727435960902</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9367,15 +9367,15 @@
       </c>
       <c r="O48" s="8">
         <f>P48-N48</f>
-        <v>5025969</v>
+        <v>5026674</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>12660204</v>
+        <v>12660909</v>
       </c>
       <c r="Q48" s="6">
         <f t="shared" si="29"/>
-        <v>0.9931380444344452</v>
+        <v>0.99319334862396114</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9387,15 +9387,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>3107630</v>
+        <v>3108088</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>8205464</v>
+        <v>8205922</v>
       </c>
       <c r="V48" s="6">
         <f t="shared" si="31"/>
-        <v>0.99299473058811127</v>
+        <v>0.99305015604444247</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9407,15 +9407,15 @@
       </c>
       <c r="Y48" s="8">
         <f>Z48-X48</f>
-        <v>1499223</v>
+        <v>1499784</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>8251850</v>
+        <v>8252411</v>
       </c>
       <c r="AA48" s="6">
         <f t="shared" si="33"/>
-        <v>0.98057389807906459</v>
+        <v>0.98064056215521989</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9427,15 +9427,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>5441885</v>
+        <v>5442897</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>12758186</v>
+        <v>12759198</v>
       </c>
       <c r="AF48" s="6">
         <f t="shared" si="35"/>
-        <v>0.99137074005469472</v>
+        <v>0.99144937718923221</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9447,15 +9447,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>3192742</v>
+        <v>3193410</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8281674</v>
+        <v>8282342</v>
       </c>
       <c r="AK48" s="6">
         <f t="shared" si="37"/>
-        <v>0.99124968087134779</v>
+        <v>0.99132963509157213</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9467,15 +9467,15 @@
       </c>
       <c r="AN48" s="8">
         <f>AO48-AM48</f>
-        <v>3010716</v>
+        <v>3011456</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>8364876</v>
+        <v>8365616</v>
       </c>
       <c r="AP48" s="6">
         <f t="shared" si="39"/>
-        <v>0.98573241652378341</v>
+        <v>0.98581961948868424</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9487,15 +9487,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>4836107</v>
+        <v>4837524</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>12936400</v>
+        <v>12937817</v>
       </c>
       <c r="AU48" s="6">
         <f t="shared" si="41"/>
-        <v>0.99538854501408547</v>
+        <v>0.99549757577753473</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9507,15 +9507,15 @@
       </c>
       <c r="AX48" s="8">
         <f>AY48-AW48</f>
-        <v>3015532</v>
+        <v>3016506</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>8436500</v>
+        <v>8437474</v>
       </c>
       <c r="AZ48" s="6">
         <f t="shared" si="43"/>
-        <v>0.99483356333663631</v>
+        <v>0.99494841758788855</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9527,15 +9527,15 @@
       </c>
       <c r="BC48" s="8">
         <f>BD48-BB48</f>
-        <v>3007169</v>
+        <v>3008277</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>8537337</v>
+        <v>8538445</v>
       </c>
       <c r="BE48" s="6">
         <f t="shared" si="45"/>
-        <v>0.98759304952577276</v>
+        <v>0.98772122217479374</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9547,25 +9547,20 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5484474</v>
+        <v>5486750</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>13154202</v>
+        <v>13156478</v>
       </c>
       <c r="BJ48" s="6">
         <f t="shared" si="47"/>
-        <v>0.9958748369444661</v>
+        <v>0.9960471477489441</v>
       </c>
       <c r="BL48" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="W8:AA8"/>
-    <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A3:B3"/>
@@ -9579,6 +9574,11 @@
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AL8:AP8"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="AB8:AF8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-1-2024-2025.xlsx
+++ b/gstdatabase/GSTR-1-2024-2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3880E656-6457-44DC-8F6D-F1004F1CB3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6526769B-95AB-4F7C-96A5-AA9AC7224CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,10 +183,10 @@
     <t>FINANCIAL YEAR 2024-2025</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -1257,14 +1257,14 @@
       </c>
       <c r="E10" s="3">
         <f>F10-D10</f>
-        <v>43281</v>
+        <v>43283</v>
       </c>
       <c r="F10" s="5">
-        <v>72950</v>
+        <v>72952</v>
       </c>
       <c r="G10" s="4">
         <f>F10/C10</f>
-        <v>1.0005486215882595</v>
+        <v>1.0005760526676726</v>
       </c>
       <c r="H10" s="5">
         <v>74548</v>
@@ -1274,14 +1274,14 @@
       </c>
       <c r="J10" s="3">
         <f>K10-I10</f>
-        <v>41341</v>
+        <v>41344</v>
       </c>
       <c r="K10" s="5">
-        <v>74012</v>
+        <v>74015</v>
       </c>
       <c r="L10" s="4">
         <f>K10/H10</f>
-        <v>0.99281000160970112</v>
+        <v>0.99285024413800504</v>
       </c>
       <c r="M10" s="5">
         <v>129395</v>
@@ -1291,14 +1291,14 @@
       </c>
       <c r="O10" s="3">
         <f>P10-N10</f>
-        <v>81220</v>
+        <v>81227</v>
       </c>
       <c r="P10" s="5">
-        <v>129310</v>
+        <v>129317</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/M10</f>
-        <v>0.99934309671934773</v>
+        <v>0.99939719463657795</v>
       </c>
       <c r="R10" s="5">
         <v>72583</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="T10" s="3">
         <f>U10-S10</f>
-        <v>42535</v>
+        <v>42538</v>
       </c>
       <c r="U10" s="5">
-        <v>72871</v>
+        <v>72874</v>
       </c>
       <c r="V10" s="4">
         <f>U10/R10</f>
-        <v>1.0039678712646212</v>
+        <v>1.004009203256961</v>
       </c>
       <c r="W10" s="5">
         <v>74384</v>
@@ -1325,14 +1325,14 @@
       </c>
       <c r="Y10" s="3">
         <f>Z10-X10</f>
-        <v>15615</v>
+        <v>15619</v>
       </c>
       <c r="Z10" s="5">
-        <v>73572</v>
+        <v>73576</v>
       </c>
       <c r="AA10" s="4">
         <f>Z10/W10</f>
-        <v>0.98908367390836738</v>
+        <v>0.98913744891374489</v>
       </c>
       <c r="AB10" s="5">
         <v>130621</v>
@@ -1342,14 +1342,14 @@
       </c>
       <c r="AD10" s="3">
         <f>AE10-AC10</f>
-        <v>83811</v>
+        <v>83818</v>
       </c>
       <c r="AE10" s="5">
-        <v>130232</v>
+        <v>130239</v>
       </c>
       <c r="AF10" s="4">
         <f>AE10/AB10</f>
-        <v>0.99702191837453391</v>
+        <v>0.99707550853231874</v>
       </c>
       <c r="AG10" s="5">
         <v>72721</v>
@@ -1359,14 +1359,14 @@
       </c>
       <c r="AI10" s="3">
         <f>AJ10-AH10</f>
-        <v>41920</v>
+        <v>41924</v>
       </c>
       <c r="AJ10" s="5">
-        <v>72600</v>
+        <v>72604</v>
       </c>
       <c r="AK10" s="4">
         <f>AJ10/AG10</f>
-        <v>0.99833610648918469</v>
+        <v>0.9983911112333439</v>
       </c>
       <c r="AL10" s="5">
         <v>74187</v>
@@ -1376,14 +1376,14 @@
       </c>
       <c r="AN10" s="3">
         <f>AO10-AM10</f>
-        <v>41513</v>
+        <v>41518</v>
       </c>
       <c r="AO10" s="5">
-        <v>73702</v>
+        <v>73707</v>
       </c>
       <c r="AP10" s="4">
         <f>AO10/AL10</f>
-        <v>0.99346246646986669</v>
+        <v>0.99352986372275465</v>
       </c>
       <c r="AQ10" s="5">
         <v>132270</v>
@@ -1393,14 +1393,14 @@
       </c>
       <c r="AS10" s="3">
         <f>AT10-AR10</f>
-        <v>79357</v>
+        <v>79369</v>
       </c>
       <c r="AT10" s="5">
-        <v>132295</v>
+        <v>132307</v>
       </c>
       <c r="AU10" s="4">
         <f>AT10/AQ10</f>
-        <v>1.0001890073334845</v>
+        <v>1.0002797308535571</v>
       </c>
       <c r="AV10" s="5">
         <v>73561</v>
@@ -1410,14 +1410,14 @@
       </c>
       <c r="AX10" s="3">
         <f>AY10-AW10</f>
-        <v>41204</v>
+        <v>41210</v>
       </c>
       <c r="AY10" s="5">
-        <v>73451</v>
+        <v>73457</v>
       </c>
       <c r="AZ10" s="4">
         <f>AY10/AV10</f>
-        <v>0.99850464240562253</v>
+        <v>0.99858620736531589</v>
       </c>
       <c r="BA10" s="5">
         <v>75582</v>
@@ -1427,14 +1427,14 @@
       </c>
       <c r="BC10" s="3">
         <f>BD10-BB10</f>
-        <v>41440</v>
+        <v>41446</v>
       </c>
       <c r="BD10" s="5">
-        <v>74412</v>
+        <v>74418</v>
       </c>
       <c r="BE10" s="4">
         <f>BD10/BA10</f>
-        <v>0.98452012383900933</v>
+        <v>0.98459950781932204</v>
       </c>
       <c r="BF10" s="5">
         <v>134150</v>
@@ -1444,14 +1444,14 @@
       </c>
       <c r="BH10" s="3">
         <f>BI10-BG10</f>
-        <v>88250</v>
+        <v>88279</v>
       </c>
       <c r="BI10" s="5">
-        <v>133814</v>
+        <v>133843</v>
       </c>
       <c r="BJ10" s="4">
         <f>BI10/BF10</f>
-        <v>0.99749534103615356</v>
+        <v>0.99771151695862836</v>
       </c>
       <c r="BL10" s="9"/>
     </row>
@@ -1470,14 +1470,14 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>14892</v>
+        <v>14896</v>
       </c>
       <c r="F11" s="5">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99189961539287941</v>
+        <v>0.99198556111815384</v>
       </c>
       <c r="H11" s="5">
         <v>47616</v>
@@ -1487,14 +1487,14 @@
       </c>
       <c r="J11" s="3">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>15039</v>
+        <v>15044</v>
       </c>
       <c r="K11" s="5">
-        <v>46973</v>
+        <v>46978</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.98649613575268813</v>
+        <v>0.98660114247311825</v>
       </c>
       <c r="M11" s="5">
         <v>108402</v>
@@ -1504,14 +1504,14 @@
       </c>
       <c r="O11" s="3">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>45252</v>
+        <v>45264</v>
       </c>
       <c r="P11" s="5">
-        <v>108087</v>
+        <v>108099</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.99709414955443632</v>
+        <v>0.99720484861902914</v>
       </c>
       <c r="R11" s="5">
         <v>46539</v>
@@ -1521,14 +1521,14 @@
       </c>
       <c r="T11" s="3">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>15179</v>
+        <v>15187</v>
       </c>
       <c r="U11" s="5">
-        <v>46234</v>
+        <v>46242</v>
       </c>
       <c r="V11" s="4">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99344635681901206</v>
+        <v>0.99361825565654616</v>
       </c>
       <c r="W11" s="5">
         <v>48300</v>
@@ -1538,14 +1538,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8214</v>
+        <v>8226</v>
       </c>
       <c r="Z11" s="5">
-        <v>46919</v>
+        <v>46931</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.971407867494824</v>
+        <v>0.97165631469979297</v>
       </c>
       <c r="AB11" s="5">
         <v>109219</v>
@@ -1555,14 +1555,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>47707</v>
+        <v>47723</v>
       </c>
       <c r="AE11" s="5">
-        <v>108635</v>
+        <v>108651</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.99465294500041201</v>
+        <v>0.99479943965793494</v>
       </c>
       <c r="AG11" s="5">
         <v>46763</v>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>15559</v>
+        <v>15569</v>
       </c>
       <c r="AJ11" s="5">
-        <v>46421</v>
+        <v>46431</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99268652567200566</v>
+        <v>0.99290036995060194</v>
       </c>
       <c r="AL11" s="5">
         <v>48206</v>
@@ -1589,14 +1589,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>14804</v>
+        <v>14815</v>
       </c>
       <c r="AO11" s="5">
-        <v>47148</v>
+        <v>47159</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.9780525245820022</v>
+        <v>0.97828071194457122</v>
       </c>
       <c r="AQ11" s="5">
         <v>110196</v>
@@ -1606,14 +1606,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>40402</v>
+        <v>40421</v>
       </c>
       <c r="AT11" s="5">
-        <v>109938</v>
+        <v>109957</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.99765871719481647</v>
+        <v>0.99783113724636108</v>
       </c>
       <c r="AV11" s="5">
         <v>47206</v>
@@ -1623,14 +1623,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>14192</v>
+        <v>14206</v>
       </c>
       <c r="AY11" s="5">
-        <v>46804</v>
+        <v>46818</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.99148413337287633</v>
+        <v>0.99178070584247768</v>
       </c>
       <c r="BA11" s="5">
         <v>48813</v>
@@ -1640,14 +1640,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>13913</v>
+        <v>13927</v>
       </c>
       <c r="BD11" s="5">
-        <v>47477</v>
+        <v>47491</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.97263024194374448</v>
+        <v>0.97291705078565138</v>
       </c>
       <c r="BF11" s="5">
         <v>111276</v>
@@ -1657,14 +1657,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>48198</v>
+        <v>48227</v>
       </c>
       <c r="BI11" s="5">
-        <v>110886</v>
+        <v>110915</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.99649520112153567</v>
+        <v>0.99675581437147276</v>
       </c>
       <c r="BL11" s="9"/>
     </row>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>38036</v>
+        <v>38042</v>
       </c>
       <c r="F12" s="5">
-        <v>175280</v>
+        <v>175286</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>0.98977361921272111</v>
+        <v>0.98980750009881924</v>
       </c>
       <c r="H12" s="5">
         <v>181172</v>
@@ -1700,14 +1700,14 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="2"/>
-        <v>37812</v>
+        <v>37817</v>
       </c>
       <c r="K12" s="5">
-        <v>177954</v>
+        <v>177959</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="3"/>
-        <v>0.98223787340207092</v>
+        <v>0.98226547148566001</v>
       </c>
       <c r="M12" s="5">
         <v>363483</v>
@@ -1717,14 +1717,14 @@
       </c>
       <c r="O12" s="3">
         <f t="shared" si="4"/>
-        <v>99737</v>
+        <v>99746</v>
       </c>
       <c r="P12" s="5">
-        <v>361059</v>
+        <v>361068</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="5"/>
-        <v>0.99333118742829785</v>
+        <v>0.99335594787101456</v>
       </c>
       <c r="R12" s="5">
         <v>177513</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="T12" s="3">
         <f t="shared" si="6"/>
-        <v>40016</v>
+        <v>40023</v>
       </c>
       <c r="U12" s="5">
-        <v>176826</v>
+        <v>176833</v>
       </c>
       <c r="V12" s="4">
         <f t="shared" si="7"/>
-        <v>0.99612986091159517</v>
+        <v>0.99616929464320925</v>
       </c>
       <c r="W12" s="5">
         <v>182324</v>
@@ -1751,14 +1751,14 @@
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="8"/>
-        <v>28599</v>
+        <v>28606</v>
       </c>
       <c r="Z12" s="5">
-        <v>178671</v>
+        <v>178678</v>
       </c>
       <c r="AA12" s="4">
         <f t="shared" si="9"/>
-        <v>0.97996423948575062</v>
+        <v>0.98000263267589571</v>
       </c>
       <c r="AB12" s="5">
         <v>365690</v>
@@ -1768,14 +1768,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="10"/>
-        <v>109271</v>
+        <v>109286</v>
       </c>
       <c r="AE12" s="5">
-        <v>363203</v>
+        <v>363218</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="11"/>
-        <v>0.99319915775656975</v>
+        <v>0.99324017610544446</v>
       </c>
       <c r="AG12" s="5">
         <v>180670</v>
@@ -1785,14 +1785,14 @@
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="12"/>
-        <v>39872</v>
+        <v>39881</v>
       </c>
       <c r="AJ12" s="5">
-        <v>177033</v>
+        <v>177042</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="13"/>
-        <v>0.97986937510378036</v>
+        <v>0.97991918968284719</v>
       </c>
       <c r="AL12" s="5">
         <v>181581</v>
@@ -1802,14 +1802,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="14"/>
-        <v>37295</v>
+        <v>37308</v>
       </c>
       <c r="AO12" s="5">
-        <v>178311</v>
+        <v>178324</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="15"/>
-        <v>0.98199150792208434</v>
+        <v>0.98206310131566632</v>
       </c>
       <c r="AQ12" s="5">
         <v>363376</v>
@@ -1819,14 +1819,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="16"/>
-        <v>94839</v>
+        <v>94870</v>
       </c>
       <c r="AT12" s="5">
-        <v>362812</v>
+        <v>362843</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="17"/>
-        <v>0.99844788868830081</v>
+        <v>0.99853319977103605</v>
       </c>
       <c r="AV12" s="5">
         <v>179534</v>
@@ -1836,14 +1836,14 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="18"/>
-        <v>36442</v>
+        <v>36455</v>
       </c>
       <c r="AY12" s="5">
-        <v>178180</v>
+        <v>178193</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="19"/>
-        <v>0.99245825303285173</v>
+        <v>0.99253066271569734</v>
       </c>
       <c r="BA12" s="5">
         <v>184469</v>
@@ -1853,14 +1853,14 @@
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="20"/>
-        <v>37185</v>
+        <v>37198</v>
       </c>
       <c r="BD12" s="5">
-        <v>181618</v>
+        <v>181631</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="21"/>
-        <v>0.98454482867039994</v>
+        <v>0.98461530121592244</v>
       </c>
       <c r="BF12" s="5">
         <v>368393</v>
@@ -1870,14 +1870,14 @@
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="22"/>
-        <v>111004</v>
+        <v>111048</v>
       </c>
       <c r="BI12" s="5">
-        <v>367838</v>
+        <v>367882</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="23"/>
-        <v>0.99849345671606138</v>
+        <v>0.99861289438181511</v>
       </c>
       <c r="BL12" s="9"/>
     </row>
@@ -2083,14 +2083,14 @@
       </c>
       <c r="BH13" s="3">
         <f t="shared" si="22"/>
-        <v>7423</v>
+        <v>7425</v>
       </c>
       <c r="BI13" s="5">
-        <v>29134</v>
+        <v>29136</v>
       </c>
       <c r="BJ13" s="4">
         <f t="shared" si="23"/>
-        <v>1.0038245529407712</v>
+        <v>1.0038934638045689</v>
       </c>
       <c r="BL13" s="9"/>
     </row>
@@ -2109,14 +2109,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>38208</v>
+        <v>38213</v>
       </c>
       <c r="F14" s="5">
-        <v>89615</v>
+        <v>89620</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>0.99057125171331295</v>
+        <v>0.99062651987443073</v>
       </c>
       <c r="H14" s="5">
         <v>94129</v>
@@ -2126,14 +2126,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>38644</v>
+        <v>38651</v>
       </c>
       <c r="K14" s="5">
-        <v>91154</v>
+        <v>91161</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.96839443742098608</v>
+        <v>0.96846880345058373</v>
       </c>
       <c r="M14" s="5">
         <v>164995</v>
@@ -2143,14 +2143,14 @@
       </c>
       <c r="O14" s="3">
         <f t="shared" si="4"/>
-        <v>80936</v>
+        <v>80951</v>
       </c>
       <c r="P14" s="5">
-        <v>164105</v>
+        <v>164120</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="5"/>
-        <v>0.99460589714839842</v>
+        <v>0.99469680899421198</v>
       </c>
       <c r="R14" s="5">
         <v>91074</v>
@@ -2160,14 +2160,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="6"/>
-        <v>39508</v>
+        <v>39516</v>
       </c>
       <c r="U14" s="5">
-        <v>90530</v>
+        <v>90538</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="7"/>
-        <v>0.99402683532072822</v>
+        <v>0.99411467597777636</v>
       </c>
       <c r="W14" s="5">
         <v>93800</v>
@@ -2177,14 +2177,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="8"/>
-        <v>18331</v>
+        <v>18340</v>
       </c>
       <c r="Z14" s="5">
-        <v>91114</v>
+        <v>91123</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="9"/>
-        <v>0.97136460554371007</v>
+        <v>0.97146055437100209</v>
       </c>
       <c r="AB14" s="5">
         <v>166352</v>
@@ -2194,14 +2194,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="10"/>
-        <v>85334</v>
+        <v>85349</v>
       </c>
       <c r="AE14" s="5">
-        <v>164817</v>
+        <v>164832</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="11"/>
-        <v>0.99077257862845047</v>
+        <v>0.99086274886986636</v>
       </c>
       <c r="AG14" s="5">
         <v>92175</v>
@@ -2211,14 +2211,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="12"/>
-        <v>39764</v>
+        <v>39775</v>
       </c>
       <c r="AJ14" s="5">
-        <v>91270</v>
+        <v>91281</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="13"/>
-        <v>0.99018171955519396</v>
+        <v>0.99030105777054511</v>
       </c>
       <c r="AL14" s="5">
         <v>94655</v>
@@ -2228,14 +2228,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="14"/>
-        <v>38537</v>
+        <v>38550</v>
       </c>
       <c r="AO14" s="5">
-        <v>92778</v>
+        <v>92791</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="15"/>
-        <v>0.98017009138450162</v>
+        <v>0.98030743225397499</v>
       </c>
       <c r="AQ14" s="5">
         <v>168400</v>
@@ -2245,14 +2245,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="16"/>
-        <v>78398</v>
+        <v>78424</v>
       </c>
       <c r="AT14" s="5">
-        <v>167810</v>
+        <v>167836</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="17"/>
-        <v>0.99649643705463187</v>
+        <v>0.99665083135391919</v>
       </c>
       <c r="AV14" s="5">
         <v>94024</v>
@@ -2262,14 +2262,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="18"/>
-        <v>38176</v>
+        <v>38194</v>
       </c>
       <c r="AY14" s="5">
-        <v>93263</v>
+        <v>93281</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="19"/>
-        <v>0.99190632179018123</v>
+        <v>0.99209776227346214</v>
       </c>
       <c r="BA14" s="5">
         <v>96514</v>
@@ -2279,14 +2279,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="20"/>
-        <v>38280</v>
+        <v>38298</v>
       </c>
       <c r="BD14" s="5">
-        <v>94745</v>
+        <v>94763</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="21"/>
-        <v>0.98167105290424184</v>
+        <v>0.98185755434444744</v>
       </c>
       <c r="BF14" s="5">
         <v>171502</v>
@@ -2296,14 +2296,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="22"/>
-        <v>86369</v>
+        <v>86405</v>
       </c>
       <c r="BI14" s="5">
-        <v>171077</v>
+        <v>171113</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="23"/>
-        <v>0.99752189478839892</v>
+        <v>0.99773180487691104</v>
       </c>
       <c r="BL14" s="9"/>
     </row>
@@ -2322,14 +2322,14 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>75145</v>
+        <v>75148</v>
       </c>
       <c r="F15" s="5">
-        <v>301289</v>
+        <v>301292</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="1"/>
-        <v>0.98928915025726394</v>
+        <v>0.98929900082416411</v>
       </c>
       <c r="H15" s="5">
         <v>309950</v>
@@ -2339,14 +2339,14 @@
       </c>
       <c r="J15" s="3">
         <f t="shared" si="2"/>
-        <v>73616</v>
+        <v>73620</v>
       </c>
       <c r="K15" s="5">
-        <v>306245</v>
+        <v>306249</v>
       </c>
       <c r="L15" s="4">
         <f t="shared" si="3"/>
-        <v>0.98804645910630751</v>
+        <v>0.98805936441361508</v>
       </c>
       <c r="M15" s="5">
         <v>517862</v>
@@ -2356,14 +2356,14 @@
       </c>
       <c r="O15" s="3">
         <f t="shared" si="4"/>
-        <v>147239</v>
+        <v>147249</v>
       </c>
       <c r="P15" s="5">
-        <v>514080</v>
+        <v>514090</v>
       </c>
       <c r="Q15" s="4">
         <f t="shared" si="5"/>
-        <v>0.99269689608428502</v>
+        <v>0.99271620624799661</v>
       </c>
       <c r="R15" s="5">
         <v>307768</v>
@@ -2373,14 +2373,14 @@
       </c>
       <c r="T15" s="3">
         <f t="shared" si="6"/>
-        <v>77313</v>
+        <v>77319</v>
       </c>
       <c r="U15" s="5">
-        <v>305831</v>
+        <v>305837</v>
       </c>
       <c r="V15" s="4">
         <f t="shared" si="7"/>
-        <v>0.99370629825063039</v>
+        <v>0.99372579345481016</v>
       </c>
       <c r="W15" s="5">
         <v>314114</v>
@@ -2390,14 +2390,14 @@
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="8"/>
-        <v>50829</v>
+        <v>50835</v>
       </c>
       <c r="Z15" s="5">
-        <v>308390</v>
+        <v>308396</v>
       </c>
       <c r="AA15" s="4">
         <f t="shared" si="9"/>
-        <v>0.98177731651565991</v>
+        <v>0.98179641786103133</v>
       </c>
       <c r="AB15" s="5">
         <v>523203</v>
@@ -2407,14 +2407,14 @@
       </c>
       <c r="AD15" s="3">
         <f t="shared" si="10"/>
-        <v>165271</v>
+        <v>165277</v>
       </c>
       <c r="AE15" s="5">
-        <v>520361</v>
+        <v>520367</v>
       </c>
       <c r="AF15" s="4">
         <f t="shared" si="11"/>
-        <v>0.99456807395982061</v>
+        <v>0.9945795417839729</v>
       </c>
       <c r="AG15" s="5">
         <v>312916</v>
@@ -2424,14 +2424,14 @@
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="12"/>
-        <v>80000</v>
+        <v>80004</v>
       </c>
       <c r="AJ15" s="5">
-        <v>310193</v>
+        <v>310197</v>
       </c>
       <c r="AK15" s="4">
         <f t="shared" si="13"/>
-        <v>0.99129798412353476</v>
+        <v>0.99131076710682742</v>
       </c>
       <c r="AL15" s="5">
         <v>318942</v>
@@ -2441,14 +2441,14 @@
       </c>
       <c r="AN15" s="3">
         <f t="shared" si="14"/>
-        <v>75116</v>
+        <v>75121</v>
       </c>
       <c r="AO15" s="5">
-        <v>313633</v>
+        <v>313638</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="15"/>
-        <v>0.98335434028757585</v>
+        <v>0.98337001711909999</v>
       </c>
       <c r="AQ15" s="5">
         <v>530087</v>
@@ -2458,14 +2458,14 @@
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="16"/>
-        <v>137448</v>
+        <v>137459</v>
       </c>
       <c r="AT15" s="5">
-        <v>527605</v>
+        <v>527616</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="17"/>
-        <v>0.9953177497278749</v>
+        <v>0.99533850103850874</v>
       </c>
       <c r="AV15" s="5">
         <v>317508</v>
@@ -2475,14 +2475,14 @@
       </c>
       <c r="AX15" s="3">
         <f t="shared" si="18"/>
-        <v>73251</v>
+        <v>73258</v>
       </c>
       <c r="AY15" s="5">
-        <v>315848</v>
+        <v>315855</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="19"/>
-        <v>0.99477178527785126</v>
+        <v>0.99479383196643867</v>
       </c>
       <c r="BA15" s="5">
         <v>324414</v>
@@ -2492,14 +2492,14 @@
       </c>
       <c r="BC15" s="3">
         <f t="shared" si="20"/>
-        <v>73952</v>
+        <v>73959</v>
       </c>
       <c r="BD15" s="5">
-        <v>320472</v>
+        <v>320479</v>
       </c>
       <c r="BE15" s="4">
         <f t="shared" si="21"/>
-        <v>0.98784885979026804</v>
+        <v>0.98787043715745926</v>
       </c>
       <c r="BF15" s="5">
         <v>538701</v>
@@ -2509,14 +2509,14 @@
       </c>
       <c r="BH15" s="3">
         <f t="shared" si="22"/>
-        <v>165642</v>
+        <v>165668</v>
       </c>
       <c r="BI15" s="5">
-        <v>537317</v>
+        <v>537343</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="23"/>
-        <v>0.99743085682038835</v>
+        <v>0.99747912107087233</v>
       </c>
       <c r="BL15" s="9"/>
     </row>
@@ -2535,14 +2535,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>111639</v>
+        <v>111667</v>
       </c>
       <c r="F16" s="5">
-        <v>439401</v>
+        <v>439429</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.9859158405844578</v>
+        <v>0.98597866621192876</v>
       </c>
       <c r="H16" s="5">
         <v>453561</v>
@@ -2552,14 +2552,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>110124</v>
+        <v>110157</v>
       </c>
       <c r="K16" s="5">
-        <v>444353</v>
+        <v>444386</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.97969843086155994</v>
+        <v>0.97977118843992317</v>
       </c>
       <c r="M16" s="5">
         <v>776551</v>
@@ -2569,14 +2569,14 @@
       </c>
       <c r="O16" s="3">
         <f t="shared" si="4"/>
-        <v>203963</v>
+        <v>204027</v>
       </c>
       <c r="P16" s="5">
-        <v>770563</v>
+        <v>770627</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="5"/>
-        <v>0.9922889803760474</v>
+        <v>0.99237139608345104</v>
       </c>
       <c r="R16" s="5">
         <v>446959</v>
@@ -2586,14 +2586,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="6"/>
-        <v>114153</v>
+        <v>114197</v>
       </c>
       <c r="U16" s="5">
-        <v>442949</v>
+        <v>442993</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="7"/>
-        <v>0.99102825986276144</v>
+        <v>0.99112670289668625</v>
       </c>
       <c r="W16" s="5">
         <v>453618</v>
@@ -2603,14 +2603,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="8"/>
-        <v>73622</v>
+        <v>73669</v>
       </c>
       <c r="Z16" s="5">
-        <v>442969</v>
+        <v>443016</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="9"/>
-        <v>0.97652430018209158</v>
+        <v>0.97662791159080986</v>
       </c>
       <c r="AB16" s="5">
         <v>775718</v>
@@ -2620,14 +2620,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="10"/>
-        <v>220911</v>
+        <v>220995</v>
       </c>
       <c r="AE16" s="5">
-        <v>769374</v>
+        <v>769458</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="11"/>
-        <v>0.99182177028249952</v>
+        <v>0.99193005705681703</v>
       </c>
       <c r="AG16" s="5">
         <v>444751</v>
@@ -2637,14 +2637,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="12"/>
-        <v>115381</v>
+        <v>115435</v>
       </c>
       <c r="AJ16" s="5">
-        <v>438758</v>
+        <v>438812</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="13"/>
-        <v>0.98652504435065913</v>
+        <v>0.98664646060379857</v>
       </c>
       <c r="AL16" s="5">
         <v>448369</v>
@@ -2654,14 +2654,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="14"/>
-        <v>107711</v>
+        <v>107772</v>
       </c>
       <c r="AO16" s="5">
-        <v>439976</v>
+        <v>440037</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="15"/>
-        <v>0.98128104306943609</v>
+        <v>0.98141709172578839</v>
       </c>
       <c r="AQ16" s="5">
         <v>770483</v>
@@ -2671,14 +2671,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="16"/>
-        <v>182956</v>
+        <v>183068</v>
       </c>
       <c r="AT16" s="5">
-        <v>768784</v>
+        <v>768896</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="17"/>
-        <v>0.99779488969905894</v>
+        <v>0.99794025306204026</v>
       </c>
       <c r="AV16" s="5">
         <v>444563</v>
@@ -2688,14 +2688,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="18"/>
-        <v>108604</v>
+        <v>108670</v>
       </c>
       <c r="AY16" s="5">
-        <v>443301</v>
+        <v>443367</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="19"/>
-        <v>0.99716125723463267</v>
+        <v>0.99730971763282139</v>
       </c>
       <c r="BA16" s="5">
         <v>453397</v>
@@ -2705,14 +2705,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="20"/>
-        <v>106035</v>
+        <v>106108</v>
       </c>
       <c r="BD16" s="5">
-        <v>447922</v>
+        <v>447995</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="21"/>
-        <v>0.98792449001647564</v>
+        <v>0.9880854968162559</v>
       </c>
       <c r="BF16" s="5">
         <v>780218</v>
@@ -2722,14 +2722,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="22"/>
-        <v>217107</v>
+        <v>217258</v>
       </c>
       <c r="BI16" s="5">
-        <v>778925</v>
+        <v>779076</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="23"/>
-        <v>0.99834277086660395</v>
+        <v>0.9985363065194599</v>
       </c>
       <c r="BL16" s="9"/>
     </row>
@@ -2748,14 +2748,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>91932</v>
+        <v>91945</v>
       </c>
       <c r="F17" s="5">
-        <v>320878</v>
+        <v>320891</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.99047119287577357</v>
+        <v>0.99051132066735603</v>
       </c>
       <c r="H17" s="5">
         <v>333085</v>
@@ -2765,14 +2765,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>90208</v>
+        <v>90223</v>
       </c>
       <c r="K17" s="5">
-        <v>328258</v>
+        <v>328273</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.98550820361169067</v>
+        <v>0.98555323716168541</v>
       </c>
       <c r="M17" s="5">
         <v>731481</v>
@@ -2782,14 +2782,14 @@
       </c>
       <c r="O17" s="3">
         <f t="shared" si="4"/>
-        <v>270422</v>
+        <v>270457</v>
       </c>
       <c r="P17" s="5">
-        <v>728705</v>
+        <v>728740</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="5"/>
-        <v>0.99620495952731514</v>
+        <v>0.99625280766007596</v>
       </c>
       <c r="R17" s="5">
         <v>324758</v>
@@ -2799,14 +2799,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="6"/>
-        <v>95215</v>
+        <v>95233</v>
       </c>
       <c r="U17" s="5">
-        <v>323161</v>
+        <v>323179</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="7"/>
-        <v>0.99508249219418765</v>
+        <v>0.99513791808053997</v>
       </c>
       <c r="W17" s="5">
         <v>336053</v>
@@ -2816,14 +2816,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="8"/>
-        <v>55978</v>
+        <v>55997</v>
       </c>
       <c r="Z17" s="5">
-        <v>326864</v>
+        <v>326883</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="9"/>
-        <v>0.97265609888916327</v>
+        <v>0.97271263758990401</v>
       </c>
       <c r="AB17" s="5">
         <v>736224</v>
@@ -2833,14 +2833,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="10"/>
-        <v>294134</v>
+        <v>294194</v>
       </c>
       <c r="AE17" s="5">
-        <v>730580</v>
+        <v>730640</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="11"/>
-        <v>0.99233385491372195</v>
+        <v>0.99241535184943708</v>
       </c>
       <c r="AG17" s="5">
         <v>328692</v>
@@ -2850,14 +2850,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="12"/>
-        <v>97327</v>
+        <v>97341</v>
       </c>
       <c r="AJ17" s="5">
-        <v>325778</v>
+        <v>325792</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="13"/>
-        <v>0.99113455757974034</v>
+        <v>0.9911771506455892</v>
       </c>
       <c r="AL17" s="5">
         <v>339621</v>
@@ -2867,14 +2867,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="14"/>
-        <v>93175</v>
+        <v>93191</v>
       </c>
       <c r="AO17" s="5">
-        <v>332308</v>
+        <v>332324</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="15"/>
-        <v>0.97846717370245062</v>
+        <v>0.97851428504126658</v>
       </c>
       <c r="AQ17" s="5">
         <v>745574</v>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="16"/>
-        <v>255988</v>
+        <v>256060</v>
       </c>
       <c r="AT17" s="5">
-        <v>741854</v>
+        <v>741926</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="17"/>
-        <v>0.99501055562559848</v>
+        <v>0.99510712551671598</v>
       </c>
       <c r="AV17" s="5">
         <v>334329</v>
@@ -2901,14 +2901,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="18"/>
-        <v>91219</v>
+        <v>91244</v>
       </c>
       <c r="AY17" s="5">
-        <v>332153</v>
+        <v>332178</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="19"/>
-        <v>0.99349144106553722</v>
+        <v>0.99356621770770703</v>
       </c>
       <c r="BA17" s="5">
         <v>348862</v>
@@ -2918,14 +2918,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="20"/>
-        <v>92899</v>
+        <v>92928</v>
       </c>
       <c r="BD17" s="5">
-        <v>339560</v>
+        <v>339589</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="21"/>
-        <v>0.97333616157678393</v>
+        <v>0.97341928900252817</v>
       </c>
       <c r="BF17" s="5">
         <v>757181</v>
@@ -2935,14 +2935,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="22"/>
-        <v>300113</v>
+        <v>300233</v>
       </c>
       <c r="BI17" s="5">
-        <v>755590</v>
+        <v>755710</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="23"/>
-        <v>0.99789878509893937</v>
+        <v>0.99805726768104319</v>
       </c>
       <c r="BL17" s="9"/>
     </row>
@@ -2961,14 +2961,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>482406</v>
+        <v>482442</v>
       </c>
       <c r="F18" s="5">
-        <v>988420</v>
+        <v>988456</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.98995244638700708</v>
+        <v>0.98998850220140777</v>
       </c>
       <c r="H18" s="5">
         <v>1018686</v>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>481918</v>
+        <v>481962</v>
       </c>
       <c r="K18" s="5">
-        <v>1001977</v>
+        <v>1002021</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.98359749716792022</v>
+        <v>0.9836406900654372</v>
       </c>
       <c r="M18" s="5">
         <v>1536859</v>
@@ -2995,14 +2995,14 @@
       </c>
       <c r="O18" s="3">
         <f t="shared" si="4"/>
-        <v>796247</v>
+        <v>796324</v>
       </c>
       <c r="P18" s="5">
-        <v>1524842</v>
+        <v>1524919</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="5"/>
-        <v>0.99218080513566953</v>
+        <v>0.99223090732461472</v>
       </c>
       <c r="R18" s="5">
         <v>1011292</v>
@@ -3012,14 +3012,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="6"/>
-        <v>495081</v>
+        <v>495128</v>
       </c>
       <c r="U18" s="5">
-        <v>1002665</v>
+        <v>1002712</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="7"/>
-        <v>0.99146932834433577</v>
+        <v>0.9915158035463546</v>
       </c>
       <c r="W18" s="5">
         <v>1030498</v>
@@ -3029,14 +3029,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="8"/>
-        <v>182339</v>
+        <v>182394</v>
       </c>
       <c r="Z18" s="5">
-        <v>1008657</v>
+        <v>1008712</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="9"/>
-        <v>0.97880539312060766</v>
+        <v>0.97885876537363492</v>
       </c>
       <c r="AB18" s="5">
         <v>1557879</v>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="10"/>
-        <v>827930</v>
+        <v>828050</v>
       </c>
       <c r="AE18" s="5">
-        <v>1541416</v>
+        <v>1541536</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="11"/>
-        <v>0.98943242703701639</v>
+        <v>0.98950945484212827</v>
       </c>
       <c r="AG18" s="5">
         <v>1025067</v>
@@ -3063,14 +3063,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="12"/>
-        <v>507267</v>
+        <v>507343</v>
       </c>
       <c r="AJ18" s="5">
-        <v>1017791</v>
+        <v>1017867</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="13"/>
-        <v>0.99290192738620986</v>
+        <v>0.99297606888135115</v>
       </c>
       <c r="AL18" s="5">
         <v>1045736</v>
@@ -3080,14 +3080,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="14"/>
-        <v>496061</v>
+        <v>496147</v>
       </c>
       <c r="AO18" s="5">
-        <v>1031850</v>
+        <v>1031936</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="15"/>
-        <v>0.98672131398364404</v>
+        <v>0.98680355271311304</v>
       </c>
       <c r="AQ18" s="5">
         <v>1584961</v>
@@ -3097,14 +3097,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="16"/>
-        <v>771281</v>
+        <v>771437</v>
       </c>
       <c r="AT18" s="5">
-        <v>1574743</v>
+        <v>1574899</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="17"/>
-        <v>0.99355315367381281</v>
+        <v>0.9936515788085637</v>
       </c>
       <c r="AV18" s="5">
         <v>1051416</v>
@@ -3114,14 +3114,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="18"/>
-        <v>501198</v>
+        <v>501303</v>
       </c>
       <c r="AY18" s="5">
-        <v>1044726</v>
+        <v>1044831</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="19"/>
-        <v>0.99363715218334137</v>
+        <v>0.99373701750781807</v>
       </c>
       <c r="BA18" s="5">
         <v>1075670</v>
@@ -3131,14 +3131,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="20"/>
-        <v>500568</v>
+        <v>500689</v>
       </c>
       <c r="BD18" s="5">
-        <v>1060556</v>
+        <v>1060677</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="21"/>
-        <v>0.98594922234514304</v>
+        <v>0.98606171037585877</v>
       </c>
       <c r="BF18" s="5">
         <v>1620029</v>
@@ -3148,14 +3148,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="22"/>
-        <v>863508</v>
+        <v>863757</v>
       </c>
       <c r="BI18" s="5">
-        <v>1609290</v>
+        <v>1609539</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="23"/>
-        <v>0.99337110631970171</v>
+        <v>0.99352480727196857</v>
       </c>
       <c r="BL18" s="9"/>
     </row>
@@ -3174,14 +3174,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>172023</v>
+        <v>172043</v>
       </c>
       <c r="F19" s="5">
-        <v>284801</v>
+        <v>284821</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.9774715562953683</v>
+        <v>0.97754019871981879</v>
       </c>
       <c r="H19" s="5">
         <v>301141</v>
@@ -3191,14 +3191,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>156417</v>
+        <v>156439</v>
       </c>
       <c r="K19" s="5">
-        <v>289006</v>
+        <v>289028</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.95970326192713717</v>
+        <v>0.95977631740613201</v>
       </c>
       <c r="M19" s="5">
         <v>505864</v>
@@ -3208,14 +3208,14 @@
       </c>
       <c r="O19" s="3">
         <f t="shared" si="4"/>
-        <v>245275</v>
+        <v>245315</v>
       </c>
       <c r="P19" s="5">
-        <v>497986</v>
+        <v>498026</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="5"/>
-        <v>0.98442664431546822</v>
+        <v>0.98450571695159173</v>
       </c>
       <c r="R19" s="5">
         <v>293000</v>
@@ -3225,14 +3225,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="6"/>
-        <v>124427</v>
+        <v>124445</v>
       </c>
       <c r="U19" s="5">
-        <v>286437</v>
+        <v>286455</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="7"/>
-        <v>0.97760068259385668</v>
+        <v>0.97766211604095565</v>
       </c>
       <c r="W19" s="5">
         <v>302979</v>
@@ -3242,14 +3242,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="8"/>
-        <v>59481</v>
+        <v>59508</v>
       </c>
       <c r="Z19" s="5">
-        <v>287541</v>
+        <v>287568</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="9"/>
-        <v>0.94904597348331077</v>
+        <v>0.949135088570495</v>
       </c>
       <c r="AB19" s="5">
         <v>514622</v>
@@ -3259,14 +3259,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="10"/>
-        <v>298724</v>
+        <v>298784</v>
       </c>
       <c r="AE19" s="5">
-        <v>498809</v>
+        <v>498869</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="11"/>
-        <v>0.96927259231047258</v>
+        <v>0.96938918273995278</v>
       </c>
       <c r="AG19" s="5">
         <v>295766</v>
@@ -3276,14 +3276,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="12"/>
-        <v>161720</v>
+        <v>161745</v>
       </c>
       <c r="AJ19" s="5">
-        <v>287225</v>
+        <v>287250</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="13"/>
-        <v>0.97112244138947679</v>
+        <v>0.97120696767038805</v>
       </c>
       <c r="AL19" s="5">
         <v>302797</v>
@@ -3293,14 +3293,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="14"/>
-        <v>149798</v>
+        <v>149832</v>
       </c>
       <c r="AO19" s="5">
-        <v>291267</v>
+        <v>291301</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="15"/>
-        <v>0.96192168350412988</v>
+        <v>0.96203396995346713</v>
       </c>
       <c r="AQ19" s="5">
         <v>519490</v>
@@ -3310,14 +3310,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="16"/>
-        <v>279089</v>
+        <v>279168</v>
       </c>
       <c r="AT19" s="5">
-        <v>507879</v>
+        <v>507958</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="17"/>
-        <v>0.97764923290149952</v>
+        <v>0.97780130512618146</v>
       </c>
       <c r="AV19" s="5">
         <v>299668</v>
@@ -3327,14 +3327,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="18"/>
-        <v>153264</v>
+        <v>153306</v>
       </c>
       <c r="AY19" s="5">
-        <v>294552</v>
+        <v>294594</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="19"/>
-        <v>0.98292777340256554</v>
+        <v>0.98306792850754832</v>
       </c>
       <c r="BA19" s="5">
         <v>313772</v>
@@ -3344,14 +3344,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="20"/>
-        <v>155010</v>
+        <v>155067</v>
       </c>
       <c r="BD19" s="5">
-        <v>299583</v>
+        <v>299640</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="21"/>
-        <v>0.95477926647374523</v>
+        <v>0.95496092704256597</v>
       </c>
       <c r="BF19" s="5">
         <v>528004</v>
@@ -3361,14 +3361,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="22"/>
-        <v>333517</v>
+        <v>333665</v>
       </c>
       <c r="BI19" s="5">
-        <v>518272</v>
+        <v>518420</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="23"/>
-        <v>0.98156832145211026</v>
+        <v>0.98184862235892156</v>
       </c>
       <c r="BL19" s="9"/>
     </row>
@@ -3421,14 +3421,14 @@
       </c>
       <c r="O20" s="3">
         <f t="shared" si="4"/>
-        <v>5541</v>
+        <v>5542</v>
       </c>
       <c r="P20" s="5">
-        <v>9849</v>
+        <v>9850</v>
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="5"/>
-        <v>0.99014778325123154</v>
+        <v>0.99024831607519859</v>
       </c>
       <c r="R20" s="5">
         <v>6587</v>
@@ -3506,14 +3506,14 @@
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="14"/>
-        <v>3758</v>
+        <v>3759</v>
       </c>
       <c r="AO20" s="5">
-        <v>6552</v>
+        <v>6553</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" si="15"/>
-        <v>0.98868266183793574</v>
+        <v>0.98883355968009656</v>
       </c>
       <c r="AQ20" s="5">
         <v>9949</v>
@@ -3574,14 +3574,14 @@
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="22"/>
-        <v>6030</v>
+        <v>6033</v>
       </c>
       <c r="BI20" s="5">
-        <v>10086</v>
+        <v>10089</v>
       </c>
       <c r="BJ20" s="4">
         <f t="shared" si="23"/>
-        <v>0.9977247996834504</v>
+        <v>0.99802156494213079</v>
       </c>
       <c r="BL20" s="9"/>
     </row>
@@ -3600,14 +3600,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>8239</v>
+        <v>8244</v>
       </c>
       <c r="F21" s="5">
-        <v>10898</v>
+        <v>10903</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>0.9918995176117229</v>
+        <v>0.99235460089196326</v>
       </c>
       <c r="H21" s="5">
         <v>10970</v>
@@ -3617,14 +3617,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>7957</v>
+        <v>7961</v>
       </c>
       <c r="K21" s="5">
-        <v>10957</v>
+        <v>10961</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>0.99881494986326347</v>
+        <v>0.99917958067456702</v>
       </c>
       <c r="M21" s="5">
         <v>14288</v>
@@ -3634,14 +3634,14 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="4"/>
-        <v>10734</v>
+        <v>10739</v>
       </c>
       <c r="P21" s="5">
-        <v>14563</v>
+        <v>14568</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="5"/>
-        <v>1.0192469204927213</v>
+        <v>1.0195968645016797</v>
       </c>
       <c r="R21" s="5">
         <v>10910</v>
@@ -3651,14 +3651,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="6"/>
-        <v>8286</v>
+        <v>8291</v>
       </c>
       <c r="U21" s="5">
-        <v>11189</v>
+        <v>11194</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="7"/>
-        <v>1.0255728689275894</v>
+        <v>1.0260311640696609</v>
       </c>
       <c r="W21" s="5">
         <v>11256</v>
@@ -3668,14 +3668,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="8"/>
-        <v>3686</v>
+        <v>3692</v>
       </c>
       <c r="Z21" s="5">
-        <v>11325</v>
+        <v>11331</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="9"/>
-        <v>1.0061300639658848</v>
+        <v>1.0066631130063965</v>
       </c>
       <c r="AB21" s="5">
         <v>14831</v>
@@ -3685,14 +3685,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="10"/>
-        <v>11310</v>
+        <v>11319</v>
       </c>
       <c r="AE21" s="5">
-        <v>15013</v>
+        <v>15022</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="11"/>
-        <v>1.0122715932843369</v>
+        <v>1.012878430314881</v>
       </c>
       <c r="AG21" s="5">
         <v>11222</v>
@@ -3702,14 +3702,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="12"/>
-        <v>8200</v>
+        <v>8209</v>
       </c>
       <c r="AJ21" s="5">
-        <v>11360</v>
+        <v>11369</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="13"/>
-        <v>1.0122972732133309</v>
+        <v>1.0130992692924612</v>
       </c>
       <c r="AL21" s="5">
         <v>11337</v>
@@ -3719,14 +3719,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="14"/>
-        <v>8336</v>
+        <v>8346</v>
       </c>
       <c r="AO21" s="5">
-        <v>11538</v>
+        <v>11548</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="15"/>
-        <v>1.0177295580841492</v>
+        <v>1.0186116256505249</v>
       </c>
       <c r="AQ21" s="5">
         <v>15149</v>
@@ -3736,14 +3736,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="16"/>
-        <v>10995</v>
+        <v>11009</v>
       </c>
       <c r="AT21" s="5">
-        <v>15411</v>
+        <v>15425</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="17"/>
-        <v>1.0172948709485774</v>
+        <v>1.0182190243580433</v>
       </c>
       <c r="AV21" s="5">
         <v>11422</v>
@@ -3753,14 +3753,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="18"/>
-        <v>8422</v>
+        <v>8434</v>
       </c>
       <c r="AY21" s="5">
-        <v>11704</v>
+        <v>11716</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="19"/>
-        <v>1.0246891962878655</v>
+        <v>1.0257398003852216</v>
       </c>
       <c r="BA21" s="5">
         <v>11689</v>
@@ -3770,14 +3770,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="20"/>
-        <v>8383</v>
+        <v>8395</v>
       </c>
       <c r="BD21" s="5">
-        <v>11860</v>
+        <v>11872</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="21"/>
-        <v>1.014629138506288</v>
+        <v>1.0156557447172556</v>
       </c>
       <c r="BF21" s="5">
         <v>15725</v>
@@ -3787,14 +3787,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="22"/>
-        <v>11899</v>
+        <v>11924</v>
       </c>
       <c r="BI21" s="5">
-        <v>15837</v>
+        <v>15862</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="23"/>
-        <v>1.0071224165341812</v>
+        <v>1.0087122416534182</v>
       </c>
       <c r="BL21" s="9"/>
     </row>
@@ -3813,14 +3813,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>4620</v>
+        <v>4623</v>
       </c>
       <c r="F22" s="5">
-        <v>6692</v>
+        <v>6695</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>0.99052693901716993</v>
+        <v>0.99097098875074008</v>
       </c>
       <c r="H22" s="5">
         <v>6770</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>4636</v>
+        <v>4639</v>
       </c>
       <c r="K22" s="5">
-        <v>6773</v>
+        <v>6776</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>1.0004431314623339</v>
+        <v>1.0008862629246678</v>
       </c>
       <c r="M22" s="5">
         <v>8074</v>
@@ -3847,14 +3847,14 @@
       </c>
       <c r="O22" s="3">
         <f t="shared" si="4"/>
-        <v>5526</v>
+        <v>5531</v>
       </c>
       <c r="P22" s="5">
-        <v>8093</v>
+        <v>8098</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="5"/>
-        <v>1.0023532325984643</v>
+        <v>1.0029725043349023</v>
       </c>
       <c r="R22" s="5">
         <v>6748</v>
@@ -3864,14 +3864,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="6"/>
-        <v>4626</v>
+        <v>4630</v>
       </c>
       <c r="U22" s="5">
-        <v>6793</v>
+        <v>6797</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="7"/>
-        <v>1.0066686425607587</v>
+        <v>1.0072614107883817</v>
       </c>
       <c r="W22" s="5">
         <v>6876</v>
@@ -3881,14 +3881,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="8"/>
-        <v>1684</v>
+        <v>1687</v>
       </c>
       <c r="Z22" s="5">
-        <v>6850</v>
+        <v>6853</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="9"/>
-        <v>0.9962187318208261</v>
+        <v>0.99665503199534611</v>
       </c>
       <c r="AB22" s="5">
         <v>8219</v>
@@ -3898,14 +3898,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="10"/>
-        <v>5742</v>
+        <v>5748</v>
       </c>
       <c r="AE22" s="5">
-        <v>8246</v>
+        <v>8252</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="11"/>
-        <v>1.0032850711765422</v>
+        <v>1.0040150869935516</v>
       </c>
       <c r="AG22" s="5">
         <v>6901</v>
@@ -3915,14 +3915,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="12"/>
-        <v>4679</v>
+        <v>4682</v>
       </c>
       <c r="AJ22" s="5">
-        <v>6915</v>
+        <v>6918</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="13"/>
-        <v>1.0020286914939864</v>
+        <v>1.0024634110998405</v>
       </c>
       <c r="AL22" s="5">
         <v>6948</v>
@@ -3932,14 +3932,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="14"/>
-        <v>4651</v>
+        <v>4654</v>
       </c>
       <c r="AO22" s="5">
-        <v>6957</v>
+        <v>6960</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="15"/>
-        <v>1.0012953367875648</v>
+        <v>1.0017271157167531</v>
       </c>
       <c r="AQ22" s="5">
         <v>8297</v>
@@ -3949,14 +3949,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="16"/>
-        <v>5579</v>
+        <v>5585</v>
       </c>
       <c r="AT22" s="5">
-        <v>8317</v>
+        <v>8323</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="17"/>
-        <v>1.0024105098228275</v>
+        <v>1.0031336627696759</v>
       </c>
       <c r="AV22" s="5">
         <v>6958</v>
@@ -3966,14 +3966,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="18"/>
-        <v>4675</v>
+        <v>4681</v>
       </c>
       <c r="AY22" s="5">
-        <v>6993</v>
+        <v>6999</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="19"/>
-        <v>1.0050301810865192</v>
+        <v>1.0058924978442081</v>
       </c>
       <c r="BA22" s="5">
         <v>7049</v>
@@ -3983,14 +3983,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="20"/>
-        <v>4656</v>
+        <v>4664</v>
       </c>
       <c r="BD22" s="5">
-        <v>7051</v>
+        <v>7059</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="21"/>
-        <v>1.0002837281883956</v>
+        <v>1.0014186409419776</v>
       </c>
       <c r="BF22" s="5">
         <v>8436</v>
@@ -4000,14 +4000,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="22"/>
-        <v>5770</v>
+        <v>5782</v>
       </c>
       <c r="BI22" s="5">
-        <v>8426</v>
+        <v>8438</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="23"/>
-        <v>0.99881460407776201</v>
+        <v>1.0002370791844477</v>
       </c>
       <c r="BL22" s="9"/>
     </row>
@@ -4026,14 +4026,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="F23" s="5">
-        <v>8687</v>
+        <v>8691</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.98626248864668487</v>
+        <v>0.98671662125340598</v>
       </c>
       <c r="H23" s="5">
         <v>8878</v>
@@ -4043,14 +4043,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>6327</v>
+        <v>6331</v>
       </c>
       <c r="K23" s="5">
-        <v>8803</v>
+        <v>8807</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.99155215138544717</v>
+        <v>0.99200270331155671</v>
       </c>
       <c r="M23" s="5">
         <v>11255</v>
@@ -4060,14 +4060,14 @@
       </c>
       <c r="O23" s="3">
         <f t="shared" si="4"/>
-        <v>7994</v>
+        <v>8001</v>
       </c>
       <c r="P23" s="5">
-        <v>11233</v>
+        <v>11240</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="5"/>
-        <v>0.99804531319413592</v>
+        <v>0.99866725899600173</v>
       </c>
       <c r="R23" s="5">
         <v>8944</v>
@@ -4077,14 +4077,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="6"/>
-        <v>6236</v>
+        <v>6241</v>
       </c>
       <c r="U23" s="5">
-        <v>8928</v>
+        <v>8933</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="7"/>
-        <v>0.99821109123434704</v>
+        <v>0.99877012522361364</v>
       </c>
       <c r="W23" s="5">
         <v>10422</v>
@@ -4094,14 +4094,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="8"/>
-        <v>2962</v>
+        <v>2967</v>
       </c>
       <c r="Z23" s="5">
-        <v>9039</v>
+        <v>9044</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="9"/>
-        <v>0.86729994242947606</v>
+        <v>0.86777969679524081</v>
       </c>
       <c r="AB23" s="5">
         <v>11673</v>
@@ -4111,14 +4111,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="10"/>
-        <v>8270</v>
+        <v>8277</v>
       </c>
       <c r="AE23" s="5">
-        <v>11436</v>
+        <v>11443</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="11"/>
-        <v>0.9796967360575688</v>
+        <v>0.98029641052000338</v>
       </c>
       <c r="AG23" s="5">
         <v>9370</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="12"/>
-        <v>6384</v>
+        <v>6389</v>
       </c>
       <c r="AJ23" s="5">
-        <v>9014</v>
+        <v>9019</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="13"/>
-        <v>0.96200640341515475</v>
+        <v>0.96254002134471717</v>
       </c>
       <c r="AL23" s="5">
         <v>9238</v>
@@ -4145,14 +4145,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="14"/>
-        <v>6436</v>
+        <v>6441</v>
       </c>
       <c r="AO23" s="5">
-        <v>9055</v>
+        <v>9060</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="15"/>
-        <v>0.98019051742801477</v>
+        <v>0.98073176012123842</v>
       </c>
       <c r="AQ23" s="5">
         <v>11727</v>
@@ -4162,14 +4162,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="16"/>
-        <v>8074</v>
+        <v>8082</v>
       </c>
       <c r="AT23" s="5">
-        <v>11554</v>
+        <v>11562</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="17"/>
-        <v>0.98524771893920016</v>
+        <v>0.98592990534663594</v>
       </c>
       <c r="AV23" s="5">
         <v>9359</v>
@@ -4179,14 +4179,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="18"/>
-        <v>6490</v>
+        <v>6496</v>
       </c>
       <c r="AY23" s="5">
-        <v>9172</v>
+        <v>9178</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="19"/>
-        <v>0.9800192328240197</v>
+        <v>0.98066032695800831</v>
       </c>
       <c r="BA23" s="5">
         <v>9570</v>
@@ -4196,14 +4196,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="20"/>
-        <v>6427</v>
+        <v>6435</v>
       </c>
       <c r="BD23" s="5">
-        <v>9224</v>
+        <v>9232</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="21"/>
-        <v>0.96384535005224659</v>
+        <v>0.96468129571577843</v>
       </c>
       <c r="BF23" s="5">
         <v>11968</v>
@@ -4213,14 +4213,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="22"/>
-        <v>8597</v>
+        <v>8612</v>
       </c>
       <c r="BI23" s="5">
-        <v>11747</v>
+        <v>11762</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="23"/>
-        <v>0.98153409090909094</v>
+        <v>0.98278743315508021</v>
       </c>
       <c r="BL23" s="9"/>
     </row>
@@ -4239,14 +4239,14 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="0"/>
-        <v>4837</v>
+        <v>4838</v>
       </c>
       <c r="F24" s="5">
-        <v>6190</v>
+        <v>6191</v>
       </c>
       <c r="G24" s="4">
         <f t="shared" si="1"/>
-        <v>0.99039999999999995</v>
+        <v>0.99056</v>
       </c>
       <c r="H24" s="5">
         <v>6322</v>
@@ -4256,14 +4256,14 @@
       </c>
       <c r="J24" s="3">
         <f t="shared" si="2"/>
-        <v>4875</v>
+        <v>4876</v>
       </c>
       <c r="K24" s="5">
-        <v>6239</v>
+        <v>6240</v>
       </c>
       <c r="L24" s="4">
         <f t="shared" si="3"/>
-        <v>0.9868712432774438</v>
+        <v>0.98702942106928182</v>
       </c>
       <c r="M24" s="5">
         <v>7266</v>
@@ -4273,14 +4273,14 @@
       </c>
       <c r="O24" s="3">
         <f t="shared" si="4"/>
-        <v>5674</v>
+        <v>5675</v>
       </c>
       <c r="P24" s="5">
-        <v>7168</v>
+        <v>7169</v>
       </c>
       <c r="Q24" s="4">
         <f t="shared" si="5"/>
-        <v>0.98651252408477841</v>
+        <v>0.98665015139003576</v>
       </c>
       <c r="R24" s="5">
         <v>6403</v>
@@ -4290,14 +4290,14 @@
       </c>
       <c r="T24" s="3">
         <f t="shared" si="6"/>
-        <v>4999</v>
+        <v>5001</v>
       </c>
       <c r="U24" s="5">
-        <v>6309</v>
+        <v>6311</v>
       </c>
       <c r="V24" s="4">
         <f t="shared" si="7"/>
-        <v>0.98531938153990317</v>
+        <v>0.98563173512416058</v>
       </c>
       <c r="W24" s="5">
         <v>6540</v>
@@ -4307,14 +4307,14 @@
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="8"/>
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="Z24" s="5">
-        <v>6407</v>
+        <v>6410</v>
       </c>
       <c r="AA24" s="4">
         <f t="shared" si="9"/>
-        <v>0.97966360856269108</v>
+        <v>0.98012232415902145</v>
       </c>
       <c r="AB24" s="5">
         <v>7473</v>
@@ -4324,14 +4324,14 @@
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="10"/>
-        <v>5851</v>
+        <v>5854</v>
       </c>
       <c r="AE24" s="5">
-        <v>7385</v>
+        <v>7388</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="11"/>
-        <v>0.98822427405325841</v>
+        <v>0.98862571925598819</v>
       </c>
       <c r="AG24" s="5">
         <v>6660</v>
@@ -4341,14 +4341,14 @@
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="12"/>
-        <v>5220</v>
+        <v>5223</v>
       </c>
       <c r="AJ24" s="5">
-        <v>6594</v>
+        <v>6597</v>
       </c>
       <c r="AK24" s="4">
         <f t="shared" si="13"/>
-        <v>0.99009009009009008</v>
+        <v>0.99054054054054053</v>
       </c>
       <c r="AL24" s="5">
         <v>6723</v>
@@ -4358,14 +4358,14 @@
       </c>
       <c r="AN24" s="3">
         <f t="shared" si="14"/>
-        <v>5005</v>
+        <v>5008</v>
       </c>
       <c r="AO24" s="5">
-        <v>6641</v>
+        <v>6644</v>
       </c>
       <c r="AP24" s="4">
         <f t="shared" si="15"/>
-        <v>0.987803064108285</v>
+        <v>0.98824929347017698</v>
       </c>
       <c r="AQ24" s="5">
         <v>7657</v>
@@ -4375,14 +4375,14 @@
       </c>
       <c r="AS24" s="3">
         <f t="shared" si="16"/>
-        <v>5941</v>
+        <v>5944</v>
       </c>
       <c r="AT24" s="5">
-        <v>7571</v>
+        <v>7574</v>
       </c>
       <c r="AU24" s="4">
         <f t="shared" si="17"/>
-        <v>0.98876844717252188</v>
+        <v>0.9891602455269688</v>
       </c>
       <c r="AV24" s="5">
         <v>6786</v>
@@ -4392,14 +4392,14 @@
       </c>
       <c r="AX24" s="3">
         <f t="shared" si="18"/>
-        <v>5259</v>
+        <v>5262</v>
       </c>
       <c r="AY24" s="5">
-        <v>6747</v>
+        <v>6750</v>
       </c>
       <c r="AZ24" s="4">
         <f t="shared" si="19"/>
-        <v>0.99425287356321834</v>
+        <v>0.99469496021220161</v>
       </c>
       <c r="BA24" s="5">
         <v>7025</v>
@@ -4409,14 +4409,14 @@
       </c>
       <c r="BC24" s="3">
         <f t="shared" si="20"/>
-        <v>5302</v>
+        <v>5306</v>
       </c>
       <c r="BD24" s="5">
-        <v>6806</v>
+        <v>6810</v>
       </c>
       <c r="BE24" s="4">
         <f t="shared" si="21"/>
-        <v>0.96882562277580075</v>
+        <v>0.96939501779359427</v>
       </c>
       <c r="BF24" s="5">
         <v>7878</v>
@@ -4426,14 +4426,14 @@
       </c>
       <c r="BH24" s="3">
         <f t="shared" si="22"/>
-        <v>6239</v>
+        <v>6246</v>
       </c>
       <c r="BI24" s="5">
-        <v>7755</v>
+        <v>7762</v>
       </c>
       <c r="BJ24" s="4">
         <f t="shared" si="23"/>
-        <v>0.98438690022848441</v>
+        <v>0.98527545062198529</v>
       </c>
       <c r="BL24" s="9"/>
     </row>
@@ -4452,14 +4452,14 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>11740</v>
+        <v>11745</v>
       </c>
       <c r="F25" s="5">
-        <v>20217</v>
+        <v>20222</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>0.96602637614678899</v>
+        <v>0.96626529051987764</v>
       </c>
       <c r="H25" s="5">
         <v>20519</v>
@@ -4469,14 +4469,14 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>11471</v>
+        <v>11476</v>
       </c>
       <c r="K25" s="5">
-        <v>20348</v>
+        <v>20353</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="3"/>
-        <v>0.99166626053901263</v>
+        <v>0.99190993713143916</v>
       </c>
       <c r="M25" s="5">
         <v>27924</v>
@@ -4486,14 +4486,14 @@
       </c>
       <c r="O25" s="3">
         <f t="shared" si="4"/>
-        <v>16477</v>
+        <v>16486</v>
       </c>
       <c r="P25" s="5">
-        <v>27924</v>
+        <v>27933</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.0003223033949291</v>
       </c>
       <c r="R25" s="5">
         <v>20481</v>
@@ -4503,14 +4503,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="6"/>
-        <v>11658</v>
+        <v>11666</v>
       </c>
       <c r="U25" s="5">
-        <v>20493</v>
+        <v>20501</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="7"/>
-        <v>1.0005859088911675</v>
+        <v>1.0009765148186123</v>
       </c>
       <c r="W25" s="5">
         <v>20934</v>
@@ -4520,14 +4520,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="8"/>
-        <v>4217</v>
+        <v>4225</v>
       </c>
       <c r="Z25" s="5">
-        <v>20616</v>
+        <v>20624</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="9"/>
-        <v>0.98480940097449121</v>
+        <v>0.98519155440909523</v>
       </c>
       <c r="AB25" s="5">
         <v>28211</v>
@@ -4537,14 +4537,14 @@
       </c>
       <c r="AD25" s="3">
         <f t="shared" si="10"/>
-        <v>18108</v>
+        <v>18121</v>
       </c>
       <c r="AE25" s="5">
-        <v>28239</v>
+        <v>28252</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="11"/>
-        <v>1.0009925206479742</v>
+        <v>1.0014533338059621</v>
       </c>
       <c r="AG25" s="5">
         <v>20778</v>
@@ -4554,14 +4554,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="12"/>
-        <v>11781</v>
+        <v>11791</v>
       </c>
       <c r="AJ25" s="5">
-        <v>20729</v>
+        <v>20739</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="13"/>
-        <v>0.99764173645201659</v>
+        <v>0.99812301472711518</v>
       </c>
       <c r="AL25" s="5">
         <v>21081</v>
@@ -4571,14 +4571,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="14"/>
-        <v>11852</v>
+        <v>11861</v>
       </c>
       <c r="AO25" s="5">
-        <v>20911</v>
+        <v>20920</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="15"/>
-        <v>0.99193586641999909</v>
+        <v>0.99236279113894033</v>
       </c>
       <c r="AQ25" s="5">
         <v>28478</v>
@@ -4588,14 +4588,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="16"/>
-        <v>16488</v>
+        <v>16501</v>
       </c>
       <c r="AT25" s="5">
-        <v>28503</v>
+        <v>28516</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="17"/>
-        <v>1.000877870636983</v>
+        <v>1.0013343633682141</v>
       </c>
       <c r="AV25" s="5">
         <v>21086</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="18"/>
-        <v>12092</v>
+        <v>12100</v>
       </c>
       <c r="AY25" s="5">
-        <v>21058</v>
+        <v>21066</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="19"/>
-        <v>0.99867210471402823</v>
+        <v>0.99905150336716309</v>
       </c>
       <c r="BA25" s="5">
         <v>21405</v>
@@ -4622,14 +4622,14 @@
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="20"/>
-        <v>12034</v>
+        <v>12044</v>
       </c>
       <c r="BD25" s="5">
-        <v>21244</v>
+        <v>21254</v>
       </c>
       <c r="BE25" s="4">
         <f t="shared" si="21"/>
-        <v>0.99247839289885542</v>
+        <v>0.99294557346414392</v>
       </c>
       <c r="BF25" s="5">
         <v>28924</v>
@@ -4639,14 +4639,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="22"/>
-        <v>17892</v>
+        <v>17910</v>
       </c>
       <c r="BI25" s="5">
-        <v>28862</v>
+        <v>28880</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="23"/>
-        <v>0.99785645138984924</v>
+        <v>0.99847877195408652</v>
       </c>
       <c r="BL25" s="9"/>
     </row>
@@ -4665,14 +4665,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>9666</v>
+        <v>9675</v>
       </c>
       <c r="F26" s="5">
-        <v>14037</v>
+        <v>14046</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.99680443118875162</v>
+        <v>0.99744354495100129</v>
       </c>
       <c r="H26" s="5">
         <v>14494</v>
@@ -4682,14 +4682,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>9755</v>
+        <v>9766</v>
       </c>
       <c r="K26" s="5">
-        <v>14321</v>
+        <v>14332</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>0.98806402649372149</v>
+        <v>0.98882296122533464</v>
       </c>
       <c r="M26" s="5">
         <v>27473</v>
@@ -4699,14 +4699,14 @@
       </c>
       <c r="O26" s="3">
         <f t="shared" si="4"/>
-        <v>19030</v>
+        <v>19047</v>
       </c>
       <c r="P26" s="5">
-        <v>27439</v>
+        <v>27456</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="5"/>
-        <v>0.99876242128635384</v>
+        <v>0.99938121064317698</v>
       </c>
       <c r="R26" s="5">
         <v>14274</v>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="6"/>
-        <v>10011</v>
+        <v>10020</v>
       </c>
       <c r="U26" s="5">
-        <v>14217</v>
+        <v>14226</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="7"/>
-        <v>0.9960067255149222</v>
+        <v>0.99663724253888186</v>
       </c>
       <c r="W26" s="5">
         <v>14651</v>
@@ -4733,14 +4733,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="8"/>
-        <v>3129</v>
+        <v>3137</v>
       </c>
       <c r="Z26" s="5">
-        <v>14442</v>
+        <v>14450</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="9"/>
-        <v>0.98573476213227762</v>
+        <v>0.98628079994539619</v>
       </c>
       <c r="AB26" s="5">
         <v>28023</v>
@@ -4750,14 +4750,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="10"/>
-        <v>20303</v>
+        <v>20320</v>
       </c>
       <c r="AE26" s="5">
-        <v>27724</v>
+        <v>27741</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="11"/>
-        <v>0.98933019305570424</v>
+        <v>0.98993683759768758</v>
       </c>
       <c r="AG26" s="5">
         <v>14346</v>
@@ -4767,14 +4767,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="12"/>
-        <v>9770</v>
+        <v>9777</v>
       </c>
       <c r="AJ26" s="5">
-        <v>14252</v>
+        <v>14259</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="13"/>
-        <v>0.99344765091314657</v>
+        <v>0.99393559180259305</v>
       </c>
       <c r="AL26" s="5">
         <v>14687</v>
@@ -4784,14 +4784,14 @@
       </c>
       <c r="AN26" s="3">
         <f t="shared" si="14"/>
-        <v>9454</v>
+        <v>9462</v>
       </c>
       <c r="AO26" s="5">
-        <v>14427</v>
+        <v>14435</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="15"/>
-        <v>0.98229726969428743</v>
+        <v>0.98284196908830934</v>
       </c>
       <c r="AQ26" s="5">
         <v>27948</v>
@@ -4801,14 +4801,14 @@
       </c>
       <c r="AS26" s="3">
         <f t="shared" si="16"/>
-        <v>18806</v>
+        <v>18823</v>
       </c>
       <c r="AT26" s="5">
-        <v>27845</v>
+        <v>27862</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="17"/>
-        <v>0.99631458422785169</v>
+        <v>0.99692285673393444</v>
       </c>
       <c r="AV26" s="5">
         <v>14478</v>
@@ -4818,14 +4818,14 @@
       </c>
       <c r="AX26" s="3">
         <f t="shared" si="18"/>
-        <v>9495</v>
+        <v>9501</v>
       </c>
       <c r="AY26" s="5">
-        <v>14391</v>
+        <v>14397</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="19"/>
-        <v>0.99399088271860758</v>
+        <v>0.99440530460008292</v>
       </c>
       <c r="BA26" s="5">
         <v>14902</v>
@@ -4835,14 +4835,14 @@
       </c>
       <c r="BC26" s="3">
         <f t="shared" si="20"/>
-        <v>9584</v>
+        <v>9591</v>
       </c>
       <c r="BD26" s="5">
-        <v>14531</v>
+        <v>14538</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="21"/>
-        <v>0.97510401288417659</v>
+        <v>0.97557374849013556</v>
       </c>
       <c r="BF26" s="5">
         <v>28105</v>
@@ -4852,14 +4852,14 @@
       </c>
       <c r="BH26" s="3">
         <f t="shared" si="22"/>
-        <v>20188</v>
+        <v>20212</v>
       </c>
       <c r="BI26" s="5">
-        <v>27951</v>
+        <v>27975</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="23"/>
-        <v>0.9945205479452055</v>
+        <v>0.99537448852517341</v>
       </c>
       <c r="BL26" s="9"/>
     </row>
@@ -4878,14 +4878,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>76327</v>
+        <v>76353</v>
       </c>
       <c r="F27" s="5">
-        <v>125114</v>
+        <v>125140</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>0.96884703841656539</v>
+        <v>0.96904837498160867</v>
       </c>
       <c r="H27" s="5">
         <v>129298</v>
@@ -4895,14 +4895,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>74630</v>
+        <v>74656</v>
       </c>
       <c r="K27" s="5">
-        <v>126026</v>
+        <v>126052</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.97469411746508061</v>
+        <v>0.97489520332874446</v>
       </c>
       <c r="M27" s="5">
         <v>186733</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="O27" s="3">
         <f t="shared" si="4"/>
-        <v>116719</v>
+        <v>116767</v>
       </c>
       <c r="P27" s="5">
-        <v>185813</v>
+        <v>185861</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="5"/>
-        <v>0.9950731793523373</v>
+        <v>0.99533023086438921</v>
       </c>
       <c r="R27" s="5">
         <v>126872</v>
@@ -4929,14 +4929,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="6"/>
-        <v>75167</v>
+        <v>75196</v>
       </c>
       <c r="U27" s="5">
-        <v>125694</v>
+        <v>125723</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="7"/>
-        <v>0.99071505139037774</v>
+        <v>0.99094362822372151</v>
       </c>
       <c r="W27" s="5">
         <v>129739</v>
@@ -4946,14 +4946,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="8"/>
-        <v>33801</v>
+        <v>33833</v>
       </c>
       <c r="Z27" s="5">
-        <v>126662</v>
+        <v>126694</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="9"/>
-        <v>0.97628315309968472</v>
+        <v>0.97652980214122198</v>
       </c>
       <c r="AB27" s="5">
         <v>188270</v>
@@ -4963,14 +4963,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="10"/>
-        <v>125744</v>
+        <v>125807</v>
       </c>
       <c r="AE27" s="5">
-        <v>187232</v>
+        <v>187295</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="11"/>
-        <v>0.99448664152546873</v>
+        <v>0.99482126732883625</v>
       </c>
       <c r="AG27" s="5">
         <v>127800</v>
@@ -4980,14 +4980,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="12"/>
-        <v>76472</v>
+        <v>76515</v>
       </c>
       <c r="AJ27" s="5">
-        <v>126817</v>
+        <v>126860</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="13"/>
-        <v>0.99230829420970268</v>
+        <v>0.99264475743348979</v>
       </c>
       <c r="AL27" s="5">
         <v>130262</v>
@@ -4997,14 +4997,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" si="14"/>
-        <v>74651</v>
+        <v>74694</v>
       </c>
       <c r="AO27" s="5">
-        <v>127892</v>
+        <v>127935</v>
       </c>
       <c r="AP27" s="4">
         <f t="shared" si="15"/>
-        <v>0.98180589888071734</v>
+        <v>0.98213600282507563</v>
       </c>
       <c r="AQ27" s="5">
         <v>189830</v>
@@ -5014,14 +5014,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" si="16"/>
-        <v>116035</v>
+        <v>116125</v>
       </c>
       <c r="AT27" s="5">
-        <v>189288</v>
+        <v>189378</v>
       </c>
       <c r="AU27" s="4">
         <f t="shared" si="17"/>
-        <v>0.99714481378075115</v>
+        <v>0.99761892219354154</v>
       </c>
       <c r="AV27" s="5">
         <v>128733</v>
@@ -5031,14 +5031,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" si="18"/>
-        <v>73883</v>
+        <v>73943</v>
       </c>
       <c r="AY27" s="5">
-        <v>128544</v>
+        <v>128604</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" si="19"/>
-        <v>0.99853184498147329</v>
+        <v>0.99899792593973569</v>
       </c>
       <c r="BA27" s="5">
         <v>132099</v>
@@ -5048,14 +5048,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" si="20"/>
-        <v>74487</v>
+        <v>74554</v>
       </c>
       <c r="BD27" s="5">
-        <v>130055</v>
+        <v>130122</v>
       </c>
       <c r="BE27" s="4">
         <f t="shared" si="21"/>
-        <v>0.98452675644781562</v>
+        <v>0.98503395180887066</v>
       </c>
       <c r="BF27" s="5">
         <v>192460</v>
@@ -5065,14 +5065,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="22"/>
-        <v>123513</v>
+        <v>123650</v>
       </c>
       <c r="BI27" s="5">
-        <v>191891</v>
+        <v>192028</v>
       </c>
       <c r="BJ27" s="4">
         <f t="shared" si="23"/>
-        <v>0.99704354151511998</v>
+        <v>0.99775537774082923</v>
       </c>
       <c r="BL27" s="9"/>
     </row>
@@ -5091,14 +5091,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>175691</v>
+        <v>175706</v>
       </c>
       <c r="F28" s="5">
-        <v>409416</v>
+        <v>409431</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.99050181205877941</v>
+        <v>0.99053810162044986</v>
       </c>
       <c r="H28" s="5">
         <v>423216</v>
@@ -5108,14 +5108,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>174269</v>
+        <v>174289</v>
       </c>
       <c r="K28" s="5">
-        <v>413838</v>
+        <v>413858</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.9778411024157877</v>
+        <v>0.97788835960833242</v>
       </c>
       <c r="M28" s="5">
         <v>688530</v>
@@ -5125,14 +5125,14 @@
       </c>
       <c r="O28" s="3">
         <f t="shared" si="4"/>
-        <v>299350</v>
+        <v>299396</v>
       </c>
       <c r="P28" s="5">
-        <v>682034</v>
+        <v>682080</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="5"/>
-        <v>0.99056540746227473</v>
+        <v>0.9906322164611564</v>
       </c>
       <c r="R28" s="5">
         <v>417505</v>
@@ -5142,14 +5142,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="6"/>
-        <v>173312</v>
+        <v>173339</v>
       </c>
       <c r="U28" s="5">
-        <v>414113</v>
+        <v>414140</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="7"/>
-        <v>0.99187554640064191</v>
+        <v>0.99194021628483486</v>
       </c>
       <c r="W28" s="5">
         <v>426115</v>
@@ -5159,14 +5159,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="8"/>
-        <v>67605</v>
+        <v>67633</v>
       </c>
       <c r="Z28" s="5">
-        <v>416270</v>
+        <v>416298</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="9"/>
-        <v>0.97689590838154017</v>
+        <v>0.9769616183424662</v>
       </c>
       <c r="AB28" s="5">
         <v>693825</v>
@@ -5176,14 +5176,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="10"/>
-        <v>332110</v>
+        <v>332173</v>
       </c>
       <c r="AE28" s="5">
-        <v>687284</v>
+        <v>687347</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="11"/>
-        <v>0.99057255071523798</v>
+        <v>0.99066335170972508</v>
       </c>
       <c r="AG28" s="5">
         <v>421441</v>
@@ -5193,14 +5193,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="12"/>
-        <v>172946</v>
+        <v>172978</v>
       </c>
       <c r="AJ28" s="5">
-        <v>416824</v>
+        <v>416856</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="13"/>
-        <v>0.98904472986728864</v>
+        <v>0.98912065983138797</v>
       </c>
       <c r="AL28" s="5">
         <v>428935</v>
@@ -5210,14 +5210,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="14"/>
-        <v>166861</v>
+        <v>166900</v>
       </c>
       <c r="AO28" s="5">
-        <v>421362</v>
+        <v>421401</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" si="15"/>
-        <v>0.98234464429342438</v>
+        <v>0.98243556716052549</v>
       </c>
       <c r="AQ28" s="5">
         <v>700018</v>
@@ -5227,14 +5227,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="16"/>
-        <v>292355</v>
+        <v>292451</v>
       </c>
       <c r="AT28" s="5">
-        <v>696341</v>
+        <v>696437</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" si="17"/>
-        <v>0.99474727792713902</v>
+        <v>0.99488441725784194</v>
       </c>
       <c r="AV28" s="5">
         <v>428584</v>
@@ -5244,14 +5244,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="18"/>
-        <v>169625</v>
+        <v>169679</v>
       </c>
       <c r="AY28" s="5">
-        <v>426349</v>
+        <v>426403</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" si="19"/>
-        <v>0.99478515296884629</v>
+        <v>0.99491114927295465</v>
       </c>
       <c r="BA28" s="5">
         <v>438333</v>
@@ -5261,14 +5261,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="20"/>
-        <v>170287</v>
+        <v>170347</v>
       </c>
       <c r="BD28" s="5">
-        <v>431627</v>
+        <v>431687</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" si="21"/>
-        <v>0.98470112905028828</v>
+        <v>0.98483801128365878</v>
       </c>
       <c r="BF28" s="5">
         <v>711748</v>
@@ -5278,14 +5278,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="22"/>
-        <v>332031</v>
+        <v>332176</v>
       </c>
       <c r="BI28" s="5">
-        <v>707349</v>
+        <v>707494</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="23"/>
-        <v>0.99381944171251624</v>
+        <v>0.99402316550239689</v>
       </c>
       <c r="BL28" s="9"/>
     </row>
@@ -5304,14 +5304,14 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>70913</v>
+        <v>70920</v>
       </c>
       <c r="F29" s="5">
-        <v>135489</v>
+        <v>135496</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>0.99046010789946926</v>
+        <v>0.99051127973449127</v>
       </c>
       <c r="H29" s="5">
         <v>138439</v>
@@ -5321,14 +5321,14 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>70909</v>
+        <v>70917</v>
       </c>
       <c r="K29" s="5">
-        <v>136693</v>
+        <v>136701</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="3"/>
-        <v>0.98738794703804567</v>
+        <v>0.98744573422229287</v>
       </c>
       <c r="M29" s="5">
         <v>184711</v>
@@ -5338,14 +5338,14 @@
       </c>
       <c r="O29" s="3">
         <f t="shared" si="4"/>
-        <v>98993</v>
+        <v>99005</v>
       </c>
       <c r="P29" s="5">
-        <v>183128</v>
+        <v>183140</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="5"/>
-        <v>0.99142985528744909</v>
+        <v>0.99149482164029212</v>
       </c>
       <c r="R29" s="5">
         <v>138323</v>
@@ -5355,14 +5355,14 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="6"/>
-        <v>72698</v>
+        <v>72707</v>
       </c>
       <c r="U29" s="5">
-        <v>136853</v>
+        <v>136862</v>
       </c>
       <c r="V29" s="4">
         <f t="shared" si="7"/>
-        <v>0.98937270012940726</v>
+        <v>0.98943776523065574</v>
       </c>
       <c r="W29" s="5">
         <v>139858</v>
@@ -5372,14 +5372,14 @@
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="8"/>
-        <v>25782</v>
+        <v>25792</v>
       </c>
       <c r="Z29" s="5">
-        <v>137334</v>
+        <v>137344</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" si="9"/>
-        <v>0.98195312388279543</v>
+        <v>0.98202462497676213</v>
       </c>
       <c r="AB29" s="5">
         <v>187429</v>
@@ -5389,14 +5389,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="10"/>
-        <v>107167</v>
+        <v>107184</v>
       </c>
       <c r="AE29" s="5">
-        <v>184507</v>
+        <v>184524</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="11"/>
-        <v>0.98441009662325463</v>
+        <v>0.98450079763537124</v>
       </c>
       <c r="AG29" s="5">
         <v>139419</v>
@@ -5406,14 +5406,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="12"/>
-        <v>74786</v>
+        <v>74796</v>
       </c>
       <c r="AJ29" s="5">
-        <v>138031</v>
+        <v>138041</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="13"/>
-        <v>0.99004439853965387</v>
+        <v>0.99011612477495892</v>
       </c>
       <c r="AL29" s="5">
         <v>141276</v>
@@ -5423,14 +5423,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="14"/>
-        <v>71126</v>
+        <v>71136</v>
       </c>
       <c r="AO29" s="5">
-        <v>139240</v>
+        <v>139250</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="15"/>
-        <v>0.98558849344545429</v>
+        <v>0.9856592768764687</v>
       </c>
       <c r="AQ29" s="5">
         <v>188424</v>
@@ -5440,14 +5440,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="16"/>
-        <v>97100</v>
+        <v>97121</v>
       </c>
       <c r="AT29" s="5">
-        <v>187207</v>
+        <v>187228</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="17"/>
-        <v>0.99354116248460922</v>
+        <v>0.9936526132552117</v>
       </c>
       <c r="AV29" s="5">
         <v>141887</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="AX29" s="3">
         <f t="shared" si="18"/>
-        <v>71694</v>
+        <v>71706</v>
       </c>
       <c r="AY29" s="5">
-        <v>140485</v>
+        <v>140497</v>
       </c>
       <c r="AZ29" s="4">
         <f t="shared" si="19"/>
-        <v>0.99011889743246384</v>
+        <v>0.99020347177683654</v>
       </c>
       <c r="BA29" s="5">
         <v>143795</v>
@@ -5474,14 +5474,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="20"/>
-        <v>71467</v>
+        <v>71482</v>
       </c>
       <c r="BD29" s="5">
-        <v>141704</v>
+        <v>141719</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="21"/>
-        <v>0.98545846517611879</v>
+        <v>0.98556278034702183</v>
       </c>
       <c r="BF29" s="5">
         <v>191754</v>
@@ -5491,14 +5491,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="22"/>
-        <v>105398</v>
+        <v>105432</v>
       </c>
       <c r="BI29" s="5">
-        <v>189604</v>
+        <v>189638</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="23"/>
-        <v>0.98878771759650386</v>
+        <v>0.98896502810893128</v>
       </c>
       <c r="BL29" s="9"/>
     </row>
@@ -5517,14 +5517,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>100980</v>
+        <v>100989</v>
       </c>
       <c r="F30" s="5">
-        <v>176016</v>
+        <v>176025</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.98748920031866072</v>
+        <v>0.98753969233531191</v>
       </c>
       <c r="H30" s="5">
         <v>181910</v>
@@ -5534,14 +5534,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>100082</v>
+        <v>100090</v>
       </c>
       <c r="K30" s="5">
-        <v>178265</v>
+        <v>178273</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.97996261887746683</v>
+        <v>0.98000659666868228</v>
       </c>
       <c r="M30" s="5">
         <v>304709</v>
@@ -5551,14 +5551,14 @@
       </c>
       <c r="O30" s="3">
         <f t="shared" si="4"/>
-        <v>185069</v>
+        <v>185092</v>
       </c>
       <c r="P30" s="5">
-        <v>301536</v>
+        <v>301559</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="5"/>
-        <v>0.98958678608114625</v>
+        <v>0.98966226793432421</v>
       </c>
       <c r="R30" s="5">
         <v>179361</v>
@@ -5568,14 +5568,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="6"/>
-        <v>100518</v>
+        <v>100528</v>
       </c>
       <c r="U30" s="5">
-        <v>177824</v>
+        <v>177834</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="7"/>
-        <v>0.99143069006082707</v>
+        <v>0.99148644354123805</v>
       </c>
       <c r="W30" s="5">
         <v>184404</v>
@@ -5585,14 +5585,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="8"/>
-        <v>38537</v>
+        <v>38549</v>
       </c>
       <c r="Z30" s="5">
-        <v>179070</v>
+        <v>179082</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="9"/>
-        <v>0.97107438016528924</v>
+        <v>0.97113945467560359</v>
       </c>
       <c r="AB30" s="5">
         <v>307610</v>
@@ -5602,14 +5602,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="10"/>
-        <v>193434</v>
+        <v>193463</v>
       </c>
       <c r="AE30" s="5">
-        <v>304559</v>
+        <v>304588</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="11"/>
-        <v>0.99008159682715124</v>
+        <v>0.99017587204577229</v>
       </c>
       <c r="AG30" s="5">
         <v>180656</v>
@@ -5619,14 +5619,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="12"/>
-        <v>99584</v>
+        <v>99599</v>
       </c>
       <c r="AJ30" s="5">
-        <v>178795</v>
+        <v>178810</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="13"/>
-        <v>0.98969865379505806</v>
+        <v>0.98978168452749982</v>
       </c>
       <c r="AL30" s="5">
         <v>185185</v>
@@ -5636,14 +5636,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="14"/>
-        <v>98842</v>
+        <v>98861</v>
       </c>
       <c r="AO30" s="5">
-        <v>181686</v>
+        <v>181705</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="15"/>
-        <v>0.98110538110538115</v>
+        <v>0.98120798120798125</v>
       </c>
       <c r="AQ30" s="5">
         <v>311830</v>
@@ -5653,14 +5653,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="16"/>
-        <v>178305</v>
+        <v>178344</v>
       </c>
       <c r="AT30" s="5">
-        <v>309543</v>
+        <v>309582</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="17"/>
-        <v>0.99266587563736652</v>
+        <v>0.99279094378347177</v>
       </c>
       <c r="AV30" s="5">
         <v>184055</v>
@@ -5670,14 +5670,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="18"/>
-        <v>100169</v>
+        <v>100196</v>
       </c>
       <c r="AY30" s="5">
-        <v>182513</v>
+        <v>182540</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="19"/>
-        <v>0.99162206949009812</v>
+        <v>0.99176876477139986</v>
       </c>
       <c r="BA30" s="5">
         <v>188792</v>
@@ -5687,14 +5687,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="20"/>
-        <v>100342</v>
+        <v>100375</v>
       </c>
       <c r="BD30" s="5">
-        <v>184889</v>
+        <v>184922</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="21"/>
-        <v>0.97932645451078437</v>
+        <v>0.9795012500529684</v>
       </c>
       <c r="BF30" s="5">
         <v>315967</v>
@@ -5704,14 +5704,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="22"/>
-        <v>193571</v>
+        <v>193644</v>
       </c>
       <c r="BI30" s="5">
-        <v>313972</v>
+        <v>314045</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="23"/>
-        <v>0.99368604949251027</v>
+        <v>0.99391708627799735</v>
       </c>
       <c r="BL30" s="9"/>
     </row>
@@ -5730,14 +5730,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>35399</v>
+        <v>35400</v>
       </c>
       <c r="F31" s="5">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>1.0009661221636053</v>
+        <v>1.0009788342973369</v>
       </c>
       <c r="H31" s="5">
         <v>80911</v>
@@ -5747,14 +5747,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>33729</v>
+        <v>33730</v>
       </c>
       <c r="K31" s="5">
-        <v>80387</v>
+        <v>80388</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.99352374831605095</v>
+        <v>0.99353610757498978</v>
       </c>
       <c r="M31" s="5">
         <v>142260</v>
@@ -5764,14 +5764,14 @@
       </c>
       <c r="O31" s="3">
         <f t="shared" si="4"/>
-        <v>72175</v>
+        <v>72184</v>
       </c>
       <c r="P31" s="5">
-        <v>142765</v>
+        <v>142774</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="5"/>
-        <v>1.0035498383241952</v>
+        <v>1.0036131027695769</v>
       </c>
       <c r="R31" s="5">
         <v>79665</v>
@@ -5781,14 +5781,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="6"/>
-        <v>33844</v>
+        <v>33846</v>
       </c>
       <c r="U31" s="5">
-        <v>79780</v>
+        <v>79782</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="7"/>
-        <v>1.0014435448440344</v>
+        <v>1.0014686499717567</v>
       </c>
       <c r="W31" s="5">
         <v>81657</v>
@@ -5798,14 +5798,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="8"/>
-        <v>20676</v>
+        <v>20678</v>
       </c>
       <c r="Z31" s="5">
-        <v>80693</v>
+        <v>80695</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="9"/>
-        <v>0.98819452098411653</v>
+        <v>0.9882190136791702</v>
       </c>
       <c r="AB31" s="5">
         <v>144167</v>
@@ -5815,14 +5815,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="10"/>
-        <v>77268</v>
+        <v>77280</v>
       </c>
       <c r="AE31" s="5">
-        <v>144617</v>
+        <v>144629</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="11"/>
-        <v>1.0031213800661734</v>
+        <v>1.0032046168679378</v>
       </c>
       <c r="AG31" s="5">
         <v>80917</v>
@@ -5832,14 +5832,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="12"/>
-        <v>35652</v>
+        <v>35655</v>
       </c>
       <c r="AJ31" s="5">
-        <v>81476</v>
+        <v>81479</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="13"/>
-        <v>1.0069083134569992</v>
+        <v>1.0069453884844966</v>
       </c>
       <c r="AL31" s="5">
         <v>83546</v>
@@ -5849,14 +5849,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="14"/>
-        <v>33670</v>
+        <v>33674</v>
       </c>
       <c r="AO31" s="5">
-        <v>82728</v>
+        <v>82732</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="15"/>
-        <v>0.9902089866660283</v>
+        <v>0.99025686448184236</v>
       </c>
       <c r="AQ31" s="5">
         <v>147023</v>
@@ -5866,14 +5866,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="16"/>
-        <v>69522</v>
+        <v>69538</v>
       </c>
       <c r="AT31" s="5">
-        <v>147335</v>
+        <v>147351</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="17"/>
-        <v>1.0021221169476884</v>
+        <v>1.0022309434578263</v>
       </c>
       <c r="AV31" s="5">
         <v>81694</v>
@@ -5883,14 +5883,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="18"/>
-        <v>33822</v>
+        <v>33825</v>
       </c>
       <c r="AY31" s="5">
-        <v>82327</v>
+        <v>82330</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="19"/>
-        <v>1.0077484270570667</v>
+        <v>1.0077851494601806</v>
       </c>
       <c r="BA31" s="5">
         <v>83957</v>
@@ -5900,14 +5900,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="20"/>
-        <v>32825</v>
+        <v>32830</v>
       </c>
       <c r="BD31" s="5">
-        <v>83382</v>
+        <v>83387</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="21"/>
-        <v>0.99315125600009524</v>
+        <v>0.99321081029574665</v>
       </c>
       <c r="BF31" s="5">
         <v>148810</v>
@@ -5917,14 +5917,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="22"/>
-        <v>78787</v>
+        <v>78811</v>
       </c>
       <c r="BI31" s="5">
-        <v>149375</v>
+        <v>149399</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="23"/>
-        <v>1.0037967878502789</v>
+        <v>1.0039580673341846</v>
       </c>
       <c r="BL31" s="9"/>
     </row>
@@ -5943,14 +5943,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>97867</v>
+        <v>97873</v>
       </c>
       <c r="F32" s="5">
-        <v>217265</v>
+        <v>217271</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.98939856917114843</v>
+        <v>0.98942589244648049</v>
       </c>
       <c r="H32" s="5">
         <v>225984</v>
@@ -5960,14 +5960,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>97769</v>
+        <v>97773</v>
       </c>
       <c r="K32" s="5">
-        <v>222087</v>
+        <v>222091</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.98275541631265928</v>
+        <v>0.98277311668082701</v>
       </c>
       <c r="M32" s="5">
         <v>469379</v>
@@ -5977,14 +5977,14 @@
       </c>
       <c r="O32" s="3">
         <f t="shared" si="4"/>
-        <v>251976</v>
+        <v>251994</v>
       </c>
       <c r="P32" s="5">
-        <v>466894</v>
+        <v>466912</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="5"/>
-        <v>0.99470577081633393</v>
+        <v>0.99474411935770457</v>
       </c>
       <c r="R32" s="5">
         <v>220673</v>
@@ -5994,14 +5994,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="6"/>
-        <v>98816</v>
+        <v>98822</v>
       </c>
       <c r="U32" s="5">
-        <v>219219</v>
+        <v>219225</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="7"/>
-        <v>0.99341106524132994</v>
+        <v>0.9934382547932914</v>
       </c>
       <c r="W32" s="5">
         <v>228851</v>
@@ -6011,14 +6011,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="8"/>
-        <v>47502</v>
+        <v>47511</v>
       </c>
       <c r="Z32" s="5">
-        <v>222452</v>
+        <v>222461</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="9"/>
-        <v>0.97203857531756466</v>
+        <v>0.97207790221585222</v>
       </c>
       <c r="AB32" s="5">
         <v>476427</v>
@@ -6028,14 +6028,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="10"/>
-        <v>269992</v>
+        <v>270014</v>
       </c>
       <c r="AE32" s="5">
-        <v>472694</v>
+        <v>472716</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="11"/>
-        <v>0.99216459184722949</v>
+        <v>0.99221076891108184</v>
       </c>
       <c r="AG32" s="5">
         <v>224544</v>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="12"/>
-        <v>99826</v>
+        <v>99837</v>
       </c>
       <c r="AJ32" s="5">
-        <v>222960</v>
+        <v>222971</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="13"/>
-        <v>0.99294570329200516</v>
+        <v>0.99299469146358843</v>
       </c>
       <c r="AL32" s="5">
         <v>231787</v>
@@ -6062,14 +6062,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="14"/>
-        <v>96357</v>
+        <v>96370</v>
       </c>
       <c r="AO32" s="5">
-        <v>227002</v>
+        <v>227015</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="15"/>
-        <v>0.9793560467153033</v>
+        <v>0.97941213269078942</v>
       </c>
       <c r="AQ32" s="5">
         <v>484390</v>
@@ -6079,14 +6079,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="16"/>
-        <v>236264</v>
+        <v>236293</v>
       </c>
       <c r="AT32" s="5">
-        <v>481431</v>
+        <v>481460</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="17"/>
-        <v>0.99389128594727394</v>
+        <v>0.99395115506100451</v>
       </c>
       <c r="AV32" s="5">
         <v>227629</v>
@@ -6096,14 +6096,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="18"/>
-        <v>94073</v>
+        <v>94086</v>
       </c>
       <c r="AY32" s="5">
-        <v>226700</v>
+        <v>226713</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="19"/>
-        <v>0.99591879769273683</v>
+        <v>0.99597590816635839</v>
       </c>
       <c r="BA32" s="5">
         <v>234918</v>
@@ -6113,14 +6113,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="20"/>
-        <v>94987</v>
+        <v>95001</v>
       </c>
       <c r="BD32" s="5">
-        <v>231452</v>
+        <v>231466</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="21"/>
-        <v>0.98524591559608032</v>
+        <v>0.98530551085910834</v>
       </c>
       <c r="BF32" s="5">
         <v>492680</v>
@@ -6130,14 +6130,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="22"/>
-        <v>270346</v>
+        <v>270400</v>
       </c>
       <c r="BI32" s="5">
-        <v>490698</v>
+        <v>490752</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="23"/>
-        <v>0.99597710481448409</v>
+        <v>0.99608670942599664</v>
       </c>
       <c r="BL32" s="9"/>
     </row>
@@ -6156,14 +6156,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>93954</v>
+        <v>93957</v>
       </c>
       <c r="F33" s="5">
-        <v>662164</v>
+        <v>662167</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>0.99811881606000497</v>
+        <v>0.99812333813678378</v>
       </c>
       <c r="H33" s="5">
         <v>674602</v>
@@ -6173,14 +6173,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>92447</v>
+        <v>92452</v>
       </c>
       <c r="K33" s="5">
-        <v>670105</v>
+        <v>670110</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>0.99333384721658102</v>
+        <v>0.99334125899419212</v>
       </c>
       <c r="M33" s="5">
         <v>1077651</v>
@@ -6190,14 +6190,14 @@
       </c>
       <c r="O33" s="3">
         <f t="shared" si="4"/>
-        <v>180261</v>
+        <v>180272</v>
       </c>
       <c r="P33" s="5">
-        <v>1078232</v>
+        <v>1078243</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="5"/>
-        <v>1.0005391355828557</v>
+        <v>1.0005493429691059</v>
       </c>
       <c r="R33" s="5">
         <v>670885</v>
@@ -6207,14 +6207,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="6"/>
-        <v>98750</v>
+        <v>98757</v>
       </c>
       <c r="U33" s="5">
-        <v>671005</v>
+        <v>671012</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="7"/>
-        <v>1.0001788682113923</v>
+        <v>1.0001893021903903</v>
       </c>
       <c r="W33" s="5">
         <v>679851</v>
@@ -6224,14 +6224,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="8"/>
-        <v>75102</v>
+        <v>75110</v>
       </c>
       <c r="Z33" s="5">
-        <v>677887</v>
+        <v>677895</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="9"/>
-        <v>0.99711113170385868</v>
+        <v>0.99712289898816064</v>
       </c>
       <c r="AB33" s="5">
         <v>1091619</v>
@@ -6241,14 +6241,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="10"/>
-        <v>205440</v>
+        <v>205451</v>
       </c>
       <c r="AE33" s="5">
-        <v>1092082</v>
+        <v>1092093</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="11"/>
-        <v>1.0004241406571341</v>
+        <v>1.0004342174330054</v>
       </c>
       <c r="AG33" s="5">
         <v>681949</v>
@@ -6258,14 +6258,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="12"/>
-        <v>121276</v>
+        <v>121284</v>
       </c>
       <c r="AJ33" s="5">
-        <v>682565</v>
+        <v>682573</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="13"/>
-        <v>1.0009032933547817</v>
+        <v>1.0009150244373113</v>
       </c>
       <c r="AL33" s="5">
         <v>691548</v>
@@ -6275,14 +6275,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="14"/>
-        <v>90815</v>
+        <v>90820</v>
       </c>
       <c r="AO33" s="5">
-        <v>689005</v>
+        <v>689010</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="15"/>
-        <v>0.99632274260065823</v>
+        <v>0.99632997275677171</v>
       </c>
       <c r="AQ33" s="5">
         <v>1107071</v>
@@ -6292,14 +6292,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="16"/>
-        <v>167894</v>
+        <v>167906</v>
       </c>
       <c r="AT33" s="5">
-        <v>1110257</v>
+        <v>1110269</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="17"/>
-        <v>1.0028778642020251</v>
+        <v>1.0028887036152152</v>
       </c>
       <c r="AV33" s="5">
         <v>697202</v>
@@ -6309,14 +6309,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="18"/>
-        <v>89916</v>
+        <v>89923</v>
       </c>
       <c r="AY33" s="5">
-        <v>698901</v>
+        <v>698908</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="19"/>
-        <v>1.0024368834283321</v>
+        <v>1.0024469235601734</v>
       </c>
       <c r="BA33" s="5">
         <v>707985</v>
@@ -6326,14 +6326,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="20"/>
-        <v>90157</v>
+        <v>90166</v>
       </c>
       <c r="BD33" s="5">
-        <v>709254</v>
+        <v>709263</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="21"/>
-        <v>1.0017924108561622</v>
+        <v>1.0018051229898939</v>
       </c>
       <c r="BF33" s="5">
         <v>1132408</v>
@@ -6343,14 +6343,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="22"/>
-        <v>207722</v>
+        <v>207746</v>
       </c>
       <c r="BI33" s="5">
-        <v>1134952</v>
+        <v>1134976</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="23"/>
-        <v>1.0022465401162832</v>
+        <v>1.0022677338909651</v>
       </c>
       <c r="BL33" s="9"/>
     </row>
@@ -6558,14 +6558,14 @@
       </c>
       <c r="E35" s="3">
         <f t="shared" ref="E35:E47" si="24">F35-D35</f>
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="F35" s="5">
-        <v>11910</v>
+        <v>11911</v>
       </c>
       <c r="G35" s="4">
         <f t="shared" ref="G35:G48" si="25">F35/C35</f>
-        <v>0.99316210807204808</v>
+        <v>0.99324549699799869</v>
       </c>
       <c r="H35" s="5">
         <v>12014</v>
@@ -6575,14 +6575,14 @@
       </c>
       <c r="J35" s="3">
         <f t="shared" ref="J35:J47" si="26">K35-I35</f>
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="K35" s="5">
-        <v>11943</v>
+        <v>11944</v>
       </c>
       <c r="L35" s="4">
         <f t="shared" ref="L35:L48" si="27">K35/H35</f>
-        <v>0.99409022806725489</v>
+        <v>0.99417346429165976</v>
       </c>
       <c r="M35" s="5">
         <v>14733</v>
@@ -6592,14 +6592,14 @@
       </c>
       <c r="O35" s="3">
         <f t="shared" ref="O35:O47" si="28">P35-N35</f>
-        <v>2863</v>
+        <v>2864</v>
       </c>
       <c r="P35" s="5">
-        <v>14686</v>
+        <v>14687</v>
       </c>
       <c r="Q35" s="4">
         <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
-        <v>0.99680988257652892</v>
+        <v>0.99687775741532614</v>
       </c>
       <c r="R35" s="5">
         <v>12053</v>
@@ -6745,14 +6745,14 @@
       </c>
       <c r="BH35" s="3">
         <f t="shared" ref="BH35:BH47" si="46">BI35-BG35</f>
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="BI35" s="5">
-        <v>14994</v>
+        <v>14995</v>
       </c>
       <c r="BJ35" s="4">
         <f t="shared" ref="BJ35:BJ48" si="47">BI35/BF35</f>
-        <v>0.99873443016052754</v>
+        <v>0.99880103909944717</v>
       </c>
       <c r="BL35" s="9"/>
     </row>
@@ -6771,14 +6771,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="24"/>
-        <v>250187</v>
+        <v>250195</v>
       </c>
       <c r="F36" s="5">
-        <v>887280</v>
+        <v>887288</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="25"/>
-        <v>0.99151832109691906</v>
+        <v>0.99152726094293031</v>
       </c>
       <c r="H36" s="5">
         <v>910737</v>
@@ -6788,14 +6788,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="26"/>
-        <v>242700</v>
+        <v>242715</v>
       </c>
       <c r="K36" s="5">
-        <v>898400</v>
+        <v>898415</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="27"/>
-        <v>0.98645382805354342</v>
+        <v>0.98647029823099319</v>
       </c>
       <c r="M36" s="5">
         <v>1579599</v>
@@ -6805,14 +6805,14 @@
       </c>
       <c r="O36" s="3">
         <f t="shared" si="28"/>
-        <v>490090</v>
+        <v>490123</v>
       </c>
       <c r="P36" s="5">
-        <v>1571279</v>
+        <v>1571312</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="29"/>
-        <v>0.99473284042342391</v>
+        <v>0.99475373180155213</v>
       </c>
       <c r="R36" s="5">
         <v>901122</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="30"/>
-        <v>252290</v>
+        <v>252314</v>
       </c>
       <c r="U36" s="5">
-        <v>897734</v>
+        <v>897758</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="31"/>
-        <v>0.99624024271963174</v>
+        <v>0.99626687618324705</v>
       </c>
       <c r="W36" s="5">
         <v>923866</v>
@@ -6839,14 +6839,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="32"/>
-        <v>177904</v>
+        <v>177930</v>
       </c>
       <c r="Z36" s="5">
-        <v>907133</v>
+        <v>907159</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="33"/>
-        <v>0.98188806601823209</v>
+        <v>0.98191620862765816</v>
       </c>
       <c r="AB36" s="5">
         <v>1592928</v>
@@ -6856,14 +6856,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="34"/>
-        <v>534658</v>
+        <v>534714</v>
       </c>
       <c r="AE36" s="5">
-        <v>1588284</v>
+        <v>1588340</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="35"/>
-        <v>0.99708461399385284</v>
+        <v>0.99711976938066249</v>
       </c>
       <c r="AG36" s="5">
         <v>914936</v>
@@ -6873,14 +6873,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="36"/>
-        <v>259730</v>
+        <v>259767</v>
       </c>
       <c r="AJ36" s="5">
-        <v>912076</v>
+        <v>912113</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="37"/>
-        <v>0.99687409829758589</v>
+        <v>0.99691453828464505</v>
       </c>
       <c r="AL36" s="5">
         <v>934551</v>
@@ -6890,14 +6890,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="38"/>
-        <v>238486</v>
+        <v>238526</v>
       </c>
       <c r="AO36" s="5">
-        <v>922750</v>
+        <v>922790</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="39"/>
-        <v>0.98737254574656708</v>
+        <v>0.98741534704901068</v>
       </c>
       <c r="AQ36" s="5">
         <v>1610673</v>
@@ -6907,14 +6907,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="40"/>
-        <v>455168</v>
+        <v>455259</v>
       </c>
       <c r="AT36" s="5">
-        <v>1612841</v>
+        <v>1612932</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="41"/>
-        <v>1.0013460211973504</v>
+        <v>1.0014025193195639</v>
       </c>
       <c r="AV36" s="5">
         <v>933166</v>
@@ -6924,14 +6924,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="42"/>
-        <v>234010</v>
+        <v>234068</v>
       </c>
       <c r="AY36" s="5">
-        <v>933204</v>
+        <v>933262</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="43"/>
-        <v>1.000040721586513</v>
+        <v>1.0001028755869803</v>
       </c>
       <c r="BA36" s="5">
         <v>952259</v>
@@ -6941,14 +6941,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="44"/>
-        <v>234281</v>
+        <v>234347</v>
       </c>
       <c r="BD36" s="5">
-        <v>945279</v>
+        <v>945345</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="45"/>
-        <v>0.99267006140136249</v>
+        <v>0.99273937027636394</v>
       </c>
       <c r="BF36" s="5">
         <v>1640364</v>
@@ -6958,14 +6958,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="46"/>
-        <v>522889</v>
+        <v>523065</v>
       </c>
       <c r="BI36" s="5">
-        <v>1641925</v>
+        <v>1642101</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="47"/>
-        <v>1.0009516180555047</v>
+        <v>1.0010589113148058</v>
       </c>
       <c r="BL36" s="9"/>
     </row>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="24"/>
-        <v>284565</v>
+        <v>284594</v>
       </c>
       <c r="F37" s="5">
-        <v>700982</v>
+        <v>701011</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="25"/>
-        <v>0.98758513033358974</v>
+        <v>0.98762598725827488</v>
       </c>
       <c r="H37" s="5">
         <v>717455</v>
@@ -7001,14 +7001,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="26"/>
-        <v>273398</v>
+        <v>273428</v>
       </c>
       <c r="K37" s="5">
-        <v>706579</v>
+        <v>706609</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="27"/>
-        <v>0.98484086109930236</v>
+        <v>0.98488267556850251</v>
       </c>
       <c r="M37" s="5">
         <v>885615</v>
@@ -7018,14 +7018,14 @@
       </c>
       <c r="O37" s="3">
         <f t="shared" si="28"/>
-        <v>352344</v>
+        <v>352396</v>
       </c>
       <c r="P37" s="5">
-        <v>879358</v>
+        <v>879410</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="29"/>
-        <v>0.99293485318112273</v>
+        <v>0.99299356944044537</v>
       </c>
       <c r="R37" s="5">
         <v>713906</v>
@@ -7035,14 +7035,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="30"/>
-        <v>285514</v>
+        <v>285549</v>
       </c>
       <c r="U37" s="5">
-        <v>707752</v>
+        <v>707787</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="31"/>
-        <v>0.9913798175109888</v>
+        <v>0.99142884357324357</v>
       </c>
       <c r="W37" s="5">
         <v>721933</v>
@@ -7052,14 +7052,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="32"/>
-        <v>129067</v>
+        <v>129108</v>
       </c>
       <c r="Z37" s="5">
-        <v>709690</v>
+        <v>709731</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="33"/>
-        <v>0.98304136256411601</v>
+        <v>0.98309815453788651</v>
       </c>
       <c r="AB37" s="5">
         <v>896229</v>
@@ -7069,14 +7069,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="34"/>
-        <v>387963</v>
+        <v>388020</v>
       </c>
       <c r="AE37" s="5">
-        <v>884778</v>
+        <v>884835</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="35"/>
-        <v>0.98722313158802044</v>
+        <v>0.98728673140458523</v>
       </c>
       <c r="AG37" s="5">
         <v>721282</v>
@@ -7086,14 +7086,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="36"/>
-        <v>283198</v>
+        <v>283246</v>
       </c>
       <c r="AJ37" s="5">
-        <v>712163</v>
+        <v>712211</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="37"/>
-        <v>0.98735723337058179</v>
+        <v>0.9874237815445277</v>
       </c>
       <c r="AL37" s="5">
         <v>727480</v>
@@ -7103,14 +7103,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="38"/>
-        <v>265643</v>
+        <v>265700</v>
       </c>
       <c r="AO37" s="5">
-        <v>718111</v>
+        <v>718168</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="39"/>
-        <v>0.98712129543080218</v>
+        <v>0.98719964810029137</v>
       </c>
       <c r="AQ37" s="5">
         <v>903787</v>
@@ -7120,14 +7120,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="40"/>
-        <v>338968</v>
+        <v>339045</v>
       </c>
       <c r="AT37" s="5">
-        <v>897342</v>
+        <v>897419</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="41"/>
-        <v>0.99286889499406383</v>
+        <v>0.99295409205930163</v>
       </c>
       <c r="AV37" s="5">
         <v>732294</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="42"/>
-        <v>269927</v>
+        <v>269998</v>
       </c>
       <c r="AY37" s="5">
-        <v>726299</v>
+        <v>726370</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="43"/>
-        <v>0.991813397351337</v>
+        <v>0.99191035294567487</v>
       </c>
       <c r="BA37" s="5">
         <v>740889</v>
@@ -7154,14 +7154,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="44"/>
-        <v>267297</v>
+        <v>267374</v>
       </c>
       <c r="BD37" s="5">
-        <v>731497</v>
+        <v>731574</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="45"/>
-        <v>0.98732333723405263</v>
+        <v>0.98742726643262346</v>
       </c>
       <c r="BF37" s="5">
         <v>918028</v>
@@ -7171,14 +7171,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="46"/>
-        <v>377856</v>
+        <v>377986</v>
       </c>
       <c r="BI37" s="5">
-        <v>910231</v>
+        <v>910361</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="47"/>
-        <v>0.99150679499971683</v>
+        <v>0.9916484028809579</v>
       </c>
       <c r="BL37" s="9"/>
     </row>
@@ -7197,14 +7197,14 @@
       </c>
       <c r="E38" s="3">
         <f t="shared" si="24"/>
-        <v>9275</v>
+        <v>9276</v>
       </c>
       <c r="F38" s="5">
-        <v>24448</v>
+        <v>24449</v>
       </c>
       <c r="G38" s="4">
         <f t="shared" si="25"/>
-        <v>1.0038185177581604</v>
+        <v>1.0038595770888934</v>
       </c>
       <c r="H38" s="5">
         <v>24747</v>
@@ -7214,14 +7214,14 @@
       </c>
       <c r="J38" s="3">
         <f t="shared" si="26"/>
-        <v>8855</v>
+        <v>8856</v>
       </c>
       <c r="K38" s="5">
-        <v>24697</v>
+        <v>24698</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="27"/>
-        <v>0.9979795530771407</v>
+        <v>0.99801996201559784</v>
       </c>
       <c r="M38" s="5">
         <v>37604</v>
@@ -7231,14 +7231,14 @@
       </c>
       <c r="O38" s="3">
         <f t="shared" si="28"/>
-        <v>13790</v>
+        <v>13791</v>
       </c>
       <c r="P38" s="5">
-        <v>37832</v>
+        <v>37833</v>
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="29"/>
-        <v>1.0060631847675778</v>
+        <v>1.0060897776832252</v>
       </c>
       <c r="R38" s="5">
         <v>24596</v>
@@ -7248,14 +7248,14 @@
       </c>
       <c r="T38" s="3">
         <f t="shared" si="30"/>
-        <v>9383</v>
+        <v>9384</v>
       </c>
       <c r="U38" s="5">
-        <v>24784</v>
+        <v>24785</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" si="31"/>
-        <v>1.0076435192714261</v>
+        <v>1.0076841762888276</v>
       </c>
       <c r="W38" s="5">
         <v>25148</v>
@@ -7265,14 +7265,14 @@
       </c>
       <c r="Y38" s="3">
         <f t="shared" si="32"/>
-        <v>6022</v>
+        <v>6023</v>
       </c>
       <c r="Z38" s="5">
-        <v>24974</v>
+        <v>24975</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" si="33"/>
-        <v>0.99308096071258156</v>
+        <v>0.99312072530618734</v>
       </c>
       <c r="AB38" s="5">
         <v>38035</v>
@@ -7282,14 +7282,14 @@
       </c>
       <c r="AD38" s="3">
         <f t="shared" si="34"/>
-        <v>14769</v>
+        <v>14772</v>
       </c>
       <c r="AE38" s="5">
-        <v>38237</v>
+        <v>38240</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" si="35"/>
-        <v>1.0053108978572367</v>
+        <v>1.0053897725778889</v>
       </c>
       <c r="AG38" s="5">
         <v>24962</v>
@@ -7299,14 +7299,14 @@
       </c>
       <c r="AI38" s="3">
         <f t="shared" si="36"/>
-        <v>9213</v>
+        <v>9217</v>
       </c>
       <c r="AJ38" s="5">
-        <v>25184</v>
+        <v>25188</v>
       </c>
       <c r="AK38" s="4">
         <f t="shared" si="37"/>
-        <v>1.0088935181475844</v>
+        <v>1.009053761717811</v>
       </c>
       <c r="AL38" s="5">
         <v>25436</v>
@@ -7316,14 +7316,14 @@
       </c>
       <c r="AN38" s="3">
         <f t="shared" si="38"/>
-        <v>8607</v>
+        <v>8611</v>
       </c>
       <c r="AO38" s="5">
-        <v>25467</v>
+        <v>25471</v>
       </c>
       <c r="AP38" s="4">
         <f t="shared" si="39"/>
-        <v>1.0012187450857053</v>
+        <v>1.0013760025161189</v>
       </c>
       <c r="AQ38" s="5">
         <v>38569</v>
@@ -7333,14 +7333,14 @@
       </c>
       <c r="AS38" s="3">
         <f t="shared" si="40"/>
-        <v>13205</v>
+        <v>13211</v>
       </c>
       <c r="AT38" s="5">
-        <v>38960</v>
+        <v>38966</v>
       </c>
       <c r="AU38" s="4">
         <f t="shared" si="41"/>
-        <v>1.0101376753351137</v>
+        <v>1.0102932406855247</v>
       </c>
       <c r="AV38" s="5">
         <v>25488</v>
@@ -7350,14 +7350,14 @@
       </c>
       <c r="AX38" s="3">
         <f t="shared" si="42"/>
-        <v>8635</v>
+        <v>8640</v>
       </c>
       <c r="AY38" s="5">
-        <v>25663</v>
+        <v>25668</v>
       </c>
       <c r="AZ38" s="4">
         <f t="shared" si="43"/>
-        <v>1.0068659761456371</v>
+        <v>1.0070621468926553</v>
       </c>
       <c r="BA38" s="5">
         <v>25933</v>
@@ -7367,14 +7367,14 @@
       </c>
       <c r="BC38" s="3">
         <f t="shared" si="44"/>
-        <v>8610</v>
+        <v>8616</v>
       </c>
       <c r="BD38" s="5">
-        <v>25942</v>
+        <v>25948</v>
       </c>
       <c r="BE38" s="4">
         <f t="shared" si="45"/>
-        <v>1.0003470481625727</v>
+        <v>1.0005784136042879</v>
       </c>
       <c r="BF38" s="5">
         <v>39379</v>
@@ -7384,14 +7384,14 @@
       </c>
       <c r="BH38" s="3">
         <f t="shared" si="46"/>
-        <v>15253</v>
+        <v>15265</v>
       </c>
       <c r="BI38" s="5">
-        <v>39592</v>
+        <v>39604</v>
       </c>
       <c r="BJ38" s="4">
         <f t="shared" si="47"/>
-        <v>1.0054089743264176</v>
+        <v>1.0057137052743848</v>
       </c>
       <c r="BL38" s="9"/>
     </row>
@@ -7623,14 +7623,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="24"/>
-        <v>112597</v>
+        <v>112615</v>
       </c>
       <c r="F40" s="5">
-        <v>289327</v>
+        <v>289345</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="25"/>
-        <v>0.99102237384739744</v>
+        <v>0.99108402866263856</v>
       </c>
       <c r="H40" s="5">
         <v>293812</v>
@@ -7640,14 +7640,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="26"/>
-        <v>110810</v>
+        <v>110833</v>
       </c>
       <c r="K40" s="5">
-        <v>290924</v>
+        <v>290947</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="27"/>
-        <v>0.99017058527221491</v>
+        <v>0.9902488666221938</v>
       </c>
       <c r="M40" s="5">
         <v>351809</v>
@@ -7657,14 +7657,14 @@
       </c>
       <c r="O40" s="3">
         <f t="shared" si="28"/>
-        <v>138060</v>
+        <v>138089</v>
       </c>
       <c r="P40" s="5">
-        <v>349796</v>
+        <v>349825</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="29"/>
-        <v>0.99427814524358382</v>
+        <v>0.99436057633545472</v>
       </c>
       <c r="R40" s="5">
         <v>293831</v>
@@ -7674,14 +7674,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="30"/>
-        <v>115511</v>
+        <v>115536</v>
       </c>
       <c r="U40" s="5">
-        <v>292915</v>
+        <v>292940</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="31"/>
-        <v>0.99688256174467638</v>
+        <v>0.99696764466649201</v>
       </c>
       <c r="W40" s="5">
         <v>297227</v>
@@ -7691,14 +7691,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="32"/>
-        <v>66821</v>
+        <v>66844</v>
       </c>
       <c r="Z40" s="5">
-        <v>294366</v>
+        <v>294389</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="33"/>
-        <v>0.99037436033738524</v>
+        <v>0.99045174227105881</v>
       </c>
       <c r="AB40" s="5">
         <v>355500</v>
@@ -7708,14 +7708,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="34"/>
-        <v>142987</v>
+        <v>143021</v>
       </c>
       <c r="AE40" s="5">
-        <v>353457</v>
+        <v>353491</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="35"/>
-        <v>0.994253164556962</v>
+        <v>0.99434880450070329</v>
       </c>
       <c r="AG40" s="5">
         <v>298328</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="36"/>
-        <v>116496</v>
+        <v>116524</v>
       </c>
       <c r="AJ40" s="5">
-        <v>296137</v>
+        <v>296165</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="37"/>
-        <v>0.9926557346276581</v>
+        <v>0.99274959105414173</v>
       </c>
       <c r="AL40" s="5">
         <v>299711</v>
@@ -7742,14 +7742,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="38"/>
-        <v>111294</v>
+        <v>111325</v>
       </c>
       <c r="AO40" s="5">
-        <v>297449</v>
+        <v>297480</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="39"/>
-        <v>0.99245272946271579</v>
+        <v>0.99255616243648048</v>
       </c>
       <c r="AQ40" s="5">
         <v>357015</v>
@@ -7759,14 +7759,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="40"/>
-        <v>136674</v>
+        <v>136720</v>
       </c>
       <c r="AT40" s="5">
-        <v>355931</v>
+        <v>355977</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="41"/>
-        <v>0.99696371300925735</v>
+        <v>0.99709255913617079</v>
       </c>
       <c r="AV40" s="5">
         <v>300800</v>
@@ -7776,14 +7776,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="42"/>
-        <v>112824</v>
+        <v>112865</v>
       </c>
       <c r="AY40" s="5">
-        <v>299451</v>
+        <v>299492</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="43"/>
-        <v>0.99551529255319149</v>
+        <v>0.99565159574468087</v>
       </c>
       <c r="BA40" s="5">
         <v>303731</v>
@@ -7793,14 +7793,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="44"/>
-        <v>110858</v>
+        <v>110903</v>
       </c>
       <c r="BD40" s="5">
-        <v>300902</v>
+        <v>300947</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="45"/>
-        <v>0.990685837138784</v>
+        <v>0.99083399455439192</v>
       </c>
       <c r="BF40" s="5">
         <v>361393</v>
@@ -7810,14 +7810,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="46"/>
-        <v>149327</v>
+        <v>149393</v>
       </c>
       <c r="BI40" s="5">
-        <v>359312</v>
+        <v>359378</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="47"/>
-        <v>0.99424172576668612</v>
+        <v>0.99442435243626748</v>
       </c>
       <c r="BL40" s="9"/>
     </row>
@@ -7836,14 +7836,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="24"/>
-        <v>362793</v>
+        <v>362832</v>
       </c>
       <c r="F41" s="5">
-        <v>945107</v>
+        <v>945146</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="25"/>
-        <v>0.99233416770963701</v>
+        <v>0.99237511654669008</v>
       </c>
       <c r="H41" s="5">
         <v>959446</v>
@@ -7853,14 +7853,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="26"/>
-        <v>364343</v>
+        <v>364375</v>
       </c>
       <c r="K41" s="5">
-        <v>948875</v>
+        <v>948907</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="27"/>
-        <v>0.98898218346837652</v>
+        <v>0.98901553604892822</v>
       </c>
       <c r="M41" s="5">
         <v>1062442</v>
@@ -7870,14 +7870,14 @@
       </c>
       <c r="O41" s="3">
         <f t="shared" si="28"/>
-        <v>401951</v>
+        <v>401997</v>
       </c>
       <c r="P41" s="5">
-        <v>1053522</v>
+        <v>1053568</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="29"/>
-        <v>0.991604247573044</v>
+        <v>0.99164754405416955</v>
       </c>
       <c r="R41" s="5">
         <v>959218</v>
@@ -7887,14 +7887,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="30"/>
-        <v>375433</v>
+        <v>375475</v>
       </c>
       <c r="U41" s="5">
-        <v>952204</v>
+        <v>952246</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="31"/>
-        <v>0.99268779359853543</v>
+        <v>0.99273157926561006</v>
       </c>
       <c r="W41" s="5">
         <v>961845</v>
@@ -7904,14 +7904,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="32"/>
-        <v>151854</v>
+        <v>151898</v>
       </c>
       <c r="Z41" s="5">
-        <v>951461</v>
+        <v>951505</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="33"/>
-        <v>0.98920408173874164</v>
+        <v>0.9892498271551029</v>
       </c>
       <c r="AB41" s="5">
         <v>1065577</v>
@@ -7921,14 +7921,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="34"/>
-        <v>434508</v>
+        <v>434566</v>
       </c>
       <c r="AE41" s="5">
-        <v>1056898</v>
+        <v>1056956</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="35"/>
-        <v>0.99185511699295315</v>
+        <v>0.99190954759721728</v>
       </c>
       <c r="AG41" s="5">
         <v>963364</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="36"/>
-        <v>374468</v>
+        <v>374521</v>
       </c>
       <c r="AJ41" s="5">
-        <v>957361</v>
+        <v>957414</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="37"/>
-        <v>0.99376871047703674</v>
+        <v>0.99382372602671476</v>
       </c>
       <c r="AL41" s="5">
         <v>968650</v>
@@ -7955,14 +7955,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="38"/>
-        <v>342401</v>
+        <v>342463</v>
       </c>
       <c r="AO41" s="5">
-        <v>959920</v>
+        <v>959982</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="39"/>
-        <v>0.9909874567697311</v>
+        <v>0.99105146337686467</v>
       </c>
       <c r="AQ41" s="5">
         <v>1071657</v>
@@ -7972,14 +7972,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="40"/>
-        <v>363839</v>
+        <v>363910</v>
       </c>
       <c r="AT41" s="5">
-        <v>1065070</v>
+        <v>1065141</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="41"/>
-        <v>0.99385344377911966</v>
+        <v>0.99391969632074439</v>
       </c>
       <c r="AV41" s="5">
         <v>970535</v>
@@ -7989,14 +7989,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="42"/>
-        <v>340736</v>
+        <v>340807</v>
       </c>
       <c r="AY41" s="5">
-        <v>965154</v>
+        <v>965225</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="43"/>
-        <v>0.99445563529393577</v>
+        <v>0.99452879082155721</v>
       </c>
       <c r="BA41" s="5">
         <v>973311</v>
@@ -8006,14 +8006,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="44"/>
-        <v>336562</v>
+        <v>336638</v>
       </c>
       <c r="BD41" s="5">
-        <v>970067</v>
+        <v>970143</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="45"/>
-        <v>0.9966670468123755</v>
+        <v>0.9967451307958094</v>
       </c>
       <c r="BF41" s="5">
         <v>1078355</v>
@@ -8023,14 +8023,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="46"/>
-        <v>404362</v>
+        <v>404470</v>
       </c>
       <c r="BI41" s="5">
-        <v>1075948</v>
+        <v>1076056</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="47"/>
-        <v>0.99776789647194108</v>
+        <v>0.99786804901910786</v>
       </c>
       <c r="BL41" s="9"/>
     </row>
@@ -8049,14 +8049,14 @@
       </c>
       <c r="E42" s="3">
         <f t="shared" si="24"/>
-        <v>8509</v>
+        <v>8510</v>
       </c>
       <c r="F42" s="5">
-        <v>18787</v>
+        <v>18788</v>
       </c>
       <c r="G42" s="4">
         <f t="shared" si="25"/>
-        <v>0.9880614284211634</v>
+        <v>0.98811402124750181</v>
       </c>
       <c r="H42" s="5">
         <v>19101</v>
@@ -8066,14 +8066,14 @@
       </c>
       <c r="J42" s="3">
         <f t="shared" si="26"/>
-        <v>8459</v>
+        <v>8460</v>
       </c>
       <c r="K42" s="5">
-        <v>18931</v>
+        <v>18932</v>
       </c>
       <c r="L42" s="4">
         <f t="shared" si="27"/>
-        <v>0.9910999424113921</v>
+        <v>0.99115229569132501</v>
       </c>
       <c r="M42" s="5">
         <v>21195</v>
@@ -8083,14 +8083,14 @@
       </c>
       <c r="O42" s="3">
         <f t="shared" si="28"/>
-        <v>9352</v>
+        <v>9353</v>
       </c>
       <c r="P42" s="5">
-        <v>21023</v>
+        <v>21024</v>
       </c>
       <c r="Q42" s="4">
         <f t="shared" si="29"/>
-        <v>0.99188487850908236</v>
+        <v>0.99193205944798302</v>
       </c>
       <c r="R42" s="5">
         <v>19210</v>
@@ -8100,14 +8100,14 @@
       </c>
       <c r="T42" s="3">
         <f t="shared" si="30"/>
-        <v>8836</v>
+        <v>8837</v>
       </c>
       <c r="U42" s="5">
-        <v>19082</v>
+        <v>19083</v>
       </c>
       <c r="V42" s="4">
         <f t="shared" si="31"/>
-        <v>0.99333680374804789</v>
+        <v>0.99338885996876625</v>
       </c>
       <c r="W42" s="5">
         <v>19384</v>
@@ -8117,14 +8117,14 @@
       </c>
       <c r="Y42" s="3">
         <f t="shared" si="32"/>
-        <v>4078</v>
+        <v>4079</v>
       </c>
       <c r="Z42" s="5">
-        <v>19103</v>
+        <v>19104</v>
       </c>
       <c r="AA42" s="4">
         <f t="shared" si="33"/>
-        <v>0.98550350804787457</v>
+        <v>0.98555509698720589</v>
       </c>
       <c r="AB42" s="5">
         <v>21463</v>
@@ -8134,14 +8134,14 @@
       </c>
       <c r="AD42" s="3">
         <f t="shared" si="34"/>
-        <v>10268</v>
+        <v>10270</v>
       </c>
       <c r="AE42" s="5">
-        <v>21193</v>
+        <v>21195</v>
       </c>
       <c r="AF42" s="4">
         <f t="shared" si="35"/>
-        <v>0.98742021152681358</v>
+        <v>0.98751339514513348</v>
       </c>
       <c r="AG42" s="5">
         <v>19423</v>
@@ -8151,14 +8151,14 @@
       </c>
       <c r="AI42" s="3">
         <f t="shared" si="36"/>
-        <v>8876</v>
+        <v>8878</v>
       </c>
       <c r="AJ42" s="5">
-        <v>19196</v>
+        <v>19198</v>
       </c>
       <c r="AK42" s="4">
         <f t="shared" si="37"/>
-        <v>0.98831282500128714</v>
+        <v>0.98841579570612159</v>
       </c>
       <c r="AL42" s="5">
         <v>19535</v>
@@ -8168,14 +8168,14 @@
       </c>
       <c r="AN42" s="3">
         <f t="shared" si="38"/>
-        <v>8604</v>
+        <v>8606</v>
       </c>
       <c r="AO42" s="5">
-        <v>19247</v>
+        <v>19249</v>
       </c>
       <c r="AP42" s="4">
         <f t="shared" si="39"/>
-        <v>0.98525723061172255</v>
+        <v>0.98535961095469671</v>
       </c>
       <c r="AQ42" s="5">
         <v>21570</v>
@@ -8185,14 +8185,14 @@
       </c>
       <c r="AS42" s="3">
         <f t="shared" si="40"/>
-        <v>9126</v>
+        <v>9129</v>
       </c>
       <c r="AT42" s="5">
-        <v>21320</v>
+        <v>21323</v>
       </c>
       <c r="AU42" s="4">
         <f t="shared" si="41"/>
-        <v>0.98840982846546133</v>
+        <v>0.98854891052387572</v>
       </c>
       <c r="AV42" s="5">
         <v>19570</v>
@@ -8202,14 +8202,14 @@
       </c>
       <c r="AX42" s="3">
         <f t="shared" si="42"/>
-        <v>8396</v>
+        <v>8398</v>
       </c>
       <c r="AY42" s="5">
-        <v>19334</v>
+        <v>19336</v>
       </c>
       <c r="AZ42" s="4">
         <f t="shared" si="43"/>
-        <v>0.9879407256004088</v>
+        <v>0.9880429228410833</v>
       </c>
       <c r="BA42" s="5">
         <v>19671</v>
@@ -8219,14 +8219,14 @@
       </c>
       <c r="BC42" s="3">
         <f t="shared" si="44"/>
-        <v>8231</v>
+        <v>8233</v>
       </c>
       <c r="BD42" s="5">
-        <v>19439</v>
+        <v>19441</v>
       </c>
       <c r="BE42" s="4">
         <f t="shared" si="45"/>
-        <v>0.98820598851100605</v>
+        <v>0.98830766102384215</v>
       </c>
       <c r="BF42" s="5">
         <v>21792</v>
@@ -8236,14 +8236,14 @@
       </c>
       <c r="BH42" s="3">
         <f t="shared" si="46"/>
-        <v>9811</v>
+        <v>9813</v>
       </c>
       <c r="BI42" s="5">
-        <v>21629</v>
+        <v>21631</v>
       </c>
       <c r="BJ42" s="4">
         <f t="shared" si="47"/>
-        <v>0.99252019089574151</v>
+        <v>0.99261196769456683</v>
       </c>
       <c r="BL42" s="9"/>
     </row>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="T43" s="3">
         <f t="shared" si="30"/>
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="U43" s="5">
-        <v>3741</v>
+        <v>3742</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" si="31"/>
-        <v>0.99919871794871795</v>
+        <v>0.99946581196581197</v>
       </c>
       <c r="W43" s="5">
         <v>3795</v>
@@ -8398,14 +8398,14 @@
       </c>
       <c r="AS43" s="3">
         <f t="shared" si="40"/>
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="AT43" s="5">
-        <v>4771</v>
+        <v>4772</v>
       </c>
       <c r="AU43" s="4">
         <f t="shared" si="41"/>
-        <v>1.0039983164983164</v>
+        <v>1.0042087542087541</v>
       </c>
       <c r="AV43" s="5">
         <v>3858</v>
@@ -8432,14 +8432,14 @@
       </c>
       <c r="BC43" s="3">
         <f t="shared" si="44"/>
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="BD43" s="5">
-        <v>3867</v>
+        <v>3868</v>
       </c>
       <c r="BE43" s="4">
         <f t="shared" si="45"/>
-        <v>0.99103024090210146</v>
+        <v>0.99128651973347004</v>
       </c>
       <c r="BF43" s="5">
         <v>4852</v>
@@ -8449,14 +8449,14 @@
       </c>
       <c r="BH43" s="3">
         <f t="shared" si="46"/>
-        <v>2839</v>
+        <v>2842</v>
       </c>
       <c r="BI43" s="5">
-        <v>4821</v>
+        <v>4824</v>
       </c>
       <c r="BJ43" s="4">
         <f t="shared" si="47"/>
-        <v>0.99361088211046988</v>
+        <v>0.99422918384171477</v>
       </c>
       <c r="BL43" s="9"/>
     </row>
@@ -8475,14 +8475,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="24"/>
-        <v>174693</v>
+        <v>174709</v>
       </c>
       <c r="F44" s="5">
-        <v>359903</v>
+        <v>359919</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="25"/>
-        <v>0.9895056636973496</v>
+        <v>0.98954965357967672</v>
       </c>
       <c r="H44" s="5">
         <v>368428</v>
@@ -8492,14 +8492,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="26"/>
-        <v>171118</v>
+        <v>171134</v>
       </c>
       <c r="K44" s="5">
-        <v>362625</v>
+        <v>362641</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="27"/>
-        <v>0.98424929701325636</v>
+        <v>0.98429272476576157</v>
       </c>
       <c r="M44" s="5">
         <v>437654</v>
@@ -8509,14 +8509,14 @@
       </c>
       <c r="O44" s="3">
         <f t="shared" si="28"/>
-        <v>205928</v>
+        <v>205949</v>
       </c>
       <c r="P44" s="5">
-        <v>431469</v>
+        <v>431490</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="29"/>
-        <v>0.98586783166611069</v>
+        <v>0.98591581477605594</v>
       </c>
       <c r="R44" s="5">
         <v>368991</v>
@@ -8526,14 +8526,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="30"/>
-        <v>177553</v>
+        <v>177571</v>
       </c>
       <c r="U44" s="5">
-        <v>364990</v>
+        <v>365008</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="31"/>
-        <v>0.98915691710637932</v>
+        <v>0.98920569878398124</v>
       </c>
       <c r="W44" s="5">
         <v>375659</v>
@@ -8543,14 +8543,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="32"/>
-        <v>79637</v>
+        <v>79659</v>
       </c>
       <c r="Z44" s="5">
-        <v>365136</v>
+        <v>365158</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="33"/>
-        <v>0.97198789327555046</v>
+        <v>0.97204645702618597</v>
       </c>
       <c r="AB44" s="5">
         <v>443838</v>
@@ -8560,14 +8560,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="34"/>
-        <v>217419</v>
+        <v>217453</v>
       </c>
       <c r="AE44" s="5">
-        <v>434581</v>
+        <v>434615</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="35"/>
-        <v>0.97914329102059761</v>
+        <v>0.97921989554747457</v>
       </c>
       <c r="AG44" s="5">
         <v>373881</v>
@@ -8577,14 +8577,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="36"/>
-        <v>174039</v>
+        <v>174068</v>
       </c>
       <c r="AJ44" s="5">
-        <v>367160</v>
+        <v>367189</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="37"/>
-        <v>0.98202369203035189</v>
+        <v>0.98210125681700866</v>
       </c>
       <c r="AL44" s="5">
         <v>377474</v>
@@ -8594,14 +8594,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="38"/>
-        <v>166946</v>
+        <v>166977</v>
       </c>
       <c r="AO44" s="5">
-        <v>370442</v>
+        <v>370473</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="39"/>
-        <v>0.98137090236678548</v>
+        <v>0.98145302722836536</v>
       </c>
       <c r="AQ44" s="5">
         <v>447335</v>
@@ -8611,14 +8611,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="40"/>
-        <v>201688</v>
+        <v>201727</v>
       </c>
       <c r="AT44" s="5">
-        <v>441325</v>
+        <v>441364</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="41"/>
-        <v>0.9865648786703477</v>
+        <v>0.98665206165401764</v>
       </c>
       <c r="AV44" s="5">
         <v>379419</v>
@@ -8628,14 +8628,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="42"/>
-        <v>167057</v>
+        <v>167097</v>
       </c>
       <c r="AY44" s="5">
-        <v>374549</v>
+        <v>374589</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="43"/>
-        <v>0.98716458585363409</v>
+        <v>0.98727001019980554</v>
       </c>
       <c r="BA44" s="5">
         <v>384239</v>
@@ -8645,14 +8645,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="44"/>
-        <v>165835</v>
+        <v>165879</v>
       </c>
       <c r="BD44" s="5">
-        <v>377495</v>
+        <v>377539</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="45"/>
-        <v>0.98244842402775356</v>
+        <v>0.98256293608925693</v>
       </c>
       <c r="BF44" s="5">
         <v>454173</v>
@@ -8662,14 +8662,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="46"/>
-        <v>219081</v>
+        <v>219146</v>
       </c>
       <c r="BI44" s="5">
-        <v>448963</v>
+        <v>449028</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="47"/>
-        <v>0.98852860033511458</v>
+        <v>0.98867171760540584</v>
       </c>
       <c r="BL44" s="9"/>
     </row>
@@ -8688,14 +8688,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="24"/>
-        <v>126119</v>
+        <v>126127</v>
       </c>
       <c r="F45" s="5">
-        <v>262628</v>
+        <v>262636</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="25"/>
-        <v>0.98501999084846714</v>
+        <v>0.98504999587430897</v>
       </c>
       <c r="H45" s="5">
         <v>269495</v>
@@ -8705,14 +8705,14 @@
       </c>
       <c r="J45" s="3">
         <f t="shared" si="26"/>
-        <v>123616</v>
+        <v>123625</v>
       </c>
       <c r="K45" s="5">
-        <v>263968</v>
+        <v>263977</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="27"/>
-        <v>0.97949127071003173</v>
+        <v>0.97952466650587211</v>
       </c>
       <c r="M45" s="5">
         <v>320759</v>
@@ -8722,14 +8722,14 @@
       </c>
       <c r="O45" s="3">
         <f t="shared" si="28"/>
-        <v>152040</v>
+        <v>152049</v>
       </c>
       <c r="P45" s="5">
-        <v>315247</v>
+        <v>315256</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="29"/>
-        <v>0.98281575887192563</v>
+        <v>0.98284381732079229</v>
       </c>
       <c r="R45" s="5">
         <v>267358</v>
@@ -8739,14 +8739,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="30"/>
-        <v>127923</v>
+        <v>127935</v>
       </c>
       <c r="U45" s="5">
-        <v>264073</v>
+        <v>264085</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="31"/>
-        <v>0.98771310377845434</v>
+        <v>0.98775798741761978</v>
       </c>
       <c r="W45" s="5">
         <v>269851</v>
@@ -8756,14 +8756,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="32"/>
-        <v>57040</v>
+        <v>57053</v>
       </c>
       <c r="Z45" s="5">
-        <v>264044</v>
+        <v>264057</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="33"/>
-        <v>0.97848071713649387</v>
+        <v>0.97852889186995784</v>
       </c>
       <c r="AB45" s="5">
         <v>321990</v>
@@ -8773,14 +8773,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="34"/>
-        <v>161794</v>
+        <v>161808</v>
       </c>
       <c r="AE45" s="5">
-        <v>316917</v>
+        <v>316931</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="35"/>
-        <v>0.98424485232460635</v>
+        <v>0.98428833193577436</v>
       </c>
       <c r="AG45" s="5">
         <v>270238</v>
@@ -8790,14 +8790,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="36"/>
-        <v>128166</v>
+        <v>128180</v>
       </c>
       <c r="AJ45" s="5">
-        <v>266757</v>
+        <v>266771</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="37"/>
-        <v>0.98711876198018045</v>
+        <v>0.98717056816583904</v>
       </c>
       <c r="AL45" s="5">
         <v>273027</v>
@@ -8807,14 +8807,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="38"/>
-        <v>124438</v>
+        <v>124452</v>
       </c>
       <c r="AO45" s="5">
-        <v>269573</v>
+        <v>269587</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="39"/>
-        <v>0.98734923652239526</v>
+        <v>0.9874005135023276</v>
       </c>
       <c r="AQ45" s="5">
         <v>326184</v>
@@ -8824,14 +8824,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="40"/>
-        <v>153609</v>
+        <v>153627</v>
       </c>
       <c r="AT45" s="5">
-        <v>323459</v>
+        <v>323477</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="41"/>
-        <v>0.99164581953743902</v>
+        <v>0.99170100311480636</v>
       </c>
       <c r="AV45" s="5">
         <v>274208</v>
@@ -8841,14 +8841,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="42"/>
-        <v>124982</v>
+        <v>125001</v>
       </c>
       <c r="AY45" s="5">
-        <v>272471</v>
+        <v>272490</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="43"/>
-        <v>0.99366539269459675</v>
+        <v>0.99373468316022873</v>
       </c>
       <c r="BA45" s="5">
         <v>277741</v>
@@ -8858,14 +8858,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="44"/>
-        <v>123920</v>
+        <v>123939</v>
       </c>
       <c r="BD45" s="5">
-        <v>274890</v>
+        <v>274909</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="45"/>
-        <v>0.98973504091941777</v>
+        <v>0.98980344997677694</v>
       </c>
       <c r="BF45" s="5">
         <v>331328</v>
@@ -8875,14 +8875,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="46"/>
-        <v>167683</v>
+        <v>167719</v>
       </c>
       <c r="BI45" s="5">
-        <v>329655</v>
+        <v>329691</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="47"/>
-        <v>0.99495062294765313</v>
+        <v>0.99505927660807414</v>
       </c>
       <c r="BL45" s="9"/>
     </row>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="E46" s="3">
         <f t="shared" si="24"/>
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="F46" s="5">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="G46" s="4">
         <f t="shared" si="25"/>
-        <v>1.0206440957886045</v>
+        <v>1.0214698596201486</v>
       </c>
       <c r="H46" s="5">
         <v>2553</v>
@@ -8918,14 +8918,14 @@
       </c>
       <c r="J46" s="3">
         <f t="shared" si="26"/>
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="K46" s="5">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="L46" s="4">
         <f t="shared" si="27"/>
-        <v>0.99373286329808064</v>
+        <v>0.99412455934195065</v>
       </c>
       <c r="M46" s="5">
         <v>7561</v>
@@ -8935,14 +8935,14 @@
       </c>
       <c r="O46" s="3">
         <f t="shared" si="28"/>
-        <v>4823</v>
+        <v>4824</v>
       </c>
       <c r="P46" s="5">
-        <v>7689</v>
+        <v>7690</v>
       </c>
       <c r="Q46" s="4">
         <f t="shared" si="29"/>
-        <v>1.0169289776484591</v>
+        <v>1.0170612352863377</v>
       </c>
       <c r="R46" s="5">
         <v>2328</v>
@@ -8952,14 +8952,14 @@
       </c>
       <c r="T46" s="3">
         <f t="shared" si="30"/>
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="U46" s="5">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="V46" s="4">
         <f t="shared" si="31"/>
-        <v>1.0227663230240549</v>
+        <v>1.0231958762886597</v>
       </c>
       <c r="W46" s="5">
         <v>2515</v>
@@ -8969,14 +8969,14 @@
       </c>
       <c r="Y46" s="3">
         <f t="shared" si="32"/>
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="Z46" s="5">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="AA46" s="4">
         <f t="shared" si="33"/>
-        <v>0.98170974155069579</v>
+        <v>0.98250497017892646</v>
       </c>
       <c r="AB46" s="5">
         <v>7764</v>
@@ -8986,14 +8986,14 @@
       </c>
       <c r="AD46" s="3">
         <f t="shared" si="34"/>
-        <v>5348</v>
+        <v>5350</v>
       </c>
       <c r="AE46" s="5">
-        <v>7914</v>
+        <v>7916</v>
       </c>
       <c r="AF46" s="4">
         <f t="shared" si="35"/>
-        <v>1.0193199381761979</v>
+        <v>1.0195775373518805</v>
       </c>
       <c r="AG46" s="5">
         <v>2401</v>
@@ -9003,14 +9003,14 @@
       </c>
       <c r="AI46" s="3">
         <f t="shared" si="36"/>
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="AJ46" s="5">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="AK46" s="4">
         <f t="shared" si="37"/>
-        <v>1.0270720533111204</v>
+        <v>1.0274885464389838</v>
       </c>
       <c r="AL46" s="5">
         <v>2561</v>
@@ -9020,14 +9020,14 @@
       </c>
       <c r="AN46" s="3">
         <f t="shared" si="38"/>
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="AO46" s="5">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="AP46" s="4">
         <f t="shared" si="39"/>
-        <v>1.0007809449433815</v>
+        <v>1.0011714174150723</v>
       </c>
       <c r="AQ46" s="5">
         <v>7981</v>
@@ -9037,14 +9037,14 @@
       </c>
       <c r="AS46" s="3">
         <f t="shared" si="40"/>
-        <v>5064</v>
+        <v>5065</v>
       </c>
       <c r="AT46" s="5">
-        <v>8158</v>
+        <v>8159</v>
       </c>
       <c r="AU46" s="4">
         <f t="shared" si="41"/>
-        <v>1.022177671970931</v>
+        <v>1.0223029695526877</v>
       </c>
       <c r="AV46" s="5">
         <v>2437</v>
@@ -9054,14 +9054,14 @@
       </c>
       <c r="AX46" s="3">
         <f t="shared" si="42"/>
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="AY46" s="5">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="AZ46" s="4">
         <f t="shared" si="43"/>
-        <v>1.0233894132129668</v>
+        <v>1.0237997537956505</v>
       </c>
       <c r="BA46" s="5">
         <v>2592</v>
@@ -9071,14 +9071,14 @@
       </c>
       <c r="BC46" s="3">
         <f t="shared" si="44"/>
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="BD46" s="5">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="BE46" s="4">
         <f t="shared" si="45"/>
-        <v>0.99382716049382713</v>
+        <v>0.99421296296296291</v>
       </c>
       <c r="BF46" s="5">
         <v>8179</v>
@@ -9088,14 +9088,14 @@
       </c>
       <c r="BH46" s="3">
         <f t="shared" si="46"/>
-        <v>5465</v>
+        <v>5466</v>
       </c>
       <c r="BI46" s="5">
-        <v>8348</v>
+        <v>8349</v>
       </c>
       <c r="BJ46" s="4">
         <f t="shared" si="47"/>
-        <v>1.0206626726983739</v>
+        <v>1.0207849370338673</v>
       </c>
       <c r="BL46" s="9"/>
     </row>
@@ -9327,15 +9327,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>3106186</v>
+        <v>3106520</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>8120457</v>
+        <v>8120791</v>
       </c>
       <c r="G48" s="6">
         <f t="shared" si="25"/>
-        <v>0.98992153240981617</v>
+        <v>0.98996224856554793</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9347,15 +9347,15 @@
       </c>
       <c r="J48" s="8">
         <f>K48-I48</f>
-        <v>3050349</v>
+        <v>3050716</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>8212335</v>
+        <v>8212702</v>
       </c>
       <c r="L48" s="6">
         <f t="shared" si="27"/>
-        <v>0.98436727435960902</v>
+        <v>0.98441126462421591</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9367,15 +9367,15 @@
       </c>
       <c r="O48" s="8">
         <f>P48-N48</f>
-        <v>5026674</v>
+        <v>5027349</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>12660909</v>
+        <v>12661584</v>
       </c>
       <c r="Q48" s="6">
         <f t="shared" si="29"/>
-        <v>0.99319334862396114</v>
+        <v>0.99324629944371046</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9387,15 +9387,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>3108088</v>
+        <v>3108530</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>8205922</v>
+        <v>8206364</v>
       </c>
       <c r="V48" s="6">
         <f t="shared" si="31"/>
-        <v>0.99305015604444247</v>
+        <v>0.99310364524029049</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9407,15 +9407,15 @@
       </c>
       <c r="Y48" s="8">
         <f>Z48-X48</f>
-        <v>1499784</v>
+        <v>1500277</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>8252411</v>
+        <v>8252904</v>
       </c>
       <c r="AA48" s="6">
         <f t="shared" si="33"/>
-        <v>0.98064056215521989</v>
+        <v>0.98069914573729577</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9427,15 +9427,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>5442897</v>
+        <v>5443812</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>12759198</v>
+        <v>12760113</v>
       </c>
       <c r="AF48" s="6">
         <f t="shared" si="35"/>
-        <v>0.99144937718923221</v>
+        <v>0.99152047696996515</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9447,15 +9447,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>3193410</v>
+        <v>3193992</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8282342</v>
+        <v>8282924</v>
       </c>
       <c r="AK48" s="6">
         <f t="shared" si="37"/>
-        <v>0.99132963509157213</v>
+        <v>0.99139929580440234</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9467,15 +9467,15 @@
       </c>
       <c r="AN48" s="8">
         <f>AO48-AM48</f>
-        <v>3011456</v>
+        <v>3012114</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>8365616</v>
+        <v>8366274</v>
       </c>
       <c r="AP48" s="6">
         <f t="shared" si="39"/>
-        <v>0.98581961948868424</v>
+        <v>0.98589715942233924</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9487,15 +9487,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>4837524</v>
+        <v>4838759</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>12937817</v>
+        <v>12939052</v>
       </c>
       <c r="AU48" s="6">
         <f t="shared" si="41"/>
-        <v>0.99549757577753473</v>
+        <v>0.99559260258971527</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9507,15 +9507,15 @@
       </c>
       <c r="AX48" s="8">
         <f>AY48-AW48</f>
-        <v>3016506</v>
+        <v>3017327</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>8437474</v>
+        <v>8438295</v>
       </c>
       <c r="AZ48" s="6">
         <f t="shared" si="43"/>
-        <v>0.99494841758788855</v>
+        <v>0.99504523005223977</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9527,15 +9527,15 @@
       </c>
       <c r="BC48" s="8">
         <f>BD48-BB48</f>
-        <v>3008277</v>
+        <v>3009204</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>8538445</v>
+        <v>8539372</v>
       </c>
       <c r="BE48" s="6">
         <f t="shared" si="45"/>
-        <v>0.98772122217479374</v>
+        <v>0.98782845687302689</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9547,15 +9547,15 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5486750</v>
+        <v>5488779</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>13156478</v>
+        <v>13158507</v>
       </c>
       <c r="BJ48" s="6">
         <f t="shared" si="47"/>
-        <v>0.9960471477489441</v>
+        <v>0.99620075874291847</v>
       </c>
       <c r="BL48" s="9"/>
     </row>
